--- a/hisobotlar/rollar/1_Buxgalteriya_Shartnoma_va_Pasport.xlsx
+++ b/hisobotlar/rollar/1_Buxgalteriya_Shartnoma_va_Pasport.xlsx
@@ -27,6 +27,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guruh 26-04" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guruh 26-05" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guruh 26-06" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guruh 26-07" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H508"/>
+  <dimension ref="A1:H510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -582,7 +583,11 @@
           <t>Abdurahmonova Zebo Tolibovna</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 216</t>
+        </is>
+      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>AD3322083</t>
@@ -618,7 +623,11 @@
           <t>Amirova Shodiyona Xasan qizi</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 33</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
           <t>AD4080530</t>
@@ -726,7 +735,11 @@
           <t>Ibodullayeva Madina Baxtiyor qizi</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A 220</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>AC2114248</t>
@@ -762,7 +775,11 @@
           <t>Isomova Durdona Akram qizi</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>25/26 SH/A57</t>
+        </is>
+      </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
           <t>AB3313151</t>
@@ -942,7 +959,11 @@
           <t>Muratova Barno Jobur qizi</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 226</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>AD3205092</t>
@@ -1266,7 +1287,11 @@
           <t>Raxmatullayev Laziz Luqmon o'g'li</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>26/27 sh/a 235</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
           <t>AC0428854</t>
@@ -1410,7 +1435,11 @@
           <t>Shodiyev Ikromjon Eshpo'lat o'g'li</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A 239</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
           <t>AB5771325</t>
@@ -1482,7 +1511,11 @@
           <t>Turayeva Manzura Yorqin qizi</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 241</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
           <t>AD5352131</t>
@@ -1626,7 +1659,11 @@
           <t>Husanova Rayxona Husan qizi</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 33</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
           <t>AD6361429</t>
@@ -1878,7 +1915,11 @@
           <t>Muxtorova Dilobar Alisher qizi</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>26/27 SH/A252</t>
+        </is>
+      </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
           <t>AA7820705</t>
@@ -2130,7 +2171,11 @@
           <t>Raxmatova Shaxlo Xolbobo qizi</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr"/>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 259</t>
+        </is>
+      </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
           <t>AB6898531</t>
@@ -2238,7 +2283,11 @@
           <t>Shoimova Laziza Shavkat qizi</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>24/25 SH/A 41</t>
+        </is>
+      </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
           <t>AD5432156</t>
@@ -2418,7 +2467,11 @@
           <t>Abdullayeva Jasmina Xolbotir qizi</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr"/>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A 268</t>
+        </is>
+      </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
           <t>AD4515836</t>
@@ -2454,7 +2507,11 @@
           <t>Arziqulova Zahro Azamat qizi</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>26/27 SH/A269</t>
+        </is>
+      </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
           <t>AD2629636</t>
@@ -2562,7 +2619,11 @@
           <t>Boyeva Muxlisa Qurbonali qizi</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr"/>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>25/26 sh/a 6</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
           <t>AA9487628</t>
@@ -2742,7 +2803,11 @@
           <t>Iskandarova Lobar Tura qizi</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>26/27 sh/a 277</t>
+        </is>
+      </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
           <t>AB6548815</t>
@@ -2994,7 +3059,11 @@
           <t>Nabiyeva Zebiniso Abdurahmonovna</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr"/>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 285</t>
+        </is>
+      </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
           <t>AD4726446</t>
@@ -3030,7 +3099,11 @@
           <t>Nabiyeva Zebiniso Soyibjon qizi</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr"/>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 285</t>
+        </is>
+      </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
           <t>AD2442920</t>
@@ -3066,7 +3139,11 @@
           <t>Nomozova Charos Shog'dor qizi</t>
         </is>
       </c>
-      <c r="D71" s="5" t="inlineStr"/>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 286</t>
+        </is>
+      </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
           <t>AD1098594</t>
@@ -3138,7 +3215,11 @@
           <t>Qurbonova Xolida Boynazar qizi</t>
         </is>
       </c>
-      <c r="D73" s="5" t="inlineStr"/>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 288</t>
+        </is>
+      </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
           <t>AD4388600</t>
@@ -3318,7 +3399,11 @@
           <t>Buxorova Farangiz Tufli qizi</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr"/>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 286</t>
+        </is>
+      </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
           <t>AC2285189</t>
@@ -3498,7 +3583,11 @@
           <t>Mirzayeva Sevara Ne'mat qizi</t>
         </is>
       </c>
-      <c r="D83" s="5" t="inlineStr"/>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 506</t>
+        </is>
+      </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
           <t>AD9179531</t>
@@ -3606,7 +3695,11 @@
           <t>Pulatova Zuhra Narzullo qizi</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr"/>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A509</t>
+        </is>
+      </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
           <t>AD4157976</t>
@@ -3678,7 +3771,11 @@
           <t>Rashidova Shaxzoda Suyun qizi</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr"/>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 511</t>
+        </is>
+      </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
           <t>AD6348784</t>
@@ -4038,7 +4135,11 @@
           <t>Yusupova Oygul Qurbonmurodovna</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr"/>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 520</t>
+        </is>
+      </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
           <t>AD8393032</t>
@@ -4218,7 +4319,11 @@
           <t>Boltayeva Shaxlo Faxriddin qizi</t>
         </is>
       </c>
-      <c r="D103" s="5" t="inlineStr"/>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>25/26 sh/a 186</t>
+        </is>
+      </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
           <t>AD7256798</t>
@@ -4290,7 +4395,11 @@
           <t>Ibodullayeva Latofat Sayit qizi</t>
         </is>
       </c>
-      <c r="D105" s="5" t="inlineStr"/>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 116</t>
+        </is>
+      </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
           <t>AB4143080</t>
@@ -4686,7 +4795,11 @@
           <t>Sattorova Sevinch Otabek qizi</t>
         </is>
       </c>
-      <c r="D116" s="2" t="inlineStr"/>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A 327</t>
+        </is>
+      </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
           <t>AC2657133</t>
@@ -5298,7 +5411,11 @@
           <t>Qurbonaliyeva Nargiza Qahramon qizi</t>
         </is>
       </c>
-      <c r="D133" s="5" t="inlineStr"/>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 15</t>
+        </is>
+      </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
           <t>AD9458240</t>
@@ -5370,7 +5487,11 @@
           <t>Salomova Jasmina Azamat qizi</t>
         </is>
       </c>
-      <c r="D135" s="5" t="inlineStr"/>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 10</t>
+        </is>
+      </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
           <t>AD5993376</t>
@@ -5622,7 +5743,11 @@
           <t>Xalilova Zuhra Faxriddin qizi</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr"/>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>25/26 SH/A84</t>
+        </is>
+      </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
           <t>AD9453010</t>
@@ -5802,7 +5927,11 @@
           <t>Abdullayeva Dildora A'zam qizi</t>
         </is>
       </c>
-      <c r="D147" s="5" t="inlineStr"/>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 26</t>
+        </is>
+      </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
           <t>AD9719700</t>
@@ -5874,7 +6003,11 @@
           <t>Baratova Mahzuna Hikmatullo qizi</t>
         </is>
       </c>
-      <c r="D149" s="5" t="inlineStr"/>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 28</t>
+        </is>
+      </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
           <t>AD2886528</t>
@@ -5946,7 +6079,11 @@
           <t>Ilhomova Gulasal Nodir qizi</t>
         </is>
       </c>
-      <c r="D151" s="5" t="inlineStr"/>
+      <c r="D151" s="5" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 107</t>
+        </is>
+      </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
           <t>AD9773960</t>
@@ -6234,7 +6371,11 @@
           <t>Shamsiddinova Fotima Ramziddin qizi</t>
         </is>
       </c>
-      <c r="D159" s="5" t="inlineStr"/>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A40</t>
+        </is>
+      </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
           <t>AD8728367</t>
@@ -6632,7 +6773,11 @@
           <t>Bozorova Marjona Sheraliyevna</t>
         </is>
       </c>
-      <c r="D170" s="2" t="inlineStr"/>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 140</t>
+        </is>
+      </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
           <t>AD9652361</t>
@@ -6668,7 +6813,11 @@
           <t>Djalolova Muslima Hamzaxon qizi</t>
         </is>
       </c>
-      <c r="D171" s="5" t="inlineStr"/>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>25/26 SH/A149</t>
+        </is>
+      </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
           <t>AD5982247</t>
@@ -6848,7 +6997,11 @@
           <t>Isamova Mohimbegim Mansur qizi</t>
         </is>
       </c>
-      <c r="D176" s="2" t="inlineStr"/>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 142</t>
+        </is>
+      </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
           <t>AD9027768</t>
@@ -6884,7 +7037,11 @@
           <t>Mamadiyeva Afruza Muhiddin qizi</t>
         </is>
       </c>
-      <c r="D177" s="5" t="inlineStr"/>
+      <c r="D177" s="5" t="inlineStr">
+        <is>
+          <t>25/26 SH/A150</t>
+        </is>
+      </c>
       <c r="E177" s="5" t="inlineStr">
         <is>
           <t>AD1928284</t>
@@ -7208,7 +7365,11 @@
           <t>Tojiddinov Idrisbek Ozod o'g'li</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr"/>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>26/27 SH/A66</t>
+        </is>
+      </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
           <t>AD9641356</t>
@@ -7532,7 +7693,11 @@
           <t>Aliyeva Shahro'za Nishon qizi</t>
         </is>
       </c>
-      <c r="D195" s="5" t="inlineStr"/>
+      <c r="D195" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 74</t>
+        </is>
+      </c>
       <c r="E195" s="5" t="inlineStr">
         <is>
           <t>AD5070455</t>
@@ -7640,7 +7805,11 @@
           <t>Bekmirzayeva Shahrizoda Zafar qizi</t>
         </is>
       </c>
-      <c r="D198" s="2" t="inlineStr"/>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 76</t>
+        </is>
+      </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
           <t>AC2300123</t>
@@ -7712,7 +7881,11 @@
           <t>Erkinova Zahro Elyorjon qizi</t>
         </is>
       </c>
-      <c r="D200" s="2" t="inlineStr"/>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>26/27 sh/a 78</t>
+        </is>
+      </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
           <t>AD8206268</t>
@@ -7748,7 +7921,11 @@
           <t>Eshqobilova Dilbar Ziyodulla qizi</t>
         </is>
       </c>
-      <c r="D201" s="5" t="inlineStr"/>
+      <c r="D201" s="5" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A79</t>
+        </is>
+      </c>
       <c r="E201" s="5" t="inlineStr">
         <is>
           <t>AD9786116</t>
@@ -7856,7 +8033,11 @@
           <t>Jurayeva Munisa Abduvoxid qizi</t>
         </is>
       </c>
-      <c r="D204" s="2" t="inlineStr"/>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>25/26 sh/a 385</t>
+        </is>
+      </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
           <t>AE2822238</t>
@@ -8000,7 +8181,11 @@
           <t>Muradova Oygul Gulamovna</t>
         </is>
       </c>
-      <c r="D208" s="2" t="inlineStr"/>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 159</t>
+        </is>
+      </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
           <t>AE3508359</t>
@@ -8036,7 +8221,11 @@
           <t>Muxammedova E'zoza Sodiq qizi</t>
         </is>
       </c>
-      <c r="D209" s="5" t="inlineStr"/>
+      <c r="D209" s="5" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 177</t>
+        </is>
+      </c>
       <c r="E209" s="5" t="inlineStr">
         <is>
           <t>AB8047094</t>
@@ -8072,7 +8261,11 @@
           <t>Niyozova Bibixonim Alisherovna</t>
         </is>
       </c>
-      <c r="D210" s="2" t="inlineStr"/>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 372</t>
+        </is>
+      </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
           <t>AD3652553</t>
@@ -8288,7 +8481,11 @@
           <t>Suvonova Sevinch Orif qizi</t>
         </is>
       </c>
-      <c r="D216" s="2" t="inlineStr"/>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A94</t>
+        </is>
+      </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
           <t>AD9767988</t>
@@ -8432,7 +8629,11 @@
           <t>Yusupova Dilnura Nuriddin qizi</t>
         </is>
       </c>
-      <c r="D220" s="2" t="inlineStr"/>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 98</t>
+        </is>
+      </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
           <t>AD9394045</t>
@@ -8504,7 +8705,11 @@
           <t>Axmadova Zarnigor Habibullo qizi</t>
         </is>
       </c>
-      <c r="D222" s="2" t="inlineStr"/>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>26/27 sh/a 100</t>
+        </is>
+      </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
           <t>AD9320444</t>
@@ -8612,7 +8817,11 @@
           <t>Egamberdiyeva Shahlo Dagar qizi</t>
         </is>
       </c>
-      <c r="D225" s="5" t="inlineStr"/>
+      <c r="D225" s="5" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A 103</t>
+        </is>
+      </c>
       <c r="E225" s="5" t="inlineStr">
         <is>
           <t>AB6730694</t>
@@ -8684,7 +8893,11 @@
           <t>Homidova Asilaxon G'ulomjon qizi</t>
         </is>
       </c>
-      <c r="D227" s="5" t="inlineStr"/>
+      <c r="D227" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A105</t>
+        </is>
+      </c>
       <c r="E227" s="5" t="inlineStr">
         <is>
           <t>AD8998916</t>
@@ -8720,7 +8933,11 @@
           <t>Ismoilova Xumoroy Qudratilla qizi</t>
         </is>
       </c>
-      <c r="D228" s="2" t="inlineStr"/>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>26/27 SH/A106</t>
+        </is>
+      </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
           <t>AD7239997</t>
@@ -8756,7 +8973,11 @@
           <t>Mavlonova Mastura Gulmurod qizi</t>
         </is>
       </c>
-      <c r="D229" s="5" t="inlineStr"/>
+      <c r="D229" s="5" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 229</t>
+        </is>
+      </c>
       <c r="E229" s="5" t="inlineStr">
         <is>
           <t>AD2081328</t>
@@ -9008,7 +9229,11 @@
           <t>Odilova Marjona Baxodir qizi</t>
         </is>
       </c>
-      <c r="D236" s="2" t="inlineStr"/>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A114</t>
+        </is>
+      </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
           <t>AD9572244</t>
@@ -9296,7 +9521,11 @@
           <t>Xoliqulova Nozima Qalandar qizi</t>
         </is>
       </c>
-      <c r="D244" s="2" t="inlineStr"/>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>26/27 SH/A123</t>
+        </is>
+      </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
           <t>AD9626141</t>
@@ -9332,7 +9561,11 @@
           <t>Xudoyorova Shahzoda Shuxrat qizi</t>
         </is>
       </c>
-      <c r="D245" s="5" t="inlineStr"/>
+      <c r="D245" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A174</t>
+        </is>
+      </c>
       <c r="E245" s="5" t="inlineStr">
         <is>
           <t>AD5989765</t>
@@ -9368,7 +9601,11 @@
           <t>Yusupova Hosila Akmal qizi</t>
         </is>
       </c>
-      <c r="D246" s="2" t="inlineStr"/>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>26/37 SH/A 125</t>
+        </is>
+      </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
           <t>AD7115916</t>
@@ -9656,7 +9893,11 @@
           <t>Ibrohimova Gulasal Nurbek qizi</t>
         </is>
       </c>
-      <c r="D254" s="2" t="inlineStr"/>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 264</t>
+        </is>
+      </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
           <t>AD8087163</t>
@@ -9764,7 +10005,11 @@
           <t>Maxmudova Nigina Maqsudjon qizi</t>
         </is>
       </c>
-      <c r="D257" s="5" t="inlineStr"/>
+      <c r="D257" s="5" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 266</t>
+        </is>
+      </c>
       <c r="E257" s="5" t="inlineStr">
         <is>
           <t>AD6910277</t>
@@ -9800,7 +10045,11 @@
           <t>Muhammadiyeva Rayhon Rahmatovna</t>
         </is>
       </c>
-      <c r="D258" s="2" t="inlineStr"/>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 272</t>
+        </is>
+      </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
           <t>AD9028774</t>
@@ -9872,7 +10121,11 @@
           <t>Normo'minova Asal Qulmamatovna</t>
         </is>
       </c>
-      <c r="D260" s="2" t="inlineStr"/>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 369</t>
+        </is>
+      </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
           <t>AC0097118</t>
@@ -10160,7 +10413,11 @@
           <t>Shodiyeva Nilufar Omonovna</t>
         </is>
       </c>
-      <c r="D268" s="2" t="inlineStr"/>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>26/27 sh/a 147</t>
+        </is>
+      </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
           <t>AD2012856</t>
@@ -10196,7 +10453,11 @@
           <t>Shukurillayeva Dilnura Jasurbek qizi</t>
         </is>
       </c>
-      <c r="D269" s="5" t="inlineStr"/>
+      <c r="D269" s="5" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 263</t>
+        </is>
+      </c>
       <c r="E269" s="5" t="inlineStr">
         <is>
           <t>AD7196673</t>
@@ -10304,7 +10565,11 @@
           <t>Umirova Sevara Avlayor qizi</t>
         </is>
       </c>
-      <c r="D272" s="2" t="inlineStr"/>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 260</t>
+        </is>
+      </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
           <t>AC2551314</t>
@@ -10376,7 +10641,11 @@
           <t>Xudoykulova Munisa Muzurovna</t>
         </is>
       </c>
-      <c r="D274" s="2" t="inlineStr"/>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>26/27 SH/A153</t>
+        </is>
+      </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
           <t>AB3909486</t>
@@ -10448,7 +10717,11 @@
           <t>Yorboboyeva Shaxzoda Zokirjon qizi</t>
         </is>
       </c>
-      <c r="D276" s="2" t="inlineStr"/>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>26/27 sh/a 155</t>
+        </is>
+      </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
           <t>AD9750298</t>
@@ -10664,7 +10937,11 @@
           <t>Esonmurodova Nurgul Nuriddin qizi</t>
         </is>
       </c>
-      <c r="D282" s="2" t="inlineStr"/>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 161</t>
+        </is>
+      </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
           <t>AD7580502</t>
@@ -10808,7 +11085,11 @@
           <t>Nosirova Umida Zafariddin qizi</t>
         </is>
       </c>
-      <c r="D286" s="2" t="inlineStr"/>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A165</t>
+        </is>
+      </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
           <t>AD9701625</t>
@@ -10880,7 +11161,11 @@
           <t>Olimova Durdona Uktam qizi</t>
         </is>
       </c>
-      <c r="D288" s="2" t="inlineStr"/>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A246</t>
+        </is>
+      </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
           <t>AE1697619</t>
@@ -11024,7 +11309,11 @@
           <t>Quysinova Sumbula G'ayrat qizi</t>
         </is>
       </c>
-      <c r="D292" s="2" t="inlineStr"/>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 338</t>
+        </is>
+      </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
           <t>AD9208348</t>
@@ -11276,7 +11565,11 @@
           <t>Turayeva Malika Abdulla qizi</t>
         </is>
       </c>
-      <c r="D299" s="5" t="inlineStr"/>
+      <c r="D299" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A178</t>
+        </is>
+      </c>
       <c r="E299" s="5" t="inlineStr">
         <is>
           <t>AB5223930</t>
@@ -11348,7 +11641,11 @@
           <t>Xayitova Madina G'ayrat qizi</t>
         </is>
       </c>
-      <c r="D301" s="5" t="inlineStr"/>
+      <c r="D301" s="5" t="inlineStr">
+        <is>
+          <t>26/27 sh/a 180</t>
+        </is>
+      </c>
       <c r="E301" s="5" t="inlineStr">
         <is>
           <t>AD8430404</t>
@@ -11528,7 +11825,11 @@
           <t>Boymurodova Shahnoza Shuxrat qizi</t>
         </is>
       </c>
-      <c r="D306" s="2" t="inlineStr"/>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A367</t>
+        </is>
+      </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
           <t>AE2896098</t>
@@ -11564,7 +11865,11 @@
           <t>Bozorova Aziza Ravshan qizi</t>
         </is>
       </c>
-      <c r="D307" s="5" t="inlineStr"/>
+      <c r="D307" s="5" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 375</t>
+        </is>
+      </c>
       <c r="E307" s="5" t="inlineStr">
         <is>
           <t>AC2525492</t>
@@ -11744,7 +12049,11 @@
           <t>Ibodova Parvina Abdurashid qizi</t>
         </is>
       </c>
-      <c r="D312" s="2" t="inlineStr"/>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>25/26 sh/a 333</t>
+        </is>
+      </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
           <t>AD9606045</t>
@@ -11780,7 +12089,11 @@
           <t>Ibragimova Odina Azamat qizi</t>
         </is>
       </c>
-      <c r="D313" s="5" t="inlineStr"/>
+      <c r="D313" s="5" t="inlineStr">
+        <is>
+          <t>25/26 sh/a 33</t>
+        </is>
+      </c>
       <c r="E313" s="5" t="inlineStr">
         <is>
           <t>AD2497814</t>
@@ -11960,7 +12273,11 @@
           <t>Ochilova Gulnora Jurayevna</t>
         </is>
       </c>
-      <c r="D318" s="2" t="inlineStr"/>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>25/26 SH/A358</t>
+        </is>
+      </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
           <t>AD1137516</t>
@@ -12104,7 +12421,11 @@
           <t>Saidova Nozima Sanjar qizi</t>
         </is>
       </c>
-      <c r="D322" s="2" t="inlineStr"/>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A361</t>
+        </is>
+      </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
           <t>AD9178885</t>
@@ -12212,7 +12533,11 @@
           <t>Shovxiddinova Latofat Ruzimurod qizi</t>
         </is>
       </c>
-      <c r="D325" s="5" t="inlineStr"/>
+      <c r="D325" s="5" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 346</t>
+        </is>
+      </c>
       <c r="E325" s="5" t="inlineStr">
         <is>
           <t>AB7877734</t>
@@ -12248,7 +12573,11 @@
           <t>Sunnatillayeva E'zoza Jamshid qizi</t>
         </is>
       </c>
-      <c r="D326" s="2" t="inlineStr"/>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A365</t>
+        </is>
+      </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
           <t>AD4807056</t>
@@ -12735,30 +13064,28 @@
       </c>
       <c r="C339" s="7" t="inlineStr">
         <is>
-          <t>Turayeva Dilsuz Oybek qizi</t>
-        </is>
-      </c>
-      <c r="D339" s="5" t="n">
-        <v>268</v>
-      </c>
+          <t>Shermatova Gulsun Xurshid qizi</t>
+        </is>
+      </c>
+      <c r="D339" s="5" t="inlineStr"/>
       <c r="E339" s="5" t="inlineStr">
         <is>
-          <t>AE5053541</t>
+          <t>AE5836574</t>
         </is>
       </c>
       <c r="F339" s="6" t="inlineStr">
         <is>
-          <t>61205095590053</t>
+          <t>60802085590029</t>
         </is>
       </c>
       <c r="G339" s="6" t="inlineStr">
         <is>
-          <t>15.11.2025</t>
+          <t>13.01.2026</t>
         </is>
       </c>
       <c r="H339" s="6" t="inlineStr">
         <is>
-          <t>12.05.2009</t>
+          <t>08.02.2008</t>
         </is>
       </c>
     </row>
@@ -12773,30 +13100,30 @@
       </c>
       <c r="C340" s="4" t="inlineStr">
         <is>
-          <t>Turg'unova Jasmina Turg'un qizi</t>
+          <t>Turayeva Dilsuz Oybek qizi</t>
         </is>
       </c>
       <c r="D340" s="2" t="n">
-        <v>122</v>
+        <v>268</v>
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>AE6171425</t>
+          <t>AE5053541</t>
         </is>
       </c>
       <c r="F340" s="3" t="inlineStr">
         <is>
-          <t>62802085590087</t>
+          <t>61205095590053</t>
         </is>
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>03.02.2026</t>
+          <t>15.11.2025</t>
         </is>
       </c>
       <c r="H340" s="3" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>12.05.2009</t>
         </is>
       </c>
     </row>
@@ -12811,30 +13138,30 @@
       </c>
       <c r="C341" s="7" t="inlineStr">
         <is>
-          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+          <t>Turg'unova Jasmina Turg'un qizi</t>
         </is>
       </c>
       <c r="D341" s="5" t="n">
-        <v>233</v>
+        <v>122</v>
       </c>
       <c r="E341" s="5" t="inlineStr">
         <is>
-          <t>AD9812146</t>
+          <t>AE6171425</t>
         </is>
       </c>
       <c r="F341" s="6" t="inlineStr">
         <is>
-          <t>61206075590076</t>
+          <t>62802085590087</t>
         </is>
       </c>
       <c r="G341" s="6" t="inlineStr">
         <is>
-          <t>13.12.2024</t>
+          <t>03.02.2026</t>
         </is>
       </c>
       <c r="H341" s="6" t="inlineStr">
         <is>
-          <t>12.06.2007</t>
+          <t>28.02.2008</t>
         </is>
       </c>
     </row>
@@ -12844,35 +13171,35 @@
       </c>
       <c r="B342" s="3" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-01</t>
         </is>
       </c>
       <c r="C342" s="4" t="inlineStr">
         <is>
-          <t>Alimova Sevinch Raxmiddin qizi</t>
+          <t>Ziyodullayeva Jasmina Alisher qizi</t>
         </is>
       </c>
       <c r="D342" s="2" t="n">
-        <v>312</v>
+        <v>233</v>
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>AB7974700</t>
+          <t>AD9812146</t>
         </is>
       </c>
       <c r="F342" s="3" t="inlineStr">
         <is>
-          <t>62707005740020</t>
+          <t>61206075590076</t>
         </is>
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>27.10.2017</t>
+          <t>13.12.2024</t>
         </is>
       </c>
       <c r="H342" s="3" t="inlineStr">
         <is>
-          <t>27.07.2000</t>
+          <t>12.06.2007</t>
         </is>
       </c>
     </row>
@@ -12887,30 +13214,30 @@
       </c>
       <c r="C343" s="7" t="inlineStr">
         <is>
-          <t>Berdiqulova Gulshan Rustam qizi</t>
+          <t>Alimova Sevinch Raxmiddin qizi</t>
         </is>
       </c>
       <c r="D343" s="5" t="n">
-        <v>239</v>
+        <v>312</v>
       </c>
       <c r="E343" s="5" t="inlineStr">
         <is>
-          <t>AE6702868</t>
+          <t>AB7974700</t>
         </is>
       </c>
       <c r="F343" s="6" t="inlineStr">
         <is>
-          <t>41001955590049</t>
+          <t>62707005740020</t>
         </is>
       </c>
       <c r="G343" s="6" t="inlineStr">
         <is>
-          <t>16.03.2026</t>
+          <t>27.10.2017</t>
         </is>
       </c>
       <c r="H343" s="6" t="inlineStr">
         <is>
-          <t>10.01.1995</t>
+          <t>27.07.2000</t>
         </is>
       </c>
     </row>
@@ -12925,30 +13252,30 @@
       </c>
       <c r="C344" s="4" t="inlineStr">
         <is>
-          <t>Eshmurotova Charos Bekqul qizi</t>
+          <t>Berdiqulova Gulshan Rustam qizi</t>
         </is>
       </c>
       <c r="D344" s="2" t="n">
-        <v>110</v>
+        <v>239</v>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>AE5720760</t>
+          <t>AE6702868</t>
         </is>
       </c>
       <c r="F344" s="3" t="inlineStr">
         <is>
-          <t>61901085720047</t>
+          <t>41001955590049</t>
         </is>
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>07.01.2026</t>
+          <t>16.03.2026</t>
         </is>
       </c>
       <c r="H344" s="3" t="inlineStr">
         <is>
-          <t>19.01.2008</t>
+          <t>10.01.1995</t>
         </is>
       </c>
     </row>
@@ -12963,30 +13290,30 @@
       </c>
       <c r="C345" s="7" t="inlineStr">
         <is>
-          <t>G'aybullayeva Ruxsora Xusniddin qizi</t>
+          <t>Eshmurotova Charos Bekqul qizi</t>
         </is>
       </c>
       <c r="D345" s="5" t="n">
-        <v>236</v>
+        <v>110</v>
       </c>
       <c r="E345" s="5" t="inlineStr">
         <is>
-          <t>AD8701218</t>
+          <t>AE5720760</t>
         </is>
       </c>
       <c r="F345" s="6" t="inlineStr">
         <is>
-          <t>61206085590028</t>
+          <t>61901085720047</t>
         </is>
       </c>
       <c r="G345" s="6" t="inlineStr">
         <is>
-          <t>20.09.2024</t>
+          <t>07.01.2026</t>
         </is>
       </c>
       <c r="H345" s="6" t="inlineStr">
         <is>
-          <t>12.06.2008</t>
+          <t>19.01.2008</t>
         </is>
       </c>
     </row>
@@ -13001,30 +13328,30 @@
       </c>
       <c r="C346" s="4" t="inlineStr">
         <is>
-          <t>Hamroqulova Farzona Odilovna</t>
+          <t>G'aybullayeva Ruxsora Xusniddin qizi</t>
         </is>
       </c>
       <c r="D346" s="2" t="n">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>AE4371486</t>
+          <t>AD8701218</t>
         </is>
       </c>
       <c r="F346" s="3" t="inlineStr">
         <is>
-          <t>62111085680033</t>
+          <t>61206085590028</t>
         </is>
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>27.09.2025</t>
+          <t>20.09.2024</t>
         </is>
       </c>
       <c r="H346" s="3" t="inlineStr">
         <is>
-          <t>21.11.2008</t>
+          <t>12.06.2008</t>
         </is>
       </c>
     </row>
@@ -13039,30 +13366,30 @@
       </c>
       <c r="C347" s="7" t="inlineStr">
         <is>
-          <t>Hasanova Dilnura Eson qizi</t>
+          <t>Hamroqulova Farzona Odilovna</t>
         </is>
       </c>
       <c r="D347" s="5" t="n">
-        <v>166</v>
+        <v>278</v>
       </c>
       <c r="E347" s="5" t="inlineStr">
         <is>
-          <t>AE3555106</t>
+          <t>AE4371486</t>
         </is>
       </c>
       <c r="F347" s="6" t="inlineStr">
         <is>
-          <t>61508085680038</t>
+          <t>62111085680033</t>
         </is>
       </c>
       <c r="G347" s="6" t="inlineStr">
         <is>
-          <t>29.07.2025</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="H347" s="6" t="inlineStr">
         <is>
-          <t>15.08.2008</t>
+          <t>21.11.2008</t>
         </is>
       </c>
     </row>
@@ -13077,30 +13404,30 @@
       </c>
       <c r="C348" s="4" t="inlineStr">
         <is>
-          <t>Hasanova Marjona Xolmurod qizi</t>
+          <t>Hasanova Dilnura Eson qizi</t>
         </is>
       </c>
       <c r="D348" s="2" t="n">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>AE5685784</t>
+          <t>AE3555106</t>
         </is>
       </c>
       <c r="F348" s="3" t="inlineStr">
         <is>
-          <t>60411085680047</t>
+          <t>61508085680038</t>
         </is>
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>06.01.2026</t>
+          <t>29.07.2025</t>
         </is>
       </c>
       <c r="H348" s="3" t="inlineStr">
         <is>
-          <t>04.11.2008</t>
+          <t>15.08.2008</t>
         </is>
       </c>
     </row>
@@ -13115,30 +13442,30 @@
       </c>
       <c r="C349" s="7" t="inlineStr">
         <is>
-          <t>Ilhomova Zuhra Davron qizi</t>
+          <t>Hasanova Marjona Xolmurod qizi</t>
         </is>
       </c>
       <c r="D349" s="5" t="n">
-        <v>294</v>
+        <v>192</v>
       </c>
       <c r="E349" s="5" t="inlineStr">
         <is>
-          <t>AE4378923</t>
+          <t>AE5685784</t>
         </is>
       </c>
       <c r="F349" s="6" t="inlineStr">
         <is>
-          <t>63110085590015</t>
+          <t>60411085680047</t>
         </is>
       </c>
       <c r="G349" s="6" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>06.01.2026</t>
         </is>
       </c>
       <c r="H349" s="6" t="inlineStr">
         <is>
-          <t>31.10.2008</t>
+          <t>04.11.2008</t>
         </is>
       </c>
     </row>
@@ -13153,30 +13480,30 @@
       </c>
       <c r="C350" s="4" t="inlineStr">
         <is>
-          <t>Islomova Nilufar Abdulxafiz qizi</t>
+          <t>Ilhomova Zuhra Davron qizi</t>
         </is>
       </c>
       <c r="D350" s="2" t="n">
-        <v>94</v>
+        <v>294</v>
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>AD9664280</t>
+          <t>AE4378923</t>
         </is>
       </c>
       <c r="F350" s="3" t="inlineStr">
         <is>
-          <t>61911085590104</t>
+          <t>63110085590015</t>
         </is>
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>03.12.2024</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="H350" s="3" t="inlineStr">
         <is>
-          <t>19.11.2008</t>
+          <t>31.10.2008</t>
         </is>
       </c>
     </row>
@@ -13191,30 +13518,30 @@
       </c>
       <c r="C351" s="7" t="inlineStr">
         <is>
-          <t>Jalolova Rayxona Akmal qizi</t>
+          <t>Islomova Nilufar Abdulxafiz qizi</t>
         </is>
       </c>
       <c r="D351" s="5" t="n">
-        <v>262</v>
+        <v>94</v>
       </c>
       <c r="E351" s="5" t="inlineStr">
         <is>
-          <t>AE3492384</t>
+          <t>AD9664280</t>
         </is>
       </c>
       <c r="F351" s="6" t="inlineStr">
         <is>
-          <t>62207085680059</t>
+          <t>61911085590104</t>
         </is>
       </c>
       <c r="G351" s="6" t="inlineStr">
         <is>
-          <t>23.07.2025</t>
+          <t>03.12.2024</t>
         </is>
       </c>
       <c r="H351" s="6" t="inlineStr">
         <is>
-          <t>22.07.2008</t>
+          <t>19.11.2008</t>
         </is>
       </c>
     </row>
@@ -13229,30 +13556,30 @@
       </c>
       <c r="C352" s="4" t="inlineStr">
         <is>
-          <t>Javliyeva Nargiza Ortiq qizi</t>
+          <t>Jalolova Rayxona Akmal qizi</t>
         </is>
       </c>
       <c r="D352" s="2" t="n">
-        <v>173</v>
+        <v>262</v>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>AE5222372</t>
+          <t>AE3492384</t>
         </is>
       </c>
       <c r="F352" s="3" t="inlineStr">
         <is>
-          <t>62401095680012</t>
+          <t>62207085680059</t>
         </is>
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>28.11.2025</t>
+          <t>23.07.2025</t>
         </is>
       </c>
       <c r="H352" s="3" t="inlineStr">
         <is>
-          <t>24.01.2009</t>
+          <t>22.07.2008</t>
         </is>
       </c>
     </row>
@@ -13267,30 +13594,30 @@
       </c>
       <c r="C353" s="7" t="inlineStr">
         <is>
-          <t>Maxmashoxova Feruza Bekmurod qizi</t>
+          <t>Javliyeva Nargiza Ortiq qizi</t>
         </is>
       </c>
       <c r="D353" s="5" t="n">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="E353" s="5" t="inlineStr">
         <is>
-          <t>AE5088010</t>
+          <t>AE5222372</t>
         </is>
       </c>
       <c r="F353" s="6" t="inlineStr">
         <is>
-          <t>60201085630050</t>
+          <t>62401095680012</t>
         </is>
       </c>
       <c r="G353" s="6" t="inlineStr">
         <is>
-          <t>18.11.2025</t>
+          <t>28.11.2025</t>
         </is>
       </c>
       <c r="H353" s="6" t="inlineStr">
         <is>
-          <t>02.01.2008</t>
+          <t>24.01.2009</t>
         </is>
       </c>
     </row>
@@ -13305,30 +13632,30 @@
       </c>
       <c r="C354" s="4" t="inlineStr">
         <is>
-          <t>Meyliqulova Hilola Farhod qizi</t>
+          <t>Maxmashoxova Feruza Bekmurod qizi</t>
         </is>
       </c>
       <c r="D354" s="2" t="n">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>AB7137876</t>
+          <t>AE5088010</t>
         </is>
       </c>
       <c r="F354" s="3" t="inlineStr">
         <is>
-          <t>61202005680055</t>
+          <t>60201085630050</t>
         </is>
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>07.07.2017</t>
+          <t>18.11.2025</t>
         </is>
       </c>
       <c r="H354" s="3" t="inlineStr">
         <is>
-          <t>12.02.2000</t>
+          <t>02.01.2008</t>
         </is>
       </c>
     </row>
@@ -13343,30 +13670,30 @@
       </c>
       <c r="C355" s="7" t="inlineStr">
         <is>
-          <t>Nu'monova Saidabonu Ulug'bek qizi</t>
+          <t>Meyliqulova Hilola Farhod qizi</t>
         </is>
       </c>
       <c r="D355" s="5" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="E355" s="5" t="inlineStr">
         <is>
-          <t>AE1067914</t>
+          <t>AB7137876</t>
         </is>
       </c>
       <c r="F355" s="6" t="inlineStr">
         <is>
-          <t>62410085590084</t>
+          <t>61202005680055</t>
         </is>
       </c>
       <c r="G355" s="6" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07.07.2017</t>
         </is>
       </c>
       <c r="H355" s="6" t="inlineStr">
         <is>
-          <t>24.10.2008</t>
+          <t>12.02.2000</t>
         </is>
       </c>
     </row>
@@ -13381,30 +13708,30 @@
       </c>
       <c r="C356" s="4" t="inlineStr">
         <is>
-          <t>Nurillayeva Dilsuz Mashrabovna</t>
+          <t>Nu'monova Saidabonu Ulug'bek qizi</t>
         </is>
       </c>
       <c r="D356" s="2" t="n">
-        <v>326</v>
+        <v>38</v>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>AD4774693</t>
+          <t>AE1067914</t>
         </is>
       </c>
       <c r="F356" s="3" t="inlineStr">
         <is>
-          <t>42506912640010</t>
+          <t>62410085590084</t>
         </is>
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>05.10.2023</t>
+          <t>07.01.2025</t>
         </is>
       </c>
       <c r="H356" s="3" t="inlineStr">
         <is>
-          <t>25.06.1991</t>
+          <t>24.10.2008</t>
         </is>
       </c>
     </row>
@@ -13419,30 +13746,30 @@
       </c>
       <c r="C357" s="7" t="inlineStr">
         <is>
-          <t>Ochildiyeva Dinora Otabek qizi</t>
+          <t>Nurillayeva Dilsuz Mashrabovna</t>
         </is>
       </c>
       <c r="D357" s="5" t="n">
-        <v>87</v>
+        <v>326</v>
       </c>
       <c r="E357" s="5" t="inlineStr">
         <is>
-          <t>AE4084333</t>
+          <t>AD4774693</t>
         </is>
       </c>
       <c r="F357" s="6" t="inlineStr">
         <is>
-          <t>62012085590055</t>
+          <t>42506912640010</t>
         </is>
       </c>
       <c r="G357" s="6" t="inlineStr">
         <is>
-          <t>08.09.2025</t>
+          <t>05.10.2023</t>
         </is>
       </c>
       <c r="H357" s="6" t="inlineStr">
         <is>
-          <t>20.12.2008</t>
+          <t>25.06.1991</t>
         </is>
       </c>
     </row>
@@ -13457,28 +13784,30 @@
       </c>
       <c r="C358" s="4" t="inlineStr">
         <is>
-          <t>Qulmatova Shabbona Azamat qizi</t>
-        </is>
-      </c>
-      <c r="D358" s="2" t="inlineStr"/>
+          <t>Ochildiyeva Dinora Otabek qizi</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="n">
+        <v>87</v>
+      </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>AE4905104</t>
+          <t>AE4084333</t>
         </is>
       </c>
       <c r="F358" s="3" t="inlineStr">
         <is>
-          <t>61008085680019</t>
+          <t>62012085590055</t>
         </is>
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>05.11.2025</t>
+          <t>08.09.2025</t>
         </is>
       </c>
       <c r="H358" s="3" t="inlineStr">
         <is>
-          <t>10.08.2008</t>
+          <t>20.12.2008</t>
         </is>
       </c>
     </row>
@@ -13493,30 +13822,28 @@
       </c>
       <c r="C359" s="7" t="inlineStr">
         <is>
-          <t>Quysinova Rohshona To'lqin qizi</t>
-        </is>
-      </c>
-      <c r="D359" s="5" t="n">
-        <v>242</v>
-      </c>
+          <t>Qulmatova Shabbona Azamat qizi</t>
+        </is>
+      </c>
+      <c r="D359" s="5" t="inlineStr"/>
       <c r="E359" s="5" t="inlineStr">
         <is>
-          <t>AE7231113</t>
+          <t>AE4905104</t>
         </is>
       </c>
       <c r="F359" s="6" t="inlineStr">
         <is>
-          <t>60406055720067</t>
+          <t>61008085680019</t>
         </is>
       </c>
       <c r="G359" s="6" t="inlineStr">
         <is>
-          <t>01.05.2026</t>
+          <t>05.11.2025</t>
         </is>
       </c>
       <c r="H359" s="6" t="inlineStr">
         <is>
-          <t>04.06.2005</t>
+          <t>10.08.2008</t>
         </is>
       </c>
     </row>
@@ -13531,30 +13858,30 @@
       </c>
       <c r="C360" s="4" t="inlineStr">
         <is>
-          <t>Ro'zimurodova Larisa Ma'matali qizi</t>
+          <t>Quysinova Rohshona To'lqin qizi</t>
         </is>
       </c>
       <c r="D360" s="2" t="n">
-        <v>100</v>
+        <v>242</v>
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>AE5324961</t>
+          <t>AE7231113</t>
         </is>
       </c>
       <c r="F360" s="3" t="inlineStr">
         <is>
-          <t>61608085630072</t>
+          <t>60406055720067</t>
         </is>
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>05.12.2025</t>
+          <t>01.05.2026</t>
         </is>
       </c>
       <c r="H360" s="3" t="inlineStr">
         <is>
-          <t>16.08.2008</t>
+          <t>04.06.2005</t>
         </is>
       </c>
     </row>
@@ -13569,30 +13896,30 @@
       </c>
       <c r="C361" s="7" t="inlineStr">
         <is>
-          <t>Samadova Nigora Abdisamiyevna</t>
+          <t>Ro'zimurodova Larisa Ma'matali qizi</t>
         </is>
       </c>
       <c r="D361" s="5" t="n">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="E361" s="5" t="inlineStr">
         <is>
-          <t>AE1836076</t>
+          <t>AE5324961</t>
         </is>
       </c>
       <c r="F361" s="6" t="inlineStr">
         <is>
-          <t>40710895590044</t>
+          <t>61608085630072</t>
         </is>
       </c>
       <c r="G361" s="6" t="inlineStr">
         <is>
-          <t>05.03.2025</t>
+          <t>05.12.2025</t>
         </is>
       </c>
       <c r="H361" s="6" t="inlineStr">
         <is>
-          <t>07.10.1989</t>
+          <t>16.08.2008</t>
         </is>
       </c>
     </row>
@@ -13607,30 +13934,30 @@
       </c>
       <c r="C362" s="4" t="inlineStr">
         <is>
-          <t>Samatova Oydin Sulaymon qizi</t>
+          <t>Samadova Nigora Abdisamiyevna</t>
         </is>
       </c>
       <c r="D362" s="2" t="n">
-        <v>146</v>
+        <v>81</v>
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>AD8980430</t>
+          <t>AE1836076</t>
         </is>
       </c>
       <c r="F362" s="3" t="inlineStr">
         <is>
-          <t>42910905720012</t>
+          <t>40710895590044</t>
         </is>
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>11.10.2024</t>
+          <t>05.03.2025</t>
         </is>
       </c>
       <c r="H362" s="3" t="inlineStr">
         <is>
-          <t>29.10.1990</t>
+          <t>07.10.1989</t>
         </is>
       </c>
     </row>
@@ -13645,30 +13972,30 @@
       </c>
       <c r="C363" s="7" t="inlineStr">
         <is>
-          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
+          <t>Samatova Oydin Sulaymon qizi</t>
         </is>
       </c>
       <c r="D363" s="5" t="n">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="E363" s="5" t="inlineStr">
         <is>
-          <t>AE3352294</t>
+          <t>AD8980430</t>
         </is>
       </c>
       <c r="F363" s="6" t="inlineStr">
         <is>
-          <t>61807085590034</t>
+          <t>42910905720012</t>
         </is>
       </c>
       <c r="G363" s="6" t="inlineStr">
         <is>
-          <t>10.07.2025</t>
+          <t>11.10.2024</t>
         </is>
       </c>
       <c r="H363" s="6" t="inlineStr">
         <is>
-          <t>18.07.2008</t>
+          <t>29.10.1990</t>
         </is>
       </c>
     </row>
@@ -13683,28 +14010,30 @@
       </c>
       <c r="C364" s="4" t="inlineStr">
         <is>
-          <t>Shonazarova Vazira Botir qizi</t>
-        </is>
-      </c>
-      <c r="D364" s="2" t="inlineStr"/>
+          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="n">
+        <v>74</v>
+      </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>AE 4233482</t>
+          <t>AE3352294</t>
         </is>
       </c>
       <c r="F364" s="3" t="inlineStr">
         <is>
-          <t>61311085680032</t>
+          <t>61807085590034</t>
         </is>
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>17.09.2025</t>
+          <t>10.07.2025</t>
         </is>
       </c>
       <c r="H364" s="3" t="inlineStr">
         <is>
-          <t>13.11.2008</t>
+          <t>18.07.2008</t>
         </is>
       </c>
     </row>
@@ -13719,30 +14048,28 @@
       </c>
       <c r="C365" s="7" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
-        </is>
-      </c>
-      <c r="D365" s="5" t="n">
-        <v>162</v>
-      </c>
+          <t>Shonazarova Vazira Botir qizi</t>
+        </is>
+      </c>
+      <c r="D365" s="5" t="inlineStr"/>
       <c r="E365" s="5" t="inlineStr">
         <is>
-          <t>AD7767171</t>
+          <t>AE 4233482</t>
         </is>
       </c>
       <c r="F365" s="6" t="inlineStr">
         <is>
-          <t>62103085590038</t>
+          <t>61311085680032</t>
         </is>
       </c>
       <c r="G365" s="6" t="inlineStr">
         <is>
-          <t>06.07.2024</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="H365" s="6" t="inlineStr">
         <is>
-          <t>21.03.2008</t>
+          <t>13.11.2008</t>
         </is>
       </c>
     </row>
@@ -13757,30 +14084,30 @@
       </c>
       <c r="C366" s="4" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
       <c r="D366" s="2" t="n">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>AB7166586</t>
+          <t>AD7767171</t>
         </is>
       </c>
       <c r="F366" s="3" t="inlineStr">
         <is>
-          <t>61409005680027</t>
+          <t>62103085590038</t>
         </is>
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>09.07.2017</t>
+          <t>06.07.2024</t>
         </is>
       </c>
       <c r="H366" s="3" t="inlineStr">
         <is>
-          <t>14.09.2000</t>
+          <t>21.03.2008</t>
         </is>
       </c>
     </row>
@@ -13795,30 +14122,30 @@
       </c>
       <c r="C367" s="7" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="D367" s="5" t="n">
-        <v>6</v>
+        <v>122</v>
       </c>
       <c r="E367" s="5" t="inlineStr">
         <is>
-          <t>AE3558477</t>
+          <t>AB7166586</t>
         </is>
       </c>
       <c r="F367" s="6" t="inlineStr">
         <is>
-          <t>62709085590070</t>
+          <t>61409005680027</t>
         </is>
       </c>
       <c r="G367" s="6" t="inlineStr">
         <is>
-          <t>29.07.2025</t>
+          <t>09.07.2017</t>
         </is>
       </c>
       <c r="H367" s="6" t="inlineStr">
         <is>
-          <t>27.09.2008</t>
+          <t>14.09.2000</t>
         </is>
       </c>
     </row>
@@ -13833,30 +14160,30 @@
       </c>
       <c r="C368" s="4" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona Nazim qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="D368" s="2" t="n">
-        <v>161</v>
+        <v>6</v>
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
-          <t>AE5199773</t>
+          <t>AE3558477</t>
         </is>
       </c>
       <c r="F368" s="3" t="inlineStr">
         <is>
-          <t>61906085680012</t>
+          <t>62709085590070</t>
         </is>
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>26.11.2025</t>
+          <t>29.07.2025</t>
         </is>
       </c>
       <c r="H368" s="3" t="inlineStr">
         <is>
-          <t>19.06.2008</t>
+          <t>27.09.2008</t>
         </is>
       </c>
     </row>
@@ -13871,30 +14198,30 @@
       </c>
       <c r="C369" s="7" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
       <c r="D369" s="5" t="n">
-        <v>11</v>
+        <v>161</v>
       </c>
       <c r="E369" s="5" t="inlineStr">
         <is>
-          <t>AD4186169</t>
+          <t>AE5199773</t>
         </is>
       </c>
       <c r="F369" s="6" t="inlineStr">
         <is>
-          <t>40404975650046</t>
+          <t>61906085680012</t>
         </is>
       </c>
       <c r="G369" s="6" t="inlineStr">
         <is>
-          <t>07.08.2023</t>
+          <t>26.11.2025</t>
         </is>
       </c>
       <c r="H369" s="6" t="inlineStr">
         <is>
-          <t>04.04.1997</t>
+          <t>19.06.2008</t>
         </is>
       </c>
     </row>
@@ -13909,30 +14236,30 @@
       </c>
       <c r="C370" s="4" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="D370" s="2" t="n">
-        <v>220</v>
+        <v>11</v>
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>AE4503488</t>
+          <t>AD4186169</t>
         </is>
       </c>
       <c r="F370" s="3" t="inlineStr">
         <is>
-          <t>51106085680031</t>
+          <t>40404975650046</t>
         </is>
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>07.10.2025</t>
+          <t>07.08.2023</t>
         </is>
       </c>
       <c r="H370" s="3" t="inlineStr">
         <is>
-          <t>11.06.2008</t>
+          <t>04.04.1997</t>
         </is>
       </c>
     </row>
@@ -13947,30 +14274,30 @@
       </c>
       <c r="C371" s="7" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="D371" s="5" t="n">
-        <v>79</v>
+        <v>220</v>
       </c>
       <c r="E371" s="5" t="inlineStr">
         <is>
-          <t>AE5293914</t>
+          <t>AE4503488</t>
         </is>
       </c>
       <c r="F371" s="6" t="inlineStr">
         <is>
-          <t>60512085590078</t>
+          <t>51106085680031</t>
         </is>
       </c>
       <c r="G371" s="6" t="inlineStr">
         <is>
-          <t>04.12.2025</t>
+          <t>07.10.2025</t>
         </is>
       </c>
       <c r="H371" s="6" t="inlineStr">
         <is>
-          <t>05.12.2008</t>
+          <t>11.06.2008</t>
         </is>
       </c>
     </row>
@@ -13985,30 +14312,30 @@
       </c>
       <c r="C372" s="4" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="D372" s="2" t="n">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>AE4989343</t>
+          <t>AE5293914</t>
         </is>
       </c>
       <c r="F372" s="3" t="inlineStr">
         <is>
-          <t>60402095590060</t>
+          <t>60512085590078</t>
         </is>
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>11.11.2025</t>
+          <t>04.12.2025</t>
         </is>
       </c>
       <c r="H372" s="3" t="inlineStr">
         <is>
-          <t>04.02.2009</t>
+          <t>05.12.2008</t>
         </is>
       </c>
     </row>
@@ -14023,30 +14350,30 @@
       </c>
       <c r="C373" s="7" t="inlineStr">
         <is>
-          <t>Usmanova Iroda Abdurazzoq qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="D373" s="5" t="n">
-        <v>279</v>
+        <v>148</v>
       </c>
       <c r="E373" s="5" t="inlineStr">
         <is>
-          <t>AE7821304</t>
+          <t>AE4989343</t>
         </is>
       </c>
       <c r="F373" s="6" t="inlineStr">
         <is>
-          <t>41406985680067</t>
+          <t>60402095590060</t>
         </is>
       </c>
       <c r="G373" s="6" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>11.11.2025</t>
         </is>
       </c>
       <c r="H373" s="6" t="inlineStr">
         <is>
-          <t>14.06.1998</t>
+          <t>04.02.2009</t>
         </is>
       </c>
     </row>
@@ -14061,30 +14388,30 @@
       </c>
       <c r="C374" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="D374" s="2" t="n">
-        <v>2</v>
+        <v>279</v>
       </c>
       <c r="E374" s="2" t="inlineStr">
         <is>
-          <t>AC1967100</t>
+          <t>AE7821304</t>
         </is>
       </c>
       <c r="F374" s="3" t="inlineStr">
         <is>
-          <t>62704025590042</t>
+          <t>41406985680067</t>
         </is>
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>12.06.2019</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="H374" s="3" t="inlineStr">
         <is>
-          <t>27.04.2002</t>
+          <t>14.06.1998</t>
         </is>
       </c>
     </row>
@@ -14099,30 +14426,30 @@
       </c>
       <c r="C375" s="7" t="inlineStr">
         <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
+          <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
       <c r="D375" s="5" t="n">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="E375" s="5" t="inlineStr">
         <is>
-          <t>AB9239333</t>
+          <t>AC1967100</t>
         </is>
       </c>
       <c r="F375" s="6" t="inlineStr">
         <is>
-          <t>42207935680042</t>
+          <t>62704025590042</t>
         </is>
       </c>
       <c r="G375" s="6" t="inlineStr">
         <is>
-          <t>09.04.2018</t>
+          <t>12.06.2019</t>
         </is>
       </c>
       <c r="H375" s="6" t="inlineStr">
         <is>
-          <t>22.07.1993</t>
+          <t>27.04.2002</t>
         </is>
       </c>
     </row>
@@ -14132,35 +14459,35 @@
       </c>
       <c r="B376" s="3" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C376" s="4" t="inlineStr">
         <is>
-          <t>Aliqulova Shaxzoda Anvar qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="D376" s="2" t="n">
-        <v>272</v>
+        <v>75</v>
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
-          <t>AC1827958</t>
+          <t>AB9239333</t>
         </is>
       </c>
       <c r="F376" s="3" t="inlineStr">
         <is>
-          <t>60301037890018</t>
+          <t>42207935680042</t>
         </is>
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>18.04.2019</t>
+          <t>09.04.2018</t>
         </is>
       </c>
       <c r="H376" s="3" t="inlineStr">
         <is>
-          <t>03.01.2003</t>
+          <t>22.07.1993</t>
         </is>
       </c>
     </row>
@@ -14175,30 +14502,30 @@
       </c>
       <c r="C377" s="7" t="inlineStr">
         <is>
-          <t>Arziqulova Laylo Bahodir qizi</t>
+          <t>Aliqulova Shaxzoda Anvar qizi</t>
         </is>
       </c>
       <c r="D377" s="5" t="n">
-        <v>79</v>
+        <v>272</v>
       </c>
       <c r="E377" s="5" t="inlineStr">
         <is>
-          <t>AD8548125</t>
+          <t>AC1827958</t>
         </is>
       </c>
       <c r="F377" s="6" t="inlineStr">
         <is>
-          <t>60110065720109</t>
+          <t>60301037890018</t>
         </is>
       </c>
       <c r="G377" s="6" t="inlineStr">
         <is>
-          <t>09.09.2024</t>
+          <t>18.04.2019</t>
         </is>
       </c>
       <c r="H377" s="6" t="inlineStr">
         <is>
-          <t>01.10.2006</t>
+          <t>03.01.2003</t>
         </is>
       </c>
     </row>
@@ -14213,30 +14540,30 @@
       </c>
       <c r="C378" s="4" t="inlineStr">
         <is>
-          <t>Eshnazarova Dilnoza Rustam qizi</t>
+          <t>Arziqulova Laylo Bahodir qizi</t>
         </is>
       </c>
       <c r="D378" s="2" t="n">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="E378" s="2" t="inlineStr">
         <is>
-          <t>AE3321050</t>
+          <t>AD8548125</t>
         </is>
       </c>
       <c r="F378" s="3" t="inlineStr">
         <is>
-          <t>60710085730098</t>
+          <t>60110065720109</t>
         </is>
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>08.07.2025</t>
+          <t>09.09.2024</t>
         </is>
       </c>
       <c r="H378" s="3" t="inlineStr">
         <is>
-          <t>07.10.2008</t>
+          <t>01.10.2006</t>
         </is>
       </c>
     </row>
@@ -14251,30 +14578,30 @@
       </c>
       <c r="C379" s="7" t="inlineStr">
         <is>
-          <t>Fayzullayeva Sarvinoz Sherbobo qizi</t>
+          <t>Eshnazarova Dilnoza Rustam qizi</t>
         </is>
       </c>
       <c r="D379" s="5" t="n">
-        <v>152</v>
+        <v>221</v>
       </c>
       <c r="E379" s="5" t="inlineStr">
         <is>
-          <t>AD1189588</t>
+          <t>AE3321050</t>
         </is>
       </c>
       <c r="F379" s="6" t="inlineStr">
         <is>
-          <t>63003055730053</t>
+          <t>60710085730098</t>
         </is>
       </c>
       <c r="G379" s="6" t="inlineStr">
         <is>
-          <t>24.03.2022</t>
+          <t>08.07.2025</t>
         </is>
       </c>
       <c r="H379" s="6" t="inlineStr">
         <is>
-          <t>30.03.2005</t>
+          <t>07.10.2008</t>
         </is>
       </c>
     </row>
@@ -14289,30 +14616,30 @@
       </c>
       <c r="C380" s="4" t="inlineStr">
         <is>
-          <t>Ibragimova Gulnoza Isroil qizi</t>
+          <t>Fayzullayeva Sarvinoz Sherbobo qizi</t>
         </is>
       </c>
       <c r="D380" s="2" t="n">
-        <v>308</v>
+        <v>152</v>
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
-          <t>AE4115057</t>
+          <t>AD1189588</t>
         </is>
       </c>
       <c r="F380" s="3" t="inlineStr">
         <is>
-          <t>60606085680085</t>
+          <t>63003055730053</t>
         </is>
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>09.09.2025</t>
+          <t>24.03.2022</t>
         </is>
       </c>
       <c r="H380" s="3" t="inlineStr">
         <is>
-          <t>06.06.2008</t>
+          <t>30.03.2005</t>
         </is>
       </c>
     </row>
@@ -14327,30 +14654,30 @@
       </c>
       <c r="C381" s="7" t="inlineStr">
         <is>
-          <t>Izzatulloyeva Vazira G'ayratzoda</t>
+          <t>Ibragimova Gulnoza Isroil qizi</t>
         </is>
       </c>
       <c r="D381" s="5" t="n">
-        <v>383</v>
+        <v>308</v>
       </c>
       <c r="E381" s="5" t="inlineStr">
         <is>
-          <t>AE5671026</t>
+          <t>AE4115057</t>
         </is>
       </c>
       <c r="F381" s="6" t="inlineStr">
         <is>
-          <t>42004975680094</t>
+          <t>60606085680085</t>
         </is>
       </c>
       <c r="G381" s="6" t="inlineStr">
         <is>
-          <t>05.01.2026</t>
+          <t>09.09.2025</t>
         </is>
       </c>
       <c r="H381" s="6" t="inlineStr">
         <is>
-          <t>20.04.1997</t>
+          <t>06.06.2008</t>
         </is>
       </c>
     </row>
@@ -14365,30 +14692,30 @@
       </c>
       <c r="C382" s="4" t="inlineStr">
         <is>
-          <t>Jurayeva Dilnoz G'oibnazarovna</t>
+          <t>Izzatulloyeva Vazira G'ayratzoda</t>
         </is>
       </c>
       <c r="D382" s="2" t="n">
-        <v>89</v>
+        <v>383</v>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>AD2957442</t>
+          <t>AE5671026</t>
         </is>
       </c>
       <c r="F382" s="3" t="inlineStr">
         <is>
-          <t>40305922560019</t>
+          <t>42004975680094</t>
         </is>
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>05.04.2023</t>
+          <t>05.01.2026</t>
         </is>
       </c>
       <c r="H382" s="3" t="inlineStr">
         <is>
-          <t>03.05.1992</t>
+          <t>20.04.1997</t>
         </is>
       </c>
     </row>
@@ -14403,30 +14730,30 @@
       </c>
       <c r="C383" s="7" t="inlineStr">
         <is>
-          <t>Mansurova Gulasal Musurmon qizi</t>
+          <t>Jurayeva Dilnoz G'oibnazarovna</t>
         </is>
       </c>
       <c r="D383" s="5" t="n">
-        <v>301</v>
+        <v>89</v>
       </c>
       <c r="E383" s="5" t="inlineStr">
         <is>
-          <t>AE4483600</t>
+          <t>AD2957442</t>
         </is>
       </c>
       <c r="F383" s="6" t="inlineStr">
         <is>
-          <t>62905085680067</t>
+          <t>40305922560019</t>
         </is>
       </c>
       <c r="G383" s="6" t="inlineStr">
         <is>
-          <t>06.10.2025</t>
+          <t>05.04.2023</t>
         </is>
       </c>
       <c r="H383" s="6" t="inlineStr">
         <is>
-          <t>29.05.2008</t>
+          <t>03.05.1992</t>
         </is>
       </c>
     </row>
@@ -14441,30 +14768,30 @@
       </c>
       <c r="C384" s="4" t="inlineStr">
         <is>
-          <t>Murtazayeva Kamola Jamoliddin qizi</t>
+          <t>Mansurova Gulasal Musurmon qizi</t>
         </is>
       </c>
       <c r="D384" s="2" t="n">
-        <v>25</v>
+        <v>301</v>
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>AC1458884</t>
+          <t>AE4483600</t>
         </is>
       </c>
       <c r="F384" s="3" t="inlineStr">
         <is>
-          <t>42708915590028</t>
+          <t>62905085680067</t>
         </is>
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>04.11.2018</t>
+          <t>06.10.2025</t>
         </is>
       </c>
       <c r="H384" s="3" t="inlineStr">
         <is>
-          <t>27.08.1991</t>
+          <t>29.05.2008</t>
         </is>
       </c>
     </row>
@@ -14479,30 +14806,30 @@
       </c>
       <c r="C385" s="7" t="inlineStr">
         <is>
-          <t>Mustafayeva Madina Ortiq qizi</t>
+          <t>Murtazayeva Kamola Jamoliddin qizi</t>
         </is>
       </c>
       <c r="D385" s="5" t="n">
-        <v>282</v>
+        <v>25</v>
       </c>
       <c r="E385" s="5" t="inlineStr">
         <is>
-          <t>AE4846447</t>
+          <t>AC1458884</t>
         </is>
       </c>
       <c r="F385" s="6" t="inlineStr">
         <is>
-          <t>63110085680103</t>
+          <t>42708915590028</t>
         </is>
       </c>
       <c r="G385" s="6" t="inlineStr">
         <is>
-          <t>31.10.2025</t>
+          <t>04.11.2018</t>
         </is>
       </c>
       <c r="H385" s="6" t="inlineStr">
         <is>
-          <t>31.10.2008</t>
+          <t>27.08.1991</t>
         </is>
       </c>
     </row>
@@ -14517,28 +14844,30 @@
       </c>
       <c r="C386" s="4" t="inlineStr">
         <is>
-          <t>Niyozova Komila Toshpulatovna</t>
-        </is>
-      </c>
-      <c r="D386" s="2" t="inlineStr"/>
+          <t>Mustafayeva Madina Ortiq qizi</t>
+        </is>
+      </c>
+      <c r="D386" s="2" t="n">
+        <v>282</v>
+      </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>AB9205278</t>
+          <t>AE4846447</t>
         </is>
       </c>
       <c r="F386" s="3" t="inlineStr">
         <is>
-          <t>42405832640057</t>
+          <t>63110085680103</t>
         </is>
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>07.04.2018</t>
+          <t>31.10.2025</t>
         </is>
       </c>
       <c r="H386" s="3" t="inlineStr">
         <is>
-          <t>24.05.1983</t>
+          <t>31.10.2008</t>
         </is>
       </c>
     </row>
@@ -14553,30 +14882,28 @@
       </c>
       <c r="C387" s="7" t="inlineStr">
         <is>
-          <t>Norboboyeva Farangiz Nuriddin qizi</t>
-        </is>
-      </c>
-      <c r="D387" s="5" t="n">
-        <v>231</v>
-      </c>
+          <t>Niyozova Komila Toshpulatovna</t>
+        </is>
+      </c>
+      <c r="D387" s="5" t="inlineStr"/>
       <c r="E387" s="5" t="inlineStr">
         <is>
-          <t>AE5898909</t>
+          <t>AB9205278</t>
         </is>
       </c>
       <c r="F387" s="6" t="inlineStr">
         <is>
-          <t>62808085590100</t>
+          <t>42405832640057</t>
         </is>
       </c>
       <c r="G387" s="6" t="inlineStr">
         <is>
-          <t>16.01.2026</t>
+          <t>07.04.2018</t>
         </is>
       </c>
       <c r="H387" s="6" t="inlineStr">
         <is>
-          <t>28.08.2008</t>
+          <t>24.05.1983</t>
         </is>
       </c>
     </row>
@@ -14591,30 +14918,30 @@
       </c>
       <c r="C388" s="4" t="inlineStr">
         <is>
-          <t>Pardaqulova Farzona Shovkatovna</t>
+          <t>Norboboyeva Farangiz Nuriddin qizi</t>
         </is>
       </c>
       <c r="D388" s="2" t="n">
-        <v>90</v>
+        <v>231</v>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>AE1336538</t>
+          <t>AE5898909</t>
         </is>
       </c>
       <c r="F388" s="3" t="inlineStr">
         <is>
-          <t>60312085590052</t>
+          <t>62808085590100</t>
         </is>
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>23.01.2025</t>
+          <t>16.01.2026</t>
         </is>
       </c>
       <c r="H388" s="3" t="inlineStr">
         <is>
-          <t>03.12.2008</t>
+          <t>28.08.2008</t>
         </is>
       </c>
     </row>
@@ -14629,30 +14956,30 @@
       </c>
       <c r="C389" s="7" t="inlineStr">
         <is>
-          <t>Pardayeva Farangiz Norali qizi</t>
+          <t>Pardaqulova Farzona Shovkatovna</t>
         </is>
       </c>
       <c r="D389" s="5" t="n">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="E389" s="5" t="inlineStr">
         <is>
-          <t>AE5643897</t>
+          <t>AE1336538</t>
         </is>
       </c>
       <c r="F389" s="6" t="inlineStr">
         <is>
-          <t>60102085590053</t>
+          <t>60312085590052</t>
         </is>
       </c>
       <c r="G389" s="6" t="inlineStr">
         <is>
-          <t>29.12.2025</t>
+          <t>23.01.2025</t>
         </is>
       </c>
       <c r="H389" s="6" t="inlineStr">
         <is>
-          <t>01.02.2008</t>
+          <t>03.12.2008</t>
         </is>
       </c>
     </row>
@@ -14667,30 +14994,30 @@
       </c>
       <c r="C390" s="4" t="inlineStr">
         <is>
-          <t>Primova Husnora Shovkat qizi</t>
+          <t>Pardayeva Farangiz Norali qizi</t>
         </is>
       </c>
       <c r="D390" s="2" t="n">
-        <v>251</v>
+        <v>105</v>
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>AC 0443770</t>
+          <t>AE5643897</t>
         </is>
       </c>
       <c r="F390" s="3" t="inlineStr">
         <is>
-          <t>61310015590029</t>
+          <t>60102085590053</t>
         </is>
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>10.12.2018</t>
+          <t>29.12.2025</t>
         </is>
       </c>
       <c r="H390" s="3" t="inlineStr">
         <is>
-          <t>13.10.2001</t>
+          <t>01.02.2008</t>
         </is>
       </c>
     </row>
@@ -14705,30 +15032,30 @@
       </c>
       <c r="C391" s="7" t="inlineStr">
         <is>
-          <t>Rasulova Husnobod Bekmurod qizi</t>
+          <t>Primova Husnora Shovkat qizi</t>
         </is>
       </c>
       <c r="D391" s="5" t="n">
-        <v>392</v>
+        <v>251</v>
       </c>
       <c r="E391" s="5" t="inlineStr">
         <is>
-          <t>AD1615363</t>
+          <t>AC 0443770</t>
         </is>
       </c>
       <c r="F391" s="6" t="inlineStr">
         <is>
-          <t>62705055720049</t>
+          <t>61310015590029</t>
         </is>
       </c>
       <c r="G391" s="6" t="inlineStr">
         <is>
-          <t>03.08.2022</t>
+          <t>10.12.2018</t>
         </is>
       </c>
       <c r="H391" s="6" t="inlineStr">
         <is>
-          <t>27.05.2005</t>
+          <t>13.10.2001</t>
         </is>
       </c>
     </row>
@@ -14743,30 +15070,30 @@
       </c>
       <c r="C392" s="4" t="inlineStr">
         <is>
-          <t>Rayimova Nozliya Laziz qizi</t>
+          <t>Rasulova Husnobod Bekmurod qizi</t>
         </is>
       </c>
       <c r="D392" s="2" t="n">
-        <v>291</v>
+        <v>392</v>
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>AE4759683</t>
+          <t>AD1615363</t>
         </is>
       </c>
       <c r="F392" s="3" t="inlineStr">
         <is>
-          <t>62606085590056</t>
+          <t>62705055720049</t>
         </is>
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>24.10.2025</t>
+          <t>03.08.2022</t>
         </is>
       </c>
       <c r="H392" s="3" t="inlineStr">
         <is>
-          <t>26.06.2008</t>
+          <t>27.05.2005</t>
         </is>
       </c>
     </row>
@@ -14781,30 +15108,30 @@
       </c>
       <c r="C393" s="7" t="inlineStr">
         <is>
-          <t>Rustamova Charos O'ktam qizi</t>
+          <t>Rayimova Nozliya Laziz qizi</t>
         </is>
       </c>
       <c r="D393" s="5" t="n">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="E393" s="5" t="inlineStr">
         <is>
-          <t>AE4730990</t>
+          <t>AE4759683</t>
         </is>
       </c>
       <c r="F393" s="6" t="inlineStr">
         <is>
-          <t>60810085680017</t>
+          <t>62606085590056</t>
         </is>
       </c>
       <c r="G393" s="6" t="inlineStr">
         <is>
-          <t>22.10.2025</t>
+          <t>24.10.2025</t>
         </is>
       </c>
       <c r="H393" s="6" t="inlineStr">
         <is>
-          <t>08.10.2008</t>
+          <t>26.06.2008</t>
         </is>
       </c>
     </row>
@@ -14819,30 +15146,30 @@
       </c>
       <c r="C394" s="4" t="inlineStr">
         <is>
-          <t>Salayeva Dilroz Muroulla qizi</t>
+          <t>Rustamova Charos O'ktam qizi</t>
         </is>
       </c>
       <c r="D394" s="2" t="n">
-        <v>205</v>
+        <v>309</v>
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>AE3039330</t>
+          <t>AE4730990</t>
         </is>
       </c>
       <c r="F394" s="3" t="inlineStr">
         <is>
-          <t>60408085730030</t>
+          <t>60810085680017</t>
         </is>
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>16.06.2025</t>
+          <t>22.10.2025</t>
         </is>
       </c>
       <c r="H394" s="3" t="inlineStr">
         <is>
-          <t>04.08.2008</t>
+          <t>08.10.2008</t>
         </is>
       </c>
     </row>
@@ -14857,30 +15184,30 @@
       </c>
       <c r="C395" s="7" t="inlineStr">
         <is>
-          <t>Sayfiyeva Zarina Axmad qizi</t>
+          <t>Salayeva Dilroz Muroulla qizi</t>
         </is>
       </c>
       <c r="D395" s="5" t="n">
-        <v>37</v>
+        <v>205</v>
       </c>
       <c r="E395" s="5" t="inlineStr">
         <is>
-          <t>AD7984192</t>
+          <t>AE3039330</t>
         </is>
       </c>
       <c r="F395" s="6" t="inlineStr">
         <is>
-          <t>61007085590081</t>
+          <t>60408085730030</t>
         </is>
       </c>
       <c r="G395" s="6" t="inlineStr">
         <is>
-          <t>23.07.2024</t>
+          <t>16.06.2025</t>
         </is>
       </c>
       <c r="H395" s="6" t="inlineStr">
         <is>
-          <t>10.07.2008</t>
+          <t>04.08.2008</t>
         </is>
       </c>
     </row>
@@ -14895,30 +15222,30 @@
       </c>
       <c r="C396" s="4" t="inlineStr">
         <is>
-          <t>Sayidova Dilafro'z Qahramon qizi</t>
+          <t>Sayfiyeva Zarina Axmad qizi</t>
         </is>
       </c>
       <c r="D396" s="2" t="n">
-        <v>263</v>
+        <v>37</v>
       </c>
       <c r="E396" s="2" t="inlineStr">
         <is>
-          <t>AE6071273</t>
+          <t>AD7984192</t>
         </is>
       </c>
       <c r="F396" s="3" t="inlineStr">
         <is>
-          <t>62708095680047</t>
+          <t>61007085590081</t>
         </is>
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>27.01.2026</t>
+          <t>23.07.2024</t>
         </is>
       </c>
       <c r="H396" s="3" t="inlineStr">
         <is>
-          <t>27.08.2009</t>
+          <t>10.07.2008</t>
         </is>
       </c>
     </row>
@@ -14933,30 +15260,30 @@
       </c>
       <c r="C397" s="7" t="inlineStr">
         <is>
-          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
+          <t>Sayidova Dilafro'z Qahramon qizi</t>
         </is>
       </c>
       <c r="D397" s="5" t="n">
-        <v>107</v>
+        <v>263</v>
       </c>
       <c r="E397" s="5" t="inlineStr">
         <is>
-          <t>AE2370999</t>
+          <t>AE6071273</t>
         </is>
       </c>
       <c r="F397" s="6" t="inlineStr">
         <is>
-          <t>60307085730074</t>
+          <t>62708095680047</t>
         </is>
       </c>
       <c r="G397" s="6" t="inlineStr">
         <is>
-          <t>17.04.2025</t>
+          <t>27.01.2026</t>
         </is>
       </c>
       <c r="H397" s="6" t="inlineStr">
         <is>
-          <t>03.07.2008</t>
+          <t>27.08.2009</t>
         </is>
       </c>
     </row>
@@ -14971,30 +15298,30 @@
       </c>
       <c r="C398" s="4" t="inlineStr">
         <is>
-          <t>Shukurova Zilola Farxod qizi</t>
+          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
         </is>
       </c>
       <c r="D398" s="2" t="n">
-        <v>172</v>
+        <v>107</v>
       </c>
       <c r="E398" s="2" t="inlineStr">
         <is>
-          <t>AE1059205</t>
+          <t>AE2370999</t>
         </is>
       </c>
       <c r="F398" s="3" t="inlineStr">
         <is>
-          <t>60610085590150</t>
+          <t>60307085730074</t>
         </is>
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>17.04.2025</t>
         </is>
       </c>
       <c r="H398" s="3" t="inlineStr">
         <is>
-          <t>06.10.2008</t>
+          <t>03.07.2008</t>
         </is>
       </c>
     </row>
@@ -15009,30 +15336,30 @@
       </c>
       <c r="C399" s="7" t="inlineStr">
         <is>
-          <t>Temirova Rushana Sarvarovna</t>
+          <t>Shukurova Zilola Farxod qizi</t>
         </is>
       </c>
       <c r="D399" s="5" t="n">
-        <v>299</v>
+        <v>172</v>
       </c>
       <c r="E399" s="5" t="inlineStr">
         <is>
-          <t>AD9123776</t>
+          <t>AE1059205</t>
         </is>
       </c>
       <c r="F399" s="6" t="inlineStr">
         <is>
-          <t>60709085590113</t>
+          <t>60610085590150</t>
         </is>
       </c>
       <c r="G399" s="6" t="inlineStr">
         <is>
-          <t>23.10.2024</t>
+          <t>07.01.2025</t>
         </is>
       </c>
       <c r="H399" s="6" t="inlineStr">
         <is>
-          <t>07.09.2008</t>
+          <t>06.10.2008</t>
         </is>
       </c>
     </row>
@@ -15047,30 +15374,30 @@
       </c>
       <c r="C400" s="4" t="inlineStr">
         <is>
-          <t>Toshpo'latova Asila Akmal qizi</t>
+          <t>Temirova Rushana Sarvarovna</t>
         </is>
       </c>
       <c r="D400" s="2" t="n">
-        <v>112</v>
+        <v>299</v>
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>AE3444231</t>
+          <t>AD9123776</t>
         </is>
       </c>
       <c r="F400" s="3" t="inlineStr">
         <is>
-          <t>61709085590015</t>
+          <t>60709085590113</t>
         </is>
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>18.07.2025</t>
+          <t>23.10.2024</t>
         </is>
       </c>
       <c r="H400" s="3" t="inlineStr">
         <is>
-          <t>17.09.2008</t>
+          <t>07.09.2008</t>
         </is>
       </c>
     </row>
@@ -15085,28 +15412,30 @@
       </c>
       <c r="C401" s="7" t="inlineStr">
         <is>
-          <t>Tursunmurodova Diyora Jasur qizi</t>
-        </is>
-      </c>
-      <c r="D401" s="5" t="inlineStr"/>
+          <t>Toshpo'latova Asila Akmal qizi</t>
+        </is>
+      </c>
+      <c r="D401" s="5" t="n">
+        <v>112</v>
+      </c>
       <c r="E401" s="5" t="inlineStr">
         <is>
-          <t>AD9513015</t>
+          <t>AE3444231</t>
         </is>
       </c>
       <c r="F401" s="6" t="inlineStr">
         <is>
-          <t>61609075680011</t>
+          <t>61709085590015</t>
         </is>
       </c>
       <c r="G401" s="6" t="inlineStr">
         <is>
-          <t>21.11.2024</t>
+          <t>18.07.2025</t>
         </is>
       </c>
       <c r="H401" s="6" t="inlineStr">
         <is>
-          <t>16.09.2007</t>
+          <t>17.09.2008</t>
         </is>
       </c>
     </row>
@@ -15121,30 +15450,28 @@
       </c>
       <c r="C402" s="4" t="inlineStr">
         <is>
-          <t>Umirova Sevinch Avlayor qizi</t>
-        </is>
-      </c>
-      <c r="D402" s="2" t="n">
-        <v>298</v>
-      </c>
+          <t>Tursunmurodova Diyora Jasur qizi</t>
+        </is>
+      </c>
+      <c r="D402" s="2" t="inlineStr"/>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>AD1671106</t>
+          <t>AD9513015</t>
         </is>
       </c>
       <c r="F402" s="3" t="inlineStr">
         <is>
-          <t>60906055720101</t>
+          <t>61609075680011</t>
         </is>
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>18.08.2022</t>
+          <t>21.11.2024</t>
         </is>
       </c>
       <c r="H402" s="3" t="inlineStr">
         <is>
-          <t>09.06.2005</t>
+          <t>16.09.2007</t>
         </is>
       </c>
     </row>
@@ -15159,30 +15486,30 @@
       </c>
       <c r="C403" s="7" t="inlineStr">
         <is>
-          <t>Usmonova Yulduz Nu'mon qizi</t>
+          <t>Umirova Sevinch Avlayor qizi</t>
         </is>
       </c>
       <c r="D403" s="5" t="n">
-        <v>209</v>
+        <v>298</v>
       </c>
       <c r="E403" s="5" t="inlineStr">
         <is>
-          <t>AD9589389</t>
+          <t>AD1671106</t>
         </is>
       </c>
       <c r="F403" s="6" t="inlineStr">
         <is>
-          <t>62112075680077</t>
+          <t>60906055720101</t>
         </is>
       </c>
       <c r="G403" s="6" t="inlineStr">
         <is>
-          <t>27.11.2024</t>
+          <t>18.08.2022</t>
         </is>
       </c>
       <c r="H403" s="6" t="inlineStr">
         <is>
-          <t>21.12.2007</t>
+          <t>09.06.2005</t>
         </is>
       </c>
     </row>
@@ -15197,30 +15524,30 @@
       </c>
       <c r="C404" s="4" t="inlineStr">
         <is>
-          <t>Xaydarova Iroda Zarif qizi</t>
+          <t>Usmonova Yulduz Nu'mon qizi</t>
         </is>
       </c>
       <c r="D404" s="2" t="n">
-        <v>113</v>
+        <v>209</v>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>AE4240266</t>
+          <t>AD9589389</t>
         </is>
       </c>
       <c r="F404" s="3" t="inlineStr">
         <is>
-          <t>61906085590032</t>
+          <t>62112075680077</t>
         </is>
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>17.09.2025</t>
+          <t>27.11.2024</t>
         </is>
       </c>
       <c r="H404" s="3" t="inlineStr">
         <is>
-          <t>19.06.2008</t>
+          <t>21.12.2007</t>
         </is>
       </c>
     </row>
@@ -15235,30 +15562,30 @@
       </c>
       <c r="C405" s="7" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida Safar qizi</t>
+          <t>Xaydarova Iroda Zarif qizi</t>
         </is>
       </c>
       <c r="D405" s="5" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E405" s="5" t="inlineStr">
         <is>
-          <t>AD9786798</t>
+          <t>AE4240266</t>
         </is>
       </c>
       <c r="F405" s="6" t="inlineStr">
         <is>
-          <t>61911085590096</t>
+          <t>61906085590032</t>
         </is>
       </c>
       <c r="G405" s="6" t="inlineStr">
         <is>
-          <t>12.12.2024</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="H405" s="6" t="inlineStr">
         <is>
-          <t>19.11.2008</t>
+          <t>19.06.2008</t>
         </is>
       </c>
     </row>
@@ -15273,30 +15600,30 @@
       </c>
       <c r="C406" s="4" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
+          <t>Xayrullayeva Umida Safar qizi</t>
         </is>
       </c>
       <c r="D406" s="2" t="n">
-        <v>243</v>
+        <v>116</v>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>AE4328716</t>
+          <t>AD9786798</t>
         </is>
       </c>
       <c r="F406" s="3" t="inlineStr">
         <is>
-          <t>60201085720092</t>
+          <t>61911085590096</t>
         </is>
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>24.09.2025</t>
+          <t>12.12.2024</t>
         </is>
       </c>
       <c r="H406" s="3" t="inlineStr">
         <is>
-          <t>02.01.2008</t>
+          <t>19.11.2008</t>
         </is>
       </c>
     </row>
@@ -15311,30 +15638,30 @@
       </c>
       <c r="C407" s="7" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="D407" s="5" t="n">
-        <v>108</v>
+        <v>243</v>
       </c>
       <c r="E407" s="5" t="inlineStr">
         <is>
-          <t>AE4729924</t>
+          <t>AE4328716</t>
         </is>
       </c>
       <c r="F407" s="6" t="inlineStr">
         <is>
-          <t>62511085730064</t>
+          <t>60201085720092</t>
         </is>
       </c>
       <c r="G407" s="6" t="inlineStr">
         <is>
-          <t>22.10.2025</t>
+          <t>24.09.2025</t>
         </is>
       </c>
       <c r="H407" s="6" t="inlineStr">
         <is>
-          <t>25.11.2008</t>
+          <t>02.01.2008</t>
         </is>
       </c>
     </row>
@@ -15349,30 +15676,30 @@
       </c>
       <c r="C408" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Lobar Ural qizi</t>
+          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
         </is>
       </c>
       <c r="D408" s="2" t="n">
-        <v>234</v>
+        <v>108</v>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>AE2656510</t>
+          <t>AE4729924</t>
         </is>
       </c>
       <c r="F408" s="3" t="inlineStr">
         <is>
-          <t>62508085680062</t>
+          <t>62511085730064</t>
         </is>
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>13.05.2025</t>
+          <t>22.10.2025</t>
         </is>
       </c>
       <c r="H408" s="3" t="inlineStr">
         <is>
-          <t>25.08.2008</t>
+          <t>25.11.2008</t>
         </is>
       </c>
     </row>
@@ -15387,30 +15714,30 @@
       </c>
       <c r="C409" s="7" t="inlineStr">
         <is>
-          <t>Xurramova Sabina Yuldosh qizi</t>
+          <t>Xurramova Lobar Ural qizi</t>
         </is>
       </c>
       <c r="D409" s="5" t="n">
-        <v>52</v>
+        <v>234</v>
       </c>
       <c r="E409" s="5" t="inlineStr">
         <is>
-          <t>AC3081523</t>
+          <t>AE2656510</t>
         </is>
       </c>
       <c r="F409" s="6" t="inlineStr">
         <is>
-          <t>60803048230011</t>
+          <t>62508085680062</t>
         </is>
       </c>
       <c r="G409" s="6" t="inlineStr">
         <is>
-          <t>16.10.2020</t>
+          <t>13.05.2025</t>
         </is>
       </c>
       <c r="H409" s="6" t="inlineStr">
         <is>
-          <t>08.03.2004</t>
+          <t>25.08.2008</t>
         </is>
       </c>
     </row>
@@ -15420,35 +15747,35 @@
       </c>
       <c r="B410" s="3" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C410" s="4" t="inlineStr">
         <is>
-          <t>A'zamov Shohjaxon Sherali o'g'li</t>
+          <t>Xurramova Sabina Yuldosh qizi</t>
         </is>
       </c>
       <c r="D410" s="2" t="n">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>AD9855395</t>
+          <t>AC3081523</t>
         </is>
       </c>
       <c r="F410" s="3" t="inlineStr">
         <is>
-          <t>52510085590064</t>
+          <t>60803048230011</t>
         </is>
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>17.12.2024</t>
+          <t>16.10.2020</t>
         </is>
       </c>
       <c r="H410" s="3" t="inlineStr">
         <is>
-          <t>25.10.2008</t>
+          <t>08.03.2004</t>
         </is>
       </c>
     </row>
@@ -15463,30 +15790,30 @@
       </c>
       <c r="C411" s="7" t="inlineStr">
         <is>
-          <t>Abdixalilova Shohzoda Bahodir qizi</t>
+          <t>A'zamov Shohjaxon Sherali o'g'li</t>
         </is>
       </c>
       <c r="D411" s="5" t="n">
-        <v>274</v>
+        <v>86</v>
       </c>
       <c r="E411" s="5" t="inlineStr">
         <is>
-          <t>AD7053449</t>
+          <t>AD9855395</t>
         </is>
       </c>
       <c r="F411" s="6" t="inlineStr">
         <is>
-          <t>60603085720124</t>
+          <t>52510085590064</t>
         </is>
       </c>
       <c r="G411" s="6" t="inlineStr">
         <is>
-          <t>06.05.2024</t>
+          <t>17.12.2024</t>
         </is>
       </c>
       <c r="H411" s="6" t="inlineStr">
         <is>
-          <t>06.03.2008</t>
+          <t>25.10.2008</t>
         </is>
       </c>
     </row>
@@ -15501,30 +15828,30 @@
       </c>
       <c r="C412" s="4" t="inlineStr">
         <is>
-          <t>Abdiyeva Sabina G'ayrat qizi</t>
+          <t>Abdixalilova Shohzoda Bahodir qizi</t>
         </is>
       </c>
       <c r="D412" s="2" t="n">
-        <v>140</v>
+        <v>274</v>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>AE4860201</t>
+          <t>AD7053449</t>
         </is>
       </c>
       <c r="F412" s="3" t="inlineStr">
         <is>
-          <t>60108085590051</t>
+          <t>60603085720124</t>
         </is>
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>03.11.2025</t>
+          <t>06.05.2024</t>
         </is>
       </c>
       <c r="H412" s="3" t="inlineStr">
         <is>
-          <t>01.08.2008</t>
+          <t>06.03.2008</t>
         </is>
       </c>
     </row>
@@ -15539,30 +15866,30 @@
       </c>
       <c r="C413" s="7" t="inlineStr">
         <is>
-          <t>Abduraxmonova Zahrobonu Toxir qizi</t>
+          <t>Abdiyeva Sabina G'ayrat qizi</t>
         </is>
       </c>
       <c r="D413" s="5" t="n">
-        <v>204</v>
+        <v>140</v>
       </c>
       <c r="E413" s="5" t="inlineStr">
         <is>
-          <t>AE4193791</t>
+          <t>AE4860201</t>
         </is>
       </c>
       <c r="F413" s="6" t="inlineStr">
         <is>
-          <t>61805095590028</t>
+          <t>60108085590051</t>
         </is>
       </c>
       <c r="G413" s="6" t="inlineStr">
         <is>
-          <t>15.09.2025</t>
+          <t>03.11.2025</t>
         </is>
       </c>
       <c r="H413" s="6" t="inlineStr">
         <is>
-          <t>18.05.2009</t>
+          <t>01.08.2008</t>
         </is>
       </c>
     </row>
@@ -15577,30 +15904,30 @@
       </c>
       <c r="C414" s="4" t="inlineStr">
         <is>
-          <t>Eshpulatova Shahnoza Sherali qizi</t>
+          <t>Abduraxmonova Zahrobonu Toxir qizi</t>
         </is>
       </c>
       <c r="D414" s="2" t="n">
-        <v>5</v>
+        <v>204</v>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>AE1541155</t>
+          <t>AE4193791</t>
         </is>
       </c>
       <c r="F414" s="3" t="inlineStr">
         <is>
-          <t>61405085590065</t>
+          <t>61805095590028</t>
         </is>
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>07.02.2025</t>
+          <t>15.09.2025</t>
         </is>
       </c>
       <c r="H414" s="3" t="inlineStr">
         <is>
-          <t>14.05.2008</t>
+          <t>18.05.2009</t>
         </is>
       </c>
     </row>
@@ -15615,30 +15942,30 @@
       </c>
       <c r="C415" s="7" t="inlineStr">
         <is>
-          <t>Eshquvatova Yulduz Asliddin qizi</t>
+          <t>Eshpulatova Shahnoza Sherali qizi</t>
         </is>
       </c>
       <c r="D415" s="5" t="n">
-        <v>267</v>
+        <v>5</v>
       </c>
       <c r="E415" s="5" t="inlineStr">
         <is>
-          <t>AB5879899</t>
+          <t>AE1541155</t>
         </is>
       </c>
       <c r="F415" s="6" t="inlineStr">
         <is>
-          <t>40511985730032</t>
+          <t>61405085590065</t>
         </is>
       </c>
       <c r="G415" s="6" t="inlineStr">
         <is>
-          <t>08.02.2017</t>
+          <t>07.02.2025</t>
         </is>
       </c>
       <c r="H415" s="6" t="inlineStr">
         <is>
-          <t>05.11.1998</t>
+          <t>14.05.2008</t>
         </is>
       </c>
     </row>
@@ -15653,30 +15980,30 @@
       </c>
       <c r="C416" s="4" t="inlineStr">
         <is>
-          <t>G'aniyeva Asila G'ani qizi</t>
+          <t>Eshquvatova Yulduz Asliddin qizi</t>
         </is>
       </c>
       <c r="D416" s="2" t="n">
-        <v>381</v>
+        <v>267</v>
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
-          <t>AE5575300</t>
+          <t>AB5879899</t>
         </is>
       </c>
       <c r="F416" s="3" t="inlineStr">
         <is>
-          <t>41011925590038</t>
+          <t>40511985730032</t>
         </is>
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>23.12.2025</t>
+          <t>08.02.2017</t>
         </is>
       </c>
       <c r="H416" s="3" t="inlineStr">
         <is>
-          <t>10.11.1992</t>
+          <t>05.11.1998</t>
         </is>
       </c>
     </row>
@@ -15691,30 +16018,30 @@
       </c>
       <c r="C417" s="7" t="inlineStr">
         <is>
-          <t>Halimova Sevinch Ravshan qizi</t>
+          <t>G'aniyeva Asila G'ani qizi</t>
         </is>
       </c>
       <c r="D417" s="5" t="n">
-        <v>26</v>
+        <v>381</v>
       </c>
       <c r="E417" s="5" t="inlineStr">
         <is>
-          <t>AD8735102</t>
+          <t>AE5575300</t>
         </is>
       </c>
       <c r="F417" s="6" t="inlineStr">
         <is>
-          <t>60908085680060</t>
+          <t>41011925590038</t>
         </is>
       </c>
       <c r="G417" s="6" t="inlineStr">
         <is>
-          <t>23.09.2024</t>
+          <t>23.12.2025</t>
         </is>
       </c>
       <c r="H417" s="6" t="inlineStr">
         <is>
-          <t>09.08.2008</t>
+          <t>10.11.1992</t>
         </is>
       </c>
     </row>
@@ -15729,30 +16056,30 @@
       </c>
       <c r="C418" s="4" t="inlineStr">
         <is>
-          <t>Hamroqulova Marjona O'ktam qizi</t>
+          <t>Halimova Sevinch Ravshan qizi</t>
         </is>
       </c>
       <c r="D418" s="2" t="n">
-        <v>275</v>
+        <v>26</v>
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>AE1525748</t>
+          <t>AD8735102</t>
         </is>
       </c>
       <c r="F418" s="3" t="inlineStr">
         <is>
-          <t>61104085680018</t>
+          <t>60908085680060</t>
         </is>
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>06.02.2025</t>
+          <t>23.09.2024</t>
         </is>
       </c>
       <c r="H418" s="3" t="inlineStr">
         <is>
-          <t>11.04.2008</t>
+          <t>09.08.2008</t>
         </is>
       </c>
     </row>
@@ -15767,30 +16094,30 @@
       </c>
       <c r="C419" s="7" t="inlineStr">
         <is>
-          <t>Isomiddinova Ruhshona Shavkat qizi</t>
+          <t>Hamroqulova Marjona O'ktam qizi</t>
         </is>
       </c>
       <c r="D419" s="5" t="n">
-        <v>65</v>
+        <v>275</v>
       </c>
       <c r="E419" s="5" t="inlineStr">
         <is>
-          <t>AD7684354</t>
+          <t>AE1525748</t>
         </is>
       </c>
       <c r="F419" s="6" t="inlineStr">
         <is>
-          <t>63006085680064</t>
+          <t>61104085680018</t>
         </is>
       </c>
       <c r="G419" s="6" t="inlineStr">
         <is>
-          <t>01.07.2024</t>
+          <t>06.02.2025</t>
         </is>
       </c>
       <c r="H419" s="6" t="inlineStr">
         <is>
-          <t>30.06.2008</t>
+          <t>11.04.2008</t>
         </is>
       </c>
     </row>
@@ -15805,30 +16132,30 @@
       </c>
       <c r="C420" s="4" t="inlineStr">
         <is>
-          <t>Jalolov Javlonbek G'ani o'g'li</t>
+          <t>Isomiddinova Ruhshona Shavkat qizi</t>
         </is>
       </c>
       <c r="D420" s="2" t="n">
-        <v>211</v>
+        <v>65</v>
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>AE 4994200</t>
+          <t>AD7684354</t>
         </is>
       </c>
       <c r="F420" s="3" t="inlineStr">
         <is>
-          <t>53005095680054</t>
+          <t>63006085680064</t>
         </is>
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>11.11.2025</t>
+          <t>01.07.2024</t>
         </is>
       </c>
       <c r="H420" s="3" t="inlineStr">
         <is>
-          <t>30.05.2009</t>
+          <t>30.06.2008</t>
         </is>
       </c>
     </row>
@@ -15843,30 +16170,30 @@
       </c>
       <c r="C421" s="7" t="inlineStr">
         <is>
-          <t>Karimova Shaxina Fayzulla qizi</t>
+          <t>Jalolov Javlonbek G'ani o'g'li</t>
         </is>
       </c>
       <c r="D421" s="5" t="n">
-        <v>293</v>
+        <v>211</v>
       </c>
       <c r="E421" s="5" t="inlineStr">
         <is>
-          <t>AC0413538</t>
+          <t>AE 4994200</t>
         </is>
       </c>
       <c r="F421" s="6" t="inlineStr">
         <is>
-          <t>61511017890023</t>
+          <t>53005095680054</t>
         </is>
       </c>
       <c r="G421" s="6" t="inlineStr">
         <is>
-          <t>07.12.2018</t>
+          <t>11.11.2025</t>
         </is>
       </c>
       <c r="H421" s="6" t="inlineStr">
         <is>
-          <t>15.11.2001</t>
+          <t>30.05.2009</t>
         </is>
       </c>
     </row>
@@ -15881,30 +16208,30 @@
       </c>
       <c r="C422" s="4" t="inlineStr">
         <is>
-          <t>Mahmudova Gulsanam Nigmatovna</t>
+          <t>Karimova Shaxina Fayzulla qizi</t>
         </is>
       </c>
       <c r="D422" s="2" t="n">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
-          <t>AE1695093</t>
+          <t>AC0413538</t>
         </is>
       </c>
       <c r="F422" s="3" t="inlineStr">
         <is>
-          <t>62308085680109</t>
+          <t>61511017890023</t>
         </is>
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>20.02.2025</t>
+          <t>07.12.2018</t>
         </is>
       </c>
       <c r="H422" s="3" t="inlineStr">
         <is>
-          <t>23.08.2008</t>
+          <t>15.11.2001</t>
         </is>
       </c>
     </row>
@@ -15919,30 +16246,30 @@
       </c>
       <c r="C423" s="7" t="inlineStr">
         <is>
-          <t>Maxmudova Musallam Qamariddin qizi</t>
+          <t>Mahmudova Gulsanam Nigmatovna</t>
         </is>
       </c>
       <c r="D423" s="5" t="n">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="E423" s="5" t="inlineStr">
         <is>
-          <t>AE5297116</t>
+          <t>AE1695093</t>
         </is>
       </c>
       <c r="F423" s="6" t="inlineStr">
         <is>
-          <t>61303085680079</t>
+          <t>62308085680109</t>
         </is>
       </c>
       <c r="G423" s="6" t="inlineStr">
         <is>
-          <t>04.12.2025</t>
+          <t>20.02.2025</t>
         </is>
       </c>
       <c r="H423" s="6" t="inlineStr">
         <is>
-          <t>13.03.2008</t>
+          <t>23.08.2008</t>
         </is>
       </c>
     </row>
@@ -15957,30 +16284,30 @@
       </c>
       <c r="C424" s="4" t="inlineStr">
         <is>
-          <t>Murodova Ruhshona Ilhomovna</t>
+          <t>Maxmudova Musallam Qamariddin qizi</t>
         </is>
       </c>
       <c r="D424" s="2" t="n">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>AE3287114</t>
+          <t>AE5297116</t>
         </is>
       </c>
       <c r="F424" s="3" t="inlineStr">
         <is>
-          <t>61009085680098</t>
+          <t>61303085680079</t>
         </is>
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>07.07.2025</t>
+          <t>04.12.2025</t>
         </is>
       </c>
       <c r="H424" s="3" t="inlineStr">
         <is>
-          <t>10.09.2008</t>
+          <t>13.03.2008</t>
         </is>
       </c>
     </row>
@@ -15995,30 +16322,30 @@
       </c>
       <c r="C425" s="7" t="inlineStr">
         <is>
-          <t>Nafasova Sevinch Bollijon qizi</t>
+          <t>Murodova Ruhshona Ilhomovna</t>
         </is>
       </c>
       <c r="D425" s="5" t="n">
-        <v>266</v>
+        <v>72</v>
       </c>
       <c r="E425" s="5" t="inlineStr">
         <is>
-          <t>AE4668322</t>
+          <t>AE3287114</t>
         </is>
       </c>
       <c r="F425" s="6" t="inlineStr">
         <is>
-          <t>62708085730015</t>
+          <t>61009085680098</t>
         </is>
       </c>
       <c r="G425" s="6" t="inlineStr">
         <is>
-          <t>17.10.2025</t>
+          <t>07.07.2025</t>
         </is>
       </c>
       <c r="H425" s="6" t="inlineStr">
         <is>
-          <t>27.08.2008</t>
+          <t>10.09.2008</t>
         </is>
       </c>
     </row>
@@ -16033,30 +16360,30 @@
       </c>
       <c r="C426" s="4" t="inlineStr">
         <is>
-          <t>Pirnazarova Jasmina Olim qizi</t>
+          <t>Nafasova Sevinch Bollijon qizi</t>
         </is>
       </c>
       <c r="D426" s="2" t="n">
-        <v>13</v>
+        <v>266</v>
       </c>
       <c r="E426" s="2" t="inlineStr">
         <is>
-          <t>AE4198928</t>
+          <t>AE4668322</t>
         </is>
       </c>
       <c r="F426" s="3" t="inlineStr">
         <is>
-          <t>60506085680077</t>
+          <t>62708085730015</t>
         </is>
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>15.09.2025</t>
+          <t>17.10.2025</t>
         </is>
       </c>
       <c r="H426" s="3" t="inlineStr">
         <is>
-          <t>05.06.2008</t>
+          <t>27.08.2008</t>
         </is>
       </c>
     </row>
@@ -16071,30 +16398,30 @@
       </c>
       <c r="C427" s="7" t="inlineStr">
         <is>
-          <t>Qodirova Sabina Suxrob qizi</t>
+          <t>Pirnazarova Jasmina Olim qizi</t>
         </is>
       </c>
       <c r="D427" s="5" t="n">
-        <v>295</v>
+        <v>13</v>
       </c>
       <c r="E427" s="5" t="inlineStr">
         <is>
-          <t>AC2359638</t>
+          <t>AE4198928</t>
         </is>
       </c>
       <c r="F427" s="6" t="inlineStr">
         <is>
-          <t>60203045680015</t>
+          <t>60506085680077</t>
         </is>
       </c>
       <c r="G427" s="6" t="inlineStr">
         <is>
-          <t>03.11.2019</t>
+          <t>15.09.2025</t>
         </is>
       </c>
       <c r="H427" s="6" t="inlineStr">
         <is>
-          <t>02.03.2004</t>
+          <t>05.06.2008</t>
         </is>
       </c>
     </row>
@@ -16109,30 +16436,30 @@
       </c>
       <c r="C428" s="4" t="inlineStr">
         <is>
-          <t>Soyipova Dinora Sanjar qizi</t>
+          <t>Qodirova Sabina Suxrob qizi</t>
         </is>
       </c>
       <c r="D428" s="2" t="n">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="E428" s="2" t="inlineStr">
         <is>
-          <t>AD9484395</t>
+          <t>AC2359638</t>
         </is>
       </c>
       <c r="F428" s="3" t="inlineStr">
         <is>
-          <t>62208085590065</t>
+          <t>60203045680015</t>
         </is>
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>20.11.2024</t>
+          <t>03.11.2019</t>
         </is>
       </c>
       <c r="H428" s="3" t="inlineStr">
         <is>
-          <t>22.08.2008</t>
+          <t>02.03.2004</t>
         </is>
       </c>
     </row>
@@ -16147,30 +16474,30 @@
       </c>
       <c r="C429" s="7" t="inlineStr">
         <is>
-          <t>Suyarova Dinora Sodiq qizi</t>
+          <t>Soyipova Dinora Sanjar qizi</t>
         </is>
       </c>
       <c r="D429" s="5" t="n">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="E429" s="5" t="inlineStr">
         <is>
-          <t>AD9863476</t>
+          <t>AD9484395</t>
         </is>
       </c>
       <c r="F429" s="6" t="inlineStr">
         <is>
-          <t>60108085590037</t>
+          <t>62208085590065</t>
         </is>
       </c>
       <c r="G429" s="6" t="inlineStr">
         <is>
-          <t>18.12.2024</t>
+          <t>20.11.2024</t>
         </is>
       </c>
       <c r="H429" s="6" t="inlineStr">
         <is>
-          <t>01.08.2008</t>
+          <t>22.08.2008</t>
         </is>
       </c>
     </row>
@@ -16185,30 +16512,30 @@
       </c>
       <c r="C430" s="4" t="inlineStr">
         <is>
-          <t>Temirboyeva Iroda Baxtiyor qizi</t>
+          <t>Suyarova Dinora Sodiq qizi</t>
         </is>
       </c>
       <c r="D430" s="2" t="n">
-        <v>20</v>
+        <v>306</v>
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
-          <t>AD6024952</t>
+          <t>AD9863476</t>
         </is>
       </c>
       <c r="F430" s="3" t="inlineStr">
         <is>
-          <t>60112075590084</t>
+          <t>60108085590037</t>
         </is>
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>05.02.2024</t>
+          <t>18.12.2024</t>
         </is>
       </c>
       <c r="H430" s="3" t="inlineStr">
         <is>
-          <t>01.12.2007</t>
+          <t>01.08.2008</t>
         </is>
       </c>
     </row>
@@ -16223,30 +16550,30 @@
       </c>
       <c r="C431" s="7" t="inlineStr">
         <is>
-          <t>Tuychiyeva Farzona Dalerovna</t>
+          <t>Temirboyeva Iroda Baxtiyor qizi</t>
         </is>
       </c>
       <c r="D431" s="5" t="n">
-        <v>280</v>
+        <v>20</v>
       </c>
       <c r="E431" s="5" t="inlineStr">
         <is>
-          <t>AE4114421</t>
+          <t>AD6024952</t>
         </is>
       </c>
       <c r="F431" s="6" t="inlineStr">
         <is>
-          <t>60508095680049</t>
+          <t>60112075590084</t>
         </is>
       </c>
       <c r="G431" s="6" t="inlineStr">
         <is>
-          <t>09.09.2025</t>
+          <t>05.02.2024</t>
         </is>
       </c>
       <c r="H431" s="6" t="inlineStr">
         <is>
-          <t>05.08.2009</t>
+          <t>01.12.2007</t>
         </is>
       </c>
     </row>
@@ -16261,30 +16588,30 @@
       </c>
       <c r="C432" s="4" t="inlineStr">
         <is>
-          <t>Ulugbekova Zara Ulug'bek qizi</t>
+          <t>Tuychiyeva Farzona Dalerovna</t>
         </is>
       </c>
       <c r="D432" s="2" t="n">
-        <v>313</v>
+        <v>280</v>
       </c>
       <c r="E432" s="2" t="inlineStr">
         <is>
-          <t>AE4760779</t>
+          <t>AE4114421</t>
         </is>
       </c>
       <c r="F432" s="3" t="inlineStr">
         <is>
-          <t>61109085590127</t>
+          <t>60508095680049</t>
         </is>
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>24.10.2025</t>
+          <t>09.09.2025</t>
         </is>
       </c>
       <c r="H432" s="3" t="inlineStr">
         <is>
-          <t>11.09.2008</t>
+          <t>05.08.2009</t>
         </is>
       </c>
     </row>
@@ -16299,30 +16626,30 @@
       </c>
       <c r="C433" s="7" t="inlineStr">
         <is>
-          <t>Xamdamova Madina Abdiqodir qizi</t>
+          <t>Ulugbekova Zara Ulug'bek qizi</t>
         </is>
       </c>
       <c r="D433" s="5" t="n">
-        <v>14</v>
+        <v>313</v>
       </c>
       <c r="E433" s="5" t="inlineStr">
         <is>
-          <t>AB8517012</t>
+          <t>AE4760779</t>
         </is>
       </c>
       <c r="F433" s="6" t="inlineStr">
         <is>
-          <t>62701015680026</t>
+          <t>61109085590127</t>
         </is>
       </c>
       <c r="G433" s="6" t="inlineStr">
         <is>
-          <t>07.01.2018</t>
+          <t>24.10.2025</t>
         </is>
       </c>
       <c r="H433" s="6" t="inlineStr">
         <is>
-          <t>27.01.2001</t>
+          <t>11.09.2008</t>
         </is>
       </c>
     </row>
@@ -16337,30 +16664,30 @@
       </c>
       <c r="C434" s="4" t="inlineStr">
         <is>
-          <t>Xannonova Shohsanam Orif qizi</t>
+          <t>Xamdamova Madina Abdiqodir qizi</t>
         </is>
       </c>
       <c r="D434" s="2" t="n">
-        <v>181</v>
+        <v>14</v>
       </c>
       <c r="E434" s="2" t="inlineStr">
         <is>
-          <t>AD0284895</t>
+          <t>AB8517012</t>
         </is>
       </c>
       <c r="F434" s="3" t="inlineStr">
         <is>
-          <t>60206045680052</t>
+          <t>62701015680026</t>
         </is>
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>01.04.2021</t>
+          <t>07.01.2018</t>
         </is>
       </c>
       <c r="H434" s="3" t="inlineStr">
         <is>
-          <t>02.06.2004</t>
+          <t>27.01.2001</t>
         </is>
       </c>
     </row>
@@ -16375,30 +16702,30 @@
       </c>
       <c r="C435" s="7" t="inlineStr">
         <is>
-          <t>Xo'jaqulova Navbahor Azim qizi</t>
+          <t>Xannonova Shohsanam Orif qizi</t>
         </is>
       </c>
       <c r="D435" s="5" t="n">
-        <v>302</v>
+        <v>181</v>
       </c>
       <c r="E435" s="5" t="inlineStr">
         <is>
-          <t>AD4186543</t>
+          <t>AD0284895</t>
         </is>
       </c>
       <c r="F435" s="6" t="inlineStr">
         <is>
-          <t>62104025680040</t>
+          <t>60206045680052</t>
         </is>
       </c>
       <c r="G435" s="6" t="inlineStr">
         <is>
-          <t>07.08.2023</t>
+          <t>01.04.2021</t>
         </is>
       </c>
       <c r="H435" s="6" t="inlineStr">
         <is>
-          <t>21.04.2002</t>
+          <t>02.06.2004</t>
         </is>
       </c>
     </row>
@@ -16413,30 +16740,30 @@
       </c>
       <c r="C436" s="4" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura Dilmurod qizi</t>
+          <t>Xo'jaqulova Navbahor Azim qizi</t>
         </is>
       </c>
       <c r="D436" s="2" t="n">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E436" s="2" t="inlineStr">
         <is>
-          <t>AE1516812</t>
+          <t>AD4186543</t>
         </is>
       </c>
       <c r="F436" s="3" t="inlineStr">
         <is>
-          <t>60110085590193</t>
+          <t>62104025680040</t>
         </is>
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>06.02.2025</t>
+          <t>07.08.2023</t>
         </is>
       </c>
       <c r="H436" s="3" t="inlineStr">
         <is>
-          <t>01.10.2008</t>
+          <t>21.04.2002</t>
         </is>
       </c>
     </row>
@@ -16451,30 +16778,30 @@
       </c>
       <c r="C437" s="7" t="inlineStr">
         <is>
-          <t>Xujamuratova Durdona Bahrom qizi</t>
+          <t>Xolmurodova Dilnura Dilmurod qizi</t>
         </is>
       </c>
       <c r="D437" s="5" t="n">
-        <v>232</v>
+        <v>307</v>
       </c>
       <c r="E437" s="5" t="inlineStr">
         <is>
-          <t>AE5954513</t>
+          <t>AE1516812</t>
         </is>
       </c>
       <c r="F437" s="6" t="inlineStr">
         <is>
-          <t>62204085720105</t>
+          <t>60110085590193</t>
         </is>
       </c>
       <c r="G437" s="6" t="inlineStr">
         <is>
-          <t>20.01.2026</t>
+          <t>06.02.2025</t>
         </is>
       </c>
       <c r="H437" s="6" t="inlineStr">
         <is>
-          <t>22.04.2008</t>
+          <t>01.10.2008</t>
         </is>
       </c>
     </row>
@@ -16489,30 +16816,30 @@
       </c>
       <c r="C438" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
+          <t>Xujamuratova Durdona Bahrom qizi</t>
         </is>
       </c>
       <c r="D438" s="2" t="n">
-        <v>29</v>
+        <v>232</v>
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
-          <t>AC1847101</t>
+          <t>AE5954513</t>
         </is>
       </c>
       <c r="F438" s="3" t="inlineStr">
         <is>
-          <t>60411015680031</t>
+          <t>62204085720105</t>
         </is>
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>24.04.2019</t>
+          <t>20.01.2026</t>
         </is>
       </c>
       <c r="H438" s="3" t="inlineStr">
         <is>
-          <t>04.11.2001</t>
+          <t>22.04.2008</t>
         </is>
       </c>
     </row>
@@ -16527,30 +16854,30 @@
       </c>
       <c r="C439" s="7" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="D439" s="5" t="n">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="E439" s="5" t="inlineStr">
         <is>
-          <t>AD4921163</t>
+          <t>AC1847101</t>
         </is>
       </c>
       <c r="F439" s="6" t="inlineStr">
         <is>
-          <t>63004075680030</t>
+          <t>60411015680031</t>
         </is>
       </c>
       <c r="G439" s="6" t="inlineStr">
         <is>
-          <t>20.10.2023</t>
+          <t>24.04.2019</t>
         </is>
       </c>
       <c r="H439" s="6" t="inlineStr">
         <is>
-          <t>30.04.2007</t>
+          <t>04.11.2001</t>
         </is>
       </c>
     </row>
@@ -16565,30 +16892,30 @@
       </c>
       <c r="C440" s="4" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="D440" s="2" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="E440" s="2" t="inlineStr">
         <is>
-          <t>AE5015467</t>
+          <t>AD4921163</t>
         </is>
       </c>
       <c r="F440" s="3" t="inlineStr">
         <is>
-          <t>60110085590092</t>
+          <t>63004075680030</t>
         </is>
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>12.11.2025</t>
+          <t>20.10.2023</t>
         </is>
       </c>
       <c r="H440" s="3" t="inlineStr">
         <is>
-          <t>01.10.2008</t>
+          <t>30.04.2007</t>
         </is>
       </c>
     </row>
@@ -16603,30 +16930,30 @@
       </c>
       <c r="C441" s="7" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
+          <t>Xusanova Aziza Fazliddin qizi</t>
         </is>
       </c>
       <c r="D441" s="5" t="n">
-        <v>387</v>
+        <v>196</v>
       </c>
       <c r="E441" s="5" t="inlineStr">
         <is>
-          <t>AE5856503</t>
+          <t>AE5015467</t>
         </is>
       </c>
       <c r="F441" s="6" t="inlineStr">
         <is>
-          <t>63112085680039</t>
+          <t>60110085590092</t>
         </is>
       </c>
       <c r="G441" s="6" t="inlineStr">
         <is>
-          <t>14.01.2026</t>
+          <t>12.11.2025</t>
         </is>
       </c>
       <c r="H441" s="6" t="inlineStr">
         <is>
-          <t>31.12.2008</t>
+          <t>01.10.2008</t>
         </is>
       </c>
     </row>
@@ -16636,35 +16963,35 @@
       </c>
       <c r="B442" s="3" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C442" s="4" t="inlineStr">
         <is>
-          <t>Abdishukurova Gulsevar Xusniddin qizi</t>
+          <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="D442" s="2" t="n">
-        <v>238</v>
+        <v>387</v>
       </c>
       <c r="E442" s="2" t="inlineStr">
         <is>
-          <t>AE4148917</t>
+          <t>AE5856503</t>
         </is>
       </c>
       <c r="F442" s="3" t="inlineStr">
         <is>
-          <t>60609085720090</t>
+          <t>63112085680039</t>
         </is>
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>11.09.2025</t>
+          <t>14.01.2026</t>
         </is>
       </c>
       <c r="H442" s="3" t="inlineStr">
         <is>
-          <t>06.09.2008</t>
+          <t>31.12.2008</t>
         </is>
       </c>
     </row>
@@ -16679,30 +17006,30 @@
       </c>
       <c r="C443" s="7" t="inlineStr">
         <is>
-          <t>Ahmadova Munisa Bekzod qizi</t>
+          <t>Abdishukurova Gulsevar Xusniddin qizi</t>
         </is>
       </c>
       <c r="D443" s="5" t="n">
-        <v>33</v>
+        <v>238</v>
       </c>
       <c r="E443" s="5" t="inlineStr">
         <is>
-          <t>AE4831229</t>
+          <t>AE4148917</t>
         </is>
       </c>
       <c r="F443" s="6" t="inlineStr">
         <is>
-          <t>60409085680037</t>
+          <t>60609085720090</t>
         </is>
       </c>
       <c r="G443" s="6" t="inlineStr">
         <is>
-          <t>30.10.2025</t>
+          <t>11.09.2025</t>
         </is>
       </c>
       <c r="H443" s="6" t="inlineStr">
         <is>
-          <t>04.09.2008</t>
+          <t>06.09.2008</t>
         </is>
       </c>
     </row>
@@ -16717,30 +17044,30 @@
       </c>
       <c r="C444" s="4" t="inlineStr">
         <is>
-          <t>Ashirova Gulsanam Abduvali qizi</t>
+          <t>Ahmadova Munisa Bekzod qizi</t>
         </is>
       </c>
       <c r="D444" s="2" t="n">
-        <v>224</v>
+        <v>33</v>
       </c>
       <c r="E444" s="2" t="inlineStr">
         <is>
-          <t>AD6820021</t>
+          <t>AE4831229</t>
         </is>
       </c>
       <c r="F444" s="3" t="inlineStr">
         <is>
-          <t>62311065590082</t>
+          <t>60409085680037</t>
         </is>
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>15.04.2024</t>
+          <t>30.10.2025</t>
         </is>
       </c>
       <c r="H444" s="3" t="inlineStr">
         <is>
-          <t>23.11.2006</t>
+          <t>04.09.2008</t>
         </is>
       </c>
     </row>
@@ -16755,30 +17082,30 @@
       </c>
       <c r="C445" s="7" t="inlineStr">
         <is>
-          <t>Berdimurodova Nafosat Javlon qizi</t>
+          <t>Ashirova Gulsanam Abduvali qizi</t>
         </is>
       </c>
       <c r="D445" s="5" t="n">
-        <v>46</v>
+        <v>224</v>
       </c>
       <c r="E445" s="5" t="inlineStr">
         <is>
-          <t>AD9709558</t>
+          <t>AD6820021</t>
         </is>
       </c>
       <c r="F445" s="6" t="inlineStr">
         <is>
-          <t>60904075680023</t>
+          <t>62311065590082</t>
         </is>
       </c>
       <c r="G445" s="6" t="inlineStr">
         <is>
-          <t>06.12.2024</t>
+          <t>15.04.2024</t>
         </is>
       </c>
       <c r="H445" s="6" t="inlineStr">
         <is>
-          <t>09.04.2007</t>
+          <t>23.11.2006</t>
         </is>
       </c>
     </row>
@@ -16793,30 +17120,30 @@
       </c>
       <c r="C446" s="4" t="inlineStr">
         <is>
-          <t>Choriyeva Zahro Xayrullo qizi</t>
+          <t>Berdimurodova Nafosat Javlon qizi</t>
         </is>
       </c>
       <c r="D446" s="2" t="n">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="E446" s="2" t="inlineStr">
         <is>
-          <t>AD9654318</t>
+          <t>AD9709558</t>
         </is>
       </c>
       <c r="F446" s="3" t="inlineStr">
         <is>
-          <t>62802085590063</t>
+          <t>60904075680023</t>
         </is>
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>03.12.2024</t>
+          <t>06.12.2024</t>
         </is>
       </c>
       <c r="H446" s="3" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>09.04.2007</t>
         </is>
       </c>
     </row>
@@ -16831,30 +17158,30 @@
       </c>
       <c r="C447" s="7" t="inlineStr">
         <is>
-          <t>Ergasheva Shabbona Shodmon qizi</t>
+          <t>Choriyeva Zahro Xayrullo qizi</t>
         </is>
       </c>
       <c r="D447" s="5" t="n">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E447" s="5" t="inlineStr">
         <is>
-          <t>AE2374828</t>
+          <t>AD9654318</t>
         </is>
       </c>
       <c r="F447" s="6" t="inlineStr">
         <is>
-          <t>61803085680050</t>
+          <t>62802085590063</t>
         </is>
       </c>
       <c r="G447" s="6" t="inlineStr">
         <is>
-          <t>17.04.2025</t>
+          <t>03.12.2024</t>
         </is>
       </c>
       <c r="H447" s="6" t="inlineStr">
         <is>
-          <t>18.03.2008</t>
+          <t>28.02.2008</t>
         </is>
       </c>
     </row>
@@ -16869,30 +17196,30 @@
       </c>
       <c r="C448" s="4" t="inlineStr">
         <is>
-          <t>Eshboboyeva Fotima Nurali qizi</t>
+          <t>Ergasheva Shabbona Shodmon qizi</t>
         </is>
       </c>
       <c r="D448" s="2" t="n">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="E448" s="2" t="inlineStr">
         <is>
-          <t>AD0697178</t>
+          <t>AE2374828</t>
         </is>
       </c>
       <c r="F448" s="3" t="inlineStr">
         <is>
-          <t>61306045630044</t>
+          <t>61803085680050</t>
         </is>
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>05.10.2021</t>
+          <t>17.04.2025</t>
         </is>
       </c>
       <c r="H448" s="3" t="inlineStr">
         <is>
-          <t>13.06.2004</t>
+          <t>18.03.2008</t>
         </is>
       </c>
     </row>
@@ -16907,30 +17234,30 @@
       </c>
       <c r="C449" s="7" t="inlineStr">
         <is>
-          <t>G'ayratova Jasmina Sherali qizi</t>
+          <t>Eshboboyeva Fotima Nurali qizi</t>
         </is>
       </c>
       <c r="D449" s="5" t="n">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="E449" s="5" t="inlineStr">
         <is>
-          <t>AE3497923</t>
+          <t>AD0697178</t>
         </is>
       </c>
       <c r="F449" s="6" t="inlineStr">
         <is>
-          <t>60208085590146</t>
+          <t>61306045630044</t>
         </is>
       </c>
       <c r="G449" s="6" t="inlineStr">
         <is>
-          <t>23.07.2025</t>
+          <t>05.10.2021</t>
         </is>
       </c>
       <c r="H449" s="6" t="inlineStr">
         <is>
-          <t>02.08.2008</t>
+          <t>13.06.2004</t>
         </is>
       </c>
     </row>
@@ -16945,30 +17272,30 @@
       </c>
       <c r="C450" s="4" t="inlineStr">
         <is>
-          <t>Ixtiyorova Niginabonu Xolovna</t>
+          <t>G'ayratova Jasmina Sherali qizi</t>
         </is>
       </c>
       <c r="D450" s="2" t="n">
-        <v>227</v>
+        <v>97</v>
       </c>
       <c r="E450" s="2" t="inlineStr">
         <is>
-          <t>AD9335686</t>
+          <t>AE3497923</t>
         </is>
       </c>
       <c r="F450" s="3" t="inlineStr">
         <is>
-          <t>60710085680054</t>
+          <t>60208085590146</t>
         </is>
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>23.07.2025</t>
         </is>
       </c>
       <c r="H450" s="3" t="inlineStr">
         <is>
-          <t>07.10.2008</t>
+          <t>02.08.2008</t>
         </is>
       </c>
     </row>
@@ -16983,30 +17310,30 @@
       </c>
       <c r="C451" s="7" t="inlineStr">
         <is>
-          <t>Jabborova Bahoroy Shukurullo qizi</t>
+          <t>Ixtiyorova Niginabonu Xolovna</t>
         </is>
       </c>
       <c r="D451" s="5" t="n">
-        <v>202</v>
+        <v>227</v>
       </c>
       <c r="E451" s="5" t="inlineStr">
         <is>
-          <t>AE4255446</t>
+          <t>AD9335686</t>
         </is>
       </c>
       <c r="F451" s="6" t="inlineStr">
         <is>
-          <t>61510085680048</t>
+          <t>60710085680054</t>
         </is>
       </c>
       <c r="G451" s="6" t="inlineStr">
         <is>
-          <t>18.09.2025</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="H451" s="6" t="inlineStr">
         <is>
-          <t>15.10.2008</t>
+          <t>07.10.2008</t>
         </is>
       </c>
     </row>
@@ -17021,30 +17348,30 @@
       </c>
       <c r="C452" s="4" t="inlineStr">
         <is>
-          <t>Jalilova Jasmina Jamshid qizi</t>
+          <t>Jabborova Bahoroy Shukurullo qizi</t>
         </is>
       </c>
       <c r="D452" s="2" t="n">
-        <v>95</v>
+        <v>202</v>
       </c>
       <c r="E452" s="2" t="inlineStr">
         <is>
-          <t>AE4319796</t>
+          <t>AE4255446</t>
         </is>
       </c>
       <c r="F452" s="3" t="inlineStr">
         <is>
-          <t>60211085680014</t>
+          <t>61510085680048</t>
         </is>
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>23.09.2025</t>
+          <t>18.09.2025</t>
         </is>
       </c>
       <c r="H452" s="3" t="inlineStr">
         <is>
-          <t>02.11.2008</t>
+          <t>15.10.2008</t>
         </is>
       </c>
     </row>
@@ -17059,30 +17386,30 @@
       </c>
       <c r="C453" s="7" t="inlineStr">
         <is>
-          <t>Jumayeva Muxlisa Komiljon qizi</t>
+          <t>Jalilova Jasmina Jamshid qizi</t>
         </is>
       </c>
       <c r="D453" s="5" t="n">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="E453" s="5" t="inlineStr">
         <is>
-          <t>AB6258375</t>
+          <t>AE4319796</t>
         </is>
       </c>
       <c r="F453" s="6" t="inlineStr">
         <is>
-          <t>61701005680057</t>
+          <t>60211085680014</t>
         </is>
       </c>
       <c r="G453" s="6" t="inlineStr">
         <is>
-          <t>29.03.2017</t>
+          <t>23.09.2025</t>
         </is>
       </c>
       <c r="H453" s="6" t="inlineStr">
         <is>
-          <t>17.01.2000</t>
+          <t>02.11.2008</t>
         </is>
       </c>
     </row>
@@ -17097,30 +17424,30 @@
       </c>
       <c r="C454" s="4" t="inlineStr">
         <is>
-          <t>Jurayeva Madina Odil qizi</t>
+          <t>Jumayeva Muxlisa Komiljon qizi</t>
         </is>
       </c>
       <c r="D454" s="2" t="n">
-        <v>215</v>
+        <v>59</v>
       </c>
       <c r="E454" s="2" t="inlineStr">
         <is>
-          <t>AD9394305</t>
+          <t>AB6258375</t>
         </is>
       </c>
       <c r="F454" s="3" t="inlineStr">
         <is>
-          <t>62512075730060</t>
+          <t>61701005680057</t>
         </is>
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>13.11.2024</t>
+          <t>29.03.2017</t>
         </is>
       </c>
       <c r="H454" s="3" t="inlineStr">
         <is>
-          <t>25.12.2007</t>
+          <t>17.01.2000</t>
         </is>
       </c>
     </row>
@@ -17135,30 +17462,30 @@
       </c>
       <c r="C455" s="7" t="inlineStr">
         <is>
-          <t>Luxmonova Nozima Ilhom qizi</t>
+          <t>Jurayeva Madina Odil qizi</t>
         </is>
       </c>
       <c r="D455" s="5" t="n">
-        <v>139</v>
+        <v>215</v>
       </c>
       <c r="E455" s="5" t="inlineStr">
         <is>
-          <t>AE4290181</t>
+          <t>AD9394305</t>
         </is>
       </c>
       <c r="F455" s="6" t="inlineStr">
         <is>
-          <t>61611085680042</t>
+          <t>62512075730060</t>
         </is>
       </c>
       <c r="G455" s="6" t="inlineStr">
         <is>
-          <t>22.09.2025</t>
+          <t>13.11.2024</t>
         </is>
       </c>
       <c r="H455" s="6" t="inlineStr">
         <is>
-          <t>16.11.2008</t>
+          <t>25.12.2007</t>
         </is>
       </c>
     </row>
@@ -17173,30 +17500,30 @@
       </c>
       <c r="C456" s="4" t="inlineStr">
         <is>
-          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
+          <t>Luxmonova Nozima Ilhom qizi</t>
         </is>
       </c>
       <c r="D456" s="2" t="n">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="E456" s="2" t="inlineStr">
         <is>
-          <t>AD7829399</t>
+          <t>AE4290181</t>
         </is>
       </c>
       <c r="F456" s="3" t="inlineStr">
         <is>
-          <t>41902975680049</t>
+          <t>61611085680042</t>
         </is>
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>11.07.2024</t>
+          <t>22.09.2025</t>
         </is>
       </c>
       <c r="H456" s="3" t="inlineStr">
         <is>
-          <t>19.02.1997</t>
+          <t>16.11.2008</t>
         </is>
       </c>
     </row>
@@ -17211,30 +17538,30 @@
       </c>
       <c r="C457" s="7" t="inlineStr">
         <is>
-          <t>Murodova Munisa Muxtor qizi</t>
+          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
         </is>
       </c>
       <c r="D457" s="5" t="n">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="E457" s="5" t="inlineStr">
         <is>
-          <t>AE2895049</t>
+          <t>AD7829399</t>
         </is>
       </c>
       <c r="F457" s="6" t="inlineStr">
         <is>
-          <t>62112085680050</t>
+          <t>41902975680049</t>
         </is>
       </c>
       <c r="G457" s="6" t="inlineStr">
         <is>
-          <t>03.06.2025</t>
+          <t>11.07.2024</t>
         </is>
       </c>
       <c r="H457" s="6" t="inlineStr">
         <is>
-          <t>21.12.2008</t>
+          <t>19.02.1997</t>
         </is>
       </c>
     </row>
@@ -17249,30 +17576,30 @@
       </c>
       <c r="C458" s="4" t="inlineStr">
         <is>
-          <t>Muzrapova Ruhshona Asrorxon qizi</t>
+          <t>Murodova Munisa Muxtor qizi</t>
         </is>
       </c>
       <c r="D458" s="2" t="n">
-        <v>69</v>
+        <v>167</v>
       </c>
       <c r="E458" s="2" t="inlineStr">
         <is>
-          <t>AD9123240</t>
+          <t>AE2895049</t>
         </is>
       </c>
       <c r="F458" s="3" t="inlineStr">
         <is>
-          <t>62710075590066</t>
+          <t>62112085680050</t>
         </is>
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>23.10.2024</t>
+          <t>03.06.2025</t>
         </is>
       </c>
       <c r="H458" s="3" t="inlineStr">
         <is>
-          <t>27.10.2007</t>
+          <t>21.12.2008</t>
         </is>
       </c>
     </row>
@@ -17287,30 +17614,30 @@
       </c>
       <c r="C459" s="7" t="inlineStr">
         <is>
-          <t>Nazarova Munisa Erkin qizi</t>
+          <t>Muzrapova Ruhshona Asrorxon qizi</t>
         </is>
       </c>
       <c r="D459" s="5" t="n">
-        <v>258</v>
+        <v>69</v>
       </c>
       <c r="E459" s="5" t="inlineStr">
         <is>
-          <t>AE7685867</t>
+          <t>AD9123240</t>
         </is>
       </c>
       <c r="F459" s="6" t="inlineStr">
         <is>
-          <t>41205925680015</t>
+          <t>62710075590066</t>
         </is>
       </c>
       <c r="G459" s="6" t="inlineStr">
         <is>
-          <t>17.06.2026</t>
+          <t>23.10.2024</t>
         </is>
       </c>
       <c r="H459" s="6" t="inlineStr">
         <is>
-          <t>12.05.1992</t>
+          <t>27.10.2007</t>
         </is>
       </c>
     </row>
@@ -17325,28 +17652,30 @@
       </c>
       <c r="C460" s="4" t="inlineStr">
         <is>
-          <t>Ne'matova Sevinch Hikmatullo qizi</t>
-        </is>
-      </c>
-      <c r="D460" s="2" t="inlineStr"/>
+          <t>Nazarova Munisa Erkin qizi</t>
+        </is>
+      </c>
+      <c r="D460" s="2" t="n">
+        <v>258</v>
+      </c>
       <c r="E460" s="2" t="inlineStr">
         <is>
-          <t>AE7082532</t>
+          <t>AE7685867</t>
         </is>
       </c>
       <c r="F460" s="3" t="inlineStr">
         <is>
-          <t>60212085680048</t>
+          <t>41205925680015</t>
         </is>
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>16.04.2026</t>
+          <t>17.06.2026</t>
         </is>
       </c>
       <c r="H460" s="3" t="inlineStr">
         <is>
-          <t>02.12.2008</t>
+          <t>12.05.1992</t>
         </is>
       </c>
     </row>
@@ -17361,30 +17690,28 @@
       </c>
       <c r="C461" s="7" t="inlineStr">
         <is>
-          <t>Normurodova Gulsanam Elyor qizi</t>
-        </is>
-      </c>
-      <c r="D461" s="5" t="n">
-        <v>136</v>
-      </c>
+          <t>Ne'matova Sevinch Hikmatullo qizi</t>
+        </is>
+      </c>
+      <c r="D461" s="5" t="inlineStr"/>
       <c r="E461" s="5" t="inlineStr">
         <is>
-          <t>AE4817469</t>
+          <t>AE7082532</t>
         </is>
       </c>
       <c r="F461" s="6" t="inlineStr">
         <is>
-          <t>61809085680096</t>
+          <t>60212085680048</t>
         </is>
       </c>
       <c r="G461" s="6" t="inlineStr">
         <is>
-          <t>29.10.2025</t>
+          <t>16.04.2026</t>
         </is>
       </c>
       <c r="H461" s="6" t="inlineStr">
         <is>
-          <t>18.09.2008</t>
+          <t>02.12.2008</t>
         </is>
       </c>
     </row>
@@ -17399,30 +17726,30 @@
       </c>
       <c r="C462" s="4" t="inlineStr">
         <is>
-          <t>Omonova Charos Orif qizi</t>
+          <t>Normurodova Gulsanam Elyor qizi</t>
         </is>
       </c>
       <c r="D462" s="2" t="n">
-        <v>230</v>
+        <v>136</v>
       </c>
       <c r="E462" s="2" t="inlineStr">
         <is>
-          <t>AE1338424</t>
+          <t>AE4817469</t>
         </is>
       </c>
       <c r="F462" s="3" t="inlineStr">
         <is>
-          <t>40306985590014</t>
+          <t>61809085680096</t>
         </is>
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>23.01.2025</t>
+          <t>29.10.2025</t>
         </is>
       </c>
       <c r="H462" s="3" t="inlineStr">
         <is>
-          <t>03.06.1998</t>
+          <t>18.09.2008</t>
         </is>
       </c>
     </row>
@@ -17437,28 +17764,30 @@
       </c>
       <c r="C463" s="7" t="inlineStr">
         <is>
-          <t>Oripova Sevinch G'olib qizi</t>
-        </is>
-      </c>
-      <c r="D463" s="5" t="inlineStr"/>
+          <t>Omonova Charos Orif qizi</t>
+        </is>
+      </c>
+      <c r="D463" s="5" t="n">
+        <v>230</v>
+      </c>
       <c r="E463" s="5" t="inlineStr">
         <is>
-          <t>AE3333890</t>
+          <t>AE1338424</t>
         </is>
       </c>
       <c r="F463" s="6" t="inlineStr">
         <is>
-          <t>62007085680095</t>
+          <t>40306985590014</t>
         </is>
       </c>
       <c r="G463" s="6" t="inlineStr">
         <is>
-          <t>09.07.2025</t>
+          <t>23.01.2025</t>
         </is>
       </c>
       <c r="H463" s="6" t="inlineStr">
         <is>
-          <t>20.07.2008</t>
+          <t>03.06.1998</t>
         </is>
       </c>
     </row>
@@ -17473,30 +17802,28 @@
       </c>
       <c r="C464" s="4" t="inlineStr">
         <is>
-          <t>Ozodova Klara Fayzullayevna</t>
-        </is>
-      </c>
-      <c r="D464" s="2" t="n">
-        <v>285</v>
-      </c>
+          <t>Oripova Sevinch G'olib qizi</t>
+        </is>
+      </c>
+      <c r="D464" s="2" t="inlineStr"/>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>AD6663341</t>
+          <t>AE3333890</t>
         </is>
       </c>
       <c r="F464" s="3" t="inlineStr">
         <is>
-          <t>60803075590140</t>
+          <t>62007085680095</t>
         </is>
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>01.04.2024</t>
+          <t>09.07.2025</t>
         </is>
       </c>
       <c r="H464" s="3" t="inlineStr">
         <is>
-          <t>08.03.2007</t>
+          <t>20.07.2008</t>
         </is>
       </c>
     </row>
@@ -17511,30 +17838,30 @@
       </c>
       <c r="C465" s="7" t="inlineStr">
         <is>
-          <t>Saidova Dilso'z Ilyos qizi</t>
+          <t>Ozodova Klara Fayzullayevna</t>
         </is>
       </c>
       <c r="D465" s="5" t="n">
-        <v>67</v>
+        <v>285</v>
       </c>
       <c r="E465" s="5" t="inlineStr">
         <is>
-          <t>AE6043288</t>
+          <t>AD6663341</t>
         </is>
       </c>
       <c r="F465" s="6" t="inlineStr">
         <is>
-          <t>60511085680024</t>
+          <t>60803075590140</t>
         </is>
       </c>
       <c r="G465" s="6" t="inlineStr">
         <is>
-          <t>26.01.2026</t>
+          <t>01.04.2024</t>
         </is>
       </c>
       <c r="H465" s="6" t="inlineStr">
         <is>
-          <t>05.11.2008</t>
+          <t>08.03.2007</t>
         </is>
       </c>
     </row>
@@ -17549,30 +17876,30 @@
       </c>
       <c r="C466" s="4" t="inlineStr">
         <is>
-          <t>Sharipova Diyora Jasur qizi</t>
+          <t>Saidova Dilso'z Ilyos qizi</t>
         </is>
       </c>
       <c r="D466" s="2" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="E466" s="2" t="inlineStr">
         <is>
-          <t>AE5776687</t>
+          <t>AE6043288</t>
         </is>
       </c>
       <c r="F466" s="3" t="inlineStr">
         <is>
-          <t>62307095590022</t>
+          <t>60511085680024</t>
         </is>
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>09.01.2026</t>
+          <t>26.01.2026</t>
         </is>
       </c>
       <c r="H466" s="3" t="inlineStr">
         <is>
-          <t>23.07.2009</t>
+          <t>05.11.2008</t>
         </is>
       </c>
     </row>
@@ -17587,30 +17914,30 @@
       </c>
       <c r="C467" s="7" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Sharipova Diyora Jasur qizi</t>
         </is>
       </c>
       <c r="D467" s="5" t="n">
-        <v>388</v>
+        <v>57</v>
       </c>
       <c r="E467" s="5" t="inlineStr">
         <is>
-          <t>AD0914473</t>
+          <t>AE5776687</t>
         </is>
       </c>
       <c r="F467" s="6" t="inlineStr">
         <is>
-          <t>62803055590089</t>
+          <t>62307095590022</t>
         </is>
       </c>
       <c r="G467" s="6" t="inlineStr">
         <is>
-          <t>14.12.2021</t>
+          <t>09.01.2026</t>
         </is>
       </c>
       <c r="H467" s="6" t="inlineStr">
         <is>
-          <t>28.03.2005</t>
+          <t>23.07.2009</t>
         </is>
       </c>
     </row>
@@ -17625,30 +17952,30 @@
       </c>
       <c r="C468" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="D468" s="2" t="n">
-        <v>276</v>
+        <v>388</v>
       </c>
       <c r="E468" s="2" t="inlineStr">
         <is>
-          <t>AD6026687</t>
+          <t>AD0914473</t>
         </is>
       </c>
       <c r="F468" s="3" t="inlineStr">
         <is>
-          <t>61407075590019</t>
+          <t>62803055590089</t>
         </is>
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>06.02.2024</t>
+          <t>14.12.2021</t>
         </is>
       </c>
       <c r="H468" s="3" t="inlineStr">
         <is>
-          <t>14.07.2007</t>
+          <t>28.03.2005</t>
         </is>
       </c>
     </row>
@@ -17663,30 +17990,30 @@
       </c>
       <c r="C469" s="7" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="D469" s="5" t="n">
-        <v>218</v>
+        <v>276</v>
       </c>
       <c r="E469" s="5" t="inlineStr">
         <is>
-          <t>AE5949204</t>
+          <t>AD6026687</t>
         </is>
       </c>
       <c r="F469" s="6" t="inlineStr">
         <is>
-          <t>62710085680012</t>
+          <t>61407075590019</t>
         </is>
       </c>
       <c r="G469" s="6" t="inlineStr">
         <is>
-          <t>20.01.2026</t>
+          <t>06.02.2024</t>
         </is>
       </c>
       <c r="H469" s="6" t="inlineStr">
         <is>
-          <t>27.10.2008</t>
+          <t>14.07.2007</t>
         </is>
       </c>
     </row>
@@ -17701,20 +18028,20 @@
       </c>
       <c r="C470" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="D470" s="2" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E470" s="2" t="inlineStr">
         <is>
-          <t>AE5949016</t>
+          <t>AE5949204</t>
         </is>
       </c>
       <c r="F470" s="3" t="inlineStr">
         <is>
-          <t>62710085680029</t>
+          <t>62710085680012</t>
         </is>
       </c>
       <c r="G470" s="3" t="inlineStr">
@@ -17739,30 +18066,30 @@
       </c>
       <c r="C471" s="7" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="D471" s="5" t="n">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="E471" s="5" t="inlineStr">
         <is>
-          <t>AE4384190</t>
+          <t>AE5949016</t>
         </is>
       </c>
       <c r="F471" s="6" t="inlineStr">
         <is>
-          <t>61810085590061</t>
+          <t>62710085680029</t>
         </is>
       </c>
       <c r="G471" s="6" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>20.01.2026</t>
         </is>
       </c>
       <c r="H471" s="6" t="inlineStr">
         <is>
-          <t>18.10.2008</t>
+          <t>27.10.2008</t>
         </is>
       </c>
     </row>
@@ -17777,30 +18104,30 @@
       </c>
       <c r="C472" s="4" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="D472" s="2" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="E472" s="2" t="inlineStr">
         <is>
-          <t>AD8362477</t>
+          <t>AE4384190</t>
         </is>
       </c>
       <c r="F472" s="3" t="inlineStr">
         <is>
-          <t>42601955730024</t>
+          <t>61810085590061</t>
         </is>
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>23.08.2024</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="H472" s="3" t="inlineStr">
         <is>
-          <t>26.01.1995</t>
+          <t>18.10.2008</t>
         </is>
       </c>
     </row>
@@ -17815,30 +18142,30 @@
       </c>
       <c r="C473" s="7" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
         </is>
       </c>
       <c r="D473" s="5" t="n">
-        <v>118</v>
+        <v>183</v>
       </c>
       <c r="E473" s="5" t="inlineStr">
         <is>
-          <t>AE1419035</t>
+          <t>AD8362477</t>
         </is>
       </c>
       <c r="F473" s="6" t="inlineStr">
         <is>
-          <t>61309085590066</t>
+          <t>42601955730024</t>
         </is>
       </c>
       <c r="G473" s="6" t="inlineStr">
         <is>
-          <t>29.01.2025</t>
+          <t>23.08.2024</t>
         </is>
       </c>
       <c r="H473" s="6" t="inlineStr">
         <is>
-          <t>13.09.2008</t>
+          <t>26.01.1995</t>
         </is>
       </c>
     </row>
@@ -17848,35 +18175,35 @@
       </c>
       <c r="B474" s="3" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C474" s="4" t="inlineStr">
         <is>
-          <t>Abdinazarova Dilafro'z Burxon qizi</t>
+          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="D474" s="2" t="n">
-        <v>273</v>
+        <v>118</v>
       </c>
       <c r="E474" s="2" t="inlineStr">
         <is>
-          <t>AE3704528</t>
+          <t>AE1419035</t>
         </is>
       </c>
       <c r="F474" s="3" t="inlineStr">
         <is>
-          <t>40401955680037</t>
+          <t>61309085590066</t>
         </is>
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>08.08.2025</t>
+          <t>29.01.2025</t>
         </is>
       </c>
       <c r="H474" s="3" t="inlineStr">
         <is>
-          <t>04.01.1995</t>
+          <t>13.09.2008</t>
         </is>
       </c>
     </row>
@@ -17891,30 +18218,30 @@
       </c>
       <c r="C475" s="7" t="inlineStr">
         <is>
-          <t>Abdixoliqova Elmira Farxod qizi</t>
+          <t>Abdinazarova Dilafro'z Burxon qizi</t>
         </is>
       </c>
       <c r="D475" s="5" t="n">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="E475" s="5" t="inlineStr">
         <is>
-          <t>AE4512271</t>
+          <t>AE3704528</t>
         </is>
       </c>
       <c r="F475" s="6" t="inlineStr">
         <is>
-          <t>62501095720012</t>
+          <t>40401955680037</t>
         </is>
       </c>
       <c r="G475" s="6" t="inlineStr">
         <is>
-          <t>07.10.2025</t>
+          <t>08.08.2025</t>
         </is>
       </c>
       <c r="H475" s="6" t="inlineStr">
         <is>
-          <t>25.01.2009</t>
+          <t>04.01.1995</t>
         </is>
       </c>
     </row>
@@ -17929,30 +18256,30 @@
       </c>
       <c r="C476" s="4" t="inlineStr">
         <is>
-          <t>Azimova Zahroxon Abdirauf qizi</t>
+          <t>Abdixoliqova Elmira Farxod qizi</t>
         </is>
       </c>
       <c r="D476" s="2" t="n">
-        <v>318</v>
+        <v>286</v>
       </c>
       <c r="E476" s="2" t="inlineStr">
         <is>
-          <t>AD5290004</t>
+          <t>AE4512271</t>
         </is>
       </c>
       <c r="F476" s="3" t="inlineStr">
         <is>
-          <t>61312065590013</t>
+          <t>62501095720012</t>
         </is>
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>01.12.2023</t>
+          <t>07.10.2025</t>
         </is>
       </c>
       <c r="H476" s="3" t="inlineStr">
         <is>
-          <t>13.12.2006</t>
+          <t>25.01.2009</t>
         </is>
       </c>
     </row>
@@ -17967,30 +18294,30 @@
       </c>
       <c r="C477" s="7" t="inlineStr">
         <is>
-          <t>Bahodirova Asila Olmos qizi</t>
+          <t>Azimova Zahroxon Abdirauf qizi</t>
         </is>
       </c>
       <c r="D477" s="5" t="n">
-        <v>44</v>
+        <v>318</v>
       </c>
       <c r="E477" s="5" t="inlineStr">
         <is>
-          <t>AE1222596</t>
+          <t>AD5290004</t>
         </is>
       </c>
       <c r="F477" s="6" t="inlineStr">
         <is>
-          <t>61711085590032</t>
+          <t>61312065590013</t>
         </is>
       </c>
       <c r="G477" s="6" t="inlineStr">
         <is>
-          <t>16.01.2025</t>
+          <t>01.12.2023</t>
         </is>
       </c>
       <c r="H477" s="6" t="inlineStr">
         <is>
-          <t>17.11.2008</t>
+          <t>13.12.2006</t>
         </is>
       </c>
     </row>
@@ -18005,30 +18332,30 @@
       </c>
       <c r="C478" s="4" t="inlineStr">
         <is>
-          <t>Davlatova Gulnoza Husan qizi</t>
+          <t>Bahodirova Asila Olmos qizi</t>
         </is>
       </c>
       <c r="D478" s="2" t="n">
-        <v>310</v>
+        <v>44</v>
       </c>
       <c r="E478" s="2" t="inlineStr">
         <is>
-          <t>AD8208717</t>
+          <t>AE1222596</t>
         </is>
       </c>
       <c r="F478" s="3" t="inlineStr">
         <is>
-          <t>41508955590021</t>
+          <t>61711085590032</t>
         </is>
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>12.08.2024</t>
+          <t>16.01.2025</t>
         </is>
       </c>
       <c r="H478" s="3" t="inlineStr">
         <is>
-          <t>15.08.1995</t>
+          <t>17.11.2008</t>
         </is>
       </c>
     </row>
@@ -18043,30 +18370,30 @@
       </c>
       <c r="C479" s="7" t="inlineStr">
         <is>
-          <t>Eshimova Zilola Bekzod qizi</t>
+          <t>Davlatova Gulnoza Husan qizi</t>
         </is>
       </c>
       <c r="D479" s="5" t="n">
-        <v>174</v>
+        <v>310</v>
       </c>
       <c r="E479" s="5" t="inlineStr">
         <is>
-          <t>AE2935693</t>
+          <t>AD8208717</t>
         </is>
       </c>
       <c r="F479" s="6" t="inlineStr">
         <is>
-          <t>61506085730076</t>
+          <t>41508955590021</t>
         </is>
       </c>
       <c r="G479" s="6" t="inlineStr">
         <is>
-          <t>09.06.2025</t>
+          <t>12.08.2024</t>
         </is>
       </c>
       <c r="H479" s="6" t="inlineStr">
         <is>
-          <t>15.06.2008</t>
+          <t>15.08.1995</t>
         </is>
       </c>
     </row>
@@ -18081,28 +18408,30 @@
       </c>
       <c r="C480" s="4" t="inlineStr">
         <is>
-          <t>Irgasheva Dinora Shodmon qizi</t>
-        </is>
-      </c>
-      <c r="D480" s="2" t="inlineStr"/>
+          <t>Eshimova Zilola Bekzod qizi</t>
+        </is>
+      </c>
+      <c r="D480" s="2" t="n">
+        <v>174</v>
+      </c>
       <c r="E480" s="2" t="inlineStr">
         <is>
-          <t>AC 2430931</t>
+          <t>AE2935693</t>
         </is>
       </c>
       <c r="F480" s="3" t="inlineStr">
         <is>
-          <t>60106035590029</t>
+          <t>61506085730076</t>
         </is>
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>15.11.2019</t>
+          <t>09.06.2025</t>
         </is>
       </c>
       <c r="H480" s="3" t="inlineStr">
         <is>
-          <t>01.06.2003</t>
+          <t>15.06.2008</t>
         </is>
       </c>
     </row>
@@ -18117,30 +18446,28 @@
       </c>
       <c r="C481" s="7" t="inlineStr">
         <is>
-          <t>Jalilova Shabnam Ozodjon qizi</t>
-        </is>
-      </c>
-      <c r="D481" s="5" t="n">
-        <v>17</v>
-      </c>
+          <t>Irgasheva Dinora Shodmon qizi</t>
+        </is>
+      </c>
+      <c r="D481" s="5" t="inlineStr"/>
       <c r="E481" s="5" t="inlineStr">
         <is>
-          <t>AD9937321</t>
+          <t>AC 2430931</t>
         </is>
       </c>
       <c r="F481" s="6" t="inlineStr">
         <is>
-          <t>60603085590037</t>
+          <t>60106035590029</t>
         </is>
       </c>
       <c r="G481" s="6" t="inlineStr">
         <is>
-          <t>24.12.2024</t>
+          <t>15.11.2019</t>
         </is>
       </c>
       <c r="H481" s="6" t="inlineStr">
         <is>
-          <t>06.03.2008</t>
+          <t>01.06.2003</t>
         </is>
       </c>
     </row>
@@ -18155,30 +18482,30 @@
       </c>
       <c r="C482" s="4" t="inlineStr">
         <is>
-          <t>Jumayeva Husnida Shovkat qizi</t>
+          <t>Jalilova Shabnam Ozodjon qizi</t>
         </is>
       </c>
       <c r="D482" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E482" s="2" t="inlineStr">
         <is>
-          <t>AE6299685</t>
+          <t>AD9937321</t>
         </is>
       </c>
       <c r="F482" s="3" t="inlineStr">
         <is>
-          <t>60907085590063</t>
+          <t>60603085590037</t>
         </is>
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>11.02.2026</t>
+          <t>24.12.2024</t>
         </is>
       </c>
       <c r="H482" s="3" t="inlineStr">
         <is>
-          <t>09.07.2008</t>
+          <t>06.03.2008</t>
         </is>
       </c>
     </row>
@@ -18193,30 +18520,30 @@
       </c>
       <c r="C483" s="7" t="inlineStr">
         <is>
-          <t>Karimova Nozliya Rustamovna</t>
+          <t>Jumayeva Husnida Shovkat qizi</t>
         </is>
       </c>
       <c r="D483" s="5" t="n">
-        <v>250</v>
+        <v>18</v>
       </c>
       <c r="E483" s="5" t="inlineStr">
         <is>
-          <t>AE4674508</t>
+          <t>AE6299685</t>
         </is>
       </c>
       <c r="F483" s="6" t="inlineStr">
         <is>
-          <t>61502085680047</t>
+          <t>60907085590063</t>
         </is>
       </c>
       <c r="G483" s="6" t="inlineStr">
         <is>
-          <t>18.10.2025</t>
+          <t>11.02.2026</t>
         </is>
       </c>
       <c r="H483" s="6" t="inlineStr">
         <is>
-          <t>15.02.2008</t>
+          <t>09.07.2008</t>
         </is>
       </c>
     </row>
@@ -18231,30 +18558,30 @@
       </c>
       <c r="C484" s="4" t="inlineStr">
         <is>
-          <t>Mahmadmurodova Sevara Safarali qizi</t>
+          <t>Karimova Nozliya Rustamovna</t>
         </is>
       </c>
       <c r="D484" s="2" t="n">
-        <v>390</v>
+        <v>250</v>
       </c>
       <c r="E484" s="2" t="inlineStr">
         <is>
-          <t>AE2103843</t>
+          <t>AE4674508</t>
         </is>
       </c>
       <c r="F484" s="3" t="inlineStr">
         <is>
-          <t>60705005680087</t>
+          <t>61502085680047</t>
         </is>
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>27.03.2025</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="H484" s="3" t="inlineStr">
         <is>
-          <t>07.05.2000</t>
+          <t>15.02.2008</t>
         </is>
       </c>
     </row>
@@ -18269,30 +18596,30 @@
       </c>
       <c r="C485" s="7" t="inlineStr">
         <is>
-          <t>Mahmatqulova Nilufar Qayum qizi</t>
+          <t>Mahmadmurodova Sevara Safarali qizi</t>
         </is>
       </c>
       <c r="D485" s="5" t="n">
-        <v>314</v>
+        <v>390</v>
       </c>
       <c r="E485" s="5" t="inlineStr">
         <is>
-          <t>AE6047826</t>
+          <t>AE2103843</t>
         </is>
       </c>
       <c r="F485" s="6" t="inlineStr">
         <is>
-          <t>60806085590115</t>
+          <t>60705005680087</t>
         </is>
       </c>
       <c r="G485" s="6" t="inlineStr">
         <is>
-          <t>26.01.2026</t>
+          <t>27.03.2025</t>
         </is>
       </c>
       <c r="H485" s="6" t="inlineStr">
         <is>
-          <t>08.06.2008</t>
+          <t>07.05.2000</t>
         </is>
       </c>
     </row>
@@ -18307,30 +18634,30 @@
       </c>
       <c r="C486" s="4" t="inlineStr">
         <is>
-          <t>Mahmudova Maftuna To'ra qizi</t>
+          <t>Mahmatqulova Nilufar Qayum qizi</t>
         </is>
       </c>
       <c r="D486" s="2" t="n">
-        <v>120</v>
+        <v>314</v>
       </c>
       <c r="E486" s="2" t="inlineStr">
         <is>
-          <t>AE4270256</t>
+          <t>AE6047826</t>
         </is>
       </c>
       <c r="F486" s="3" t="inlineStr">
         <is>
-          <t>61707085680068</t>
+          <t>60806085590115</t>
         </is>
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>19.09.2025</t>
+          <t>26.01.2026</t>
         </is>
       </c>
       <c r="H486" s="3" t="inlineStr">
         <is>
-          <t>17.07.2008</t>
+          <t>08.06.2008</t>
         </is>
       </c>
     </row>
@@ -18345,20 +18672,20 @@
       </c>
       <c r="C487" s="7" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda Nosir qizi</t>
+          <t>Mahmudova Maftuna To'ra qizi</t>
         </is>
       </c>
       <c r="D487" s="5" t="n">
-        <v>199</v>
+        <v>120</v>
       </c>
       <c r="E487" s="5" t="inlineStr">
         <is>
-          <t>AE4263249</t>
+          <t>AE4270256</t>
         </is>
       </c>
       <c r="F487" s="6" t="inlineStr">
         <is>
-          <t>60710085680047</t>
+          <t>61707085680068</t>
         </is>
       </c>
       <c r="G487" s="6" t="inlineStr">
@@ -18368,7 +18695,7 @@
       </c>
       <c r="H487" s="6" t="inlineStr">
         <is>
-          <t>07.10.2008</t>
+          <t>17.07.2008</t>
         </is>
       </c>
     </row>
@@ -18383,30 +18710,30 @@
       </c>
       <c r="C488" s="4" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda Hasan qizi</t>
+          <t>Mannonova Shahrizoda Nosir qizi</t>
         </is>
       </c>
       <c r="D488" s="2" t="n">
-        <v>253</v>
+        <v>199</v>
       </c>
       <c r="E488" s="2" t="inlineStr">
         <is>
-          <t>AE5221552</t>
+          <t>AE4263249</t>
         </is>
       </c>
       <c r="F488" s="3" t="inlineStr">
         <is>
-          <t>60106075720246</t>
+          <t>60710085680047</t>
         </is>
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>28.11.2025</t>
+          <t>19.09.2025</t>
         </is>
       </c>
       <c r="H488" s="3" t="inlineStr">
         <is>
-          <t>01.06.2007</t>
+          <t>07.10.2008</t>
         </is>
       </c>
     </row>
@@ -18421,30 +18748,30 @@
       </c>
       <c r="C489" s="7" t="inlineStr">
         <is>
-          <t>Muminova Sevinch Uchqun qizi</t>
+          <t>Maxmarajabova Zerda Hasan qizi</t>
         </is>
       </c>
       <c r="D489" s="5" t="n">
-        <v>163</v>
+        <v>253</v>
       </c>
       <c r="E489" s="5" t="inlineStr">
         <is>
-          <t>AE2259069</t>
+          <t>AE5221552</t>
         </is>
       </c>
       <c r="F489" s="6" t="inlineStr">
         <is>
-          <t>63001085590111</t>
+          <t>60106075720246</t>
         </is>
       </c>
       <c r="G489" s="6" t="inlineStr">
         <is>
-          <t>09.04.2025</t>
+          <t>28.11.2025</t>
         </is>
       </c>
       <c r="H489" s="6" t="inlineStr">
         <is>
-          <t>30.01.2008</t>
+          <t>01.06.2007</t>
         </is>
       </c>
     </row>
@@ -18459,30 +18786,30 @@
       </c>
       <c r="C490" s="4" t="inlineStr">
         <is>
-          <t>Mustafayeva Nargiza Ulug'bek qizi</t>
+          <t>Muminova Sevinch Uchqun qizi</t>
         </is>
       </c>
       <c r="D490" s="2" t="n">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="E490" s="2" t="inlineStr">
         <is>
-          <t>AB8521319</t>
+          <t>AE2259069</t>
         </is>
       </c>
       <c r="F490" s="3" t="inlineStr">
         <is>
-          <t>62906005590060</t>
+          <t>63001085590111</t>
         </is>
       </c>
       <c r="G490" s="3" t="inlineStr">
         <is>
-          <t>02.01.2018</t>
+          <t>09.04.2025</t>
         </is>
       </c>
       <c r="H490" s="3" t="inlineStr">
         <is>
-          <t>29.06.2000</t>
+          <t>30.01.2008</t>
         </is>
       </c>
     </row>
@@ -18497,30 +18824,30 @@
       </c>
       <c r="C491" s="7" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Mustafayeva Nargiza Ulug'bek qizi</t>
         </is>
       </c>
       <c r="D491" s="5" t="n">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="E491" s="5" t="inlineStr">
         <is>
-          <t>AE2428256</t>
+          <t>AB8521319</t>
         </is>
       </c>
       <c r="F491" s="6" t="inlineStr">
         <is>
-          <t>60506085590066</t>
+          <t>62906005590060</t>
         </is>
       </c>
       <c r="G491" s="6" t="inlineStr">
         <is>
-          <t>22.04.2025</t>
+          <t>02.01.2018</t>
         </is>
       </c>
       <c r="H491" s="6" t="inlineStr">
         <is>
-          <t>05.06.2008</t>
+          <t>29.06.2000</t>
         </is>
       </c>
     </row>
@@ -18535,30 +18862,30 @@
       </c>
       <c r="C492" s="4" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
         </is>
       </c>
       <c r="D492" s="2" t="n">
-        <v>212</v>
+        <v>176</v>
       </c>
       <c r="E492" s="2" t="inlineStr">
         <is>
-          <t>AB5359926</t>
+          <t>AE2428256</t>
         </is>
       </c>
       <c r="F492" s="3" t="inlineStr">
         <is>
-          <t>40211995680023</t>
+          <t>60506085590066</t>
         </is>
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>12.12.2016</t>
+          <t>22.04.2025</t>
         </is>
       </c>
       <c r="H492" s="3" t="inlineStr">
         <is>
-          <t>02.11.1999</t>
+          <t>05.06.2008</t>
         </is>
       </c>
     </row>
@@ -18573,30 +18900,30 @@
       </c>
       <c r="C493" s="7" t="inlineStr">
         <is>
-          <t>Niyozova Sevara Turoqulovna</t>
+          <t>Narziyeva Intizor Iskandar qizi</t>
         </is>
       </c>
       <c r="D493" s="5" t="n">
-        <v>304</v>
+        <v>212</v>
       </c>
       <c r="E493" s="5" t="inlineStr">
         <is>
-          <t>AD9706738</t>
+          <t>AB5359926</t>
         </is>
       </c>
       <c r="F493" s="6" t="inlineStr">
         <is>
-          <t>412068 9256 0120</t>
+          <t>40211995680023</t>
         </is>
       </c>
       <c r="G493" s="6" t="inlineStr">
         <is>
-          <t>05.12.2024</t>
+          <t>12.12.2016</t>
         </is>
       </c>
       <c r="H493" s="6" t="inlineStr">
         <is>
-          <t>12.06.1989</t>
+          <t>02.11.1999</t>
         </is>
       </c>
     </row>
@@ -18611,30 +18938,30 @@
       </c>
       <c r="C494" s="4" t="inlineStr">
         <is>
-          <t>Nurillayeva Sevinch Mashrab qizi</t>
+          <t>Niyozova Sevara Turoqulovna</t>
         </is>
       </c>
       <c r="D494" s="2" t="n">
-        <v>246</v>
+        <v>304</v>
       </c>
       <c r="E494" s="2" t="inlineStr">
         <is>
-          <t>AD9494409</t>
+          <t>AD9706738</t>
         </is>
       </c>
       <c r="F494" s="3" t="inlineStr">
         <is>
-          <t>60504085680019</t>
+          <t>412068 9256 0120</t>
         </is>
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>26.09.2025</t>
+          <t>05.12.2024</t>
         </is>
       </c>
       <c r="H494" s="3" t="inlineStr">
         <is>
-          <t>05.04.2008</t>
+          <t>12.06.1989</t>
         </is>
       </c>
     </row>
@@ -18649,30 +18976,30 @@
       </c>
       <c r="C495" s="7" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Nurillayeva Sevinch Mashrab qizi</t>
         </is>
       </c>
       <c r="D495" s="5" t="n">
-        <v>47</v>
+        <v>246</v>
       </c>
       <c r="E495" s="5" t="inlineStr">
         <is>
-          <t>AD0776916</t>
+          <t>AD9494409</t>
         </is>
       </c>
       <c r="F495" s="6" t="inlineStr">
         <is>
-          <t>62012045590040</t>
+          <t>60504085680019</t>
         </is>
       </c>
       <c r="G495" s="6" t="inlineStr">
         <is>
-          <t>02.11.2021</t>
+          <t>26.09.2025</t>
         </is>
       </c>
       <c r="H495" s="6" t="inlineStr">
         <is>
-          <t>20.12.2004</t>
+          <t>05.04.2008</t>
         </is>
       </c>
     </row>
@@ -18687,30 +19014,30 @@
       </c>
       <c r="C496" s="4" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="D496" s="2" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E496" s="2" t="inlineStr">
         <is>
-          <t>AE2118072</t>
+          <t>AD0776916</t>
         </is>
       </c>
       <c r="F496" s="3" t="inlineStr">
         <is>
-          <t>62201085590064</t>
+          <t>62012045590040</t>
         </is>
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>28.03.2025</t>
+          <t>02.11.2021</t>
         </is>
       </c>
       <c r="H496" s="3" t="inlineStr">
         <is>
-          <t>22.01.2008</t>
+          <t>20.12.2004</t>
         </is>
       </c>
     </row>
@@ -18725,30 +19052,30 @@
       </c>
       <c r="C497" s="7" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso Farhod qizi</t>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
         </is>
       </c>
       <c r="D497" s="5" t="n">
-        <v>187</v>
+        <v>55</v>
       </c>
       <c r="E497" s="5" t="inlineStr">
         <is>
-          <t>AE1143288</t>
+          <t>AE2118072</t>
         </is>
       </c>
       <c r="F497" s="6" t="inlineStr">
         <is>
-          <t>62911085630012</t>
+          <t>62201085590064</t>
         </is>
       </c>
       <c r="G497" s="6" t="inlineStr">
         <is>
-          <t>10.01.2025</t>
+          <t>28.03.2025</t>
         </is>
       </c>
       <c r="H497" s="6" t="inlineStr">
         <is>
-          <t>29.11.2008</t>
+          <t>22.01.2008</t>
         </is>
       </c>
     </row>
@@ -18763,30 +19090,30 @@
       </c>
       <c r="C498" s="4" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
+          <t>Quchqarova Zebiniso Farhod qizi</t>
         </is>
       </c>
       <c r="D498" s="2" t="n">
-        <v>271</v>
+        <v>187</v>
       </c>
       <c r="E498" s="2" t="inlineStr">
         <is>
-          <t>AE4246251</t>
+          <t>AE1143288</t>
         </is>
       </c>
       <c r="F498" s="3" t="inlineStr">
         <is>
-          <t>62702085680028</t>
+          <t>62911085630012</t>
         </is>
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>18.09.2025</t>
+          <t>10.01.2025</t>
         </is>
       </c>
       <c r="H498" s="3" t="inlineStr">
         <is>
-          <t>27.02.2008</t>
+          <t>29.11.2008</t>
         </is>
       </c>
     </row>
@@ -18801,30 +19128,30 @@
       </c>
       <c r="C499" s="7" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="D499" s="5" t="n">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="E499" s="5" t="inlineStr">
         <is>
-          <t>AD8686485</t>
+          <t>AE4246251</t>
         </is>
       </c>
       <c r="F499" s="6" t="inlineStr">
         <is>
-          <t>62201085590019</t>
+          <t>62702085680028</t>
         </is>
       </c>
       <c r="G499" s="6" t="inlineStr">
         <is>
-          <t>19.09.2024</t>
+          <t>18.09.2025</t>
         </is>
       </c>
       <c r="H499" s="6" t="inlineStr">
         <is>
-          <t>22.01.2008</t>
+          <t>27.02.2008</t>
         </is>
       </c>
     </row>
@@ -18839,30 +19166,30 @@
       </c>
       <c r="C500" s="4" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="D500" s="2" t="n">
-        <v>32</v>
+        <v>254</v>
       </c>
       <c r="E500" s="2" t="inlineStr">
         <is>
-          <t>AC1805235</t>
+          <t>AD8686485</t>
         </is>
       </c>
       <c r="F500" s="3" t="inlineStr">
         <is>
-          <t>60409015590065</t>
+          <t>62201085590019</t>
         </is>
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>08.04.2019</t>
+          <t>19.09.2024</t>
         </is>
       </c>
       <c r="H500" s="3" t="inlineStr">
         <is>
-          <t>04.09.2001</t>
+          <t>22.01.2008</t>
         </is>
       </c>
     </row>
@@ -18877,28 +19204,30 @@
       </c>
       <c r="C501" s="7" t="inlineStr">
         <is>
-          <t>Sayfieva Sarvinoz Zafar qizi</t>
-        </is>
-      </c>
-      <c r="D501" s="5" t="inlineStr"/>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
+        </is>
+      </c>
+      <c r="D501" s="5" t="n">
+        <v>32</v>
+      </c>
       <c r="E501" s="5" t="inlineStr">
         <is>
-          <t>AB6304158</t>
+          <t>AC1805235</t>
         </is>
       </c>
       <c r="F501" s="6" t="inlineStr">
         <is>
-          <t>415079 8559 0074</t>
+          <t>60409015590065</t>
         </is>
       </c>
       <c r="G501" s="6" t="inlineStr">
         <is>
-          <t>28.03.2017</t>
+          <t>08.04.2019</t>
         </is>
       </c>
       <c r="H501" s="6" t="inlineStr">
         <is>
-          <t>15.07.1998</t>
+          <t>04.09.2001</t>
         </is>
       </c>
     </row>
@@ -18913,30 +19242,28 @@
       </c>
       <c r="C502" s="4" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
-        </is>
-      </c>
-      <c r="D502" s="2" t="n">
-        <v>3</v>
-      </c>
+          <t>Sayfieva Sarvinoz Zafar qizi</t>
+        </is>
+      </c>
+      <c r="D502" s="2" t="inlineStr"/>
       <c r="E502" s="2" t="inlineStr">
         <is>
-          <t>AE4385111</t>
+          <t>AB6304158</t>
         </is>
       </c>
       <c r="F502" s="3" t="inlineStr">
         <is>
-          <t>62203085730015</t>
+          <t>415079 8559 0074</t>
         </is>
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>28.03.2017</t>
         </is>
       </c>
       <c r="H502" s="3" t="inlineStr">
         <is>
-          <t>22.03.2008</t>
+          <t>15.07.1998</t>
         </is>
       </c>
     </row>
@@ -18951,30 +19278,30 @@
       </c>
       <c r="C503" s="7" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="D503" s="5" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E503" s="5" t="inlineStr">
         <is>
-          <t>AD2624840</t>
+          <t>AE4385111</t>
         </is>
       </c>
       <c r="F503" s="6" t="inlineStr">
         <is>
-          <t>62408065590018</t>
+          <t>62203085730015</t>
         </is>
       </c>
       <c r="G503" s="6" t="inlineStr">
         <is>
-          <t>18.02.2023</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="H503" s="6" t="inlineStr">
         <is>
-          <t>24.08.2006</t>
+          <t>22.03.2008</t>
         </is>
       </c>
     </row>
@@ -18989,30 +19316,30 @@
       </c>
       <c r="C504" s="4" t="inlineStr">
         <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="D504" s="2" t="n">
-        <v>283</v>
+        <v>21</v>
       </c>
       <c r="E504" s="2" t="inlineStr">
         <is>
-          <t>AB5702170</t>
+          <t>AD2624840</t>
         </is>
       </c>
       <c r="F504" s="3" t="inlineStr">
         <is>
-          <t>42601925680010</t>
+          <t>62408065590018</t>
         </is>
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>19.01.2017</t>
+          <t>18.02.2023</t>
         </is>
       </c>
       <c r="H504" s="3" t="inlineStr">
         <is>
-          <t>26.01.1992</t>
+          <t>24.08.2006</t>
         </is>
       </c>
     </row>
@@ -19027,28 +19354,30 @@
       </c>
       <c r="C505" s="7" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
-        </is>
-      </c>
-      <c r="D505" s="5" t="inlineStr"/>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
+        </is>
+      </c>
+      <c r="D505" s="5" t="n">
+        <v>283</v>
+      </c>
       <c r="E505" s="5" t="inlineStr">
         <is>
-          <t>AE 4385291</t>
+          <t>AB5702170</t>
         </is>
       </c>
       <c r="F505" s="6" t="inlineStr">
         <is>
-          <t>407129 0256 0079</t>
+          <t>42601925680010</t>
         </is>
       </c>
       <c r="G505" s="6" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>19.01.2017</t>
         </is>
       </c>
       <c r="H505" s="6" t="inlineStr">
         <is>
-          <t>07.12.1990</t>
+          <t>26.01.1992</t>
         </is>
       </c>
     </row>
@@ -19063,30 +19392,28 @@
       </c>
       <c r="C506" s="4" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
-        </is>
-      </c>
-      <c r="D506" s="2" t="n">
-        <v>138</v>
-      </c>
+          <t>Uzoqova Fazilat Nurali qizi</t>
+        </is>
+      </c>
+      <c r="D506" s="2" t="inlineStr"/>
       <c r="E506" s="2" t="inlineStr">
         <is>
-          <t>AD2922676</t>
+          <t>AE 4385291</t>
         </is>
       </c>
       <c r="F506" s="3" t="inlineStr">
         <is>
-          <t>61604065590015</t>
+          <t>407129 0256 0079</t>
         </is>
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>01.04.2023</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="H506" s="3" t="inlineStr">
         <is>
-          <t>16.04.2006</t>
+          <t>07.12.1990</t>
         </is>
       </c>
     </row>
@@ -19101,30 +19428,30 @@
       </c>
       <c r="C507" s="7" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="D507" s="5" t="n">
-        <v>247</v>
+        <v>138</v>
       </c>
       <c r="E507" s="5" t="inlineStr">
         <is>
-          <t>AE4629898</t>
+          <t>AD2922676</t>
         </is>
       </c>
       <c r="F507" s="6" t="inlineStr">
         <is>
-          <t>62802085680012</t>
+          <t>61604065590015</t>
         </is>
       </c>
       <c r="G507" s="6" t="inlineStr">
         <is>
-          <t>15.10.2025</t>
+          <t>01.04.2023</t>
         </is>
       </c>
       <c r="H507" s="6" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>16.04.2006</t>
         </is>
       </c>
     </row>
@@ -19139,30 +19466,104 @@
       </c>
       <c r="C508" s="4" t="inlineStr">
         <is>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+        </is>
+      </c>
+      <c r="D508" s="2" t="n">
+        <v>247</v>
+      </c>
+      <c r="E508" s="2" t="inlineStr">
+        <is>
+          <t>AE4629898</t>
+        </is>
+      </c>
+      <c r="F508" s="3" t="inlineStr">
+        <is>
+          <t>62802085680012</t>
+        </is>
+      </c>
+      <c r="G508" s="3" t="inlineStr">
+        <is>
+          <t>15.10.2025</t>
+        </is>
+      </c>
+      <c r="H508" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="509" ht="22" customHeight="1">
+      <c r="A509" s="5" t="n">
+        <v>508</v>
+      </c>
+      <c r="B509" s="6" t="inlineStr">
+        <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C509" s="7" t="inlineStr">
+        <is>
           <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
-      <c r="D508" s="2" t="n">
+      <c r="D509" s="5" t="n">
         <v>93</v>
       </c>
-      <c r="E508" s="2" t="inlineStr">
+      <c r="E509" s="5" t="inlineStr">
         <is>
           <t>AE4688777</t>
         </is>
       </c>
-      <c r="F508" s="3" t="inlineStr">
+      <c r="F509" s="6" t="inlineStr">
         <is>
           <t>63007085680074</t>
         </is>
       </c>
-      <c r="G508" s="3" t="inlineStr">
+      <c r="G509" s="6" t="inlineStr">
         <is>
           <t>20.10.2025</t>
         </is>
       </c>
-      <c r="H508" s="3" t="inlineStr">
+      <c r="H509" s="6" t="inlineStr">
         <is>
           <t>30.07.2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="510" ht="22" customHeight="1">
+      <c r="A510" s="2" t="n">
+        <v>509</v>
+      </c>
+      <c r="B510" s="3" t="inlineStr">
+        <is>
+          <t>26-07</t>
+        </is>
+      </c>
+      <c r="C510" s="4" t="inlineStr">
+        <is>
+          <t>Ergasheva Madina Tulqin qizi</t>
+        </is>
+      </c>
+      <c r="D510" s="2" t="inlineStr"/>
+      <c r="E510" s="2" t="inlineStr">
+        <is>
+          <t>AC0429133</t>
+        </is>
+      </c>
+      <c r="F510" s="3" t="inlineStr">
+        <is>
+          <t>62501027890026</t>
+        </is>
+      </c>
+      <c r="G510" s="3" t="inlineStr">
+        <is>
+          <t>07.12.2018</t>
+        </is>
+      </c>
+      <c r="H510" s="3" t="inlineStr">
+        <is>
+          <t>25.01.2002</t>
         </is>
       </c>
     </row>
@@ -19282,7 +19683,11 @@
           <t>Aliyeva Shahro'za Nishon qizi</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 74</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
           <t>AD5070455</t>
@@ -19390,7 +19795,11 @@
           <t>Bekmirzayeva Shahrizoda Zafar qizi</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 76</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>AC2300123</t>
@@ -19462,7 +19871,11 @@
           <t>Erkinova Zahro Elyorjon qizi</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>26/27 sh/a 78</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>AD8206268</t>
@@ -19498,7 +19911,11 @@
           <t>Eshqobilova Dilbar Ziyodulla qizi</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A79</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
           <t>AD9786116</t>
@@ -19606,7 +20023,11 @@
           <t>Jurayeva Munisa Abduvoxid qizi</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>25/26 sh/a 385</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>AE2822238</t>
@@ -19750,7 +20171,11 @@
           <t>Muradova Oygul Gulamovna</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 159</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>AE3508359</t>
@@ -19786,7 +20211,11 @@
           <t>Muxammedova E'zoza Sodiq qizi</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 177</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
           <t>AB8047094</t>
@@ -19822,7 +20251,11 @@
           <t>Niyozova Bibixonim Alisherovna</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 372</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>AD3652553</t>
@@ -20038,7 +20471,11 @@
           <t>Suvonova Sevinch Orif qizi</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A94</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>AD9767988</t>
@@ -20182,7 +20619,11 @@
           <t>Yusupova Dilnura Nuriddin qizi</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 98</t>
+        </is>
+      </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
           <t>AD9394045</t>
@@ -20320,7 +20761,11 @@
           <t>Axmadova Zarnigor Habibullo qizi</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>26/27 sh/a 100</t>
+        </is>
+      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>AD9320444</t>
@@ -20428,7 +20873,11 @@
           <t>Egamberdiyeva Shahlo Dagar qizi</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A 103</t>
+        </is>
+      </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
           <t>AB6730694</t>
@@ -20500,7 +20949,11 @@
           <t>Homidova Asilaxon G'ulomjon qizi</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A105</t>
+        </is>
+      </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
           <t>AD8998916</t>
@@ -20536,7 +20989,11 @@
           <t>Ismoilova Xumoroy Qudratilla qizi</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>26/27 SH/A106</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>AD7239997</t>
@@ -20572,7 +21029,11 @@
           <t>Mavlonova Mastura Gulmurod qizi</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 229</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
           <t>AD2081328</t>
@@ -20824,7 +21285,11 @@
           <t>Odilova Marjona Baxodir qizi</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A114</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>AD9572244</t>
@@ -21112,7 +21577,11 @@
           <t>Xoliqulova Nozima Qalandar qizi</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>26/27 SH/A123</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>AD9626141</t>
@@ -21148,7 +21617,11 @@
           <t>Xudoyorova Shahzoda Shuxrat qizi</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A174</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
           <t>AD5989765</t>
@@ -21184,7 +21657,11 @@
           <t>Yusupova Hosila Akmal qizi</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>26/37 SH/A 125</t>
+        </is>
+      </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
           <t>AD7115916</t>
@@ -21538,7 +22015,11 @@
           <t>Ibrohimova Gulasal Nurbek qizi</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 264</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
           <t>AD8087163</t>
@@ -21646,7 +22127,11 @@
           <t>Maxmudova Nigina Maqsudjon qizi</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 266</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>AD6910277</t>
@@ -21682,7 +22167,11 @@
           <t>Muhammadiyeva Rayhon Rahmatovna</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 272</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
           <t>AD9028774</t>
@@ -21754,7 +22243,11 @@
           <t>Normo'minova Asal Qulmamatovna</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 369</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
           <t>AC0097118</t>
@@ -22042,7 +22535,11 @@
           <t>Shodiyeva Nilufar Omonovna</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>26/27 sh/a 147</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
           <t>AD2012856</t>
@@ -22078,7 +22575,11 @@
           <t>Shukurillayeva Dilnura Jasurbek qizi</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 263</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>AD7196673</t>
@@ -22186,7 +22687,11 @@
           <t>Umirova Sevara Avlayor qizi</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 260</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
           <t>AC2551314</t>
@@ -22258,7 +22763,11 @@
           <t>Xudoykulova Munisa Muzurovna</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A153</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
           <t>AB3909486</t>
@@ -22330,7 +22839,11 @@
           <t>Yorboboyeva Shaxzoda Zokirjon qizi</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>26/27 sh/a 155</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
           <t>AD9750298</t>
@@ -22612,7 +23125,11 @@
           <t>Esonmurodova Nurgul Nuriddin qizi</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 161</t>
+        </is>
+      </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
           <t>AD7580502</t>
@@ -22756,7 +23273,11 @@
           <t>Nosirova Umida Zafariddin qizi</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A165</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
           <t>AD9701625</t>
@@ -22828,7 +23349,11 @@
           <t>Olimova Durdona Uktam qizi</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A246</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
           <t>AE1697619</t>
@@ -22972,7 +23497,11 @@
           <t>Quysinova Sumbula G'ayrat qizi</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 338</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
           <t>AD9208348</t>
@@ -23224,7 +23753,11 @@
           <t>Turayeva Malika Abdulla qizi</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>26/27 SH/A178</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>AB5223930</t>
@@ -23296,7 +23829,11 @@
           <t>Xayitova Madina G'ayrat qizi</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>26/27 sh/a 180</t>
+        </is>
+      </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
           <t>AD8430404</t>
@@ -23542,7 +24079,11 @@
           <t>Boymurodova Shahnoza Shuxrat qizi</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A367</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
           <t>AE2896098</t>
@@ -23578,7 +24119,11 @@
           <t>Bozorova Aziza Ravshan qizi</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 375</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>AC2525492</t>
@@ -23758,7 +24303,11 @@
           <t>Ibodova Parvina Abdurashid qizi</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>25/26 sh/a 333</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
           <t>AD9606045</t>
@@ -23794,7 +24343,11 @@
           <t>Ibragimova Odina Azamat qizi</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25/26 sh/a 33</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>AD2497814</t>
@@ -23974,7 +24527,11 @@
           <t>Ochilova Gulnora Jurayevna</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>25/26 SH/A358</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
           <t>AD1137516</t>
@@ -24118,7 +24675,11 @@
           <t>Saidova Nozima Sanjar qizi</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A361</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
           <t>AD9178885</t>
@@ -24226,7 +24787,11 @@
           <t>Shovxiddinova Latofat Ruzimurod qizi</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 346</t>
+        </is>
+      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>AB7877734</t>
@@ -24262,7 +24827,11 @@
           <t>Sunnatillayeva E'zoza Jamshid qizi</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A365</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
           <t>AD4807056</t>
@@ -24331,7 +24900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -24815,30 +25384,28 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Turayeva Dilsuz Oybek qizi</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>268</v>
-      </c>
+          <t>Shermatova Gulsun Xurshid qizi</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>AE5053541</t>
+          <t>AE5836574</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>61205095590053</t>
+          <t>60802085590029</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>15.11.2025</t>
+          <t>13.01.2026</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>12.05.2009</t>
+          <t>08.02.2008</t>
         </is>
       </c>
     </row>
@@ -24853,30 +25420,30 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Turg'unova Jasmina Turg'un qizi</t>
+          <t>Turayeva Dilsuz Oybek qizi</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>122</v>
+        <v>268</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>AE6171425</t>
+          <t>AE5053541</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>62802085590087</t>
+          <t>61205095590053</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>03.02.2026</t>
+          <t>15.11.2025</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>12.05.2009</t>
         </is>
       </c>
     </row>
@@ -24891,28 +25458,66 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
+          <t>Turg'unova Jasmina Turg'un qizi</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>122</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>AE6171425</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>62802085590087</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>03.02.2026</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>28.02.2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>26-01</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
           <t>Ziyodullayeva Jasmina Alisher qizi</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D16" s="2" t="n">
         <v>233</v>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>AD9812146</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>61206075590076</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>13.12.2024</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>12.06.2007</t>
         </is>
@@ -30266,7 +30871,11 @@
           <t>Abdurahmonova Zebo Tolibovna</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 216</t>
+        </is>
+      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>AD3322083</t>
@@ -30302,7 +30911,11 @@
           <t>Amirova Shodiyona Xasan qizi</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 33</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
           <t>AD4080530</t>
@@ -30410,7 +31023,11 @@
           <t>Ibodullayeva Madina Baxtiyor qizi</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A 220</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>AC2114248</t>
@@ -30446,7 +31063,11 @@
           <t>Isomova Durdona Akram qizi</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>25/26 SH/A57</t>
+        </is>
+      </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
           <t>AB3313151</t>
@@ -30626,7 +31247,11 @@
           <t>Muratova Barno Jobur qizi</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 226</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>AD3205092</t>
@@ -30950,7 +31575,11 @@
           <t>Raxmatullayev Laziz Luqmon o'g'li</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>26/27 sh/a 235</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
           <t>AC0428854</t>
@@ -31094,7 +31723,11 @@
           <t>Shodiyev Ikromjon Eshpo'lat o'g'li</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A 239</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
           <t>AB5771325</t>
@@ -31166,7 +31799,11 @@
           <t>Turayeva Manzura Yorqin qizi</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 241</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
           <t>AD5352131</t>
@@ -32619,6 +33256,108 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>T/R</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Guruh</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>F.I.SH (Talaba)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Shartnoma №</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Pasport seriya va raqami</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>JSHSHIR (PINFL)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Pasport berilgan sanasi</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Tug'ilgan sanasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>26-07</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Ergasheva Madina Tulqin qizi</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>AC0429133</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>62501027890026</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>07.12.2018</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>25.01.2002</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -32766,7 +33505,11 @@
           <t>Husanova Rayxona Husan qizi</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 33</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>AD6361429</t>
@@ -33018,7 +33761,11 @@
           <t>Muxtorova Dilobar Alisher qizi</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A252</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
           <t>AA7820705</t>
@@ -33270,7 +34017,11 @@
           <t>Raxmatova Shaxlo Xolbobo qizi</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 259</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>AB6898531</t>
@@ -33378,7 +34129,11 @@
           <t>Shoimova Laziza Shavkat qizi</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>24/25 SH/A 41</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
           <t>AD5432156</t>
@@ -33624,7 +34379,11 @@
           <t>Abdullayeva Jasmina Xolbotir qizi</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A 268</t>
+        </is>
+      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>AD4515836</t>
@@ -33660,7 +34419,11 @@
           <t>Arziqulova Zahro Azamat qizi</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A269</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
           <t>AD2629636</t>
@@ -33768,7 +34531,11 @@
           <t>Boyeva Muxlisa Qurbonali qizi</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>25/26 sh/a 6</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>AA9487628</t>
@@ -33948,7 +34715,11 @@
           <t>Iskandarova Lobar Tura qizi</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>26/27 sh/a 277</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
           <t>AB6548815</t>
@@ -34200,7 +34971,11 @@
           <t>Nabiyeva Zebiniso Abdurahmonovna</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 285</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>AD4726446</t>
@@ -34236,7 +35011,11 @@
           <t>Nabiyeva Zebiniso Soyibjon qizi</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 285</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
           <t>AD2442920</t>
@@ -34272,7 +35051,11 @@
           <t>Nomozova Charos Shog'dor qizi</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 286</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
           <t>AD1098594</t>
@@ -34344,7 +35127,11 @@
           <t>Qurbonova Xolida Boynazar qizi</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 288</t>
+        </is>
+      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>AD4388600</t>
@@ -34590,7 +35377,11 @@
           <t>Buxorova Farangiz Tufli qizi</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 286</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
           <t>AC2285189</t>
@@ -34770,7 +35561,11 @@
           <t>Mirzayeva Sevara Ne'mat qizi</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 506</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>AD9179531</t>
@@ -34878,7 +35673,11 @@
           <t>Pulatova Zuhra Narzullo qizi</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A509</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
           <t>AD4157976</t>
@@ -34950,7 +35749,11 @@
           <t>Rashidova Shaxzoda Suyun qizi</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 511</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
           <t>AD6348784</t>
@@ -35310,7 +36113,11 @@
           <t>Yusupova Oygul Qurbonmurodovna</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 520</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
           <t>AD8393032</t>
@@ -35556,7 +36363,11 @@
           <t>Boltayeva Shaxlo Faxriddin qizi</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>25/26 sh/a 186</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>AD7256798</t>
@@ -35628,7 +36439,11 @@
           <t>Ibodullayeva Latofat Sayit qizi</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 116</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>AB4143080</t>
@@ -36024,7 +36839,11 @@
           <t>Sattorova Sevinch Otabek qizi</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A 327</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
           <t>AC2657133</t>
@@ -36702,7 +37521,11 @@
           <t>Qurbonaliyeva Nargiza Qahramon qizi</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 15</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>AD9458240</t>
@@ -36774,7 +37597,11 @@
           <t>Salomova Jasmina Azamat qizi</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 10</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>AD5993376</t>
@@ -37026,7 +37853,11 @@
           <t>Xalilova Zuhra Faxriddin qizi</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>25/26 SH/A84</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
           <t>AD9453010</t>
@@ -37272,7 +38103,11 @@
           <t>Abdullayeva Dildora A'zam qizi</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 26</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
           <t>AD9719700</t>
@@ -37344,7 +38179,11 @@
           <t>Baratova Mahzuna Hikmatullo qizi</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 28</t>
+        </is>
+      </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
           <t>AD2886528</t>
@@ -37416,7 +38255,11 @@
           <t>Ilhomova Gulasal Nodir qizi</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 107</t>
+        </is>
+      </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
           <t>AD9773960</t>
@@ -37704,7 +38547,11 @@
           <t>Shamsiddinova Fotima Ramziddin qizi</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A40</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
           <t>AD8728367</t>
@@ -38168,7 +39015,11 @@
           <t>Bozorova Marjona Sheraliyevna</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 140</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
           <t>AD9652361</t>
@@ -38204,7 +39055,11 @@
           <t>Djalolova Muslima Hamzaxon qizi</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25/26 SH/A149</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>AD5982247</t>
@@ -38384,7 +39239,11 @@
           <t>Isamova Mohimbegim Mansur qizi</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 142</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
           <t>AD9027768</t>
@@ -38420,7 +39279,11 @@
           <t>Mamadiyeva Afruza Muhiddin qizi</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25/26 SH/A150</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>AD1928284</t>
@@ -38744,7 +39607,11 @@
           <t>Tojiddinov Idrisbek Ozod o'g'li</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A66</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
           <t>AD9641356</t>

--- a/hisobotlar/rollar/1_Buxgalteriya_Shartnoma_va_Pasport.xlsx
+++ b/hisobotlar/rollar/1_Buxgalteriya_Shartnoma_va_Pasport.xlsx
@@ -27,7 +27,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guruh 26-04" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guruh 26-05" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guruh 26-06" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guruh 26-07" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -514,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H510"/>
+  <dimension ref="A1:H507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -13064,28 +13063,30 @@
       </c>
       <c r="C339" s="7" t="inlineStr">
         <is>
-          <t>Shermatova Gulsun Xurshid qizi</t>
-        </is>
-      </c>
-      <c r="D339" s="5" t="inlineStr"/>
+          <t>Turayeva Dilsuz Oybek qizi</t>
+        </is>
+      </c>
+      <c r="D339" s="5" t="n">
+        <v>268</v>
+      </c>
       <c r="E339" s="5" t="inlineStr">
         <is>
-          <t>AE5836574</t>
+          <t>AE5053541</t>
         </is>
       </c>
       <c r="F339" s="6" t="inlineStr">
         <is>
-          <t>60802085590029</t>
+          <t>61205095590053</t>
         </is>
       </c>
       <c r="G339" s="6" t="inlineStr">
         <is>
-          <t>13.01.2026</t>
+          <t>15.11.2025</t>
         </is>
       </c>
       <c r="H339" s="6" t="inlineStr">
         <is>
-          <t>08.02.2008</t>
+          <t>12.05.2009</t>
         </is>
       </c>
     </row>
@@ -13100,30 +13101,30 @@
       </c>
       <c r="C340" s="4" t="inlineStr">
         <is>
-          <t>Turayeva Dilsuz Oybek qizi</t>
+          <t>Turg'unova Jasmina Turg'un qizi</t>
         </is>
       </c>
       <c r="D340" s="2" t="n">
-        <v>268</v>
+        <v>122</v>
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>AE5053541</t>
+          <t>AE6171425</t>
         </is>
       </c>
       <c r="F340" s="3" t="inlineStr">
         <is>
-          <t>61205095590053</t>
+          <t>62802085590087</t>
         </is>
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>15.11.2025</t>
+          <t>03.02.2026</t>
         </is>
       </c>
       <c r="H340" s="3" t="inlineStr">
         <is>
-          <t>12.05.2009</t>
+          <t>28.02.2008</t>
         </is>
       </c>
     </row>
@@ -13138,30 +13139,30 @@
       </c>
       <c r="C341" s="7" t="inlineStr">
         <is>
-          <t>Turg'unova Jasmina Turg'un qizi</t>
+          <t>Ziyodullayeva Jasmina Alisher qizi</t>
         </is>
       </c>
       <c r="D341" s="5" t="n">
-        <v>122</v>
+        <v>233</v>
       </c>
       <c r="E341" s="5" t="inlineStr">
         <is>
-          <t>AE6171425</t>
+          <t>AD9812146</t>
         </is>
       </c>
       <c r="F341" s="6" t="inlineStr">
         <is>
-          <t>62802085590087</t>
+          <t>61206075590076</t>
         </is>
       </c>
       <c r="G341" s="6" t="inlineStr">
         <is>
-          <t>03.02.2026</t>
+          <t>13.12.2024</t>
         </is>
       </c>
       <c r="H341" s="6" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>12.06.2007</t>
         </is>
       </c>
     </row>
@@ -13171,35 +13172,35 @@
       </c>
       <c r="B342" s="3" t="inlineStr">
         <is>
-          <t>26-01</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C342" s="4" t="inlineStr">
         <is>
-          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+          <t>Alimova Sevinch Raxmiddin qizi</t>
         </is>
       </c>
       <c r="D342" s="2" t="n">
-        <v>233</v>
+        <v>312</v>
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>AD9812146</t>
+          <t>AB7974700</t>
         </is>
       </c>
       <c r="F342" s="3" t="inlineStr">
         <is>
-          <t>61206075590076</t>
+          <t>62707005740020</t>
         </is>
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>13.12.2024</t>
+          <t>27.10.2017</t>
         </is>
       </c>
       <c r="H342" s="3" t="inlineStr">
         <is>
-          <t>12.06.2007</t>
+          <t>27.07.2000</t>
         </is>
       </c>
     </row>
@@ -13214,30 +13215,30 @@
       </c>
       <c r="C343" s="7" t="inlineStr">
         <is>
-          <t>Alimova Sevinch Raxmiddin qizi</t>
+          <t>Berdiqulova Gulshan Rustam qizi</t>
         </is>
       </c>
       <c r="D343" s="5" t="n">
-        <v>312</v>
+        <v>239</v>
       </c>
       <c r="E343" s="5" t="inlineStr">
         <is>
-          <t>AB7974700</t>
+          <t>AE6702868</t>
         </is>
       </c>
       <c r="F343" s="6" t="inlineStr">
         <is>
-          <t>62707005740020</t>
+          <t>41001955590049</t>
         </is>
       </c>
       <c r="G343" s="6" t="inlineStr">
         <is>
-          <t>27.10.2017</t>
+          <t>16.03.2026</t>
         </is>
       </c>
       <c r="H343" s="6" t="inlineStr">
         <is>
-          <t>27.07.2000</t>
+          <t>10.01.1995</t>
         </is>
       </c>
     </row>
@@ -13252,30 +13253,30 @@
       </c>
       <c r="C344" s="4" t="inlineStr">
         <is>
-          <t>Berdiqulova Gulshan Rustam qizi</t>
+          <t>Eshmurotova Charos Bekqul qizi</t>
         </is>
       </c>
       <c r="D344" s="2" t="n">
-        <v>239</v>
+        <v>110</v>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>AE6702868</t>
+          <t>AE5720760</t>
         </is>
       </c>
       <c r="F344" s="3" t="inlineStr">
         <is>
-          <t>41001955590049</t>
+          <t>61901085720047</t>
         </is>
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>16.03.2026</t>
+          <t>07.01.2026</t>
         </is>
       </c>
       <c r="H344" s="3" t="inlineStr">
         <is>
-          <t>10.01.1995</t>
+          <t>19.01.2008</t>
         </is>
       </c>
     </row>
@@ -13290,30 +13291,30 @@
       </c>
       <c r="C345" s="7" t="inlineStr">
         <is>
-          <t>Eshmurotova Charos Bekqul qizi</t>
+          <t>G'aybullayeva Ruxsora Xusniddin qizi</t>
         </is>
       </c>
       <c r="D345" s="5" t="n">
-        <v>110</v>
+        <v>236</v>
       </c>
       <c r="E345" s="5" t="inlineStr">
         <is>
-          <t>AE5720760</t>
+          <t>AD8701218</t>
         </is>
       </c>
       <c r="F345" s="6" t="inlineStr">
         <is>
-          <t>61901085720047</t>
+          <t>61206085590028</t>
         </is>
       </c>
       <c r="G345" s="6" t="inlineStr">
         <is>
-          <t>07.01.2026</t>
+          <t>20.09.2024</t>
         </is>
       </c>
       <c r="H345" s="6" t="inlineStr">
         <is>
-          <t>19.01.2008</t>
+          <t>12.06.2008</t>
         </is>
       </c>
     </row>
@@ -13328,30 +13329,30 @@
       </c>
       <c r="C346" s="4" t="inlineStr">
         <is>
-          <t>G'aybullayeva Ruxsora Xusniddin qizi</t>
+          <t>Hamroqulova Farzona Odilovna</t>
         </is>
       </c>
       <c r="D346" s="2" t="n">
-        <v>236</v>
+        <v>278</v>
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>AD8701218</t>
+          <t>AE4371486</t>
         </is>
       </c>
       <c r="F346" s="3" t="inlineStr">
         <is>
-          <t>61206085590028</t>
+          <t>62111085680033</t>
         </is>
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>20.09.2024</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="H346" s="3" t="inlineStr">
         <is>
-          <t>12.06.2008</t>
+          <t>21.11.2008</t>
         </is>
       </c>
     </row>
@@ -13366,30 +13367,30 @@
       </c>
       <c r="C347" s="7" t="inlineStr">
         <is>
-          <t>Hamroqulova Farzona Odilovna</t>
+          <t>Hasanova Dilnura Eson qizi</t>
         </is>
       </c>
       <c r="D347" s="5" t="n">
-        <v>278</v>
+        <v>166</v>
       </c>
       <c r="E347" s="5" t="inlineStr">
         <is>
-          <t>AE4371486</t>
+          <t>AE3555106</t>
         </is>
       </c>
       <c r="F347" s="6" t="inlineStr">
         <is>
-          <t>62111085680033</t>
+          <t>61508085680038</t>
         </is>
       </c>
       <c r="G347" s="6" t="inlineStr">
         <is>
-          <t>27.09.2025</t>
+          <t>29.07.2025</t>
         </is>
       </c>
       <c r="H347" s="6" t="inlineStr">
         <is>
-          <t>21.11.2008</t>
+          <t>15.08.2008</t>
         </is>
       </c>
     </row>
@@ -13404,30 +13405,30 @@
       </c>
       <c r="C348" s="4" t="inlineStr">
         <is>
-          <t>Hasanova Dilnura Eson qizi</t>
+          <t>Hasanova Marjona Xolmurod qizi</t>
         </is>
       </c>
       <c r="D348" s="2" t="n">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>AE3555106</t>
+          <t>AE5685784</t>
         </is>
       </c>
       <c r="F348" s="3" t="inlineStr">
         <is>
-          <t>61508085680038</t>
+          <t>60411085680047</t>
         </is>
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>29.07.2025</t>
+          <t>06.01.2026</t>
         </is>
       </c>
       <c r="H348" s="3" t="inlineStr">
         <is>
-          <t>15.08.2008</t>
+          <t>04.11.2008</t>
         </is>
       </c>
     </row>
@@ -13442,30 +13443,30 @@
       </c>
       <c r="C349" s="7" t="inlineStr">
         <is>
-          <t>Hasanova Marjona Xolmurod qizi</t>
+          <t>Ilhomova Zuhra Davron qizi</t>
         </is>
       </c>
       <c r="D349" s="5" t="n">
-        <v>192</v>
+        <v>294</v>
       </c>
       <c r="E349" s="5" t="inlineStr">
         <is>
-          <t>AE5685784</t>
+          <t>AE4378923</t>
         </is>
       </c>
       <c r="F349" s="6" t="inlineStr">
         <is>
-          <t>60411085680047</t>
+          <t>63110085590015</t>
         </is>
       </c>
       <c r="G349" s="6" t="inlineStr">
         <is>
-          <t>06.01.2026</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="H349" s="6" t="inlineStr">
         <is>
-          <t>04.11.2008</t>
+          <t>31.10.2008</t>
         </is>
       </c>
     </row>
@@ -13480,30 +13481,30 @@
       </c>
       <c r="C350" s="4" t="inlineStr">
         <is>
-          <t>Ilhomova Zuhra Davron qizi</t>
+          <t>Islomova Nilufar Abdulxafiz qizi</t>
         </is>
       </c>
       <c r="D350" s="2" t="n">
-        <v>294</v>
+        <v>94</v>
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>AE4378923</t>
+          <t>AD9664280</t>
         </is>
       </c>
       <c r="F350" s="3" t="inlineStr">
         <is>
-          <t>63110085590015</t>
+          <t>61911085590104</t>
         </is>
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>03.12.2024</t>
         </is>
       </c>
       <c r="H350" s="3" t="inlineStr">
         <is>
-          <t>31.10.2008</t>
+          <t>19.11.2008</t>
         </is>
       </c>
     </row>
@@ -13518,30 +13519,30 @@
       </c>
       <c r="C351" s="7" t="inlineStr">
         <is>
-          <t>Islomova Nilufar Abdulxafiz qizi</t>
+          <t>Jalolova Rayxona Akmal qizi</t>
         </is>
       </c>
       <c r="D351" s="5" t="n">
-        <v>94</v>
+        <v>262</v>
       </c>
       <c r="E351" s="5" t="inlineStr">
         <is>
-          <t>AD9664280</t>
+          <t>AE3492384</t>
         </is>
       </c>
       <c r="F351" s="6" t="inlineStr">
         <is>
-          <t>61911085590104</t>
+          <t>62207085680059</t>
         </is>
       </c>
       <c r="G351" s="6" t="inlineStr">
         <is>
-          <t>03.12.2024</t>
+          <t>23.07.2025</t>
         </is>
       </c>
       <c r="H351" s="6" t="inlineStr">
         <is>
-          <t>19.11.2008</t>
+          <t>22.07.2008</t>
         </is>
       </c>
     </row>
@@ -13556,30 +13557,30 @@
       </c>
       <c r="C352" s="4" t="inlineStr">
         <is>
-          <t>Jalolova Rayxona Akmal qizi</t>
+          <t>Javliyeva Nargiza Ortiq qizi</t>
         </is>
       </c>
       <c r="D352" s="2" t="n">
-        <v>262</v>
+        <v>173</v>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>AE3492384</t>
+          <t>AE5222372</t>
         </is>
       </c>
       <c r="F352" s="3" t="inlineStr">
         <is>
-          <t>62207085680059</t>
+          <t>62401095680012</t>
         </is>
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>23.07.2025</t>
+          <t>28.11.2025</t>
         </is>
       </c>
       <c r="H352" s="3" t="inlineStr">
         <is>
-          <t>22.07.2008</t>
+          <t>24.01.2009</t>
         </is>
       </c>
     </row>
@@ -13594,30 +13595,30 @@
       </c>
       <c r="C353" s="7" t="inlineStr">
         <is>
-          <t>Javliyeva Nargiza Ortiq qizi</t>
+          <t>Maxmashoxova Feruza Bekmurod qizi</t>
         </is>
       </c>
       <c r="D353" s="5" t="n">
-        <v>173</v>
+        <v>101</v>
       </c>
       <c r="E353" s="5" t="inlineStr">
         <is>
-          <t>AE5222372</t>
+          <t>AE5088010</t>
         </is>
       </c>
       <c r="F353" s="6" t="inlineStr">
         <is>
-          <t>62401095680012</t>
+          <t>60201085630050</t>
         </is>
       </c>
       <c r="G353" s="6" t="inlineStr">
         <is>
-          <t>28.11.2025</t>
+          <t>18.11.2025</t>
         </is>
       </c>
       <c r="H353" s="6" t="inlineStr">
         <is>
-          <t>24.01.2009</t>
+          <t>02.01.2008</t>
         </is>
       </c>
     </row>
@@ -13632,30 +13633,30 @@
       </c>
       <c r="C354" s="4" t="inlineStr">
         <is>
-          <t>Maxmashoxova Feruza Bekmurod qizi</t>
+          <t>Meyliqulova Hilola Farhod qizi</t>
         </is>
       </c>
       <c r="D354" s="2" t="n">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>AE5088010</t>
+          <t>AB7137876</t>
         </is>
       </c>
       <c r="F354" s="3" t="inlineStr">
         <is>
-          <t>60201085630050</t>
+          <t>61202005680055</t>
         </is>
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>18.11.2025</t>
+          <t>07.07.2017</t>
         </is>
       </c>
       <c r="H354" s="3" t="inlineStr">
         <is>
-          <t>02.01.2008</t>
+          <t>12.02.2000</t>
         </is>
       </c>
     </row>
@@ -13670,30 +13671,30 @@
       </c>
       <c r="C355" s="7" t="inlineStr">
         <is>
-          <t>Meyliqulova Hilola Farhod qizi</t>
+          <t>Nu'monova Saidabonu Ulug'bek qizi</t>
         </is>
       </c>
       <c r="D355" s="5" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="E355" s="5" t="inlineStr">
         <is>
-          <t>AB7137876</t>
+          <t>AE1067914</t>
         </is>
       </c>
       <c r="F355" s="6" t="inlineStr">
         <is>
-          <t>61202005680055</t>
+          <t>62410085590084</t>
         </is>
       </c>
       <c r="G355" s="6" t="inlineStr">
         <is>
-          <t>07.07.2017</t>
+          <t>07.01.2025</t>
         </is>
       </c>
       <c r="H355" s="6" t="inlineStr">
         <is>
-          <t>12.02.2000</t>
+          <t>24.10.2008</t>
         </is>
       </c>
     </row>
@@ -13708,30 +13709,30 @@
       </c>
       <c r="C356" s="4" t="inlineStr">
         <is>
-          <t>Nu'monova Saidabonu Ulug'bek qizi</t>
+          <t>Nurillayeva Dilsuz Mashrabovna</t>
         </is>
       </c>
       <c r="D356" s="2" t="n">
-        <v>38</v>
+        <v>326</v>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>AE1067914</t>
+          <t>AD4774693</t>
         </is>
       </c>
       <c r="F356" s="3" t="inlineStr">
         <is>
-          <t>62410085590084</t>
+          <t>42506912640010</t>
         </is>
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>05.10.2023</t>
         </is>
       </c>
       <c r="H356" s="3" t="inlineStr">
         <is>
-          <t>24.10.2008</t>
+          <t>25.06.1991</t>
         </is>
       </c>
     </row>
@@ -13746,30 +13747,30 @@
       </c>
       <c r="C357" s="7" t="inlineStr">
         <is>
-          <t>Nurillayeva Dilsuz Mashrabovna</t>
+          <t>Ochildiyeva Dinora Otabek qizi</t>
         </is>
       </c>
       <c r="D357" s="5" t="n">
-        <v>326</v>
+        <v>87</v>
       </c>
       <c r="E357" s="5" t="inlineStr">
         <is>
-          <t>AD4774693</t>
+          <t>AE4084333</t>
         </is>
       </c>
       <c r="F357" s="6" t="inlineStr">
         <is>
-          <t>42506912640010</t>
+          <t>62012085590055</t>
         </is>
       </c>
       <c r="G357" s="6" t="inlineStr">
         <is>
-          <t>05.10.2023</t>
+          <t>08.09.2025</t>
         </is>
       </c>
       <c r="H357" s="6" t="inlineStr">
         <is>
-          <t>25.06.1991</t>
+          <t>20.12.2008</t>
         </is>
       </c>
     </row>
@@ -13784,30 +13785,28 @@
       </c>
       <c r="C358" s="4" t="inlineStr">
         <is>
-          <t>Ochildiyeva Dinora Otabek qizi</t>
-        </is>
-      </c>
-      <c r="D358" s="2" t="n">
-        <v>87</v>
-      </c>
+          <t>Qulmatova Shabbona Azamat qizi</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="inlineStr"/>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>AE4084333</t>
+          <t>AE4905104</t>
         </is>
       </c>
       <c r="F358" s="3" t="inlineStr">
         <is>
-          <t>62012085590055</t>
+          <t>61008085680019</t>
         </is>
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>08.09.2025</t>
+          <t>05.11.2025</t>
         </is>
       </c>
       <c r="H358" s="3" t="inlineStr">
         <is>
-          <t>20.12.2008</t>
+          <t>10.08.2008</t>
         </is>
       </c>
     </row>
@@ -13822,28 +13821,30 @@
       </c>
       <c r="C359" s="7" t="inlineStr">
         <is>
-          <t>Qulmatova Shabbona Azamat qizi</t>
-        </is>
-      </c>
-      <c r="D359" s="5" t="inlineStr"/>
+          <t>Quysinova Rohshona To'lqin qizi</t>
+        </is>
+      </c>
+      <c r="D359" s="5" t="n">
+        <v>242</v>
+      </c>
       <c r="E359" s="5" t="inlineStr">
         <is>
-          <t>AE4905104</t>
+          <t>AE7231113</t>
         </is>
       </c>
       <c r="F359" s="6" t="inlineStr">
         <is>
-          <t>61008085680019</t>
+          <t>60406055720067</t>
         </is>
       </c>
       <c r="G359" s="6" t="inlineStr">
         <is>
-          <t>05.11.2025</t>
+          <t>01.05.2026</t>
         </is>
       </c>
       <c r="H359" s="6" t="inlineStr">
         <is>
-          <t>10.08.2008</t>
+          <t>04.06.2005</t>
         </is>
       </c>
     </row>
@@ -13858,30 +13859,30 @@
       </c>
       <c r="C360" s="4" t="inlineStr">
         <is>
-          <t>Quysinova Rohshona To'lqin qizi</t>
+          <t>Ro'zimurodova Larisa Ma'matali qizi</t>
         </is>
       </c>
       <c r="D360" s="2" t="n">
-        <v>242</v>
+        <v>100</v>
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>AE7231113</t>
+          <t>AE5324961</t>
         </is>
       </c>
       <c r="F360" s="3" t="inlineStr">
         <is>
-          <t>60406055720067</t>
+          <t>61608085630072</t>
         </is>
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>01.05.2026</t>
+          <t>05.12.2025</t>
         </is>
       </c>
       <c r="H360" s="3" t="inlineStr">
         <is>
-          <t>04.06.2005</t>
+          <t>16.08.2008</t>
         </is>
       </c>
     </row>
@@ -13896,30 +13897,30 @@
       </c>
       <c r="C361" s="7" t="inlineStr">
         <is>
-          <t>Ro'zimurodova Larisa Ma'matali qizi</t>
+          <t>Samadova Nigora Abdisamiyevna</t>
         </is>
       </c>
       <c r="D361" s="5" t="n">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="E361" s="5" t="inlineStr">
         <is>
-          <t>AE5324961</t>
+          <t>AE1836076</t>
         </is>
       </c>
       <c r="F361" s="6" t="inlineStr">
         <is>
-          <t>61608085630072</t>
+          <t>40710895590044</t>
         </is>
       </c>
       <c r="G361" s="6" t="inlineStr">
         <is>
-          <t>05.12.2025</t>
+          <t>05.03.2025</t>
         </is>
       </c>
       <c r="H361" s="6" t="inlineStr">
         <is>
-          <t>16.08.2008</t>
+          <t>07.10.1989</t>
         </is>
       </c>
     </row>
@@ -13934,30 +13935,30 @@
       </c>
       <c r="C362" s="4" t="inlineStr">
         <is>
-          <t>Samadova Nigora Abdisamiyevna</t>
+          <t>Samatova Oydin Sulaymon qizi</t>
         </is>
       </c>
       <c r="D362" s="2" t="n">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>AE1836076</t>
+          <t>AD8980430</t>
         </is>
       </c>
       <c r="F362" s="3" t="inlineStr">
         <is>
-          <t>40710895590044</t>
+          <t>42910905720012</t>
         </is>
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>05.03.2025</t>
+          <t>11.10.2024</t>
         </is>
       </c>
       <c r="H362" s="3" t="inlineStr">
         <is>
-          <t>07.10.1989</t>
+          <t>29.10.1990</t>
         </is>
       </c>
     </row>
@@ -13972,30 +13973,30 @@
       </c>
       <c r="C363" s="7" t="inlineStr">
         <is>
-          <t>Samatova Oydin Sulaymon qizi</t>
+          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
         </is>
       </c>
       <c r="D363" s="5" t="n">
-        <v>146</v>
+        <v>74</v>
       </c>
       <c r="E363" s="5" t="inlineStr">
         <is>
-          <t>AD8980430</t>
+          <t>AE3352294</t>
         </is>
       </c>
       <c r="F363" s="6" t="inlineStr">
         <is>
-          <t>42910905720012</t>
+          <t>61807085590034</t>
         </is>
       </c>
       <c r="G363" s="6" t="inlineStr">
         <is>
-          <t>11.10.2024</t>
+          <t>10.07.2025</t>
         </is>
       </c>
       <c r="H363" s="6" t="inlineStr">
         <is>
-          <t>29.10.1990</t>
+          <t>18.07.2008</t>
         </is>
       </c>
     </row>
@@ -14010,30 +14011,28 @@
       </c>
       <c r="C364" s="4" t="inlineStr">
         <is>
-          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
-        </is>
-      </c>
-      <c r="D364" s="2" t="n">
-        <v>74</v>
-      </c>
+          <t>Shonazarova Vazira Botir qizi</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="inlineStr"/>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>AE3352294</t>
+          <t>AE 4233482</t>
         </is>
       </c>
       <c r="F364" s="3" t="inlineStr">
         <is>
-          <t>61807085590034</t>
+          <t>61311085680032</t>
         </is>
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>10.07.2025</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="H364" s="3" t="inlineStr">
         <is>
-          <t>18.07.2008</t>
+          <t>13.11.2008</t>
         </is>
       </c>
     </row>
@@ -14048,28 +14047,30 @@
       </c>
       <c r="C365" s="7" t="inlineStr">
         <is>
-          <t>Shonazarova Vazira Botir qizi</t>
-        </is>
-      </c>
-      <c r="D365" s="5" t="inlineStr"/>
+          <t>Shukriyeva Nariye Redvanovna</t>
+        </is>
+      </c>
+      <c r="D365" s="5" t="n">
+        <v>162</v>
+      </c>
       <c r="E365" s="5" t="inlineStr">
         <is>
-          <t>AE 4233482</t>
+          <t>AD7767171</t>
         </is>
       </c>
       <c r="F365" s="6" t="inlineStr">
         <is>
-          <t>61311085680032</t>
+          <t>62103085590038</t>
         </is>
       </c>
       <c r="G365" s="6" t="inlineStr">
         <is>
-          <t>17.09.2025</t>
+          <t>06.07.2024</t>
         </is>
       </c>
       <c r="H365" s="6" t="inlineStr">
         <is>
-          <t>13.11.2008</t>
+          <t>21.03.2008</t>
         </is>
       </c>
     </row>
@@ -14084,30 +14085,30 @@
       </c>
       <c r="C366" s="4" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="D366" s="2" t="n">
-        <v>162</v>
+        <v>122</v>
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>AD7767171</t>
+          <t>AB7166586</t>
         </is>
       </c>
       <c r="F366" s="3" t="inlineStr">
         <is>
-          <t>62103085590038</t>
+          <t>61409005680027</t>
         </is>
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>06.07.2024</t>
+          <t>09.07.2017</t>
         </is>
       </c>
       <c r="H366" s="3" t="inlineStr">
         <is>
-          <t>21.03.2008</t>
+          <t>14.09.2000</t>
         </is>
       </c>
     </row>
@@ -14122,30 +14123,30 @@
       </c>
       <c r="C367" s="7" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="D367" s="5" t="n">
-        <v>122</v>
+        <v>6</v>
       </c>
       <c r="E367" s="5" t="inlineStr">
         <is>
-          <t>AB7166586</t>
+          <t>AE3558477</t>
         </is>
       </c>
       <c r="F367" s="6" t="inlineStr">
         <is>
-          <t>61409005680027</t>
+          <t>62709085590070</t>
         </is>
       </c>
       <c r="G367" s="6" t="inlineStr">
         <is>
-          <t>09.07.2017</t>
+          <t>29.07.2025</t>
         </is>
       </c>
       <c r="H367" s="6" t="inlineStr">
         <is>
-          <t>14.09.2000</t>
+          <t>27.09.2008</t>
         </is>
       </c>
     </row>
@@ -14160,30 +14161,30 @@
       </c>
       <c r="C368" s="4" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
       <c r="D368" s="2" t="n">
-        <v>6</v>
+        <v>161</v>
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
-          <t>AE3558477</t>
+          <t>AE5199773</t>
         </is>
       </c>
       <c r="F368" s="3" t="inlineStr">
         <is>
-          <t>62709085590070</t>
+          <t>61906085680012</t>
         </is>
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>29.07.2025</t>
+          <t>26.11.2025</t>
         </is>
       </c>
       <c r="H368" s="3" t="inlineStr">
         <is>
-          <t>27.09.2008</t>
+          <t>19.06.2008</t>
         </is>
       </c>
     </row>
@@ -14198,30 +14199,30 @@
       </c>
       <c r="C369" s="7" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona Nazim qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="D369" s="5" t="n">
-        <v>161</v>
+        <v>11</v>
       </c>
       <c r="E369" s="5" t="inlineStr">
         <is>
-          <t>AE5199773</t>
+          <t>AD4186169</t>
         </is>
       </c>
       <c r="F369" s="6" t="inlineStr">
         <is>
-          <t>61906085680012</t>
+          <t>40404975650046</t>
         </is>
       </c>
       <c r="G369" s="6" t="inlineStr">
         <is>
-          <t>26.11.2025</t>
+          <t>07.08.2023</t>
         </is>
       </c>
       <c r="H369" s="6" t="inlineStr">
         <is>
-          <t>19.06.2008</t>
+          <t>04.04.1997</t>
         </is>
       </c>
     </row>
@@ -14236,30 +14237,30 @@
       </c>
       <c r="C370" s="4" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="D370" s="2" t="n">
-        <v>11</v>
+        <v>220</v>
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>AD4186169</t>
+          <t>AE4503488</t>
         </is>
       </c>
       <c r="F370" s="3" t="inlineStr">
         <is>
-          <t>40404975650046</t>
+          <t>51106085680031</t>
         </is>
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>07.08.2023</t>
+          <t>07.10.2025</t>
         </is>
       </c>
       <c r="H370" s="3" t="inlineStr">
         <is>
-          <t>04.04.1997</t>
+          <t>11.06.2008</t>
         </is>
       </c>
     </row>
@@ -14274,30 +14275,30 @@
       </c>
       <c r="C371" s="7" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="D371" s="5" t="n">
-        <v>220</v>
+        <v>79</v>
       </c>
       <c r="E371" s="5" t="inlineStr">
         <is>
-          <t>AE4503488</t>
+          <t>AE5293914</t>
         </is>
       </c>
       <c r="F371" s="6" t="inlineStr">
         <is>
-          <t>51106085680031</t>
+          <t>60512085590078</t>
         </is>
       </c>
       <c r="G371" s="6" t="inlineStr">
         <is>
-          <t>07.10.2025</t>
+          <t>04.12.2025</t>
         </is>
       </c>
       <c r="H371" s="6" t="inlineStr">
         <is>
-          <t>11.06.2008</t>
+          <t>05.12.2008</t>
         </is>
       </c>
     </row>
@@ -14312,30 +14313,30 @@
       </c>
       <c r="C372" s="4" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="D372" s="2" t="n">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>AE5293914</t>
+          <t>AE4989343</t>
         </is>
       </c>
       <c r="F372" s="3" t="inlineStr">
         <is>
-          <t>60512085590078</t>
+          <t>60402095590060</t>
         </is>
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>04.12.2025</t>
+          <t>11.11.2025</t>
         </is>
       </c>
       <c r="H372" s="3" t="inlineStr">
         <is>
-          <t>05.12.2008</t>
+          <t>04.02.2009</t>
         </is>
       </c>
     </row>
@@ -14350,30 +14351,30 @@
       </c>
       <c r="C373" s="7" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="D373" s="5" t="n">
-        <v>148</v>
+        <v>279</v>
       </c>
       <c r="E373" s="5" t="inlineStr">
         <is>
-          <t>AE4989343</t>
+          <t>AE7821304</t>
         </is>
       </c>
       <c r="F373" s="6" t="inlineStr">
         <is>
-          <t>60402095590060</t>
+          <t>41406985680067</t>
         </is>
       </c>
       <c r="G373" s="6" t="inlineStr">
         <is>
-          <t>11.11.2025</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="H373" s="6" t="inlineStr">
         <is>
-          <t>04.02.2009</t>
+          <t>14.06.1998</t>
         </is>
       </c>
     </row>
@@ -14388,30 +14389,30 @@
       </c>
       <c r="C374" s="4" t="inlineStr">
         <is>
-          <t>Usmanova Iroda Abdurazzoq qizi</t>
+          <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
       <c r="D374" s="2" t="n">
-        <v>279</v>
+        <v>2</v>
       </c>
       <c r="E374" s="2" t="inlineStr">
         <is>
-          <t>AE7821304</t>
+          <t>AC1967100</t>
         </is>
       </c>
       <c r="F374" s="3" t="inlineStr">
         <is>
-          <t>41406985680067</t>
+          <t>62704025590042</t>
         </is>
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>12.06.2019</t>
         </is>
       </c>
       <c r="H374" s="3" t="inlineStr">
         <is>
-          <t>14.06.1998</t>
+          <t>27.04.2002</t>
         </is>
       </c>
     </row>
@@ -14426,30 +14427,30 @@
       </c>
       <c r="C375" s="7" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="D375" s="5" t="n">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="E375" s="5" t="inlineStr">
         <is>
-          <t>AC1967100</t>
+          <t>AB9239333</t>
         </is>
       </c>
       <c r="F375" s="6" t="inlineStr">
         <is>
-          <t>62704025590042</t>
+          <t>42207935680042</t>
         </is>
       </c>
       <c r="G375" s="6" t="inlineStr">
         <is>
-          <t>12.06.2019</t>
+          <t>09.04.2018</t>
         </is>
       </c>
       <c r="H375" s="6" t="inlineStr">
         <is>
-          <t>27.04.2002</t>
+          <t>22.07.1993</t>
         </is>
       </c>
     </row>
@@ -14459,35 +14460,35 @@
       </c>
       <c r="B376" s="3" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C376" s="4" t="inlineStr">
         <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
+          <t>Aliqulova Shaxzoda Anvar qizi</t>
         </is>
       </c>
       <c r="D376" s="2" t="n">
-        <v>75</v>
+        <v>272</v>
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
-          <t>AB9239333</t>
+          <t>AC1827958</t>
         </is>
       </c>
       <c r="F376" s="3" t="inlineStr">
         <is>
-          <t>42207935680042</t>
+          <t>60301037890018</t>
         </is>
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>09.04.2018</t>
+          <t>18.04.2019</t>
         </is>
       </c>
       <c r="H376" s="3" t="inlineStr">
         <is>
-          <t>22.07.1993</t>
+          <t>03.01.2003</t>
         </is>
       </c>
     </row>
@@ -14502,30 +14503,30 @@
       </c>
       <c r="C377" s="7" t="inlineStr">
         <is>
-          <t>Aliqulova Shaxzoda Anvar qizi</t>
+          <t>Arziqulova Laylo Bahodir qizi</t>
         </is>
       </c>
       <c r="D377" s="5" t="n">
-        <v>272</v>
+        <v>79</v>
       </c>
       <c r="E377" s="5" t="inlineStr">
         <is>
-          <t>AC1827958</t>
+          <t>AD8548125</t>
         </is>
       </c>
       <c r="F377" s="6" t="inlineStr">
         <is>
-          <t>60301037890018</t>
+          <t>60110065720109</t>
         </is>
       </c>
       <c r="G377" s="6" t="inlineStr">
         <is>
-          <t>18.04.2019</t>
+          <t>09.09.2024</t>
         </is>
       </c>
       <c r="H377" s="6" t="inlineStr">
         <is>
-          <t>03.01.2003</t>
+          <t>01.10.2006</t>
         </is>
       </c>
     </row>
@@ -14540,30 +14541,30 @@
       </c>
       <c r="C378" s="4" t="inlineStr">
         <is>
-          <t>Arziqulova Laylo Bahodir qizi</t>
+          <t>Eshnazarova Dilnoza Rustam qizi</t>
         </is>
       </c>
       <c r="D378" s="2" t="n">
-        <v>79</v>
+        <v>221</v>
       </c>
       <c r="E378" s="2" t="inlineStr">
         <is>
-          <t>AD8548125</t>
+          <t>AE3321050</t>
         </is>
       </c>
       <c r="F378" s="3" t="inlineStr">
         <is>
-          <t>60110065720109</t>
+          <t>60710085730098</t>
         </is>
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>09.09.2024</t>
+          <t>08.07.2025</t>
         </is>
       </c>
       <c r="H378" s="3" t="inlineStr">
         <is>
-          <t>01.10.2006</t>
+          <t>07.10.2008</t>
         </is>
       </c>
     </row>
@@ -14578,30 +14579,30 @@
       </c>
       <c r="C379" s="7" t="inlineStr">
         <is>
-          <t>Eshnazarova Dilnoza Rustam qizi</t>
+          <t>Fayzullayeva Sarvinoz Sherbobo qizi</t>
         </is>
       </c>
       <c r="D379" s="5" t="n">
-        <v>221</v>
+        <v>152</v>
       </c>
       <c r="E379" s="5" t="inlineStr">
         <is>
-          <t>AE3321050</t>
+          <t>AD1189588</t>
         </is>
       </c>
       <c r="F379" s="6" t="inlineStr">
         <is>
-          <t>60710085730098</t>
+          <t>63003055730053</t>
         </is>
       </c>
       <c r="G379" s="6" t="inlineStr">
         <is>
-          <t>08.07.2025</t>
+          <t>24.03.2022</t>
         </is>
       </c>
       <c r="H379" s="6" t="inlineStr">
         <is>
-          <t>07.10.2008</t>
+          <t>30.03.2005</t>
         </is>
       </c>
     </row>
@@ -14616,30 +14617,30 @@
       </c>
       <c r="C380" s="4" t="inlineStr">
         <is>
-          <t>Fayzullayeva Sarvinoz Sherbobo qizi</t>
+          <t>Ibragimova Gulnoza Isroil qizi</t>
         </is>
       </c>
       <c r="D380" s="2" t="n">
-        <v>152</v>
+        <v>308</v>
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
-          <t>AD1189588</t>
+          <t>AE4115057</t>
         </is>
       </c>
       <c r="F380" s="3" t="inlineStr">
         <is>
-          <t>63003055730053</t>
+          <t>60606085680085</t>
         </is>
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>24.03.2022</t>
+          <t>09.09.2025</t>
         </is>
       </c>
       <c r="H380" s="3" t="inlineStr">
         <is>
-          <t>30.03.2005</t>
+          <t>06.06.2008</t>
         </is>
       </c>
     </row>
@@ -14654,30 +14655,30 @@
       </c>
       <c r="C381" s="7" t="inlineStr">
         <is>
-          <t>Ibragimova Gulnoza Isroil qizi</t>
+          <t>Izzatulloyeva Vazira G'ayratzoda</t>
         </is>
       </c>
       <c r="D381" s="5" t="n">
-        <v>308</v>
+        <v>383</v>
       </c>
       <c r="E381" s="5" t="inlineStr">
         <is>
-          <t>AE4115057</t>
+          <t>AE5671026</t>
         </is>
       </c>
       <c r="F381" s="6" t="inlineStr">
         <is>
-          <t>60606085680085</t>
+          <t>42004975680094</t>
         </is>
       </c>
       <c r="G381" s="6" t="inlineStr">
         <is>
-          <t>09.09.2025</t>
+          <t>05.01.2026</t>
         </is>
       </c>
       <c r="H381" s="6" t="inlineStr">
         <is>
-          <t>06.06.2008</t>
+          <t>20.04.1997</t>
         </is>
       </c>
     </row>
@@ -14692,30 +14693,30 @@
       </c>
       <c r="C382" s="4" t="inlineStr">
         <is>
-          <t>Izzatulloyeva Vazira G'ayratzoda</t>
+          <t>Jurayeva Dilnoz G'oibnazarovna</t>
         </is>
       </c>
       <c r="D382" s="2" t="n">
-        <v>383</v>
+        <v>89</v>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>AE5671026</t>
+          <t>AD2957442</t>
         </is>
       </c>
       <c r="F382" s="3" t="inlineStr">
         <is>
-          <t>42004975680094</t>
+          <t>40305922560019</t>
         </is>
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>05.01.2026</t>
+          <t>05.04.2023</t>
         </is>
       </c>
       <c r="H382" s="3" t="inlineStr">
         <is>
-          <t>20.04.1997</t>
+          <t>03.05.1992</t>
         </is>
       </c>
     </row>
@@ -14730,30 +14731,30 @@
       </c>
       <c r="C383" s="7" t="inlineStr">
         <is>
-          <t>Jurayeva Dilnoz G'oibnazarovna</t>
+          <t>Mansurova Gulasal Musurmon qizi</t>
         </is>
       </c>
       <c r="D383" s="5" t="n">
-        <v>89</v>
+        <v>301</v>
       </c>
       <c r="E383" s="5" t="inlineStr">
         <is>
-          <t>AD2957442</t>
+          <t>AE4483600</t>
         </is>
       </c>
       <c r="F383" s="6" t="inlineStr">
         <is>
-          <t>40305922560019</t>
+          <t>62905085680067</t>
         </is>
       </c>
       <c r="G383" s="6" t="inlineStr">
         <is>
-          <t>05.04.2023</t>
+          <t>06.10.2025</t>
         </is>
       </c>
       <c r="H383" s="6" t="inlineStr">
         <is>
-          <t>03.05.1992</t>
+          <t>29.05.2008</t>
         </is>
       </c>
     </row>
@@ -14768,30 +14769,30 @@
       </c>
       <c r="C384" s="4" t="inlineStr">
         <is>
-          <t>Mansurova Gulasal Musurmon qizi</t>
+          <t>Murtazayeva Kamola Jamoliddin qizi</t>
         </is>
       </c>
       <c r="D384" s="2" t="n">
-        <v>301</v>
+        <v>25</v>
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>AE4483600</t>
+          <t>AC1458884</t>
         </is>
       </c>
       <c r="F384" s="3" t="inlineStr">
         <is>
-          <t>62905085680067</t>
+          <t>42708915590028</t>
         </is>
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>06.10.2025</t>
+          <t>04.11.2018</t>
         </is>
       </c>
       <c r="H384" s="3" t="inlineStr">
         <is>
-          <t>29.05.2008</t>
+          <t>27.08.1991</t>
         </is>
       </c>
     </row>
@@ -14806,30 +14807,30 @@
       </c>
       <c r="C385" s="7" t="inlineStr">
         <is>
-          <t>Murtazayeva Kamola Jamoliddin qizi</t>
+          <t>Mustafayeva Madina Ortiq qizi</t>
         </is>
       </c>
       <c r="D385" s="5" t="n">
-        <v>25</v>
+        <v>282</v>
       </c>
       <c r="E385" s="5" t="inlineStr">
         <is>
-          <t>AC1458884</t>
+          <t>AE4846447</t>
         </is>
       </c>
       <c r="F385" s="6" t="inlineStr">
         <is>
-          <t>42708915590028</t>
+          <t>63110085680103</t>
         </is>
       </c>
       <c r="G385" s="6" t="inlineStr">
         <is>
-          <t>04.11.2018</t>
+          <t>31.10.2025</t>
         </is>
       </c>
       <c r="H385" s="6" t="inlineStr">
         <is>
-          <t>27.08.1991</t>
+          <t>31.10.2008</t>
         </is>
       </c>
     </row>
@@ -14844,30 +14845,28 @@
       </c>
       <c r="C386" s="4" t="inlineStr">
         <is>
-          <t>Mustafayeva Madina Ortiq qizi</t>
-        </is>
-      </c>
-      <c r="D386" s="2" t="n">
-        <v>282</v>
-      </c>
+          <t>Niyozova Komila Toshpulatovna</t>
+        </is>
+      </c>
+      <c r="D386" s="2" t="inlineStr"/>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>AE4846447</t>
+          <t>AB9205278</t>
         </is>
       </c>
       <c r="F386" s="3" t="inlineStr">
         <is>
-          <t>63110085680103</t>
+          <t>42405832640057</t>
         </is>
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>31.10.2025</t>
+          <t>07.04.2018</t>
         </is>
       </c>
       <c r="H386" s="3" t="inlineStr">
         <is>
-          <t>31.10.2008</t>
+          <t>24.05.1983</t>
         </is>
       </c>
     </row>
@@ -14882,28 +14881,30 @@
       </c>
       <c r="C387" s="7" t="inlineStr">
         <is>
-          <t>Niyozova Komila Toshpulatovna</t>
-        </is>
-      </c>
-      <c r="D387" s="5" t="inlineStr"/>
+          <t>Norboboyeva Farangiz Nuriddin qizi</t>
+        </is>
+      </c>
+      <c r="D387" s="5" t="n">
+        <v>231</v>
+      </c>
       <c r="E387" s="5" t="inlineStr">
         <is>
-          <t>AB9205278</t>
+          <t>AE5898909</t>
         </is>
       </c>
       <c r="F387" s="6" t="inlineStr">
         <is>
-          <t>42405832640057</t>
+          <t>62808085590100</t>
         </is>
       </c>
       <c r="G387" s="6" t="inlineStr">
         <is>
-          <t>07.04.2018</t>
+          <t>16.01.2026</t>
         </is>
       </c>
       <c r="H387" s="6" t="inlineStr">
         <is>
-          <t>24.05.1983</t>
+          <t>28.08.2008</t>
         </is>
       </c>
     </row>
@@ -14918,30 +14919,30 @@
       </c>
       <c r="C388" s="4" t="inlineStr">
         <is>
-          <t>Norboboyeva Farangiz Nuriddin qizi</t>
+          <t>Pardaqulova Farzona Shovkatovna</t>
         </is>
       </c>
       <c r="D388" s="2" t="n">
-        <v>231</v>
+        <v>90</v>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>AE5898909</t>
+          <t>AE1336538</t>
         </is>
       </c>
       <c r="F388" s="3" t="inlineStr">
         <is>
-          <t>62808085590100</t>
+          <t>60312085590052</t>
         </is>
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>16.01.2026</t>
+          <t>23.01.2025</t>
         </is>
       </c>
       <c r="H388" s="3" t="inlineStr">
         <is>
-          <t>28.08.2008</t>
+          <t>03.12.2008</t>
         </is>
       </c>
     </row>
@@ -14956,30 +14957,30 @@
       </c>
       <c r="C389" s="7" t="inlineStr">
         <is>
-          <t>Pardaqulova Farzona Shovkatovna</t>
+          <t>Pardayeva Farangiz Norali qizi</t>
         </is>
       </c>
       <c r="D389" s="5" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="E389" s="5" t="inlineStr">
         <is>
-          <t>AE1336538</t>
+          <t>AE5643897</t>
         </is>
       </c>
       <c r="F389" s="6" t="inlineStr">
         <is>
-          <t>60312085590052</t>
+          <t>60102085590053</t>
         </is>
       </c>
       <c r="G389" s="6" t="inlineStr">
         <is>
-          <t>23.01.2025</t>
+          <t>29.12.2025</t>
         </is>
       </c>
       <c r="H389" s="6" t="inlineStr">
         <is>
-          <t>03.12.2008</t>
+          <t>01.02.2008</t>
         </is>
       </c>
     </row>
@@ -14994,30 +14995,30 @@
       </c>
       <c r="C390" s="4" t="inlineStr">
         <is>
-          <t>Pardayeva Farangiz Norali qizi</t>
+          <t>Primova Husnora Shovkat qizi</t>
         </is>
       </c>
       <c r="D390" s="2" t="n">
-        <v>105</v>
+        <v>251</v>
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>AE5643897</t>
+          <t>AC 0443770</t>
         </is>
       </c>
       <c r="F390" s="3" t="inlineStr">
         <is>
-          <t>60102085590053</t>
+          <t>61310015590029</t>
         </is>
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>29.12.2025</t>
+          <t>10.12.2018</t>
         </is>
       </c>
       <c r="H390" s="3" t="inlineStr">
         <is>
-          <t>01.02.2008</t>
+          <t>13.10.2001</t>
         </is>
       </c>
     </row>
@@ -15032,30 +15033,30 @@
       </c>
       <c r="C391" s="7" t="inlineStr">
         <is>
-          <t>Primova Husnora Shovkat qizi</t>
+          <t>Rasulova Husnobod Bekmurod qizi</t>
         </is>
       </c>
       <c r="D391" s="5" t="n">
-        <v>251</v>
+        <v>392</v>
       </c>
       <c r="E391" s="5" t="inlineStr">
         <is>
-          <t>AC 0443770</t>
+          <t>AD1615363</t>
         </is>
       </c>
       <c r="F391" s="6" t="inlineStr">
         <is>
-          <t>61310015590029</t>
+          <t>62705055720049</t>
         </is>
       </c>
       <c r="G391" s="6" t="inlineStr">
         <is>
-          <t>10.12.2018</t>
+          <t>03.08.2022</t>
         </is>
       </c>
       <c r="H391" s="6" t="inlineStr">
         <is>
-          <t>13.10.2001</t>
+          <t>27.05.2005</t>
         </is>
       </c>
     </row>
@@ -15070,30 +15071,30 @@
       </c>
       <c r="C392" s="4" t="inlineStr">
         <is>
-          <t>Rasulova Husnobod Bekmurod qizi</t>
+          <t>Rayimova Nozliya Laziz qizi</t>
         </is>
       </c>
       <c r="D392" s="2" t="n">
-        <v>392</v>
+        <v>291</v>
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>AD1615363</t>
+          <t>AE4759683</t>
         </is>
       </c>
       <c r="F392" s="3" t="inlineStr">
         <is>
-          <t>62705055720049</t>
+          <t>62606085590056</t>
         </is>
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>03.08.2022</t>
+          <t>24.10.2025</t>
         </is>
       </c>
       <c r="H392" s="3" t="inlineStr">
         <is>
-          <t>27.05.2005</t>
+          <t>26.06.2008</t>
         </is>
       </c>
     </row>
@@ -15108,30 +15109,30 @@
       </c>
       <c r="C393" s="7" t="inlineStr">
         <is>
-          <t>Rayimova Nozliya Laziz qizi</t>
+          <t>Rustamova Charos O'ktam qizi</t>
         </is>
       </c>
       <c r="D393" s="5" t="n">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="E393" s="5" t="inlineStr">
         <is>
-          <t>AE4759683</t>
+          <t>AE4730990</t>
         </is>
       </c>
       <c r="F393" s="6" t="inlineStr">
         <is>
-          <t>62606085590056</t>
+          <t>60810085680017</t>
         </is>
       </c>
       <c r="G393" s="6" t="inlineStr">
         <is>
-          <t>24.10.2025</t>
+          <t>22.10.2025</t>
         </is>
       </c>
       <c r="H393" s="6" t="inlineStr">
         <is>
-          <t>26.06.2008</t>
+          <t>08.10.2008</t>
         </is>
       </c>
     </row>
@@ -15146,30 +15147,30 @@
       </c>
       <c r="C394" s="4" t="inlineStr">
         <is>
-          <t>Rustamova Charos O'ktam qizi</t>
+          <t>Salayeva Dilroz Muroulla qizi</t>
         </is>
       </c>
       <c r="D394" s="2" t="n">
-        <v>309</v>
+        <v>205</v>
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>AE4730990</t>
+          <t>AE3039330</t>
         </is>
       </c>
       <c r="F394" s="3" t="inlineStr">
         <is>
-          <t>60810085680017</t>
+          <t>60408085730030</t>
         </is>
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>22.10.2025</t>
+          <t>16.06.2025</t>
         </is>
       </c>
       <c r="H394" s="3" t="inlineStr">
         <is>
-          <t>08.10.2008</t>
+          <t>04.08.2008</t>
         </is>
       </c>
     </row>
@@ -15184,30 +15185,30 @@
       </c>
       <c r="C395" s="7" t="inlineStr">
         <is>
-          <t>Salayeva Dilroz Muroulla qizi</t>
+          <t>Sayfiyeva Zarina Axmad qizi</t>
         </is>
       </c>
       <c r="D395" s="5" t="n">
-        <v>205</v>
+        <v>37</v>
       </c>
       <c r="E395" s="5" t="inlineStr">
         <is>
-          <t>AE3039330</t>
+          <t>AD7984192</t>
         </is>
       </c>
       <c r="F395" s="6" t="inlineStr">
         <is>
-          <t>60408085730030</t>
+          <t>61007085590081</t>
         </is>
       </c>
       <c r="G395" s="6" t="inlineStr">
         <is>
-          <t>16.06.2025</t>
+          <t>23.07.2024</t>
         </is>
       </c>
       <c r="H395" s="6" t="inlineStr">
         <is>
-          <t>04.08.2008</t>
+          <t>10.07.2008</t>
         </is>
       </c>
     </row>
@@ -15222,30 +15223,30 @@
       </c>
       <c r="C396" s="4" t="inlineStr">
         <is>
-          <t>Sayfiyeva Zarina Axmad qizi</t>
+          <t>Sayidova Dilafro'z Qahramon qizi</t>
         </is>
       </c>
       <c r="D396" s="2" t="n">
-        <v>37</v>
+        <v>263</v>
       </c>
       <c r="E396" s="2" t="inlineStr">
         <is>
-          <t>AD7984192</t>
+          <t>AE6071273</t>
         </is>
       </c>
       <c r="F396" s="3" t="inlineStr">
         <is>
-          <t>61007085590081</t>
+          <t>62708095680047</t>
         </is>
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>23.07.2024</t>
+          <t>27.01.2026</t>
         </is>
       </c>
       <c r="H396" s="3" t="inlineStr">
         <is>
-          <t>10.07.2008</t>
+          <t>27.08.2009</t>
         </is>
       </c>
     </row>
@@ -15260,30 +15261,30 @@
       </c>
       <c r="C397" s="7" t="inlineStr">
         <is>
-          <t>Sayidova Dilafro'z Qahramon qizi</t>
+          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
         </is>
       </c>
       <c r="D397" s="5" t="n">
-        <v>263</v>
+        <v>107</v>
       </c>
       <c r="E397" s="5" t="inlineStr">
         <is>
-          <t>AE6071273</t>
+          <t>AE2370999</t>
         </is>
       </c>
       <c r="F397" s="6" t="inlineStr">
         <is>
-          <t>62708095680047</t>
+          <t>60307085730074</t>
         </is>
       </c>
       <c r="G397" s="6" t="inlineStr">
         <is>
-          <t>27.01.2026</t>
+          <t>17.04.2025</t>
         </is>
       </c>
       <c r="H397" s="6" t="inlineStr">
         <is>
-          <t>27.08.2009</t>
+          <t>03.07.2008</t>
         </is>
       </c>
     </row>
@@ -15298,30 +15299,30 @@
       </c>
       <c r="C398" s="4" t="inlineStr">
         <is>
-          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
+          <t>Shukurova Zilola Farxod qizi</t>
         </is>
       </c>
       <c r="D398" s="2" t="n">
-        <v>107</v>
+        <v>172</v>
       </c>
       <c r="E398" s="2" t="inlineStr">
         <is>
-          <t>AE2370999</t>
+          <t>AE1059205</t>
         </is>
       </c>
       <c r="F398" s="3" t="inlineStr">
         <is>
-          <t>60307085730074</t>
+          <t>60610085590150</t>
         </is>
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>17.04.2025</t>
+          <t>07.01.2025</t>
         </is>
       </c>
       <c r="H398" s="3" t="inlineStr">
         <is>
-          <t>03.07.2008</t>
+          <t>06.10.2008</t>
         </is>
       </c>
     </row>
@@ -15336,30 +15337,30 @@
       </c>
       <c r="C399" s="7" t="inlineStr">
         <is>
-          <t>Shukurova Zilola Farxod qizi</t>
+          <t>Temirova Rushana Sarvarovna</t>
         </is>
       </c>
       <c r="D399" s="5" t="n">
-        <v>172</v>
+        <v>299</v>
       </c>
       <c r="E399" s="5" t="inlineStr">
         <is>
-          <t>AE1059205</t>
+          <t>AD9123776</t>
         </is>
       </c>
       <c r="F399" s="6" t="inlineStr">
         <is>
-          <t>60610085590150</t>
+          <t>60709085590113</t>
         </is>
       </c>
       <c r="G399" s="6" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>23.10.2024</t>
         </is>
       </c>
       <c r="H399" s="6" t="inlineStr">
         <is>
-          <t>06.10.2008</t>
+          <t>07.09.2008</t>
         </is>
       </c>
     </row>
@@ -15374,30 +15375,30 @@
       </c>
       <c r="C400" s="4" t="inlineStr">
         <is>
-          <t>Temirova Rushana Sarvarovna</t>
+          <t>Toshpo'latova Asila Akmal qizi</t>
         </is>
       </c>
       <c r="D400" s="2" t="n">
-        <v>299</v>
+        <v>112</v>
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>AD9123776</t>
+          <t>AE3444231</t>
         </is>
       </c>
       <c r="F400" s="3" t="inlineStr">
         <is>
-          <t>60709085590113</t>
+          <t>61709085590015</t>
         </is>
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>23.10.2024</t>
+          <t>18.07.2025</t>
         </is>
       </c>
       <c r="H400" s="3" t="inlineStr">
         <is>
-          <t>07.09.2008</t>
+          <t>17.09.2008</t>
         </is>
       </c>
     </row>
@@ -15412,30 +15413,28 @@
       </c>
       <c r="C401" s="7" t="inlineStr">
         <is>
-          <t>Toshpo'latova Asila Akmal qizi</t>
-        </is>
-      </c>
-      <c r="D401" s="5" t="n">
-        <v>112</v>
-      </c>
+          <t>Tursunmurodova Diyora Jasur qizi</t>
+        </is>
+      </c>
+      <c r="D401" s="5" t="inlineStr"/>
       <c r="E401" s="5" t="inlineStr">
         <is>
-          <t>AE3444231</t>
+          <t>AD9513015</t>
         </is>
       </c>
       <c r="F401" s="6" t="inlineStr">
         <is>
-          <t>61709085590015</t>
+          <t>61609075680011</t>
         </is>
       </c>
       <c r="G401" s="6" t="inlineStr">
         <is>
-          <t>18.07.2025</t>
+          <t>21.11.2024</t>
         </is>
       </c>
       <c r="H401" s="6" t="inlineStr">
         <is>
-          <t>17.09.2008</t>
+          <t>16.09.2007</t>
         </is>
       </c>
     </row>
@@ -15450,28 +15449,30 @@
       </c>
       <c r="C402" s="4" t="inlineStr">
         <is>
-          <t>Tursunmurodova Diyora Jasur qizi</t>
-        </is>
-      </c>
-      <c r="D402" s="2" t="inlineStr"/>
+          <t>Umirova Sevinch Avlayor qizi</t>
+        </is>
+      </c>
+      <c r="D402" s="2" t="n">
+        <v>298</v>
+      </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>AD9513015</t>
+          <t>AD1671106</t>
         </is>
       </c>
       <c r="F402" s="3" t="inlineStr">
         <is>
-          <t>61609075680011</t>
+          <t>60906055720101</t>
         </is>
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>21.11.2024</t>
+          <t>18.08.2022</t>
         </is>
       </c>
       <c r="H402" s="3" t="inlineStr">
         <is>
-          <t>16.09.2007</t>
+          <t>09.06.2005</t>
         </is>
       </c>
     </row>
@@ -15486,30 +15487,30 @@
       </c>
       <c r="C403" s="7" t="inlineStr">
         <is>
-          <t>Umirova Sevinch Avlayor qizi</t>
+          <t>Usmonova Yulduz Nu'mon qizi</t>
         </is>
       </c>
       <c r="D403" s="5" t="n">
-        <v>298</v>
+        <v>209</v>
       </c>
       <c r="E403" s="5" t="inlineStr">
         <is>
-          <t>AD1671106</t>
+          <t>AD9589389</t>
         </is>
       </c>
       <c r="F403" s="6" t="inlineStr">
         <is>
-          <t>60906055720101</t>
+          <t>62112075680077</t>
         </is>
       </c>
       <c r="G403" s="6" t="inlineStr">
         <is>
-          <t>18.08.2022</t>
+          <t>27.11.2024</t>
         </is>
       </c>
       <c r="H403" s="6" t="inlineStr">
         <is>
-          <t>09.06.2005</t>
+          <t>21.12.2007</t>
         </is>
       </c>
     </row>
@@ -15524,30 +15525,30 @@
       </c>
       <c r="C404" s="4" t="inlineStr">
         <is>
-          <t>Usmonova Yulduz Nu'mon qizi</t>
+          <t>Xaydarova Iroda Zarif qizi</t>
         </is>
       </c>
       <c r="D404" s="2" t="n">
-        <v>209</v>
+        <v>113</v>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>AD9589389</t>
+          <t>AE4240266</t>
         </is>
       </c>
       <c r="F404" s="3" t="inlineStr">
         <is>
-          <t>62112075680077</t>
+          <t>61906085590032</t>
         </is>
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>27.11.2024</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="H404" s="3" t="inlineStr">
         <is>
-          <t>21.12.2007</t>
+          <t>19.06.2008</t>
         </is>
       </c>
     </row>
@@ -15562,30 +15563,30 @@
       </c>
       <c r="C405" s="7" t="inlineStr">
         <is>
-          <t>Xaydarova Iroda Zarif qizi</t>
+          <t>Xayrullayeva Umida Safar qizi</t>
         </is>
       </c>
       <c r="D405" s="5" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E405" s="5" t="inlineStr">
         <is>
-          <t>AE4240266</t>
+          <t>AD9786798</t>
         </is>
       </c>
       <c r="F405" s="6" t="inlineStr">
         <is>
-          <t>61906085590032</t>
+          <t>61911085590096</t>
         </is>
       </c>
       <c r="G405" s="6" t="inlineStr">
         <is>
-          <t>17.09.2025</t>
+          <t>12.12.2024</t>
         </is>
       </c>
       <c r="H405" s="6" t="inlineStr">
         <is>
-          <t>19.06.2008</t>
+          <t>19.11.2008</t>
         </is>
       </c>
     </row>
@@ -15600,30 +15601,30 @@
       </c>
       <c r="C406" s="4" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida Safar qizi</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="D406" s="2" t="n">
-        <v>116</v>
+        <v>243</v>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>AD9786798</t>
+          <t>AE4328716</t>
         </is>
       </c>
       <c r="F406" s="3" t="inlineStr">
         <is>
-          <t>61911085590096</t>
+          <t>60201085720092</t>
         </is>
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>12.12.2024</t>
+          <t>24.09.2025</t>
         </is>
       </c>
       <c r="H406" s="3" t="inlineStr">
         <is>
-          <t>19.11.2008</t>
+          <t>02.01.2008</t>
         </is>
       </c>
     </row>
@@ -15638,30 +15639,30 @@
       </c>
       <c r="C407" s="7" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
+          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
         </is>
       </c>
       <c r="D407" s="5" t="n">
-        <v>243</v>
+        <v>108</v>
       </c>
       <c r="E407" s="5" t="inlineStr">
         <is>
-          <t>AE4328716</t>
+          <t>AE4729924</t>
         </is>
       </c>
       <c r="F407" s="6" t="inlineStr">
         <is>
-          <t>60201085720092</t>
+          <t>62511085730064</t>
         </is>
       </c>
       <c r="G407" s="6" t="inlineStr">
         <is>
-          <t>24.09.2025</t>
+          <t>22.10.2025</t>
         </is>
       </c>
       <c r="H407" s="6" t="inlineStr">
         <is>
-          <t>02.01.2008</t>
+          <t>25.11.2008</t>
         </is>
       </c>
     </row>
@@ -15676,30 +15677,30 @@
       </c>
       <c r="C408" s="4" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
+          <t>Xurramova Lobar Ural qizi</t>
         </is>
       </c>
       <c r="D408" s="2" t="n">
-        <v>108</v>
+        <v>234</v>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>AE4729924</t>
+          <t>AE2656510</t>
         </is>
       </c>
       <c r="F408" s="3" t="inlineStr">
         <is>
-          <t>62511085730064</t>
+          <t>62508085680062</t>
         </is>
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>22.10.2025</t>
+          <t>13.05.2025</t>
         </is>
       </c>
       <c r="H408" s="3" t="inlineStr">
         <is>
-          <t>25.11.2008</t>
+          <t>25.08.2008</t>
         </is>
       </c>
     </row>
@@ -15714,30 +15715,30 @@
       </c>
       <c r="C409" s="7" t="inlineStr">
         <is>
-          <t>Xurramova Lobar Ural qizi</t>
+          <t>Xurramova Sabina Yuldosh qizi</t>
         </is>
       </c>
       <c r="D409" s="5" t="n">
-        <v>234</v>
+        <v>52</v>
       </c>
       <c r="E409" s="5" t="inlineStr">
         <is>
-          <t>AE2656510</t>
+          <t>AC3081523</t>
         </is>
       </c>
       <c r="F409" s="6" t="inlineStr">
         <is>
-          <t>62508085680062</t>
+          <t>60803048230011</t>
         </is>
       </c>
       <c r="G409" s="6" t="inlineStr">
         <is>
-          <t>13.05.2025</t>
+          <t>16.10.2020</t>
         </is>
       </c>
       <c r="H409" s="6" t="inlineStr">
         <is>
-          <t>25.08.2008</t>
+          <t>08.03.2004</t>
         </is>
       </c>
     </row>
@@ -15747,35 +15748,35 @@
       </c>
       <c r="B410" s="3" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C410" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Sabina Yuldosh qizi</t>
+          <t>A'zamov Shohjaxon Sherali o'g'li</t>
         </is>
       </c>
       <c r="D410" s="2" t="n">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>AC3081523</t>
+          <t>AD9855395</t>
         </is>
       </c>
       <c r="F410" s="3" t="inlineStr">
         <is>
-          <t>60803048230011</t>
+          <t>52510085590064</t>
         </is>
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>16.10.2020</t>
+          <t>17.12.2024</t>
         </is>
       </c>
       <c r="H410" s="3" t="inlineStr">
         <is>
-          <t>08.03.2004</t>
+          <t>25.10.2008</t>
         </is>
       </c>
     </row>
@@ -15790,30 +15791,30 @@
       </c>
       <c r="C411" s="7" t="inlineStr">
         <is>
-          <t>A'zamov Shohjaxon Sherali o'g'li</t>
+          <t>Abdixalilova Shohzoda Bahodir qizi</t>
         </is>
       </c>
       <c r="D411" s="5" t="n">
-        <v>86</v>
+        <v>274</v>
       </c>
       <c r="E411" s="5" t="inlineStr">
         <is>
-          <t>AD9855395</t>
+          <t>AD7053449</t>
         </is>
       </c>
       <c r="F411" s="6" t="inlineStr">
         <is>
-          <t>52510085590064</t>
+          <t>60603085720124</t>
         </is>
       </c>
       <c r="G411" s="6" t="inlineStr">
         <is>
-          <t>17.12.2024</t>
+          <t>06.05.2024</t>
         </is>
       </c>
       <c r="H411" s="6" t="inlineStr">
         <is>
-          <t>25.10.2008</t>
+          <t>06.03.2008</t>
         </is>
       </c>
     </row>
@@ -15828,30 +15829,30 @@
       </c>
       <c r="C412" s="4" t="inlineStr">
         <is>
-          <t>Abdixalilova Shohzoda Bahodir qizi</t>
+          <t>Abdiyeva Sabina G'ayrat qizi</t>
         </is>
       </c>
       <c r="D412" s="2" t="n">
-        <v>274</v>
+        <v>140</v>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>AD7053449</t>
+          <t>AE4860201</t>
         </is>
       </c>
       <c r="F412" s="3" t="inlineStr">
         <is>
-          <t>60603085720124</t>
+          <t>60108085590051</t>
         </is>
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>06.05.2024</t>
+          <t>03.11.2025</t>
         </is>
       </c>
       <c r="H412" s="3" t="inlineStr">
         <is>
-          <t>06.03.2008</t>
+          <t>01.08.2008</t>
         </is>
       </c>
     </row>
@@ -15866,30 +15867,30 @@
       </c>
       <c r="C413" s="7" t="inlineStr">
         <is>
-          <t>Abdiyeva Sabina G'ayrat qizi</t>
+          <t>Abduraxmonova Zahrobonu Toxir qizi</t>
         </is>
       </c>
       <c r="D413" s="5" t="n">
-        <v>140</v>
+        <v>204</v>
       </c>
       <c r="E413" s="5" t="inlineStr">
         <is>
-          <t>AE4860201</t>
+          <t>AE4193791</t>
         </is>
       </c>
       <c r="F413" s="6" t="inlineStr">
         <is>
-          <t>60108085590051</t>
+          <t>61805095590028</t>
         </is>
       </c>
       <c r="G413" s="6" t="inlineStr">
         <is>
-          <t>03.11.2025</t>
+          <t>15.09.2025</t>
         </is>
       </c>
       <c r="H413" s="6" t="inlineStr">
         <is>
-          <t>01.08.2008</t>
+          <t>18.05.2009</t>
         </is>
       </c>
     </row>
@@ -15904,30 +15905,30 @@
       </c>
       <c r="C414" s="4" t="inlineStr">
         <is>
-          <t>Abduraxmonova Zahrobonu Toxir qizi</t>
+          <t>Eshpulatova Shahnoza Sherali qizi</t>
         </is>
       </c>
       <c r="D414" s="2" t="n">
-        <v>204</v>
+        <v>5</v>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>AE4193791</t>
+          <t>AE1541155</t>
         </is>
       </c>
       <c r="F414" s="3" t="inlineStr">
         <is>
-          <t>61805095590028</t>
+          <t>61405085590065</t>
         </is>
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>15.09.2025</t>
+          <t>07.02.2025</t>
         </is>
       </c>
       <c r="H414" s="3" t="inlineStr">
         <is>
-          <t>18.05.2009</t>
+          <t>14.05.2008</t>
         </is>
       </c>
     </row>
@@ -15942,30 +15943,30 @@
       </c>
       <c r="C415" s="7" t="inlineStr">
         <is>
-          <t>Eshpulatova Shahnoza Sherali qizi</t>
+          <t>Eshquvatova Yulduz Asliddin qizi</t>
         </is>
       </c>
       <c r="D415" s="5" t="n">
-        <v>5</v>
+        <v>267</v>
       </c>
       <c r="E415" s="5" t="inlineStr">
         <is>
-          <t>AE1541155</t>
+          <t>AB5879899</t>
         </is>
       </c>
       <c r="F415" s="6" t="inlineStr">
         <is>
-          <t>61405085590065</t>
+          <t>40511985730032</t>
         </is>
       </c>
       <c r="G415" s="6" t="inlineStr">
         <is>
-          <t>07.02.2025</t>
+          <t>08.02.2017</t>
         </is>
       </c>
       <c r="H415" s="6" t="inlineStr">
         <is>
-          <t>14.05.2008</t>
+          <t>05.11.1998</t>
         </is>
       </c>
     </row>
@@ -15980,30 +15981,30 @@
       </c>
       <c r="C416" s="4" t="inlineStr">
         <is>
-          <t>Eshquvatova Yulduz Asliddin qizi</t>
+          <t>G'aniyeva Asila G'ani qizi</t>
         </is>
       </c>
       <c r="D416" s="2" t="n">
-        <v>267</v>
+        <v>381</v>
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
-          <t>AB5879899</t>
+          <t>AE5575300</t>
         </is>
       </c>
       <c r="F416" s="3" t="inlineStr">
         <is>
-          <t>40511985730032</t>
+          <t>41011925590038</t>
         </is>
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>08.02.2017</t>
+          <t>23.12.2025</t>
         </is>
       </c>
       <c r="H416" s="3" t="inlineStr">
         <is>
-          <t>05.11.1998</t>
+          <t>10.11.1992</t>
         </is>
       </c>
     </row>
@@ -16018,30 +16019,30 @@
       </c>
       <c r="C417" s="7" t="inlineStr">
         <is>
-          <t>G'aniyeva Asila G'ani qizi</t>
+          <t>Halimova Sevinch Ravshan qizi</t>
         </is>
       </c>
       <c r="D417" s="5" t="n">
-        <v>381</v>
+        <v>26</v>
       </c>
       <c r="E417" s="5" t="inlineStr">
         <is>
-          <t>AE5575300</t>
+          <t>AD8735102</t>
         </is>
       </c>
       <c r="F417" s="6" t="inlineStr">
         <is>
-          <t>41011925590038</t>
+          <t>60908085680060</t>
         </is>
       </c>
       <c r="G417" s="6" t="inlineStr">
         <is>
-          <t>23.12.2025</t>
+          <t>23.09.2024</t>
         </is>
       </c>
       <c r="H417" s="6" t="inlineStr">
         <is>
-          <t>10.11.1992</t>
+          <t>09.08.2008</t>
         </is>
       </c>
     </row>
@@ -16056,30 +16057,30 @@
       </c>
       <c r="C418" s="4" t="inlineStr">
         <is>
-          <t>Halimova Sevinch Ravshan qizi</t>
+          <t>Hamroqulova Marjona O'ktam qizi</t>
         </is>
       </c>
       <c r="D418" s="2" t="n">
-        <v>26</v>
+        <v>275</v>
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>AD8735102</t>
+          <t>AE1525748</t>
         </is>
       </c>
       <c r="F418" s="3" t="inlineStr">
         <is>
-          <t>60908085680060</t>
+          <t>61104085680018</t>
         </is>
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>23.09.2024</t>
+          <t>06.02.2025</t>
         </is>
       </c>
       <c r="H418" s="3" t="inlineStr">
         <is>
-          <t>09.08.2008</t>
+          <t>11.04.2008</t>
         </is>
       </c>
     </row>
@@ -16094,30 +16095,30 @@
       </c>
       <c r="C419" s="7" t="inlineStr">
         <is>
-          <t>Hamroqulova Marjona O'ktam qizi</t>
+          <t>Isomiddinova Ruhshona Shavkat qizi</t>
         </is>
       </c>
       <c r="D419" s="5" t="n">
-        <v>275</v>
+        <v>65</v>
       </c>
       <c r="E419" s="5" t="inlineStr">
         <is>
-          <t>AE1525748</t>
+          <t>AD7684354</t>
         </is>
       </c>
       <c r="F419" s="6" t="inlineStr">
         <is>
-          <t>61104085680018</t>
+          <t>63006085680064</t>
         </is>
       </c>
       <c r="G419" s="6" t="inlineStr">
         <is>
-          <t>06.02.2025</t>
+          <t>01.07.2024</t>
         </is>
       </c>
       <c r="H419" s="6" t="inlineStr">
         <is>
-          <t>11.04.2008</t>
+          <t>30.06.2008</t>
         </is>
       </c>
     </row>
@@ -16132,30 +16133,30 @@
       </c>
       <c r="C420" s="4" t="inlineStr">
         <is>
-          <t>Isomiddinova Ruhshona Shavkat qizi</t>
+          <t>Jalolov Javlonbek G'ani o'g'li</t>
         </is>
       </c>
       <c r="D420" s="2" t="n">
-        <v>65</v>
+        <v>211</v>
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>AD7684354</t>
+          <t>AE 4994200</t>
         </is>
       </c>
       <c r="F420" s="3" t="inlineStr">
         <is>
-          <t>63006085680064</t>
+          <t>53005095680054</t>
         </is>
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>01.07.2024</t>
+          <t>11.11.2025</t>
         </is>
       </c>
       <c r="H420" s="3" t="inlineStr">
         <is>
-          <t>30.06.2008</t>
+          <t>30.05.2009</t>
         </is>
       </c>
     </row>
@@ -16170,30 +16171,30 @@
       </c>
       <c r="C421" s="7" t="inlineStr">
         <is>
-          <t>Jalolov Javlonbek G'ani o'g'li</t>
+          <t>Karimova Shaxina Fayzulla qizi</t>
         </is>
       </c>
       <c r="D421" s="5" t="n">
-        <v>211</v>
+        <v>293</v>
       </c>
       <c r="E421" s="5" t="inlineStr">
         <is>
-          <t>AE 4994200</t>
+          <t>AC0413538</t>
         </is>
       </c>
       <c r="F421" s="6" t="inlineStr">
         <is>
-          <t>53005095680054</t>
+          <t>61511017890023</t>
         </is>
       </c>
       <c r="G421" s="6" t="inlineStr">
         <is>
-          <t>11.11.2025</t>
+          <t>07.12.2018</t>
         </is>
       </c>
       <c r="H421" s="6" t="inlineStr">
         <is>
-          <t>30.05.2009</t>
+          <t>15.11.2001</t>
         </is>
       </c>
     </row>
@@ -16208,30 +16209,30 @@
       </c>
       <c r="C422" s="4" t="inlineStr">
         <is>
-          <t>Karimova Shaxina Fayzulla qizi</t>
+          <t>Mahmudova Gulsanam Nigmatovna</t>
         </is>
       </c>
       <c r="D422" s="2" t="n">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
-          <t>AC0413538</t>
+          <t>AE1695093</t>
         </is>
       </c>
       <c r="F422" s="3" t="inlineStr">
         <is>
-          <t>61511017890023</t>
+          <t>62308085680109</t>
         </is>
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>07.12.2018</t>
+          <t>20.02.2025</t>
         </is>
       </c>
       <c r="H422" s="3" t="inlineStr">
         <is>
-          <t>15.11.2001</t>
+          <t>23.08.2008</t>
         </is>
       </c>
     </row>
@@ -16246,30 +16247,30 @@
       </c>
       <c r="C423" s="7" t="inlineStr">
         <is>
-          <t>Mahmudova Gulsanam Nigmatovna</t>
+          <t>Maxmudova Musallam Qamariddin qizi</t>
         </is>
       </c>
       <c r="D423" s="5" t="n">
-        <v>277</v>
+        <v>11</v>
       </c>
       <c r="E423" s="5" t="inlineStr">
         <is>
-          <t>AE1695093</t>
+          <t>AE5297116</t>
         </is>
       </c>
       <c r="F423" s="6" t="inlineStr">
         <is>
-          <t>62308085680109</t>
+          <t>61303085680079</t>
         </is>
       </c>
       <c r="G423" s="6" t="inlineStr">
         <is>
-          <t>20.02.2025</t>
+          <t>04.12.2025</t>
         </is>
       </c>
       <c r="H423" s="6" t="inlineStr">
         <is>
-          <t>23.08.2008</t>
+          <t>13.03.2008</t>
         </is>
       </c>
     </row>
@@ -16284,30 +16285,30 @@
       </c>
       <c r="C424" s="4" t="inlineStr">
         <is>
-          <t>Maxmudova Musallam Qamariddin qizi</t>
+          <t>Murodova Ruhshona Ilhomovna</t>
         </is>
       </c>
       <c r="D424" s="2" t="n">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>AE5297116</t>
+          <t>AE3287114</t>
         </is>
       </c>
       <c r="F424" s="3" t="inlineStr">
         <is>
-          <t>61303085680079</t>
+          <t>61009085680098</t>
         </is>
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>04.12.2025</t>
+          <t>07.07.2025</t>
         </is>
       </c>
       <c r="H424" s="3" t="inlineStr">
         <is>
-          <t>13.03.2008</t>
+          <t>10.09.2008</t>
         </is>
       </c>
     </row>
@@ -16322,30 +16323,30 @@
       </c>
       <c r="C425" s="7" t="inlineStr">
         <is>
-          <t>Murodova Ruhshona Ilhomovna</t>
+          <t>Nafasova Sevinch Bollijon qizi</t>
         </is>
       </c>
       <c r="D425" s="5" t="n">
-        <v>72</v>
+        <v>266</v>
       </c>
       <c r="E425" s="5" t="inlineStr">
         <is>
-          <t>AE3287114</t>
+          <t>AE4668322</t>
         </is>
       </c>
       <c r="F425" s="6" t="inlineStr">
         <is>
-          <t>61009085680098</t>
+          <t>62708085730015</t>
         </is>
       </c>
       <c r="G425" s="6" t="inlineStr">
         <is>
-          <t>07.07.2025</t>
+          <t>17.10.2025</t>
         </is>
       </c>
       <c r="H425" s="6" t="inlineStr">
         <is>
-          <t>10.09.2008</t>
+          <t>27.08.2008</t>
         </is>
       </c>
     </row>
@@ -16360,30 +16361,30 @@
       </c>
       <c r="C426" s="4" t="inlineStr">
         <is>
-          <t>Nafasova Sevinch Bollijon qizi</t>
+          <t>Pirnazarova Jasmina Olim qizi</t>
         </is>
       </c>
       <c r="D426" s="2" t="n">
-        <v>266</v>
+        <v>13</v>
       </c>
       <c r="E426" s="2" t="inlineStr">
         <is>
-          <t>AE4668322</t>
+          <t>AE4198928</t>
         </is>
       </c>
       <c r="F426" s="3" t="inlineStr">
         <is>
-          <t>62708085730015</t>
+          <t>60506085680077</t>
         </is>
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>17.10.2025</t>
+          <t>15.09.2025</t>
         </is>
       </c>
       <c r="H426" s="3" t="inlineStr">
         <is>
-          <t>27.08.2008</t>
+          <t>05.06.2008</t>
         </is>
       </c>
     </row>
@@ -16398,30 +16399,30 @@
       </c>
       <c r="C427" s="7" t="inlineStr">
         <is>
-          <t>Pirnazarova Jasmina Olim qizi</t>
+          <t>Qodirova Sabina Suxrob qizi</t>
         </is>
       </c>
       <c r="D427" s="5" t="n">
-        <v>13</v>
+        <v>295</v>
       </c>
       <c r="E427" s="5" t="inlineStr">
         <is>
-          <t>AE4198928</t>
+          <t>AC2359638</t>
         </is>
       </c>
       <c r="F427" s="6" t="inlineStr">
         <is>
-          <t>60506085680077</t>
+          <t>60203045680015</t>
         </is>
       </c>
       <c r="G427" s="6" t="inlineStr">
         <is>
-          <t>15.09.2025</t>
+          <t>03.11.2019</t>
         </is>
       </c>
       <c r="H427" s="6" t="inlineStr">
         <is>
-          <t>05.06.2008</t>
+          <t>02.03.2004</t>
         </is>
       </c>
     </row>
@@ -16436,30 +16437,30 @@
       </c>
       <c r="C428" s="4" t="inlineStr">
         <is>
-          <t>Qodirova Sabina Suxrob qizi</t>
+          <t>Soyipova Dinora Sanjar qizi</t>
         </is>
       </c>
       <c r="D428" s="2" t="n">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="E428" s="2" t="inlineStr">
         <is>
-          <t>AC2359638</t>
+          <t>AD9484395</t>
         </is>
       </c>
       <c r="F428" s="3" t="inlineStr">
         <is>
-          <t>60203045680015</t>
+          <t>62208085590065</t>
         </is>
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>03.11.2019</t>
+          <t>20.11.2024</t>
         </is>
       </c>
       <c r="H428" s="3" t="inlineStr">
         <is>
-          <t>02.03.2004</t>
+          <t>22.08.2008</t>
         </is>
       </c>
     </row>
@@ -16474,30 +16475,30 @@
       </c>
       <c r="C429" s="7" t="inlineStr">
         <is>
-          <t>Soyipova Dinora Sanjar qizi</t>
+          <t>Suyarova Dinora Sodiq qizi</t>
         </is>
       </c>
       <c r="D429" s="5" t="n">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="E429" s="5" t="inlineStr">
         <is>
-          <t>AD9484395</t>
+          <t>AD9863476</t>
         </is>
       </c>
       <c r="F429" s="6" t="inlineStr">
         <is>
-          <t>62208085590065</t>
+          <t>60108085590037</t>
         </is>
       </c>
       <c r="G429" s="6" t="inlineStr">
         <is>
-          <t>20.11.2024</t>
+          <t>18.12.2024</t>
         </is>
       </c>
       <c r="H429" s="6" t="inlineStr">
         <is>
-          <t>22.08.2008</t>
+          <t>01.08.2008</t>
         </is>
       </c>
     </row>
@@ -16512,30 +16513,30 @@
       </c>
       <c r="C430" s="4" t="inlineStr">
         <is>
-          <t>Suyarova Dinora Sodiq qizi</t>
+          <t>Temirboyeva Iroda Baxtiyor qizi</t>
         </is>
       </c>
       <c r="D430" s="2" t="n">
-        <v>306</v>
+        <v>20</v>
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
-          <t>AD9863476</t>
+          <t>AD6024952</t>
         </is>
       </c>
       <c r="F430" s="3" t="inlineStr">
         <is>
-          <t>60108085590037</t>
+          <t>60112075590084</t>
         </is>
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>18.12.2024</t>
+          <t>05.02.2024</t>
         </is>
       </c>
       <c r="H430" s="3" t="inlineStr">
         <is>
-          <t>01.08.2008</t>
+          <t>01.12.2007</t>
         </is>
       </c>
     </row>
@@ -16550,30 +16551,30 @@
       </c>
       <c r="C431" s="7" t="inlineStr">
         <is>
-          <t>Temirboyeva Iroda Baxtiyor qizi</t>
+          <t>Tuychiyeva Farzona Dalerovna</t>
         </is>
       </c>
       <c r="D431" s="5" t="n">
-        <v>20</v>
+        <v>280</v>
       </c>
       <c r="E431" s="5" t="inlineStr">
         <is>
-          <t>AD6024952</t>
+          <t>AE4114421</t>
         </is>
       </c>
       <c r="F431" s="6" t="inlineStr">
         <is>
-          <t>60112075590084</t>
+          <t>60508095680049</t>
         </is>
       </c>
       <c r="G431" s="6" t="inlineStr">
         <is>
-          <t>05.02.2024</t>
+          <t>09.09.2025</t>
         </is>
       </c>
       <c r="H431" s="6" t="inlineStr">
         <is>
-          <t>01.12.2007</t>
+          <t>05.08.2009</t>
         </is>
       </c>
     </row>
@@ -16588,30 +16589,30 @@
       </c>
       <c r="C432" s="4" t="inlineStr">
         <is>
-          <t>Tuychiyeva Farzona Dalerovna</t>
+          <t>Ulugbekova Zara Ulug'bek qizi</t>
         </is>
       </c>
       <c r="D432" s="2" t="n">
-        <v>280</v>
+        <v>313</v>
       </c>
       <c r="E432" s="2" t="inlineStr">
         <is>
-          <t>AE4114421</t>
+          <t>AE4760779</t>
         </is>
       </c>
       <c r="F432" s="3" t="inlineStr">
         <is>
-          <t>60508095680049</t>
+          <t>61109085590127</t>
         </is>
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>09.09.2025</t>
+          <t>24.10.2025</t>
         </is>
       </c>
       <c r="H432" s="3" t="inlineStr">
         <is>
-          <t>05.08.2009</t>
+          <t>11.09.2008</t>
         </is>
       </c>
     </row>
@@ -16626,30 +16627,30 @@
       </c>
       <c r="C433" s="7" t="inlineStr">
         <is>
-          <t>Ulugbekova Zara Ulug'bek qizi</t>
+          <t>Xamdamova Madina Abdiqodir qizi</t>
         </is>
       </c>
       <c r="D433" s="5" t="n">
-        <v>313</v>
+        <v>14</v>
       </c>
       <c r="E433" s="5" t="inlineStr">
         <is>
-          <t>AE4760779</t>
+          <t>AB8517012</t>
         </is>
       </c>
       <c r="F433" s="6" t="inlineStr">
         <is>
-          <t>61109085590127</t>
+          <t>62701015680026</t>
         </is>
       </c>
       <c r="G433" s="6" t="inlineStr">
         <is>
-          <t>24.10.2025</t>
+          <t>07.01.2018</t>
         </is>
       </c>
       <c r="H433" s="6" t="inlineStr">
         <is>
-          <t>11.09.2008</t>
+          <t>27.01.2001</t>
         </is>
       </c>
     </row>
@@ -16664,30 +16665,30 @@
       </c>
       <c r="C434" s="4" t="inlineStr">
         <is>
-          <t>Xamdamova Madina Abdiqodir qizi</t>
+          <t>Xannonova Shohsanam Orif qizi</t>
         </is>
       </c>
       <c r="D434" s="2" t="n">
-        <v>14</v>
+        <v>181</v>
       </c>
       <c r="E434" s="2" t="inlineStr">
         <is>
-          <t>AB8517012</t>
+          <t>AD0284895</t>
         </is>
       </c>
       <c r="F434" s="3" t="inlineStr">
         <is>
-          <t>62701015680026</t>
+          <t>60206045680052</t>
         </is>
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>07.01.2018</t>
+          <t>01.04.2021</t>
         </is>
       </c>
       <c r="H434" s="3" t="inlineStr">
         <is>
-          <t>27.01.2001</t>
+          <t>02.06.2004</t>
         </is>
       </c>
     </row>
@@ -16702,30 +16703,30 @@
       </c>
       <c r="C435" s="7" t="inlineStr">
         <is>
-          <t>Xannonova Shohsanam Orif qizi</t>
+          <t>Xo'jaqulova Navbahor Azim qizi</t>
         </is>
       </c>
       <c r="D435" s="5" t="n">
-        <v>181</v>
+        <v>302</v>
       </c>
       <c r="E435" s="5" t="inlineStr">
         <is>
-          <t>AD0284895</t>
+          <t>AD4186543</t>
         </is>
       </c>
       <c r="F435" s="6" t="inlineStr">
         <is>
-          <t>60206045680052</t>
+          <t>62104025680040</t>
         </is>
       </c>
       <c r="G435" s="6" t="inlineStr">
         <is>
-          <t>01.04.2021</t>
+          <t>07.08.2023</t>
         </is>
       </c>
       <c r="H435" s="6" t="inlineStr">
         <is>
-          <t>02.06.2004</t>
+          <t>21.04.2002</t>
         </is>
       </c>
     </row>
@@ -16740,30 +16741,30 @@
       </c>
       <c r="C436" s="4" t="inlineStr">
         <is>
-          <t>Xo'jaqulova Navbahor Azim qizi</t>
+          <t>Xolmurodova Dilnura Dilmurod qizi</t>
         </is>
       </c>
       <c r="D436" s="2" t="n">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E436" s="2" t="inlineStr">
         <is>
-          <t>AD4186543</t>
+          <t>AE1516812</t>
         </is>
       </c>
       <c r="F436" s="3" t="inlineStr">
         <is>
-          <t>62104025680040</t>
+          <t>60110085590193</t>
         </is>
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>07.08.2023</t>
+          <t>06.02.2025</t>
         </is>
       </c>
       <c r="H436" s="3" t="inlineStr">
         <is>
-          <t>21.04.2002</t>
+          <t>01.10.2008</t>
         </is>
       </c>
     </row>
@@ -16778,30 +16779,30 @@
       </c>
       <c r="C437" s="7" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura Dilmurod qizi</t>
+          <t>Xujamuratova Durdona Bahrom qizi</t>
         </is>
       </c>
       <c r="D437" s="5" t="n">
-        <v>307</v>
+        <v>232</v>
       </c>
       <c r="E437" s="5" t="inlineStr">
         <is>
-          <t>AE1516812</t>
+          <t>AE5954513</t>
         </is>
       </c>
       <c r="F437" s="6" t="inlineStr">
         <is>
-          <t>60110085590193</t>
+          <t>62204085720105</t>
         </is>
       </c>
       <c r="G437" s="6" t="inlineStr">
         <is>
-          <t>06.02.2025</t>
+          <t>20.01.2026</t>
         </is>
       </c>
       <c r="H437" s="6" t="inlineStr">
         <is>
-          <t>01.10.2008</t>
+          <t>22.04.2008</t>
         </is>
       </c>
     </row>
@@ -16816,30 +16817,30 @@
       </c>
       <c r="C438" s="4" t="inlineStr">
         <is>
-          <t>Xujamuratova Durdona Bahrom qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="D438" s="2" t="n">
-        <v>232</v>
+        <v>29</v>
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
-          <t>AE5954513</t>
+          <t>AC1847101</t>
         </is>
       </c>
       <c r="F438" s="3" t="inlineStr">
         <is>
-          <t>62204085720105</t>
+          <t>60411015680031</t>
         </is>
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>20.01.2026</t>
+          <t>24.04.2019</t>
         </is>
       </c>
       <c r="H438" s="3" t="inlineStr">
         <is>
-          <t>22.04.2008</t>
+          <t>04.11.2001</t>
         </is>
       </c>
     </row>
@@ -16854,30 +16855,30 @@
       </c>
       <c r="C439" s="7" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="D439" s="5" t="n">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="E439" s="5" t="inlineStr">
         <is>
-          <t>AC1847101</t>
+          <t>AD4921163</t>
         </is>
       </c>
       <c r="F439" s="6" t="inlineStr">
         <is>
-          <t>60411015680031</t>
+          <t>63004075680030</t>
         </is>
       </c>
       <c r="G439" s="6" t="inlineStr">
         <is>
-          <t>24.04.2019</t>
+          <t>20.10.2023</t>
         </is>
       </c>
       <c r="H439" s="6" t="inlineStr">
         <is>
-          <t>04.11.2001</t>
+          <t>30.04.2007</t>
         </is>
       </c>
     </row>
@@ -16892,30 +16893,30 @@
       </c>
       <c r="C440" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xusanova Aziza Fazliddin qizi</t>
         </is>
       </c>
       <c r="D440" s="2" t="n">
-        <v>96</v>
+        <v>196</v>
       </c>
       <c r="E440" s="2" t="inlineStr">
         <is>
-          <t>AD4921163</t>
+          <t>AE5015467</t>
         </is>
       </c>
       <c r="F440" s="3" t="inlineStr">
         <is>
-          <t>63004075680030</t>
+          <t>60110085590092</t>
         </is>
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>20.10.2023</t>
+          <t>12.11.2025</t>
         </is>
       </c>
       <c r="H440" s="3" t="inlineStr">
         <is>
-          <t>30.04.2007</t>
+          <t>01.10.2008</t>
         </is>
       </c>
     </row>
@@ -16930,30 +16931,30 @@
       </c>
       <c r="C441" s="7" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
+          <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="D441" s="5" t="n">
-        <v>196</v>
+        <v>387</v>
       </c>
       <c r="E441" s="5" t="inlineStr">
         <is>
-          <t>AE5015467</t>
+          <t>AE5856503</t>
         </is>
       </c>
       <c r="F441" s="6" t="inlineStr">
         <is>
-          <t>60110085590092</t>
+          <t>63112085680039</t>
         </is>
       </c>
       <c r="G441" s="6" t="inlineStr">
         <is>
-          <t>12.11.2025</t>
+          <t>14.01.2026</t>
         </is>
       </c>
       <c r="H441" s="6" t="inlineStr">
         <is>
-          <t>01.10.2008</t>
+          <t>31.12.2008</t>
         </is>
       </c>
     </row>
@@ -16963,35 +16964,35 @@
       </c>
       <c r="B442" s="3" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C442" s="4" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
+          <t>Abdishukurova Gulsevar Xusniddin qizi</t>
         </is>
       </c>
       <c r="D442" s="2" t="n">
-        <v>387</v>
+        <v>238</v>
       </c>
       <c r="E442" s="2" t="inlineStr">
         <is>
-          <t>AE5856503</t>
+          <t>AE4148917</t>
         </is>
       </c>
       <c r="F442" s="3" t="inlineStr">
         <is>
-          <t>63112085680039</t>
+          <t>60609085720090</t>
         </is>
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>14.01.2026</t>
+          <t>11.09.2025</t>
         </is>
       </c>
       <c r="H442" s="3" t="inlineStr">
         <is>
-          <t>31.12.2008</t>
+          <t>06.09.2008</t>
         </is>
       </c>
     </row>
@@ -17006,30 +17007,30 @@
       </c>
       <c r="C443" s="7" t="inlineStr">
         <is>
-          <t>Abdishukurova Gulsevar Xusniddin qizi</t>
+          <t>Ahmadova Munisa Bekzod qizi</t>
         </is>
       </c>
       <c r="D443" s="5" t="n">
-        <v>238</v>
+        <v>33</v>
       </c>
       <c r="E443" s="5" t="inlineStr">
         <is>
-          <t>AE4148917</t>
+          <t>AE4831229</t>
         </is>
       </c>
       <c r="F443" s="6" t="inlineStr">
         <is>
-          <t>60609085720090</t>
+          <t>60409085680037</t>
         </is>
       </c>
       <c r="G443" s="6" t="inlineStr">
         <is>
-          <t>11.09.2025</t>
+          <t>30.10.2025</t>
         </is>
       </c>
       <c r="H443" s="6" t="inlineStr">
         <is>
-          <t>06.09.2008</t>
+          <t>04.09.2008</t>
         </is>
       </c>
     </row>
@@ -17044,30 +17045,30 @@
       </c>
       <c r="C444" s="4" t="inlineStr">
         <is>
-          <t>Ahmadova Munisa Bekzod qizi</t>
+          <t>Ashirova Gulsanam Abduvali qizi</t>
         </is>
       </c>
       <c r="D444" s="2" t="n">
-        <v>33</v>
+        <v>224</v>
       </c>
       <c r="E444" s="2" t="inlineStr">
         <is>
-          <t>AE4831229</t>
+          <t>AD6820021</t>
         </is>
       </c>
       <c r="F444" s="3" t="inlineStr">
         <is>
-          <t>60409085680037</t>
+          <t>62311065590082</t>
         </is>
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>30.10.2025</t>
+          <t>15.04.2024</t>
         </is>
       </c>
       <c r="H444" s="3" t="inlineStr">
         <is>
-          <t>04.09.2008</t>
+          <t>23.11.2006</t>
         </is>
       </c>
     </row>
@@ -17082,30 +17083,30 @@
       </c>
       <c r="C445" s="7" t="inlineStr">
         <is>
-          <t>Ashirova Gulsanam Abduvali qizi</t>
+          <t>Berdimurodova Nafosat Javlon qizi</t>
         </is>
       </c>
       <c r="D445" s="5" t="n">
-        <v>224</v>
+        <v>46</v>
       </c>
       <c r="E445" s="5" t="inlineStr">
         <is>
-          <t>AD6820021</t>
+          <t>AD9709558</t>
         </is>
       </c>
       <c r="F445" s="6" t="inlineStr">
         <is>
-          <t>62311065590082</t>
+          <t>60904075680023</t>
         </is>
       </c>
       <c r="G445" s="6" t="inlineStr">
         <is>
-          <t>15.04.2024</t>
+          <t>06.12.2024</t>
         </is>
       </c>
       <c r="H445" s="6" t="inlineStr">
         <is>
-          <t>23.11.2006</t>
+          <t>09.04.2007</t>
         </is>
       </c>
     </row>
@@ -17120,30 +17121,30 @@
       </c>
       <c r="C446" s="4" t="inlineStr">
         <is>
-          <t>Berdimurodova Nafosat Javlon qizi</t>
+          <t>Choriyeva Zahro Xayrullo qizi</t>
         </is>
       </c>
       <c r="D446" s="2" t="n">
-        <v>46</v>
+        <v>109</v>
       </c>
       <c r="E446" s="2" t="inlineStr">
         <is>
-          <t>AD9709558</t>
+          <t>AD9654318</t>
         </is>
       </c>
       <c r="F446" s="3" t="inlineStr">
         <is>
-          <t>60904075680023</t>
+          <t>62802085590063</t>
         </is>
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>06.12.2024</t>
+          <t>03.12.2024</t>
         </is>
       </c>
       <c r="H446" s="3" t="inlineStr">
         <is>
-          <t>09.04.2007</t>
+          <t>28.02.2008</t>
         </is>
       </c>
     </row>
@@ -17158,30 +17159,30 @@
       </c>
       <c r="C447" s="7" t="inlineStr">
         <is>
-          <t>Choriyeva Zahro Xayrullo qizi</t>
+          <t>Ergasheva Shabbona Shodmon qizi</t>
         </is>
       </c>
       <c r="D447" s="5" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="E447" s="5" t="inlineStr">
         <is>
-          <t>AD9654318</t>
+          <t>AE2374828</t>
         </is>
       </c>
       <c r="F447" s="6" t="inlineStr">
         <is>
-          <t>62802085590063</t>
+          <t>61803085680050</t>
         </is>
       </c>
       <c r="G447" s="6" t="inlineStr">
         <is>
-          <t>03.12.2024</t>
+          <t>17.04.2025</t>
         </is>
       </c>
       <c r="H447" s="6" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>18.03.2008</t>
         </is>
       </c>
     </row>
@@ -17196,30 +17197,30 @@
       </c>
       <c r="C448" s="4" t="inlineStr">
         <is>
-          <t>Ergasheva Shabbona Shodmon qizi</t>
+          <t>Eshboboyeva Fotima Nurali qizi</t>
         </is>
       </c>
       <c r="D448" s="2" t="n">
-        <v>123</v>
+        <v>45</v>
       </c>
       <c r="E448" s="2" t="inlineStr">
         <is>
-          <t>AE2374828</t>
+          <t>AD0697178</t>
         </is>
       </c>
       <c r="F448" s="3" t="inlineStr">
         <is>
-          <t>61803085680050</t>
+          <t>61306045630044</t>
         </is>
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>17.04.2025</t>
+          <t>05.10.2021</t>
         </is>
       </c>
       <c r="H448" s="3" t="inlineStr">
         <is>
-          <t>18.03.2008</t>
+          <t>13.06.2004</t>
         </is>
       </c>
     </row>
@@ -17234,30 +17235,30 @@
       </c>
       <c r="C449" s="7" t="inlineStr">
         <is>
-          <t>Eshboboyeva Fotima Nurali qizi</t>
+          <t>G'ayratova Jasmina Sherali qizi</t>
         </is>
       </c>
       <c r="D449" s="5" t="n">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="E449" s="5" t="inlineStr">
         <is>
-          <t>AD0697178</t>
+          <t>AE3497923</t>
         </is>
       </c>
       <c r="F449" s="6" t="inlineStr">
         <is>
-          <t>61306045630044</t>
+          <t>60208085590146</t>
         </is>
       </c>
       <c r="G449" s="6" t="inlineStr">
         <is>
-          <t>05.10.2021</t>
+          <t>23.07.2025</t>
         </is>
       </c>
       <c r="H449" s="6" t="inlineStr">
         <is>
-          <t>13.06.2004</t>
+          <t>02.08.2008</t>
         </is>
       </c>
     </row>
@@ -17272,30 +17273,30 @@
       </c>
       <c r="C450" s="4" t="inlineStr">
         <is>
-          <t>G'ayratova Jasmina Sherali qizi</t>
+          <t>Ixtiyorova Niginabonu Xolovna</t>
         </is>
       </c>
       <c r="D450" s="2" t="n">
-        <v>97</v>
+        <v>227</v>
       </c>
       <c r="E450" s="2" t="inlineStr">
         <is>
-          <t>AE3497923</t>
+          <t>AD9335686</t>
         </is>
       </c>
       <c r="F450" s="3" t="inlineStr">
         <is>
-          <t>60208085590146</t>
+          <t>60710085680054</t>
         </is>
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>23.07.2025</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="H450" s="3" t="inlineStr">
         <is>
-          <t>02.08.2008</t>
+          <t>07.10.2008</t>
         </is>
       </c>
     </row>
@@ -17310,30 +17311,30 @@
       </c>
       <c r="C451" s="7" t="inlineStr">
         <is>
-          <t>Ixtiyorova Niginabonu Xolovna</t>
+          <t>Jabborova Bahoroy Shukurullo qizi</t>
         </is>
       </c>
       <c r="D451" s="5" t="n">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="E451" s="5" t="inlineStr">
         <is>
-          <t>AD9335686</t>
+          <t>AE4255446</t>
         </is>
       </c>
       <c r="F451" s="6" t="inlineStr">
         <is>
-          <t>60710085680054</t>
+          <t>61510085680048</t>
         </is>
       </c>
       <c r="G451" s="6" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>18.09.2025</t>
         </is>
       </c>
       <c r="H451" s="6" t="inlineStr">
         <is>
-          <t>07.10.2008</t>
+          <t>15.10.2008</t>
         </is>
       </c>
     </row>
@@ -17348,30 +17349,30 @@
       </c>
       <c r="C452" s="4" t="inlineStr">
         <is>
-          <t>Jabborova Bahoroy Shukurullo qizi</t>
+          <t>Jalilova Jasmina Jamshid qizi</t>
         </is>
       </c>
       <c r="D452" s="2" t="n">
-        <v>202</v>
+        <v>95</v>
       </c>
       <c r="E452" s="2" t="inlineStr">
         <is>
-          <t>AE4255446</t>
+          <t>AE4319796</t>
         </is>
       </c>
       <c r="F452" s="3" t="inlineStr">
         <is>
-          <t>61510085680048</t>
+          <t>60211085680014</t>
         </is>
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>18.09.2025</t>
+          <t>23.09.2025</t>
         </is>
       </c>
       <c r="H452" s="3" t="inlineStr">
         <is>
-          <t>15.10.2008</t>
+          <t>02.11.2008</t>
         </is>
       </c>
     </row>
@@ -17386,30 +17387,30 @@
       </c>
       <c r="C453" s="7" t="inlineStr">
         <is>
-          <t>Jalilova Jasmina Jamshid qizi</t>
+          <t>Jumayeva Muxlisa Komiljon qizi</t>
         </is>
       </c>
       <c r="D453" s="5" t="n">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="E453" s="5" t="inlineStr">
         <is>
-          <t>AE4319796</t>
+          <t>AB6258375</t>
         </is>
       </c>
       <c r="F453" s="6" t="inlineStr">
         <is>
-          <t>60211085680014</t>
+          <t>61701005680057</t>
         </is>
       </c>
       <c r="G453" s="6" t="inlineStr">
         <is>
-          <t>23.09.2025</t>
+          <t>29.03.2017</t>
         </is>
       </c>
       <c r="H453" s="6" t="inlineStr">
         <is>
-          <t>02.11.2008</t>
+          <t>17.01.2000</t>
         </is>
       </c>
     </row>
@@ -17424,30 +17425,30 @@
       </c>
       <c r="C454" s="4" t="inlineStr">
         <is>
-          <t>Jumayeva Muxlisa Komiljon qizi</t>
+          <t>Jurayeva Madina Odil qizi</t>
         </is>
       </c>
       <c r="D454" s="2" t="n">
-        <v>59</v>
+        <v>215</v>
       </c>
       <c r="E454" s="2" t="inlineStr">
         <is>
-          <t>AB6258375</t>
+          <t>AD9394305</t>
         </is>
       </c>
       <c r="F454" s="3" t="inlineStr">
         <is>
-          <t>61701005680057</t>
+          <t>62512075730060</t>
         </is>
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>29.03.2017</t>
+          <t>13.11.2024</t>
         </is>
       </c>
       <c r="H454" s="3" t="inlineStr">
         <is>
-          <t>17.01.2000</t>
+          <t>25.12.2007</t>
         </is>
       </c>
     </row>
@@ -17462,30 +17463,30 @@
       </c>
       <c r="C455" s="7" t="inlineStr">
         <is>
-          <t>Jurayeva Madina Odil qizi</t>
+          <t>Luxmonova Nozima Ilhom qizi</t>
         </is>
       </c>
       <c r="D455" s="5" t="n">
-        <v>215</v>
+        <v>139</v>
       </c>
       <c r="E455" s="5" t="inlineStr">
         <is>
-          <t>AD9394305</t>
+          <t>AE4290181</t>
         </is>
       </c>
       <c r="F455" s="6" t="inlineStr">
         <is>
-          <t>62512075730060</t>
+          <t>61611085680042</t>
         </is>
       </c>
       <c r="G455" s="6" t="inlineStr">
         <is>
-          <t>13.11.2024</t>
+          <t>22.09.2025</t>
         </is>
       </c>
       <c r="H455" s="6" t="inlineStr">
         <is>
-          <t>25.12.2007</t>
+          <t>16.11.2008</t>
         </is>
       </c>
     </row>
@@ -17500,30 +17501,30 @@
       </c>
       <c r="C456" s="4" t="inlineStr">
         <is>
-          <t>Luxmonova Nozima Ilhom qizi</t>
+          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
         </is>
       </c>
       <c r="D456" s="2" t="n">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="E456" s="2" t="inlineStr">
         <is>
-          <t>AE4290181</t>
+          <t>AD7829399</t>
         </is>
       </c>
       <c r="F456" s="3" t="inlineStr">
         <is>
-          <t>61611085680042</t>
+          <t>41902975680049</t>
         </is>
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>22.09.2025</t>
+          <t>11.07.2024</t>
         </is>
       </c>
       <c r="H456" s="3" t="inlineStr">
         <is>
-          <t>16.11.2008</t>
+          <t>19.02.1997</t>
         </is>
       </c>
     </row>
@@ -17538,30 +17539,30 @@
       </c>
       <c r="C457" s="7" t="inlineStr">
         <is>
-          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
+          <t>Murodova Munisa Muxtor qizi</t>
         </is>
       </c>
       <c r="D457" s="5" t="n">
-        <v>81</v>
+        <v>167</v>
       </c>
       <c r="E457" s="5" t="inlineStr">
         <is>
-          <t>AD7829399</t>
+          <t>AE2895049</t>
         </is>
       </c>
       <c r="F457" s="6" t="inlineStr">
         <is>
-          <t>41902975680049</t>
+          <t>62112085680050</t>
         </is>
       </c>
       <c r="G457" s="6" t="inlineStr">
         <is>
-          <t>11.07.2024</t>
+          <t>03.06.2025</t>
         </is>
       </c>
       <c r="H457" s="6" t="inlineStr">
         <is>
-          <t>19.02.1997</t>
+          <t>21.12.2008</t>
         </is>
       </c>
     </row>
@@ -17576,30 +17577,30 @@
       </c>
       <c r="C458" s="4" t="inlineStr">
         <is>
-          <t>Murodova Munisa Muxtor qizi</t>
+          <t>Muzrapova Ruhshona Asrorxon qizi</t>
         </is>
       </c>
       <c r="D458" s="2" t="n">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="E458" s="2" t="inlineStr">
         <is>
-          <t>AE2895049</t>
+          <t>AD9123240</t>
         </is>
       </c>
       <c r="F458" s="3" t="inlineStr">
         <is>
-          <t>62112085680050</t>
+          <t>62710075590066</t>
         </is>
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>03.06.2025</t>
+          <t>23.10.2024</t>
         </is>
       </c>
       <c r="H458" s="3" t="inlineStr">
         <is>
-          <t>21.12.2008</t>
+          <t>27.10.2007</t>
         </is>
       </c>
     </row>
@@ -17614,30 +17615,30 @@
       </c>
       <c r="C459" s="7" t="inlineStr">
         <is>
-          <t>Muzrapova Ruhshona Asrorxon qizi</t>
+          <t>Nazarova Munisa Erkin qizi</t>
         </is>
       </c>
       <c r="D459" s="5" t="n">
-        <v>69</v>
+        <v>258</v>
       </c>
       <c r="E459" s="5" t="inlineStr">
         <is>
-          <t>AD9123240</t>
+          <t>AE7685867</t>
         </is>
       </c>
       <c r="F459" s="6" t="inlineStr">
         <is>
-          <t>62710075590066</t>
+          <t>41205925680015</t>
         </is>
       </c>
       <c r="G459" s="6" t="inlineStr">
         <is>
-          <t>23.10.2024</t>
+          <t>17.06.2026</t>
         </is>
       </c>
       <c r="H459" s="6" t="inlineStr">
         <is>
-          <t>27.10.2007</t>
+          <t>12.05.1992</t>
         </is>
       </c>
     </row>
@@ -17652,30 +17653,28 @@
       </c>
       <c r="C460" s="4" t="inlineStr">
         <is>
-          <t>Nazarova Munisa Erkin qizi</t>
-        </is>
-      </c>
-      <c r="D460" s="2" t="n">
-        <v>258</v>
-      </c>
+          <t>Ne'matova Sevinch Hikmatullo qizi</t>
+        </is>
+      </c>
+      <c r="D460" s="2" t="inlineStr"/>
       <c r="E460" s="2" t="inlineStr">
         <is>
-          <t>AE7685867</t>
+          <t>AE7082532</t>
         </is>
       </c>
       <c r="F460" s="3" t="inlineStr">
         <is>
-          <t>41205925680015</t>
+          <t>60212085680048</t>
         </is>
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>17.06.2026</t>
+          <t>16.04.2026</t>
         </is>
       </c>
       <c r="H460" s="3" t="inlineStr">
         <is>
-          <t>12.05.1992</t>
+          <t>02.12.2008</t>
         </is>
       </c>
     </row>
@@ -17690,28 +17689,30 @@
       </c>
       <c r="C461" s="7" t="inlineStr">
         <is>
-          <t>Ne'matova Sevinch Hikmatullo qizi</t>
-        </is>
-      </c>
-      <c r="D461" s="5" t="inlineStr"/>
+          <t>Normurodova Gulsanam Elyor qizi</t>
+        </is>
+      </c>
+      <c r="D461" s="5" t="n">
+        <v>136</v>
+      </c>
       <c r="E461" s="5" t="inlineStr">
         <is>
-          <t>AE7082532</t>
+          <t>AE4817469</t>
         </is>
       </c>
       <c r="F461" s="6" t="inlineStr">
         <is>
-          <t>60212085680048</t>
+          <t>61809085680096</t>
         </is>
       </c>
       <c r="G461" s="6" t="inlineStr">
         <is>
-          <t>16.04.2026</t>
+          <t>29.10.2025</t>
         </is>
       </c>
       <c r="H461" s="6" t="inlineStr">
         <is>
-          <t>02.12.2008</t>
+          <t>18.09.2008</t>
         </is>
       </c>
     </row>
@@ -17726,30 +17727,30 @@
       </c>
       <c r="C462" s="4" t="inlineStr">
         <is>
-          <t>Normurodova Gulsanam Elyor qizi</t>
+          <t>Omonova Charos Orif qizi</t>
         </is>
       </c>
       <c r="D462" s="2" t="n">
-        <v>136</v>
+        <v>230</v>
       </c>
       <c r="E462" s="2" t="inlineStr">
         <is>
-          <t>AE4817469</t>
+          <t>AE1338424</t>
         </is>
       </c>
       <c r="F462" s="3" t="inlineStr">
         <is>
-          <t>61809085680096</t>
+          <t>40306985590014</t>
         </is>
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>29.10.2025</t>
+          <t>23.01.2025</t>
         </is>
       </c>
       <c r="H462" s="3" t="inlineStr">
         <is>
-          <t>18.09.2008</t>
+          <t>03.06.1998</t>
         </is>
       </c>
     </row>
@@ -17764,30 +17765,28 @@
       </c>
       <c r="C463" s="7" t="inlineStr">
         <is>
-          <t>Omonova Charos Orif qizi</t>
-        </is>
-      </c>
-      <c r="D463" s="5" t="n">
-        <v>230</v>
-      </c>
+          <t>Oripova Sevinch G'olib qizi</t>
+        </is>
+      </c>
+      <c r="D463" s="5" t="inlineStr"/>
       <c r="E463" s="5" t="inlineStr">
         <is>
-          <t>AE1338424</t>
+          <t>AE3333890</t>
         </is>
       </c>
       <c r="F463" s="6" t="inlineStr">
         <is>
-          <t>40306985590014</t>
+          <t>62007085680095</t>
         </is>
       </c>
       <c r="G463" s="6" t="inlineStr">
         <is>
-          <t>23.01.2025</t>
+          <t>09.07.2025</t>
         </is>
       </c>
       <c r="H463" s="6" t="inlineStr">
         <is>
-          <t>03.06.1998</t>
+          <t>20.07.2008</t>
         </is>
       </c>
     </row>
@@ -17802,28 +17801,30 @@
       </c>
       <c r="C464" s="4" t="inlineStr">
         <is>
-          <t>Oripova Sevinch G'olib qizi</t>
-        </is>
-      </c>
-      <c r="D464" s="2" t="inlineStr"/>
+          <t>Ozodova Klara Fayzullayevna</t>
+        </is>
+      </c>
+      <c r="D464" s="2" t="n">
+        <v>285</v>
+      </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>AE3333890</t>
+          <t>AD6663341</t>
         </is>
       </c>
       <c r="F464" s="3" t="inlineStr">
         <is>
-          <t>62007085680095</t>
+          <t>60803075590140</t>
         </is>
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>09.07.2025</t>
+          <t>01.04.2024</t>
         </is>
       </c>
       <c r="H464" s="3" t="inlineStr">
         <is>
-          <t>20.07.2008</t>
+          <t>08.03.2007</t>
         </is>
       </c>
     </row>
@@ -17838,30 +17839,30 @@
       </c>
       <c r="C465" s="7" t="inlineStr">
         <is>
-          <t>Ozodova Klara Fayzullayevna</t>
+          <t>Saidova Dilso'z Ilyos qizi</t>
         </is>
       </c>
       <c r="D465" s="5" t="n">
-        <v>285</v>
+        <v>67</v>
       </c>
       <c r="E465" s="5" t="inlineStr">
         <is>
-          <t>AD6663341</t>
+          <t>AE6043288</t>
         </is>
       </c>
       <c r="F465" s="6" t="inlineStr">
         <is>
-          <t>60803075590140</t>
+          <t>60511085680024</t>
         </is>
       </c>
       <c r="G465" s="6" t="inlineStr">
         <is>
-          <t>01.04.2024</t>
+          <t>26.01.2026</t>
         </is>
       </c>
       <c r="H465" s="6" t="inlineStr">
         <is>
-          <t>08.03.2007</t>
+          <t>05.11.2008</t>
         </is>
       </c>
     </row>
@@ -17876,30 +17877,30 @@
       </c>
       <c r="C466" s="4" t="inlineStr">
         <is>
-          <t>Saidova Dilso'z Ilyos qizi</t>
+          <t>Sharipova Diyora Jasur qizi</t>
         </is>
       </c>
       <c r="D466" s="2" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E466" s="2" t="inlineStr">
         <is>
-          <t>AE6043288</t>
+          <t>AE5776687</t>
         </is>
       </c>
       <c r="F466" s="3" t="inlineStr">
         <is>
-          <t>60511085680024</t>
+          <t>62307095590022</t>
         </is>
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>26.01.2026</t>
+          <t>09.01.2026</t>
         </is>
       </c>
       <c r="H466" s="3" t="inlineStr">
         <is>
-          <t>05.11.2008</t>
+          <t>23.07.2009</t>
         </is>
       </c>
     </row>
@@ -17914,30 +17915,30 @@
       </c>
       <c r="C467" s="7" t="inlineStr">
         <is>
-          <t>Sharipova Diyora Jasur qizi</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="D467" s="5" t="n">
-        <v>57</v>
+        <v>388</v>
       </c>
       <c r="E467" s="5" t="inlineStr">
         <is>
-          <t>AE5776687</t>
+          <t>AD0914473</t>
         </is>
       </c>
       <c r="F467" s="6" t="inlineStr">
         <is>
-          <t>62307095590022</t>
+          <t>62803055590089</t>
         </is>
       </c>
       <c r="G467" s="6" t="inlineStr">
         <is>
-          <t>09.01.2026</t>
+          <t>14.12.2021</t>
         </is>
       </c>
       <c r="H467" s="6" t="inlineStr">
         <is>
-          <t>23.07.2009</t>
+          <t>28.03.2005</t>
         </is>
       </c>
     </row>
@@ -17952,30 +17953,30 @@
       </c>
       <c r="C468" s="4" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="D468" s="2" t="n">
-        <v>388</v>
+        <v>276</v>
       </c>
       <c r="E468" s="2" t="inlineStr">
         <is>
-          <t>AD0914473</t>
+          <t>AD6026687</t>
         </is>
       </c>
       <c r="F468" s="3" t="inlineStr">
         <is>
-          <t>62803055590089</t>
+          <t>61407075590019</t>
         </is>
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>14.12.2021</t>
+          <t>06.02.2024</t>
         </is>
       </c>
       <c r="H468" s="3" t="inlineStr">
         <is>
-          <t>28.03.2005</t>
+          <t>14.07.2007</t>
         </is>
       </c>
     </row>
@@ -17990,30 +17991,30 @@
       </c>
       <c r="C469" s="7" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="D469" s="5" t="n">
-        <v>276</v>
+        <v>218</v>
       </c>
       <c r="E469" s="5" t="inlineStr">
         <is>
-          <t>AD6026687</t>
+          <t>AE5949204</t>
         </is>
       </c>
       <c r="F469" s="6" t="inlineStr">
         <is>
-          <t>61407075590019</t>
+          <t>62710085680012</t>
         </is>
       </c>
       <c r="G469" s="6" t="inlineStr">
         <is>
-          <t>06.02.2024</t>
+          <t>20.01.2026</t>
         </is>
       </c>
       <c r="H469" s="6" t="inlineStr">
         <is>
-          <t>14.07.2007</t>
+          <t>27.10.2008</t>
         </is>
       </c>
     </row>
@@ -18028,20 +18029,20 @@
       </c>
       <c r="C470" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="D470" s="2" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E470" s="2" t="inlineStr">
         <is>
-          <t>AE5949204</t>
+          <t>AE5949016</t>
         </is>
       </c>
       <c r="F470" s="3" t="inlineStr">
         <is>
-          <t>62710085680012</t>
+          <t>62710085680029</t>
         </is>
       </c>
       <c r="G470" s="3" t="inlineStr">
@@ -18066,30 +18067,30 @@
       </c>
       <c r="C471" s="7" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="D471" s="5" t="n">
-        <v>219</v>
+        <v>188</v>
       </c>
       <c r="E471" s="5" t="inlineStr">
         <is>
-          <t>AE5949016</t>
+          <t>AE4384190</t>
         </is>
       </c>
       <c r="F471" s="6" t="inlineStr">
         <is>
-          <t>62710085680029</t>
+          <t>61810085590061</t>
         </is>
       </c>
       <c r="G471" s="6" t="inlineStr">
         <is>
-          <t>20.01.2026</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="H471" s="6" t="inlineStr">
         <is>
-          <t>27.10.2008</t>
+          <t>18.10.2008</t>
         </is>
       </c>
     </row>
@@ -18104,30 +18105,30 @@
       </c>
       <c r="C472" s="4" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
         </is>
       </c>
       <c r="D472" s="2" t="n">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E472" s="2" t="inlineStr">
         <is>
-          <t>AE4384190</t>
+          <t>AD8362477</t>
         </is>
       </c>
       <c r="F472" s="3" t="inlineStr">
         <is>
-          <t>61810085590061</t>
+          <t>42601955730024</t>
         </is>
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>23.08.2024</t>
         </is>
       </c>
       <c r="H472" s="3" t="inlineStr">
         <is>
-          <t>18.10.2008</t>
+          <t>26.01.1995</t>
         </is>
       </c>
     </row>
@@ -18142,30 +18143,30 @@
       </c>
       <c r="C473" s="7" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
+          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="D473" s="5" t="n">
-        <v>183</v>
+        <v>118</v>
       </c>
       <c r="E473" s="5" t="inlineStr">
         <is>
-          <t>AD8362477</t>
+          <t>AE1419035</t>
         </is>
       </c>
       <c r="F473" s="6" t="inlineStr">
         <is>
-          <t>42601955730024</t>
+          <t>61309085590066</t>
         </is>
       </c>
       <c r="G473" s="6" t="inlineStr">
         <is>
-          <t>23.08.2024</t>
+          <t>29.01.2025</t>
         </is>
       </c>
       <c r="H473" s="6" t="inlineStr">
         <is>
-          <t>26.01.1995</t>
+          <t>13.09.2008</t>
         </is>
       </c>
     </row>
@@ -18175,35 +18176,35 @@
       </c>
       <c r="B474" s="3" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C474" s="4" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+          <t>Abdinazarova Dilafro'z Burxon qizi</t>
         </is>
       </c>
       <c r="D474" s="2" t="n">
-        <v>118</v>
+        <v>273</v>
       </c>
       <c r="E474" s="2" t="inlineStr">
         <is>
-          <t>AE1419035</t>
+          <t>AE3704528</t>
         </is>
       </c>
       <c r="F474" s="3" t="inlineStr">
         <is>
-          <t>61309085590066</t>
+          <t>40401955680037</t>
         </is>
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>29.01.2025</t>
+          <t>08.08.2025</t>
         </is>
       </c>
       <c r="H474" s="3" t="inlineStr">
         <is>
-          <t>13.09.2008</t>
+          <t>04.01.1995</t>
         </is>
       </c>
     </row>
@@ -18218,30 +18219,30 @@
       </c>
       <c r="C475" s="7" t="inlineStr">
         <is>
-          <t>Abdinazarova Dilafro'z Burxon qizi</t>
+          <t>Abdixoliqova Elmira Farxod qizi</t>
         </is>
       </c>
       <c r="D475" s="5" t="n">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="E475" s="5" t="inlineStr">
         <is>
-          <t>AE3704528</t>
+          <t>AE4512271</t>
         </is>
       </c>
       <c r="F475" s="6" t="inlineStr">
         <is>
-          <t>40401955680037</t>
+          <t>62501095720012</t>
         </is>
       </c>
       <c r="G475" s="6" t="inlineStr">
         <is>
-          <t>08.08.2025</t>
+          <t>07.10.2025</t>
         </is>
       </c>
       <c r="H475" s="6" t="inlineStr">
         <is>
-          <t>04.01.1995</t>
+          <t>25.01.2009</t>
         </is>
       </c>
     </row>
@@ -18256,30 +18257,30 @@
       </c>
       <c r="C476" s="4" t="inlineStr">
         <is>
-          <t>Abdixoliqova Elmira Farxod qizi</t>
+          <t>Azimova Zahroxon Abdirauf qizi</t>
         </is>
       </c>
       <c r="D476" s="2" t="n">
-        <v>286</v>
+        <v>318</v>
       </c>
       <c r="E476" s="2" t="inlineStr">
         <is>
-          <t>AE4512271</t>
+          <t>AD5290004</t>
         </is>
       </c>
       <c r="F476" s="3" t="inlineStr">
         <is>
-          <t>62501095720012</t>
+          <t>61312065590013</t>
         </is>
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>07.10.2025</t>
+          <t>01.12.2023</t>
         </is>
       </c>
       <c r="H476" s="3" t="inlineStr">
         <is>
-          <t>25.01.2009</t>
+          <t>13.12.2006</t>
         </is>
       </c>
     </row>
@@ -18294,30 +18295,30 @@
       </c>
       <c r="C477" s="7" t="inlineStr">
         <is>
-          <t>Azimova Zahroxon Abdirauf qizi</t>
+          <t>Bahodirova Asila Olmos qizi</t>
         </is>
       </c>
       <c r="D477" s="5" t="n">
-        <v>318</v>
+        <v>44</v>
       </c>
       <c r="E477" s="5" t="inlineStr">
         <is>
-          <t>AD5290004</t>
+          <t>AE1222596</t>
         </is>
       </c>
       <c r="F477" s="6" t="inlineStr">
         <is>
-          <t>61312065590013</t>
+          <t>61711085590032</t>
         </is>
       </c>
       <c r="G477" s="6" t="inlineStr">
         <is>
-          <t>01.12.2023</t>
+          <t>16.01.2025</t>
         </is>
       </c>
       <c r="H477" s="6" t="inlineStr">
         <is>
-          <t>13.12.2006</t>
+          <t>17.11.2008</t>
         </is>
       </c>
     </row>
@@ -18332,30 +18333,30 @@
       </c>
       <c r="C478" s="4" t="inlineStr">
         <is>
-          <t>Bahodirova Asila Olmos qizi</t>
+          <t>Davlatova Gulnoza Husan qizi</t>
         </is>
       </c>
       <c r="D478" s="2" t="n">
-        <v>44</v>
+        <v>310</v>
       </c>
       <c r="E478" s="2" t="inlineStr">
         <is>
-          <t>AE1222596</t>
+          <t>AD8208717</t>
         </is>
       </c>
       <c r="F478" s="3" t="inlineStr">
         <is>
-          <t>61711085590032</t>
+          <t>41508955590021</t>
         </is>
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>16.01.2025</t>
+          <t>12.08.2024</t>
         </is>
       </c>
       <c r="H478" s="3" t="inlineStr">
         <is>
-          <t>17.11.2008</t>
+          <t>15.08.1995</t>
         </is>
       </c>
     </row>
@@ -18370,30 +18371,30 @@
       </c>
       <c r="C479" s="7" t="inlineStr">
         <is>
-          <t>Davlatova Gulnoza Husan qizi</t>
+          <t>Eshimova Zilola Bekzod qizi</t>
         </is>
       </c>
       <c r="D479" s="5" t="n">
-        <v>310</v>
+        <v>174</v>
       </c>
       <c r="E479" s="5" t="inlineStr">
         <is>
-          <t>AD8208717</t>
+          <t>AE2935693</t>
         </is>
       </c>
       <c r="F479" s="6" t="inlineStr">
         <is>
-          <t>41508955590021</t>
+          <t>61506085730076</t>
         </is>
       </c>
       <c r="G479" s="6" t="inlineStr">
         <is>
-          <t>12.08.2024</t>
+          <t>09.06.2025</t>
         </is>
       </c>
       <c r="H479" s="6" t="inlineStr">
         <is>
-          <t>15.08.1995</t>
+          <t>15.06.2008</t>
         </is>
       </c>
     </row>
@@ -18408,30 +18409,28 @@
       </c>
       <c r="C480" s="4" t="inlineStr">
         <is>
-          <t>Eshimova Zilola Bekzod qizi</t>
-        </is>
-      </c>
-      <c r="D480" s="2" t="n">
-        <v>174</v>
-      </c>
+          <t>Irgasheva Dinora Shodmon qizi</t>
+        </is>
+      </c>
+      <c r="D480" s="2" t="inlineStr"/>
       <c r="E480" s="2" t="inlineStr">
         <is>
-          <t>AE2935693</t>
+          <t>AC 2430931</t>
         </is>
       </c>
       <c r="F480" s="3" t="inlineStr">
         <is>
-          <t>61506085730076</t>
+          <t>60106035590029</t>
         </is>
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>09.06.2025</t>
+          <t>15.11.2019</t>
         </is>
       </c>
       <c r="H480" s="3" t="inlineStr">
         <is>
-          <t>15.06.2008</t>
+          <t>01.06.2003</t>
         </is>
       </c>
     </row>
@@ -18446,28 +18445,30 @@
       </c>
       <c r="C481" s="7" t="inlineStr">
         <is>
-          <t>Irgasheva Dinora Shodmon qizi</t>
-        </is>
-      </c>
-      <c r="D481" s="5" t="inlineStr"/>
+          <t>Jalilova Shabnam Ozodjon qizi</t>
+        </is>
+      </c>
+      <c r="D481" s="5" t="n">
+        <v>17</v>
+      </c>
       <c r="E481" s="5" t="inlineStr">
         <is>
-          <t>AC 2430931</t>
+          <t>AD9937321</t>
         </is>
       </c>
       <c r="F481" s="6" t="inlineStr">
         <is>
-          <t>60106035590029</t>
+          <t>60603085590037</t>
         </is>
       </c>
       <c r="G481" s="6" t="inlineStr">
         <is>
-          <t>15.11.2019</t>
+          <t>24.12.2024</t>
         </is>
       </c>
       <c r="H481" s="6" t="inlineStr">
         <is>
-          <t>01.06.2003</t>
+          <t>06.03.2008</t>
         </is>
       </c>
     </row>
@@ -18482,30 +18483,30 @@
       </c>
       <c r="C482" s="4" t="inlineStr">
         <is>
-          <t>Jalilova Shabnam Ozodjon qizi</t>
+          <t>Jumayeva Husnida Shovkat qizi</t>
         </is>
       </c>
       <c r="D482" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E482" s="2" t="inlineStr">
         <is>
-          <t>AD9937321</t>
+          <t>AE6299685</t>
         </is>
       </c>
       <c r="F482" s="3" t="inlineStr">
         <is>
-          <t>60603085590037</t>
+          <t>60907085590063</t>
         </is>
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>24.12.2024</t>
+          <t>11.02.2026</t>
         </is>
       </c>
       <c r="H482" s="3" t="inlineStr">
         <is>
-          <t>06.03.2008</t>
+          <t>09.07.2008</t>
         </is>
       </c>
     </row>
@@ -18520,30 +18521,30 @@
       </c>
       <c r="C483" s="7" t="inlineStr">
         <is>
-          <t>Jumayeva Husnida Shovkat qizi</t>
+          <t>Karimova Nozliya Rustamovna</t>
         </is>
       </c>
       <c r="D483" s="5" t="n">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="E483" s="5" t="inlineStr">
         <is>
-          <t>AE6299685</t>
+          <t>AE4674508</t>
         </is>
       </c>
       <c r="F483" s="6" t="inlineStr">
         <is>
-          <t>60907085590063</t>
+          <t>61502085680047</t>
         </is>
       </c>
       <c r="G483" s="6" t="inlineStr">
         <is>
-          <t>11.02.2026</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="H483" s="6" t="inlineStr">
         <is>
-          <t>09.07.2008</t>
+          <t>15.02.2008</t>
         </is>
       </c>
     </row>
@@ -18558,30 +18559,30 @@
       </c>
       <c r="C484" s="4" t="inlineStr">
         <is>
-          <t>Karimova Nozliya Rustamovna</t>
+          <t>Mahmadmurodova Sevara Safarali qizi</t>
         </is>
       </c>
       <c r="D484" s="2" t="n">
-        <v>250</v>
+        <v>390</v>
       </c>
       <c r="E484" s="2" t="inlineStr">
         <is>
-          <t>AE4674508</t>
+          <t>AE2103843</t>
         </is>
       </c>
       <c r="F484" s="3" t="inlineStr">
         <is>
-          <t>61502085680047</t>
+          <t>60705005680087</t>
         </is>
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>18.10.2025</t>
+          <t>27.03.2025</t>
         </is>
       </c>
       <c r="H484" s="3" t="inlineStr">
         <is>
-          <t>15.02.2008</t>
+          <t>07.05.2000</t>
         </is>
       </c>
     </row>
@@ -18596,30 +18597,30 @@
       </c>
       <c r="C485" s="7" t="inlineStr">
         <is>
-          <t>Mahmadmurodova Sevara Safarali qizi</t>
+          <t>Mahmatqulova Nilufar Qayum qizi</t>
         </is>
       </c>
       <c r="D485" s="5" t="n">
-        <v>390</v>
+        <v>314</v>
       </c>
       <c r="E485" s="5" t="inlineStr">
         <is>
-          <t>AE2103843</t>
+          <t>AE6047826</t>
         </is>
       </c>
       <c r="F485" s="6" t="inlineStr">
         <is>
-          <t>60705005680087</t>
+          <t>60806085590115</t>
         </is>
       </c>
       <c r="G485" s="6" t="inlineStr">
         <is>
-          <t>27.03.2025</t>
+          <t>26.01.2026</t>
         </is>
       </c>
       <c r="H485" s="6" t="inlineStr">
         <is>
-          <t>07.05.2000</t>
+          <t>08.06.2008</t>
         </is>
       </c>
     </row>
@@ -18634,30 +18635,30 @@
       </c>
       <c r="C486" s="4" t="inlineStr">
         <is>
-          <t>Mahmatqulova Nilufar Qayum qizi</t>
+          <t>Mahmudova Maftuna To'ra qizi</t>
         </is>
       </c>
       <c r="D486" s="2" t="n">
-        <v>314</v>
+        <v>120</v>
       </c>
       <c r="E486" s="2" t="inlineStr">
         <is>
-          <t>AE6047826</t>
+          <t>AE4270256</t>
         </is>
       </c>
       <c r="F486" s="3" t="inlineStr">
         <is>
-          <t>60806085590115</t>
+          <t>61707085680068</t>
         </is>
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>26.01.2026</t>
+          <t>19.09.2025</t>
         </is>
       </c>
       <c r="H486" s="3" t="inlineStr">
         <is>
-          <t>08.06.2008</t>
+          <t>17.07.2008</t>
         </is>
       </c>
     </row>
@@ -18672,20 +18673,20 @@
       </c>
       <c r="C487" s="7" t="inlineStr">
         <is>
-          <t>Mahmudova Maftuna To'ra qizi</t>
+          <t>Mannonova Shahrizoda Nosir qizi</t>
         </is>
       </c>
       <c r="D487" s="5" t="n">
-        <v>120</v>
+        <v>199</v>
       </c>
       <c r="E487" s="5" t="inlineStr">
         <is>
-          <t>AE4270256</t>
+          <t>AE4263249</t>
         </is>
       </c>
       <c r="F487" s="6" t="inlineStr">
         <is>
-          <t>61707085680068</t>
+          <t>60710085680047</t>
         </is>
       </c>
       <c r="G487" s="6" t="inlineStr">
@@ -18695,7 +18696,7 @@
       </c>
       <c r="H487" s="6" t="inlineStr">
         <is>
-          <t>17.07.2008</t>
+          <t>07.10.2008</t>
         </is>
       </c>
     </row>
@@ -18710,30 +18711,30 @@
       </c>
       <c r="C488" s="4" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda Nosir qizi</t>
+          <t>Maxmarajabova Zerda Hasan qizi</t>
         </is>
       </c>
       <c r="D488" s="2" t="n">
-        <v>199</v>
+        <v>253</v>
       </c>
       <c r="E488" s="2" t="inlineStr">
         <is>
-          <t>AE4263249</t>
+          <t>AE5221552</t>
         </is>
       </c>
       <c r="F488" s="3" t="inlineStr">
         <is>
-          <t>60710085680047</t>
+          <t>60106075720246</t>
         </is>
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>19.09.2025</t>
+          <t>28.11.2025</t>
         </is>
       </c>
       <c r="H488" s="3" t="inlineStr">
         <is>
-          <t>07.10.2008</t>
+          <t>01.06.2007</t>
         </is>
       </c>
     </row>
@@ -18748,30 +18749,30 @@
       </c>
       <c r="C489" s="7" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda Hasan qizi</t>
+          <t>Muminova Sevinch Uchqun qizi</t>
         </is>
       </c>
       <c r="D489" s="5" t="n">
-        <v>253</v>
+        <v>163</v>
       </c>
       <c r="E489" s="5" t="inlineStr">
         <is>
-          <t>AE5221552</t>
+          <t>AE2259069</t>
         </is>
       </c>
       <c r="F489" s="6" t="inlineStr">
         <is>
-          <t>60106075720246</t>
+          <t>63001085590111</t>
         </is>
       </c>
       <c r="G489" s="6" t="inlineStr">
         <is>
-          <t>28.11.2025</t>
+          <t>09.04.2025</t>
         </is>
       </c>
       <c r="H489" s="6" t="inlineStr">
         <is>
-          <t>01.06.2007</t>
+          <t>30.01.2008</t>
         </is>
       </c>
     </row>
@@ -18786,30 +18787,30 @@
       </c>
       <c r="C490" s="4" t="inlineStr">
         <is>
-          <t>Muminova Sevinch Uchqun qizi</t>
+          <t>Mustafayeva Nargiza Ulug'bek qizi</t>
         </is>
       </c>
       <c r="D490" s="2" t="n">
-        <v>163</v>
+        <v>206</v>
       </c>
       <c r="E490" s="2" t="inlineStr">
         <is>
-          <t>AE2259069</t>
+          <t>AB8521319</t>
         </is>
       </c>
       <c r="F490" s="3" t="inlineStr">
         <is>
-          <t>63001085590111</t>
+          <t>62906005590060</t>
         </is>
       </c>
       <c r="G490" s="3" t="inlineStr">
         <is>
-          <t>09.04.2025</t>
+          <t>02.01.2018</t>
         </is>
       </c>
       <c r="H490" s="3" t="inlineStr">
         <is>
-          <t>30.01.2008</t>
+          <t>29.06.2000</t>
         </is>
       </c>
     </row>
@@ -18824,30 +18825,30 @@
       </c>
       <c r="C491" s="7" t="inlineStr">
         <is>
-          <t>Mustafayeva Nargiza Ulug'bek qizi</t>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
         </is>
       </c>
       <c r="D491" s="5" t="n">
-        <v>206</v>
+        <v>176</v>
       </c>
       <c r="E491" s="5" t="inlineStr">
         <is>
-          <t>AB8521319</t>
+          <t>AE2428256</t>
         </is>
       </c>
       <c r="F491" s="6" t="inlineStr">
         <is>
-          <t>62906005590060</t>
+          <t>60506085590066</t>
         </is>
       </c>
       <c r="G491" s="6" t="inlineStr">
         <is>
-          <t>02.01.2018</t>
+          <t>22.04.2025</t>
         </is>
       </c>
       <c r="H491" s="6" t="inlineStr">
         <is>
-          <t>29.06.2000</t>
+          <t>05.06.2008</t>
         </is>
       </c>
     </row>
@@ -18862,30 +18863,30 @@
       </c>
       <c r="C492" s="4" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Narziyeva Intizor Iskandar qizi</t>
         </is>
       </c>
       <c r="D492" s="2" t="n">
-        <v>176</v>
+        <v>212</v>
       </c>
       <c r="E492" s="2" t="inlineStr">
         <is>
-          <t>AE2428256</t>
+          <t>AB5359926</t>
         </is>
       </c>
       <c r="F492" s="3" t="inlineStr">
         <is>
-          <t>60506085590066</t>
+          <t>40211995680023</t>
         </is>
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>22.04.2025</t>
+          <t>12.12.2016</t>
         </is>
       </c>
       <c r="H492" s="3" t="inlineStr">
         <is>
-          <t>05.06.2008</t>
+          <t>02.11.1999</t>
         </is>
       </c>
     </row>
@@ -18900,30 +18901,30 @@
       </c>
       <c r="C493" s="7" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
+          <t>Niyozova Sevara Turoqulovna</t>
         </is>
       </c>
       <c r="D493" s="5" t="n">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="E493" s="5" t="inlineStr">
         <is>
-          <t>AB5359926</t>
+          <t>AD9706738</t>
         </is>
       </c>
       <c r="F493" s="6" t="inlineStr">
         <is>
-          <t>40211995680023</t>
+          <t>412068 9256 0120</t>
         </is>
       </c>
       <c r="G493" s="6" t="inlineStr">
         <is>
-          <t>12.12.2016</t>
+          <t>05.12.2024</t>
         </is>
       </c>
       <c r="H493" s="6" t="inlineStr">
         <is>
-          <t>02.11.1999</t>
+          <t>12.06.1989</t>
         </is>
       </c>
     </row>
@@ -18938,30 +18939,30 @@
       </c>
       <c r="C494" s="4" t="inlineStr">
         <is>
-          <t>Niyozova Sevara Turoqulovna</t>
+          <t>Nurillayeva Sevinch Mashrab qizi</t>
         </is>
       </c>
       <c r="D494" s="2" t="n">
-        <v>304</v>
+        <v>246</v>
       </c>
       <c r="E494" s="2" t="inlineStr">
         <is>
-          <t>AD9706738</t>
+          <t>AD9494409</t>
         </is>
       </c>
       <c r="F494" s="3" t="inlineStr">
         <is>
-          <t>412068 9256 0120</t>
+          <t>60504085680019</t>
         </is>
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>05.12.2024</t>
+          <t>26.09.2025</t>
         </is>
       </c>
       <c r="H494" s="3" t="inlineStr">
         <is>
-          <t>12.06.1989</t>
+          <t>05.04.2008</t>
         </is>
       </c>
     </row>
@@ -18976,30 +18977,30 @@
       </c>
       <c r="C495" s="7" t="inlineStr">
         <is>
-          <t>Nurillayeva Sevinch Mashrab qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="D495" s="5" t="n">
-        <v>246</v>
+        <v>47</v>
       </c>
       <c r="E495" s="5" t="inlineStr">
         <is>
-          <t>AD9494409</t>
+          <t>AD0776916</t>
         </is>
       </c>
       <c r="F495" s="6" t="inlineStr">
         <is>
-          <t>60504085680019</t>
+          <t>62012045590040</t>
         </is>
       </c>
       <c r="G495" s="6" t="inlineStr">
         <is>
-          <t>26.09.2025</t>
+          <t>02.11.2021</t>
         </is>
       </c>
       <c r="H495" s="6" t="inlineStr">
         <is>
-          <t>05.04.2008</t>
+          <t>20.12.2004</t>
         </is>
       </c>
     </row>
@@ -19014,30 +19015,30 @@
       </c>
       <c r="C496" s="4" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
         </is>
       </c>
       <c r="D496" s="2" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E496" s="2" t="inlineStr">
         <is>
-          <t>AD0776916</t>
+          <t>AE2118072</t>
         </is>
       </c>
       <c r="F496" s="3" t="inlineStr">
         <is>
-          <t>62012045590040</t>
+          <t>62201085590064</t>
         </is>
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>02.11.2021</t>
+          <t>28.03.2025</t>
         </is>
       </c>
       <c r="H496" s="3" t="inlineStr">
         <is>
-          <t>20.12.2004</t>
+          <t>22.01.2008</t>
         </is>
       </c>
     </row>
@@ -19052,30 +19053,30 @@
       </c>
       <c r="C497" s="7" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Quchqarova Zebiniso Farhod qizi</t>
         </is>
       </c>
       <c r="D497" s="5" t="n">
-        <v>55</v>
+        <v>187</v>
       </c>
       <c r="E497" s="5" t="inlineStr">
         <is>
-          <t>AE2118072</t>
+          <t>AE1143288</t>
         </is>
       </c>
       <c r="F497" s="6" t="inlineStr">
         <is>
-          <t>62201085590064</t>
+          <t>62911085630012</t>
         </is>
       </c>
       <c r="G497" s="6" t="inlineStr">
         <is>
-          <t>28.03.2025</t>
+          <t>10.01.2025</t>
         </is>
       </c>
       <c r="H497" s="6" t="inlineStr">
         <is>
-          <t>22.01.2008</t>
+          <t>29.11.2008</t>
         </is>
       </c>
     </row>
@@ -19090,30 +19091,30 @@
       </c>
       <c r="C498" s="4" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso Farhod qizi</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="D498" s="2" t="n">
-        <v>187</v>
+        <v>271</v>
       </c>
       <c r="E498" s="2" t="inlineStr">
         <is>
-          <t>AE1143288</t>
+          <t>AE4246251</t>
         </is>
       </c>
       <c r="F498" s="3" t="inlineStr">
         <is>
-          <t>62911085630012</t>
+          <t>62702085680028</t>
         </is>
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>10.01.2025</t>
+          <t>18.09.2025</t>
         </is>
       </c>
       <c r="H498" s="3" t="inlineStr">
         <is>
-          <t>29.11.2008</t>
+          <t>27.02.2008</t>
         </is>
       </c>
     </row>
@@ -19128,30 +19129,30 @@
       </c>
       <c r="C499" s="7" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="D499" s="5" t="n">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="E499" s="5" t="inlineStr">
         <is>
-          <t>AE4246251</t>
+          <t>AD8686485</t>
         </is>
       </c>
       <c r="F499" s="6" t="inlineStr">
         <is>
-          <t>62702085680028</t>
+          <t>62201085590019</t>
         </is>
       </c>
       <c r="G499" s="6" t="inlineStr">
         <is>
-          <t>18.09.2025</t>
+          <t>19.09.2024</t>
         </is>
       </c>
       <c r="H499" s="6" t="inlineStr">
         <is>
-          <t>27.02.2008</t>
+          <t>22.01.2008</t>
         </is>
       </c>
     </row>
@@ -19166,30 +19167,30 @@
       </c>
       <c r="C500" s="4" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="D500" s="2" t="n">
-        <v>254</v>
+        <v>32</v>
       </c>
       <c r="E500" s="2" t="inlineStr">
         <is>
-          <t>AD8686485</t>
+          <t>AC1805235</t>
         </is>
       </c>
       <c r="F500" s="3" t="inlineStr">
         <is>
-          <t>62201085590019</t>
+          <t>60409015590065</t>
         </is>
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>19.09.2024</t>
+          <t>08.04.2019</t>
         </is>
       </c>
       <c r="H500" s="3" t="inlineStr">
         <is>
-          <t>22.01.2008</t>
+          <t>04.09.2001</t>
         </is>
       </c>
     </row>
@@ -19204,30 +19205,28 @@
       </c>
       <c r="C501" s="7" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
-        </is>
-      </c>
-      <c r="D501" s="5" t="n">
-        <v>32</v>
-      </c>
+          <t>Sayfieva Sarvinoz Zafar qizi</t>
+        </is>
+      </c>
+      <c r="D501" s="5" t="inlineStr"/>
       <c r="E501" s="5" t="inlineStr">
         <is>
-          <t>AC1805235</t>
+          <t>AB6304158</t>
         </is>
       </c>
       <c r="F501" s="6" t="inlineStr">
         <is>
-          <t>60409015590065</t>
+          <t>415079 8559 0074</t>
         </is>
       </c>
       <c r="G501" s="6" t="inlineStr">
         <is>
-          <t>08.04.2019</t>
+          <t>28.03.2017</t>
         </is>
       </c>
       <c r="H501" s="6" t="inlineStr">
         <is>
-          <t>04.09.2001</t>
+          <t>15.07.1998</t>
         </is>
       </c>
     </row>
@@ -19242,28 +19241,30 @@
       </c>
       <c r="C502" s="4" t="inlineStr">
         <is>
-          <t>Sayfieva Sarvinoz Zafar qizi</t>
-        </is>
-      </c>
-      <c r="D502" s="2" t="inlineStr"/>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+        </is>
+      </c>
+      <c r="D502" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="E502" s="2" t="inlineStr">
         <is>
-          <t>AB6304158</t>
+          <t>AE4385111</t>
         </is>
       </c>
       <c r="F502" s="3" t="inlineStr">
         <is>
-          <t>415079 8559 0074</t>
+          <t>62203085730015</t>
         </is>
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>28.03.2017</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="H502" s="3" t="inlineStr">
         <is>
-          <t>15.07.1998</t>
+          <t>22.03.2008</t>
         </is>
       </c>
     </row>
@@ -19278,30 +19279,30 @@
       </c>
       <c r="C503" s="7" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="D503" s="5" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E503" s="5" t="inlineStr">
         <is>
-          <t>AE4385111</t>
+          <t>AD2624840</t>
         </is>
       </c>
       <c r="F503" s="6" t="inlineStr">
         <is>
-          <t>62203085730015</t>
+          <t>62408065590018</t>
         </is>
       </c>
       <c r="G503" s="6" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>18.02.2023</t>
         </is>
       </c>
       <c r="H503" s="6" t="inlineStr">
         <is>
-          <t>22.03.2008</t>
+          <t>24.08.2006</t>
         </is>
       </c>
     </row>
@@ -19316,30 +19317,30 @@
       </c>
       <c r="C504" s="4" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
         </is>
       </c>
       <c r="D504" s="2" t="n">
-        <v>21</v>
+        <v>283</v>
       </c>
       <c r="E504" s="2" t="inlineStr">
         <is>
-          <t>AD2624840</t>
+          <t>AB5702170</t>
         </is>
       </c>
       <c r="F504" s="3" t="inlineStr">
         <is>
-          <t>62408065590018</t>
+          <t>42601925680010</t>
         </is>
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>18.02.2023</t>
+          <t>19.01.2017</t>
         </is>
       </c>
       <c r="H504" s="3" t="inlineStr">
         <is>
-          <t>24.08.2006</t>
+          <t>26.01.1992</t>
         </is>
       </c>
     </row>
@@ -19354,30 +19355,30 @@
       </c>
       <c r="C505" s="7" t="inlineStr">
         <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="D505" s="5" t="n">
-        <v>283</v>
+        <v>138</v>
       </c>
       <c r="E505" s="5" t="inlineStr">
         <is>
-          <t>AB5702170</t>
+          <t>AD2922676</t>
         </is>
       </c>
       <c r="F505" s="6" t="inlineStr">
         <is>
-          <t>42601925680010</t>
+          <t>61604065590015</t>
         </is>
       </c>
       <c r="G505" s="6" t="inlineStr">
         <is>
-          <t>19.01.2017</t>
+          <t>01.04.2023</t>
         </is>
       </c>
       <c r="H505" s="6" t="inlineStr">
         <is>
-          <t>26.01.1992</t>
+          <t>16.04.2006</t>
         </is>
       </c>
     </row>
@@ -19392,28 +19393,30 @@
       </c>
       <c r="C506" s="4" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
-        </is>
-      </c>
-      <c r="D506" s="2" t="inlineStr"/>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+        </is>
+      </c>
+      <c r="D506" s="2" t="n">
+        <v>247</v>
+      </c>
       <c r="E506" s="2" t="inlineStr">
         <is>
-          <t>AE 4385291</t>
+          <t>AE4629898</t>
         </is>
       </c>
       <c r="F506" s="3" t="inlineStr">
         <is>
-          <t>407129 0256 0079</t>
+          <t>62802085680012</t>
         </is>
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>15.10.2025</t>
         </is>
       </c>
       <c r="H506" s="3" t="inlineStr">
         <is>
-          <t>07.12.1990</t>
+          <t>28.02.2008</t>
         </is>
       </c>
     </row>
@@ -19428,142 +19431,30 @@
       </c>
       <c r="C507" s="7" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="D507" s="5" t="n">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="E507" s="5" t="inlineStr">
         <is>
-          <t>AD2922676</t>
+          <t>AE4688777</t>
         </is>
       </c>
       <c r="F507" s="6" t="inlineStr">
         <is>
-          <t>61604065590015</t>
+          <t>63007085680074</t>
         </is>
       </c>
       <c r="G507" s="6" t="inlineStr">
         <is>
-          <t>01.04.2023</t>
+          <t>20.10.2025</t>
         </is>
       </c>
       <c r="H507" s="6" t="inlineStr">
         <is>
-          <t>16.04.2006</t>
-        </is>
-      </c>
-    </row>
-    <row r="508" ht="22" customHeight="1">
-      <c r="A508" s="2" t="n">
-        <v>507</v>
-      </c>
-      <c r="B508" s="3" t="inlineStr">
-        <is>
-          <t>26-06</t>
-        </is>
-      </c>
-      <c r="C508" s="4" t="inlineStr">
-        <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
-        </is>
-      </c>
-      <c r="D508" s="2" t="n">
-        <v>247</v>
-      </c>
-      <c r="E508" s="2" t="inlineStr">
-        <is>
-          <t>AE4629898</t>
-        </is>
-      </c>
-      <c r="F508" s="3" t="inlineStr">
-        <is>
-          <t>62802085680012</t>
-        </is>
-      </c>
-      <c r="G508" s="3" t="inlineStr">
-        <is>
-          <t>15.10.2025</t>
-        </is>
-      </c>
-      <c r="H508" s="3" t="inlineStr">
-        <is>
-          <t>28.02.2008</t>
-        </is>
-      </c>
-    </row>
-    <row r="509" ht="22" customHeight="1">
-      <c r="A509" s="5" t="n">
-        <v>508</v>
-      </c>
-      <c r="B509" s="6" t="inlineStr">
-        <is>
-          <t>26-06</t>
-        </is>
-      </c>
-      <c r="C509" s="7" t="inlineStr">
-        <is>
-          <t>Zarifova Marjona Samijon qizi</t>
-        </is>
-      </c>
-      <c r="D509" s="5" t="n">
-        <v>93</v>
-      </c>
-      <c r="E509" s="5" t="inlineStr">
-        <is>
-          <t>AE4688777</t>
-        </is>
-      </c>
-      <c r="F509" s="6" t="inlineStr">
-        <is>
-          <t>63007085680074</t>
-        </is>
-      </c>
-      <c r="G509" s="6" t="inlineStr">
-        <is>
-          <t>20.10.2025</t>
-        </is>
-      </c>
-      <c r="H509" s="6" t="inlineStr">
-        <is>
           <t>30.07.2008</t>
-        </is>
-      </c>
-    </row>
-    <row r="510" ht="22" customHeight="1">
-      <c r="A510" s="2" t="n">
-        <v>509</v>
-      </c>
-      <c r="B510" s="3" t="inlineStr">
-        <is>
-          <t>26-07</t>
-        </is>
-      </c>
-      <c r="C510" s="4" t="inlineStr">
-        <is>
-          <t>Ergasheva Madina Tulqin qizi</t>
-        </is>
-      </c>
-      <c r="D510" s="2" t="inlineStr"/>
-      <c r="E510" s="2" t="inlineStr">
-        <is>
-          <t>AC0429133</t>
-        </is>
-      </c>
-      <c r="F510" s="3" t="inlineStr">
-        <is>
-          <t>62501027890026</t>
-        </is>
-      </c>
-      <c r="G510" s="3" t="inlineStr">
-        <is>
-          <t>07.12.2018</t>
-        </is>
-      </c>
-      <c r="H510" s="3" t="inlineStr">
-        <is>
-          <t>25.01.2002</t>
         </is>
       </c>
     </row>
@@ -24900,7 +24791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -25384,28 +25275,30 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Shermatova Gulsun Xurshid qizi</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr"/>
+          <t>Turayeva Dilsuz Oybek qizi</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>268</v>
+      </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>AE5836574</t>
+          <t>AE5053541</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>60802085590029</t>
+          <t>61205095590053</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>13.01.2026</t>
+          <t>15.11.2025</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>08.02.2008</t>
+          <t>12.05.2009</t>
         </is>
       </c>
     </row>
@@ -25420,30 +25313,30 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Turayeva Dilsuz Oybek qizi</t>
+          <t>Turg'unova Jasmina Turg'un qizi</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>268</v>
+        <v>122</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>AE5053541</t>
+          <t>AE6171425</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>61205095590053</t>
+          <t>62802085590087</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>15.11.2025</t>
+          <t>03.02.2026</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>12.05.2009</t>
+          <t>28.02.2008</t>
         </is>
       </c>
     </row>
@@ -25458,66 +25351,28 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Turg'unova Jasmina Turg'un qizi</t>
+          <t>Ziyodullayeva Jasmina Alisher qizi</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>122</v>
+        <v>233</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>AE6171425</t>
+          <t>AD9812146</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>62802085590087</t>
+          <t>61206075590076</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>03.02.2026</t>
+          <t>13.12.2024</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>28.02.2008</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>26-01</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Ziyodullayeva Jasmina Alisher qizi</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>233</v>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>AD9812146</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>61206075590076</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>13.12.2024</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>12.06.2007</t>
         </is>
@@ -31872,7 +31727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -33112,28 +32967,30 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr"/>
+          <t>Xolmurodova Sabina A'zam qizi</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>138</v>
+      </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>AE 4385291</t>
+          <t>AD2922676</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>407129 0256 0079</t>
+          <t>61604065590015</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>01.04.2023</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>07.12.1990</t>
+          <t>16.04.2006</t>
         </is>
       </c>
     </row>
@@ -33148,30 +33005,30 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>138</v>
+        <v>247</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>AD2922676</t>
+          <t>AE4629898</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>61604065590015</t>
+          <t>62802085680012</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>01.04.2023</t>
+          <t>15.10.2025</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>16.04.2006</t>
+          <t>28.02.2008</t>
         </is>
       </c>
     </row>
@@ -33186,170 +33043,30 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>247</v>
+        <v>93</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>AE4629898</t>
+          <t>AE4688777</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>62802085680012</t>
+          <t>63007085680074</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>15.10.2025</t>
+          <t>20.10.2025</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>26-06</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Zarifova Marjona Samijon qizi</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>AE4688777</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>63007085680074</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>20.10.2025</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
           <t>30.07.2008</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>T/R</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Guruh</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>F.I.SH (Talaba)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Shartnoma №</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Pasport seriya va raqami</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>JSHSHIR (PINFL)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Pasport berilgan sanasi</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Tug'ilgan sanasi</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>26-07</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Ergasheva Madina Tulqin qizi</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>AC0429133</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>62501027890026</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>07.12.2018</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>25.01.2002</t>
         </is>
       </c>
     </row>

--- a/hisobotlar/rollar/1_Buxgalteriya_Shartnoma_va_Pasport.xlsx
+++ b/hisobotlar/rollar/1_Buxgalteriya_Shartnoma_va_Pasport.xlsx
@@ -27,6 +27,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guruh 26-04" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guruh 26-05" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guruh 26-06" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guruh 26-07" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H507"/>
+  <dimension ref="A1:H509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -13063,30 +13064,28 @@
       </c>
       <c r="C339" s="7" t="inlineStr">
         <is>
-          <t>Turayeva Dilsuz Oybek qizi</t>
-        </is>
-      </c>
-      <c r="D339" s="5" t="n">
-        <v>268</v>
-      </c>
+          <t>Shermatova Gulsun Xurshid qizi</t>
+        </is>
+      </c>
+      <c r="D339" s="5" t="inlineStr"/>
       <c r="E339" s="5" t="inlineStr">
         <is>
-          <t>AE5053541</t>
+          <t>AE5836574</t>
         </is>
       </c>
       <c r="F339" s="6" t="inlineStr">
         <is>
-          <t>61205095590053</t>
+          <t>60802085590029</t>
         </is>
       </c>
       <c r="G339" s="6" t="inlineStr">
         <is>
-          <t>15.11.2025</t>
+          <t>13.01.2026</t>
         </is>
       </c>
       <c r="H339" s="6" t="inlineStr">
         <is>
-          <t>12.05.2009</t>
+          <t>08.02.2008</t>
         </is>
       </c>
     </row>
@@ -13101,30 +13100,30 @@
       </c>
       <c r="C340" s="4" t="inlineStr">
         <is>
-          <t>Turg'unova Jasmina Turg'un qizi</t>
+          <t>Turayeva Dilsuz Oybek qizi</t>
         </is>
       </c>
       <c r="D340" s="2" t="n">
-        <v>122</v>
+        <v>268</v>
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>AE6171425</t>
+          <t>AE5053541</t>
         </is>
       </c>
       <c r="F340" s="3" t="inlineStr">
         <is>
-          <t>62802085590087</t>
+          <t>61205095590053</t>
         </is>
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>03.02.2026</t>
+          <t>15.11.2025</t>
         </is>
       </c>
       <c r="H340" s="3" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>12.05.2009</t>
         </is>
       </c>
     </row>
@@ -13139,30 +13138,30 @@
       </c>
       <c r="C341" s="7" t="inlineStr">
         <is>
-          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+          <t>Turg'unova Jasmina Turg'un qizi</t>
         </is>
       </c>
       <c r="D341" s="5" t="n">
-        <v>233</v>
+        <v>122</v>
       </c>
       <c r="E341" s="5" t="inlineStr">
         <is>
-          <t>AD9812146</t>
+          <t>AE6171425</t>
         </is>
       </c>
       <c r="F341" s="6" t="inlineStr">
         <is>
-          <t>61206075590076</t>
+          <t>62802085590087</t>
         </is>
       </c>
       <c r="G341" s="6" t="inlineStr">
         <is>
-          <t>13.12.2024</t>
+          <t>03.02.2026</t>
         </is>
       </c>
       <c r="H341" s="6" t="inlineStr">
         <is>
-          <t>12.06.2007</t>
+          <t>28.02.2008</t>
         </is>
       </c>
     </row>
@@ -13172,35 +13171,35 @@
       </c>
       <c r="B342" s="3" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-01</t>
         </is>
       </c>
       <c r="C342" s="4" t="inlineStr">
         <is>
-          <t>Alimova Sevinch Raxmiddin qizi</t>
+          <t>Ziyodullayeva Jasmina Alisher qizi</t>
         </is>
       </c>
       <c r="D342" s="2" t="n">
-        <v>312</v>
+        <v>233</v>
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>AB7974700</t>
+          <t>AD9812146</t>
         </is>
       </c>
       <c r="F342" s="3" t="inlineStr">
         <is>
-          <t>62707005740020</t>
+          <t>61206075590076</t>
         </is>
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>27.10.2017</t>
+          <t>13.12.2024</t>
         </is>
       </c>
       <c r="H342" s="3" t="inlineStr">
         <is>
-          <t>27.07.2000</t>
+          <t>12.06.2007</t>
         </is>
       </c>
     </row>
@@ -13215,30 +13214,30 @@
       </c>
       <c r="C343" s="7" t="inlineStr">
         <is>
-          <t>Berdiqulova Gulshan Rustam qizi</t>
+          <t>Alimova Sevinch Raxmiddin qizi</t>
         </is>
       </c>
       <c r="D343" s="5" t="n">
-        <v>239</v>
+        <v>312</v>
       </c>
       <c r="E343" s="5" t="inlineStr">
         <is>
-          <t>AE6702868</t>
+          <t>AB7974700</t>
         </is>
       </c>
       <c r="F343" s="6" t="inlineStr">
         <is>
-          <t>41001955590049</t>
+          <t>62707005740020</t>
         </is>
       </c>
       <c r="G343" s="6" t="inlineStr">
         <is>
-          <t>16.03.2026</t>
+          <t>27.10.2017</t>
         </is>
       </c>
       <c r="H343" s="6" t="inlineStr">
         <is>
-          <t>10.01.1995</t>
+          <t>27.07.2000</t>
         </is>
       </c>
     </row>
@@ -13253,30 +13252,30 @@
       </c>
       <c r="C344" s="4" t="inlineStr">
         <is>
-          <t>Eshmurotova Charos Bekqul qizi</t>
+          <t>Berdiqulova Gulshan Rustam qizi</t>
         </is>
       </c>
       <c r="D344" s="2" t="n">
-        <v>110</v>
+        <v>239</v>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>AE5720760</t>
+          <t>AE6702868</t>
         </is>
       </c>
       <c r="F344" s="3" t="inlineStr">
         <is>
-          <t>61901085720047</t>
+          <t>41001955590049</t>
         </is>
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>07.01.2026</t>
+          <t>16.03.2026</t>
         </is>
       </c>
       <c r="H344" s="3" t="inlineStr">
         <is>
-          <t>19.01.2008</t>
+          <t>10.01.1995</t>
         </is>
       </c>
     </row>
@@ -13291,30 +13290,30 @@
       </c>
       <c r="C345" s="7" t="inlineStr">
         <is>
-          <t>G'aybullayeva Ruxsora Xusniddin qizi</t>
+          <t>Eshmurotova Charos Bekqul qizi</t>
         </is>
       </c>
       <c r="D345" s="5" t="n">
-        <v>236</v>
+        <v>110</v>
       </c>
       <c r="E345" s="5" t="inlineStr">
         <is>
-          <t>AD8701218</t>
+          <t>AE5720760</t>
         </is>
       </c>
       <c r="F345" s="6" t="inlineStr">
         <is>
-          <t>61206085590028</t>
+          <t>61901085720047</t>
         </is>
       </c>
       <c r="G345" s="6" t="inlineStr">
         <is>
-          <t>20.09.2024</t>
+          <t>07.01.2026</t>
         </is>
       </c>
       <c r="H345" s="6" t="inlineStr">
         <is>
-          <t>12.06.2008</t>
+          <t>19.01.2008</t>
         </is>
       </c>
     </row>
@@ -13329,30 +13328,30 @@
       </c>
       <c r="C346" s="4" t="inlineStr">
         <is>
-          <t>Hamroqulova Farzona Odilovna</t>
+          <t>G'aybullayeva Ruxsora Xusniddin qizi</t>
         </is>
       </c>
       <c r="D346" s="2" t="n">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>AE4371486</t>
+          <t>AD8701218</t>
         </is>
       </c>
       <c r="F346" s="3" t="inlineStr">
         <is>
-          <t>62111085680033</t>
+          <t>61206085590028</t>
         </is>
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>27.09.2025</t>
+          <t>20.09.2024</t>
         </is>
       </c>
       <c r="H346" s="3" t="inlineStr">
         <is>
-          <t>21.11.2008</t>
+          <t>12.06.2008</t>
         </is>
       </c>
     </row>
@@ -13367,30 +13366,30 @@
       </c>
       <c r="C347" s="7" t="inlineStr">
         <is>
-          <t>Hasanova Dilnura Eson qizi</t>
+          <t>Hamroqulova Farzona Odilovna</t>
         </is>
       </c>
       <c r="D347" s="5" t="n">
-        <v>166</v>
+        <v>278</v>
       </c>
       <c r="E347" s="5" t="inlineStr">
         <is>
-          <t>AE3555106</t>
+          <t>AE4371486</t>
         </is>
       </c>
       <c r="F347" s="6" t="inlineStr">
         <is>
-          <t>61508085680038</t>
+          <t>62111085680033</t>
         </is>
       </c>
       <c r="G347" s="6" t="inlineStr">
         <is>
-          <t>29.07.2025</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="H347" s="6" t="inlineStr">
         <is>
-          <t>15.08.2008</t>
+          <t>21.11.2008</t>
         </is>
       </c>
     </row>
@@ -13405,30 +13404,30 @@
       </c>
       <c r="C348" s="4" t="inlineStr">
         <is>
-          <t>Hasanova Marjona Xolmurod qizi</t>
+          <t>Hasanova Dilnura Eson qizi</t>
         </is>
       </c>
       <c r="D348" s="2" t="n">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>AE5685784</t>
+          <t>AE3555106</t>
         </is>
       </c>
       <c r="F348" s="3" t="inlineStr">
         <is>
-          <t>60411085680047</t>
+          <t>61508085680038</t>
         </is>
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>06.01.2026</t>
+          <t>29.07.2025</t>
         </is>
       </c>
       <c r="H348" s="3" t="inlineStr">
         <is>
-          <t>04.11.2008</t>
+          <t>15.08.2008</t>
         </is>
       </c>
     </row>
@@ -13443,30 +13442,30 @@
       </c>
       <c r="C349" s="7" t="inlineStr">
         <is>
-          <t>Ilhomova Zuhra Davron qizi</t>
+          <t>Hasanova Marjona Xolmurod qizi</t>
         </is>
       </c>
       <c r="D349" s="5" t="n">
-        <v>294</v>
+        <v>192</v>
       </c>
       <c r="E349" s="5" t="inlineStr">
         <is>
-          <t>AE4378923</t>
+          <t>AE5685784</t>
         </is>
       </c>
       <c r="F349" s="6" t="inlineStr">
         <is>
-          <t>63110085590015</t>
+          <t>60411085680047</t>
         </is>
       </c>
       <c r="G349" s="6" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>06.01.2026</t>
         </is>
       </c>
       <c r="H349" s="6" t="inlineStr">
         <is>
-          <t>31.10.2008</t>
+          <t>04.11.2008</t>
         </is>
       </c>
     </row>
@@ -13481,30 +13480,30 @@
       </c>
       <c r="C350" s="4" t="inlineStr">
         <is>
-          <t>Islomova Nilufar Abdulxafiz qizi</t>
+          <t>Ilhomova Zuhra Davron qizi</t>
         </is>
       </c>
       <c r="D350" s="2" t="n">
-        <v>94</v>
+        <v>294</v>
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>AD9664280</t>
+          <t>AE4378923</t>
         </is>
       </c>
       <c r="F350" s="3" t="inlineStr">
         <is>
-          <t>61911085590104</t>
+          <t>63110085590015</t>
         </is>
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>03.12.2024</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="H350" s="3" t="inlineStr">
         <is>
-          <t>19.11.2008</t>
+          <t>31.10.2008</t>
         </is>
       </c>
     </row>
@@ -13519,30 +13518,30 @@
       </c>
       <c r="C351" s="7" t="inlineStr">
         <is>
-          <t>Jalolova Rayxona Akmal qizi</t>
+          <t>Islomova Nilufar Abdulxafiz qizi</t>
         </is>
       </c>
       <c r="D351" s="5" t="n">
-        <v>262</v>
+        <v>94</v>
       </c>
       <c r="E351" s="5" t="inlineStr">
         <is>
-          <t>AE3492384</t>
+          <t>AD9664280</t>
         </is>
       </c>
       <c r="F351" s="6" t="inlineStr">
         <is>
-          <t>62207085680059</t>
+          <t>61911085590104</t>
         </is>
       </c>
       <c r="G351" s="6" t="inlineStr">
         <is>
-          <t>23.07.2025</t>
+          <t>03.12.2024</t>
         </is>
       </c>
       <c r="H351" s="6" t="inlineStr">
         <is>
-          <t>22.07.2008</t>
+          <t>19.11.2008</t>
         </is>
       </c>
     </row>
@@ -13557,30 +13556,30 @@
       </c>
       <c r="C352" s="4" t="inlineStr">
         <is>
-          <t>Javliyeva Nargiza Ortiq qizi</t>
+          <t>Jalolova Rayxona Akmal qizi</t>
         </is>
       </c>
       <c r="D352" s="2" t="n">
-        <v>173</v>
+        <v>262</v>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>AE5222372</t>
+          <t>AE3492384</t>
         </is>
       </c>
       <c r="F352" s="3" t="inlineStr">
         <is>
-          <t>62401095680012</t>
+          <t>62207085680059</t>
         </is>
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>28.11.2025</t>
+          <t>23.07.2025</t>
         </is>
       </c>
       <c r="H352" s="3" t="inlineStr">
         <is>
-          <t>24.01.2009</t>
+          <t>22.07.2008</t>
         </is>
       </c>
     </row>
@@ -13595,30 +13594,30 @@
       </c>
       <c r="C353" s="7" t="inlineStr">
         <is>
-          <t>Maxmashoxova Feruza Bekmurod qizi</t>
+          <t>Javliyeva Nargiza Ortiq qizi</t>
         </is>
       </c>
       <c r="D353" s="5" t="n">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="E353" s="5" t="inlineStr">
         <is>
-          <t>AE5088010</t>
+          <t>AE5222372</t>
         </is>
       </c>
       <c r="F353" s="6" t="inlineStr">
         <is>
-          <t>60201085630050</t>
+          <t>62401095680012</t>
         </is>
       </c>
       <c r="G353" s="6" t="inlineStr">
         <is>
-          <t>18.11.2025</t>
+          <t>28.11.2025</t>
         </is>
       </c>
       <c r="H353" s="6" t="inlineStr">
         <is>
-          <t>02.01.2008</t>
+          <t>24.01.2009</t>
         </is>
       </c>
     </row>
@@ -13633,30 +13632,30 @@
       </c>
       <c r="C354" s="4" t="inlineStr">
         <is>
-          <t>Meyliqulova Hilola Farhod qizi</t>
+          <t>Maxmashoxova Feruza Bekmurod qizi</t>
         </is>
       </c>
       <c r="D354" s="2" t="n">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>AB7137876</t>
+          <t>AE5088010</t>
         </is>
       </c>
       <c r="F354" s="3" t="inlineStr">
         <is>
-          <t>61202005680055</t>
+          <t>60201085630050</t>
         </is>
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>07.07.2017</t>
+          <t>18.11.2025</t>
         </is>
       </c>
       <c r="H354" s="3" t="inlineStr">
         <is>
-          <t>12.02.2000</t>
+          <t>02.01.2008</t>
         </is>
       </c>
     </row>
@@ -13671,30 +13670,30 @@
       </c>
       <c r="C355" s="7" t="inlineStr">
         <is>
-          <t>Nu'monova Saidabonu Ulug'bek qizi</t>
+          <t>Meyliqulova Hilola Farhod qizi</t>
         </is>
       </c>
       <c r="D355" s="5" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="E355" s="5" t="inlineStr">
         <is>
-          <t>AE1067914</t>
+          <t>AB7137876</t>
         </is>
       </c>
       <c r="F355" s="6" t="inlineStr">
         <is>
-          <t>62410085590084</t>
+          <t>61202005680055</t>
         </is>
       </c>
       <c r="G355" s="6" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07.07.2017</t>
         </is>
       </c>
       <c r="H355" s="6" t="inlineStr">
         <is>
-          <t>24.10.2008</t>
+          <t>12.02.2000</t>
         </is>
       </c>
     </row>
@@ -13709,30 +13708,30 @@
       </c>
       <c r="C356" s="4" t="inlineStr">
         <is>
-          <t>Nurillayeva Dilsuz Mashrabovna</t>
+          <t>Nu'monova Saidabonu Ulug'bek qizi</t>
         </is>
       </c>
       <c r="D356" s="2" t="n">
-        <v>326</v>
+        <v>38</v>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>AD4774693</t>
+          <t>AE1067914</t>
         </is>
       </c>
       <c r="F356" s="3" t="inlineStr">
         <is>
-          <t>42506912640010</t>
+          <t>62410085590084</t>
         </is>
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>05.10.2023</t>
+          <t>07.01.2025</t>
         </is>
       </c>
       <c r="H356" s="3" t="inlineStr">
         <is>
-          <t>25.06.1991</t>
+          <t>24.10.2008</t>
         </is>
       </c>
     </row>
@@ -13747,30 +13746,30 @@
       </c>
       <c r="C357" s="7" t="inlineStr">
         <is>
-          <t>Ochildiyeva Dinora Otabek qizi</t>
+          <t>Nurillayeva Dilsuz Mashrabovna</t>
         </is>
       </c>
       <c r="D357" s="5" t="n">
-        <v>87</v>
+        <v>326</v>
       </c>
       <c r="E357" s="5" t="inlineStr">
         <is>
-          <t>AE4084333</t>
+          <t>AD4774693</t>
         </is>
       </c>
       <c r="F357" s="6" t="inlineStr">
         <is>
-          <t>62012085590055</t>
+          <t>42506912640010</t>
         </is>
       </c>
       <c r="G357" s="6" t="inlineStr">
         <is>
-          <t>08.09.2025</t>
+          <t>05.10.2023</t>
         </is>
       </c>
       <c r="H357" s="6" t="inlineStr">
         <is>
-          <t>20.12.2008</t>
+          <t>25.06.1991</t>
         </is>
       </c>
     </row>
@@ -13785,28 +13784,30 @@
       </c>
       <c r="C358" s="4" t="inlineStr">
         <is>
-          <t>Qulmatova Shabbona Azamat qizi</t>
-        </is>
-      </c>
-      <c r="D358" s="2" t="inlineStr"/>
+          <t>Ochildiyeva Dinora Otabek qizi</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="n">
+        <v>87</v>
+      </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>AE4905104</t>
+          <t>AE4084333</t>
         </is>
       </c>
       <c r="F358" s="3" t="inlineStr">
         <is>
-          <t>61008085680019</t>
+          <t>62012085590055</t>
         </is>
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>05.11.2025</t>
+          <t>08.09.2025</t>
         </is>
       </c>
       <c r="H358" s="3" t="inlineStr">
         <is>
-          <t>10.08.2008</t>
+          <t>20.12.2008</t>
         </is>
       </c>
     </row>
@@ -13821,30 +13822,28 @@
       </c>
       <c r="C359" s="7" t="inlineStr">
         <is>
-          <t>Quysinova Rohshona To'lqin qizi</t>
-        </is>
-      </c>
-      <c r="D359" s="5" t="n">
-        <v>242</v>
-      </c>
+          <t>Qulmatova Shabbona Azamat qizi</t>
+        </is>
+      </c>
+      <c r="D359" s="5" t="inlineStr"/>
       <c r="E359" s="5" t="inlineStr">
         <is>
-          <t>AE7231113</t>
+          <t>AE4905104</t>
         </is>
       </c>
       <c r="F359" s="6" t="inlineStr">
         <is>
-          <t>60406055720067</t>
+          <t>61008085680019</t>
         </is>
       </c>
       <c r="G359" s="6" t="inlineStr">
         <is>
-          <t>01.05.2026</t>
+          <t>05.11.2025</t>
         </is>
       </c>
       <c r="H359" s="6" t="inlineStr">
         <is>
-          <t>04.06.2005</t>
+          <t>10.08.2008</t>
         </is>
       </c>
     </row>
@@ -13859,30 +13858,30 @@
       </c>
       <c r="C360" s="4" t="inlineStr">
         <is>
-          <t>Ro'zimurodova Larisa Ma'matali qizi</t>
+          <t>Quysinova Rohshona To'lqin qizi</t>
         </is>
       </c>
       <c r="D360" s="2" t="n">
-        <v>100</v>
+        <v>242</v>
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>AE5324961</t>
+          <t>AE7231113</t>
         </is>
       </c>
       <c r="F360" s="3" t="inlineStr">
         <is>
-          <t>61608085630072</t>
+          <t>60406055720067</t>
         </is>
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>05.12.2025</t>
+          <t>01.05.2026</t>
         </is>
       </c>
       <c r="H360" s="3" t="inlineStr">
         <is>
-          <t>16.08.2008</t>
+          <t>04.06.2005</t>
         </is>
       </c>
     </row>
@@ -13897,30 +13896,30 @@
       </c>
       <c r="C361" s="7" t="inlineStr">
         <is>
-          <t>Samadova Nigora Abdisamiyevna</t>
+          <t>Ro'zimurodova Larisa Ma'matali qizi</t>
         </is>
       </c>
       <c r="D361" s="5" t="n">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="E361" s="5" t="inlineStr">
         <is>
-          <t>AE1836076</t>
+          <t>AE5324961</t>
         </is>
       </c>
       <c r="F361" s="6" t="inlineStr">
         <is>
-          <t>40710895590044</t>
+          <t>61608085630072</t>
         </is>
       </c>
       <c r="G361" s="6" t="inlineStr">
         <is>
-          <t>05.03.2025</t>
+          <t>05.12.2025</t>
         </is>
       </c>
       <c r="H361" s="6" t="inlineStr">
         <is>
-          <t>07.10.1989</t>
+          <t>16.08.2008</t>
         </is>
       </c>
     </row>
@@ -13935,30 +13934,30 @@
       </c>
       <c r="C362" s="4" t="inlineStr">
         <is>
-          <t>Samatova Oydin Sulaymon qizi</t>
+          <t>Samadova Nigora Abdisamiyevna</t>
         </is>
       </c>
       <c r="D362" s="2" t="n">
-        <v>146</v>
+        <v>81</v>
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>AD8980430</t>
+          <t>AE1836076</t>
         </is>
       </c>
       <c r="F362" s="3" t="inlineStr">
         <is>
-          <t>42910905720012</t>
+          <t>40710895590044</t>
         </is>
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>11.10.2024</t>
+          <t>05.03.2025</t>
         </is>
       </c>
       <c r="H362" s="3" t="inlineStr">
         <is>
-          <t>29.10.1990</t>
+          <t>07.10.1989</t>
         </is>
       </c>
     </row>
@@ -13973,30 +13972,30 @@
       </c>
       <c r="C363" s="7" t="inlineStr">
         <is>
-          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
+          <t>Samatova Oydin Sulaymon qizi</t>
         </is>
       </c>
       <c r="D363" s="5" t="n">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="E363" s="5" t="inlineStr">
         <is>
-          <t>AE3352294</t>
+          <t>AD8980430</t>
         </is>
       </c>
       <c r="F363" s="6" t="inlineStr">
         <is>
-          <t>61807085590034</t>
+          <t>42910905720012</t>
         </is>
       </c>
       <c r="G363" s="6" t="inlineStr">
         <is>
-          <t>10.07.2025</t>
+          <t>11.10.2024</t>
         </is>
       </c>
       <c r="H363" s="6" t="inlineStr">
         <is>
-          <t>18.07.2008</t>
+          <t>29.10.1990</t>
         </is>
       </c>
     </row>
@@ -14011,28 +14010,30 @@
       </c>
       <c r="C364" s="4" t="inlineStr">
         <is>
-          <t>Shonazarova Vazira Botir qizi</t>
-        </is>
-      </c>
-      <c r="D364" s="2" t="inlineStr"/>
+          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="n">
+        <v>74</v>
+      </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>AE 4233482</t>
+          <t>AE3352294</t>
         </is>
       </c>
       <c r="F364" s="3" t="inlineStr">
         <is>
-          <t>61311085680032</t>
+          <t>61807085590034</t>
         </is>
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>17.09.2025</t>
+          <t>10.07.2025</t>
         </is>
       </c>
       <c r="H364" s="3" t="inlineStr">
         <is>
-          <t>13.11.2008</t>
+          <t>18.07.2008</t>
         </is>
       </c>
     </row>
@@ -14047,30 +14048,28 @@
       </c>
       <c r="C365" s="7" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
-        </is>
-      </c>
-      <c r="D365" s="5" t="n">
-        <v>162</v>
-      </c>
+          <t>Shonazarova Vazira Botir qizi</t>
+        </is>
+      </c>
+      <c r="D365" s="5" t="inlineStr"/>
       <c r="E365" s="5" t="inlineStr">
         <is>
-          <t>AD7767171</t>
+          <t>AE 4233482</t>
         </is>
       </c>
       <c r="F365" s="6" t="inlineStr">
         <is>
-          <t>62103085590038</t>
+          <t>61311085680032</t>
         </is>
       </c>
       <c r="G365" s="6" t="inlineStr">
         <is>
-          <t>06.07.2024</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="H365" s="6" t="inlineStr">
         <is>
-          <t>21.03.2008</t>
+          <t>13.11.2008</t>
         </is>
       </c>
     </row>
@@ -14085,30 +14084,30 @@
       </c>
       <c r="C366" s="4" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
       <c r="D366" s="2" t="n">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>AB7166586</t>
+          <t>AD7767171</t>
         </is>
       </c>
       <c r="F366" s="3" t="inlineStr">
         <is>
-          <t>61409005680027</t>
+          <t>62103085590038</t>
         </is>
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>09.07.2017</t>
+          <t>06.07.2024</t>
         </is>
       </c>
       <c r="H366" s="3" t="inlineStr">
         <is>
-          <t>14.09.2000</t>
+          <t>21.03.2008</t>
         </is>
       </c>
     </row>
@@ -14123,30 +14122,30 @@
       </c>
       <c r="C367" s="7" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="D367" s="5" t="n">
-        <v>6</v>
+        <v>122</v>
       </c>
       <c r="E367" s="5" t="inlineStr">
         <is>
-          <t>AE3558477</t>
+          <t>AB7166586</t>
         </is>
       </c>
       <c r="F367" s="6" t="inlineStr">
         <is>
-          <t>62709085590070</t>
+          <t>61409005680027</t>
         </is>
       </c>
       <c r="G367" s="6" t="inlineStr">
         <is>
-          <t>29.07.2025</t>
+          <t>09.07.2017</t>
         </is>
       </c>
       <c r="H367" s="6" t="inlineStr">
         <is>
-          <t>27.09.2008</t>
+          <t>14.09.2000</t>
         </is>
       </c>
     </row>
@@ -14161,30 +14160,30 @@
       </c>
       <c r="C368" s="4" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona Nazim qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="D368" s="2" t="n">
-        <v>161</v>
+        <v>6</v>
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
-          <t>AE5199773</t>
+          <t>AE3558477</t>
         </is>
       </c>
       <c r="F368" s="3" t="inlineStr">
         <is>
-          <t>61906085680012</t>
+          <t>62709085590070</t>
         </is>
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>26.11.2025</t>
+          <t>29.07.2025</t>
         </is>
       </c>
       <c r="H368" s="3" t="inlineStr">
         <is>
-          <t>19.06.2008</t>
+          <t>27.09.2008</t>
         </is>
       </c>
     </row>
@@ -14199,30 +14198,30 @@
       </c>
       <c r="C369" s="7" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
       <c r="D369" s="5" t="n">
-        <v>11</v>
+        <v>161</v>
       </c>
       <c r="E369" s="5" t="inlineStr">
         <is>
-          <t>AD4186169</t>
+          <t>AE5199773</t>
         </is>
       </c>
       <c r="F369" s="6" t="inlineStr">
         <is>
-          <t>40404975650046</t>
+          <t>61906085680012</t>
         </is>
       </c>
       <c r="G369" s="6" t="inlineStr">
         <is>
-          <t>07.08.2023</t>
+          <t>26.11.2025</t>
         </is>
       </c>
       <c r="H369" s="6" t="inlineStr">
         <is>
-          <t>04.04.1997</t>
+          <t>19.06.2008</t>
         </is>
       </c>
     </row>
@@ -14237,30 +14236,30 @@
       </c>
       <c r="C370" s="4" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="D370" s="2" t="n">
-        <v>220</v>
+        <v>11</v>
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>AE4503488</t>
+          <t>AD4186169</t>
         </is>
       </c>
       <c r="F370" s="3" t="inlineStr">
         <is>
-          <t>51106085680031</t>
+          <t>40404975650046</t>
         </is>
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>07.10.2025</t>
+          <t>07.08.2023</t>
         </is>
       </c>
       <c r="H370" s="3" t="inlineStr">
         <is>
-          <t>11.06.2008</t>
+          <t>04.04.1997</t>
         </is>
       </c>
     </row>
@@ -14275,30 +14274,30 @@
       </c>
       <c r="C371" s="7" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="D371" s="5" t="n">
-        <v>79</v>
+        <v>220</v>
       </c>
       <c r="E371" s="5" t="inlineStr">
         <is>
-          <t>AE5293914</t>
+          <t>AE4503488</t>
         </is>
       </c>
       <c r="F371" s="6" t="inlineStr">
         <is>
-          <t>60512085590078</t>
+          <t>51106085680031</t>
         </is>
       </c>
       <c r="G371" s="6" t="inlineStr">
         <is>
-          <t>04.12.2025</t>
+          <t>07.10.2025</t>
         </is>
       </c>
       <c r="H371" s="6" t="inlineStr">
         <is>
-          <t>05.12.2008</t>
+          <t>11.06.2008</t>
         </is>
       </c>
     </row>
@@ -14313,30 +14312,30 @@
       </c>
       <c r="C372" s="4" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="D372" s="2" t="n">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>AE4989343</t>
+          <t>AE5293914</t>
         </is>
       </c>
       <c r="F372" s="3" t="inlineStr">
         <is>
-          <t>60402095590060</t>
+          <t>60512085590078</t>
         </is>
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>11.11.2025</t>
+          <t>04.12.2025</t>
         </is>
       </c>
       <c r="H372" s="3" t="inlineStr">
         <is>
-          <t>04.02.2009</t>
+          <t>05.12.2008</t>
         </is>
       </c>
     </row>
@@ -14351,30 +14350,30 @@
       </c>
       <c r="C373" s="7" t="inlineStr">
         <is>
-          <t>Usmanova Iroda Abdurazzoq qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="D373" s="5" t="n">
-        <v>279</v>
+        <v>148</v>
       </c>
       <c r="E373" s="5" t="inlineStr">
         <is>
-          <t>AE7821304</t>
+          <t>AE4989343</t>
         </is>
       </c>
       <c r="F373" s="6" t="inlineStr">
         <is>
-          <t>41406985680067</t>
+          <t>60402095590060</t>
         </is>
       </c>
       <c r="G373" s="6" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>11.11.2025</t>
         </is>
       </c>
       <c r="H373" s="6" t="inlineStr">
         <is>
-          <t>14.06.1998</t>
+          <t>04.02.2009</t>
         </is>
       </c>
     </row>
@@ -14389,30 +14388,30 @@
       </c>
       <c r="C374" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="D374" s="2" t="n">
-        <v>2</v>
+        <v>279</v>
       </c>
       <c r="E374" s="2" t="inlineStr">
         <is>
-          <t>AC1967100</t>
+          <t>AE7821304</t>
         </is>
       </c>
       <c r="F374" s="3" t="inlineStr">
         <is>
-          <t>62704025590042</t>
+          <t>41406985680067</t>
         </is>
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>12.06.2019</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="H374" s="3" t="inlineStr">
         <is>
-          <t>27.04.2002</t>
+          <t>14.06.1998</t>
         </is>
       </c>
     </row>
@@ -14427,30 +14426,30 @@
       </c>
       <c r="C375" s="7" t="inlineStr">
         <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
+          <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
       <c r="D375" s="5" t="n">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="E375" s="5" t="inlineStr">
         <is>
-          <t>AB9239333</t>
+          <t>AC1967100</t>
         </is>
       </c>
       <c r="F375" s="6" t="inlineStr">
         <is>
-          <t>42207935680042</t>
+          <t>62704025590042</t>
         </is>
       </c>
       <c r="G375" s="6" t="inlineStr">
         <is>
-          <t>09.04.2018</t>
+          <t>12.06.2019</t>
         </is>
       </c>
       <c r="H375" s="6" t="inlineStr">
         <is>
-          <t>22.07.1993</t>
+          <t>27.04.2002</t>
         </is>
       </c>
     </row>
@@ -14460,35 +14459,35 @@
       </c>
       <c r="B376" s="3" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C376" s="4" t="inlineStr">
         <is>
-          <t>Aliqulova Shaxzoda Anvar qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="D376" s="2" t="n">
-        <v>272</v>
+        <v>75</v>
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
-          <t>AC1827958</t>
+          <t>AB9239333</t>
         </is>
       </c>
       <c r="F376" s="3" t="inlineStr">
         <is>
-          <t>60301037890018</t>
+          <t>42207935680042</t>
         </is>
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>18.04.2019</t>
+          <t>09.04.2018</t>
         </is>
       </c>
       <c r="H376" s="3" t="inlineStr">
         <is>
-          <t>03.01.2003</t>
+          <t>22.07.1993</t>
         </is>
       </c>
     </row>
@@ -14503,30 +14502,30 @@
       </c>
       <c r="C377" s="7" t="inlineStr">
         <is>
-          <t>Arziqulova Laylo Bahodir qizi</t>
+          <t>Aliqulova Shaxzoda Anvar qizi</t>
         </is>
       </c>
       <c r="D377" s="5" t="n">
-        <v>79</v>
+        <v>272</v>
       </c>
       <c r="E377" s="5" t="inlineStr">
         <is>
-          <t>AD8548125</t>
+          <t>AC1827958</t>
         </is>
       </c>
       <c r="F377" s="6" t="inlineStr">
         <is>
-          <t>60110065720109</t>
+          <t>60301037890018</t>
         </is>
       </c>
       <c r="G377" s="6" t="inlineStr">
         <is>
-          <t>09.09.2024</t>
+          <t>18.04.2019</t>
         </is>
       </c>
       <c r="H377" s="6" t="inlineStr">
         <is>
-          <t>01.10.2006</t>
+          <t>03.01.2003</t>
         </is>
       </c>
     </row>
@@ -14541,30 +14540,30 @@
       </c>
       <c r="C378" s="4" t="inlineStr">
         <is>
-          <t>Eshnazarova Dilnoza Rustam qizi</t>
+          <t>Arziqulova Laylo Bahodir qizi</t>
         </is>
       </c>
       <c r="D378" s="2" t="n">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="E378" s="2" t="inlineStr">
         <is>
-          <t>AE3321050</t>
+          <t>AD8548125</t>
         </is>
       </c>
       <c r="F378" s="3" t="inlineStr">
         <is>
-          <t>60710085730098</t>
+          <t>60110065720109</t>
         </is>
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>08.07.2025</t>
+          <t>09.09.2024</t>
         </is>
       </c>
       <c r="H378" s="3" t="inlineStr">
         <is>
-          <t>07.10.2008</t>
+          <t>01.10.2006</t>
         </is>
       </c>
     </row>
@@ -14579,30 +14578,30 @@
       </c>
       <c r="C379" s="7" t="inlineStr">
         <is>
-          <t>Fayzullayeva Sarvinoz Sherbobo qizi</t>
+          <t>Eshnazarova Dilnoza Rustam qizi</t>
         </is>
       </c>
       <c r="D379" s="5" t="n">
-        <v>152</v>
+        <v>221</v>
       </c>
       <c r="E379" s="5" t="inlineStr">
         <is>
-          <t>AD1189588</t>
+          <t>AE3321050</t>
         </is>
       </c>
       <c r="F379" s="6" t="inlineStr">
         <is>
-          <t>63003055730053</t>
+          <t>60710085730098</t>
         </is>
       </c>
       <c r="G379" s="6" t="inlineStr">
         <is>
-          <t>24.03.2022</t>
+          <t>08.07.2025</t>
         </is>
       </c>
       <c r="H379" s="6" t="inlineStr">
         <is>
-          <t>30.03.2005</t>
+          <t>07.10.2008</t>
         </is>
       </c>
     </row>
@@ -14617,30 +14616,30 @@
       </c>
       <c r="C380" s="4" t="inlineStr">
         <is>
-          <t>Ibragimova Gulnoza Isroil qizi</t>
+          <t>Fayzullayeva Sarvinoz Sherbobo qizi</t>
         </is>
       </c>
       <c r="D380" s="2" t="n">
-        <v>308</v>
+        <v>152</v>
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
-          <t>AE4115057</t>
+          <t>AD1189588</t>
         </is>
       </c>
       <c r="F380" s="3" t="inlineStr">
         <is>
-          <t>60606085680085</t>
+          <t>63003055730053</t>
         </is>
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>09.09.2025</t>
+          <t>24.03.2022</t>
         </is>
       </c>
       <c r="H380" s="3" t="inlineStr">
         <is>
-          <t>06.06.2008</t>
+          <t>30.03.2005</t>
         </is>
       </c>
     </row>
@@ -14655,30 +14654,30 @@
       </c>
       <c r="C381" s="7" t="inlineStr">
         <is>
-          <t>Izzatulloyeva Vazira G'ayratzoda</t>
+          <t>Ibragimova Gulnoza Isroil qizi</t>
         </is>
       </c>
       <c r="D381" s="5" t="n">
-        <v>383</v>
+        <v>308</v>
       </c>
       <c r="E381" s="5" t="inlineStr">
         <is>
-          <t>AE5671026</t>
+          <t>AE4115057</t>
         </is>
       </c>
       <c r="F381" s="6" t="inlineStr">
         <is>
-          <t>42004975680094</t>
+          <t>60606085680085</t>
         </is>
       </c>
       <c r="G381" s="6" t="inlineStr">
         <is>
-          <t>05.01.2026</t>
+          <t>09.09.2025</t>
         </is>
       </c>
       <c r="H381" s="6" t="inlineStr">
         <is>
-          <t>20.04.1997</t>
+          <t>06.06.2008</t>
         </is>
       </c>
     </row>
@@ -14693,30 +14692,30 @@
       </c>
       <c r="C382" s="4" t="inlineStr">
         <is>
-          <t>Jurayeva Dilnoz G'oibnazarovna</t>
+          <t>Izzatulloyeva Vazira G'ayratzoda</t>
         </is>
       </c>
       <c r="D382" s="2" t="n">
-        <v>89</v>
+        <v>383</v>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>AD2957442</t>
+          <t>AE5671026</t>
         </is>
       </c>
       <c r="F382" s="3" t="inlineStr">
         <is>
-          <t>40305922560019</t>
+          <t>42004975680094</t>
         </is>
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>05.04.2023</t>
+          <t>05.01.2026</t>
         </is>
       </c>
       <c r="H382" s="3" t="inlineStr">
         <is>
-          <t>03.05.1992</t>
+          <t>20.04.1997</t>
         </is>
       </c>
     </row>
@@ -14731,30 +14730,30 @@
       </c>
       <c r="C383" s="7" t="inlineStr">
         <is>
-          <t>Mansurova Gulasal Musurmon qizi</t>
+          <t>Jurayeva Dilnoz G'oibnazarovna</t>
         </is>
       </c>
       <c r="D383" s="5" t="n">
-        <v>301</v>
+        <v>89</v>
       </c>
       <c r="E383" s="5" t="inlineStr">
         <is>
-          <t>AE4483600</t>
+          <t>AD2957442</t>
         </is>
       </c>
       <c r="F383" s="6" t="inlineStr">
         <is>
-          <t>62905085680067</t>
+          <t>40305922560019</t>
         </is>
       </c>
       <c r="G383" s="6" t="inlineStr">
         <is>
-          <t>06.10.2025</t>
+          <t>05.04.2023</t>
         </is>
       </c>
       <c r="H383" s="6" t="inlineStr">
         <is>
-          <t>29.05.2008</t>
+          <t>03.05.1992</t>
         </is>
       </c>
     </row>
@@ -14769,30 +14768,30 @@
       </c>
       <c r="C384" s="4" t="inlineStr">
         <is>
-          <t>Murtazayeva Kamola Jamoliddin qizi</t>
+          <t>Mansurova Gulasal Musurmon qizi</t>
         </is>
       </c>
       <c r="D384" s="2" t="n">
-        <v>25</v>
+        <v>301</v>
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>AC1458884</t>
+          <t>AE4483600</t>
         </is>
       </c>
       <c r="F384" s="3" t="inlineStr">
         <is>
-          <t>42708915590028</t>
+          <t>62905085680067</t>
         </is>
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>04.11.2018</t>
+          <t>06.10.2025</t>
         </is>
       </c>
       <c r="H384" s="3" t="inlineStr">
         <is>
-          <t>27.08.1991</t>
+          <t>29.05.2008</t>
         </is>
       </c>
     </row>
@@ -14807,30 +14806,30 @@
       </c>
       <c r="C385" s="7" t="inlineStr">
         <is>
-          <t>Mustafayeva Madina Ortiq qizi</t>
+          <t>Murtazayeva Kamola Jamoliddin qizi</t>
         </is>
       </c>
       <c r="D385" s="5" t="n">
-        <v>282</v>
+        <v>25</v>
       </c>
       <c r="E385" s="5" t="inlineStr">
         <is>
-          <t>AE4846447</t>
+          <t>AC1458884</t>
         </is>
       </c>
       <c r="F385" s="6" t="inlineStr">
         <is>
-          <t>63110085680103</t>
+          <t>42708915590028</t>
         </is>
       </c>
       <c r="G385" s="6" t="inlineStr">
         <is>
-          <t>31.10.2025</t>
+          <t>04.11.2018</t>
         </is>
       </c>
       <c r="H385" s="6" t="inlineStr">
         <is>
-          <t>31.10.2008</t>
+          <t>27.08.1991</t>
         </is>
       </c>
     </row>
@@ -14845,28 +14844,30 @@
       </c>
       <c r="C386" s="4" t="inlineStr">
         <is>
-          <t>Niyozova Komila Toshpulatovna</t>
-        </is>
-      </c>
-      <c r="D386" s="2" t="inlineStr"/>
+          <t>Mustafayeva Madina Ortiq qizi</t>
+        </is>
+      </c>
+      <c r="D386" s="2" t="n">
+        <v>282</v>
+      </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>AB9205278</t>
+          <t>AE4846447</t>
         </is>
       </c>
       <c r="F386" s="3" t="inlineStr">
         <is>
-          <t>42405832640057</t>
+          <t>63110085680103</t>
         </is>
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>07.04.2018</t>
+          <t>31.10.2025</t>
         </is>
       </c>
       <c r="H386" s="3" t="inlineStr">
         <is>
-          <t>24.05.1983</t>
+          <t>31.10.2008</t>
         </is>
       </c>
     </row>
@@ -14881,30 +14882,28 @@
       </c>
       <c r="C387" s="7" t="inlineStr">
         <is>
-          <t>Norboboyeva Farangiz Nuriddin qizi</t>
-        </is>
-      </c>
-      <c r="D387" s="5" t="n">
-        <v>231</v>
-      </c>
+          <t>Niyozova Komila Toshpulatovna</t>
+        </is>
+      </c>
+      <c r="D387" s="5" t="inlineStr"/>
       <c r="E387" s="5" t="inlineStr">
         <is>
-          <t>AE5898909</t>
+          <t>AB9205278</t>
         </is>
       </c>
       <c r="F387" s="6" t="inlineStr">
         <is>
-          <t>62808085590100</t>
+          <t>42405832640057</t>
         </is>
       </c>
       <c r="G387" s="6" t="inlineStr">
         <is>
-          <t>16.01.2026</t>
+          <t>07.04.2018</t>
         </is>
       </c>
       <c r="H387" s="6" t="inlineStr">
         <is>
-          <t>28.08.2008</t>
+          <t>24.05.1983</t>
         </is>
       </c>
     </row>
@@ -14919,30 +14918,30 @@
       </c>
       <c r="C388" s="4" t="inlineStr">
         <is>
-          <t>Pardaqulova Farzona Shovkatovna</t>
+          <t>Norboboyeva Farangiz Nuriddin qizi</t>
         </is>
       </c>
       <c r="D388" s="2" t="n">
-        <v>90</v>
+        <v>231</v>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>AE1336538</t>
+          <t>AE5898909</t>
         </is>
       </c>
       <c r="F388" s="3" t="inlineStr">
         <is>
-          <t>60312085590052</t>
+          <t>62808085590100</t>
         </is>
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>23.01.2025</t>
+          <t>16.01.2026</t>
         </is>
       </c>
       <c r="H388" s="3" t="inlineStr">
         <is>
-          <t>03.12.2008</t>
+          <t>28.08.2008</t>
         </is>
       </c>
     </row>
@@ -14957,30 +14956,30 @@
       </c>
       <c r="C389" s="7" t="inlineStr">
         <is>
-          <t>Pardayeva Farangiz Norali qizi</t>
+          <t>Pardaqulova Farzona Shovkatovna</t>
         </is>
       </c>
       <c r="D389" s="5" t="n">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="E389" s="5" t="inlineStr">
         <is>
-          <t>AE5643897</t>
+          <t>AE1336538</t>
         </is>
       </c>
       <c r="F389" s="6" t="inlineStr">
         <is>
-          <t>60102085590053</t>
+          <t>60312085590052</t>
         </is>
       </c>
       <c r="G389" s="6" t="inlineStr">
         <is>
-          <t>29.12.2025</t>
+          <t>23.01.2025</t>
         </is>
       </c>
       <c r="H389" s="6" t="inlineStr">
         <is>
-          <t>01.02.2008</t>
+          <t>03.12.2008</t>
         </is>
       </c>
     </row>
@@ -14995,30 +14994,30 @@
       </c>
       <c r="C390" s="4" t="inlineStr">
         <is>
-          <t>Primova Husnora Shovkat qizi</t>
+          <t>Pardayeva Farangiz Norali qizi</t>
         </is>
       </c>
       <c r="D390" s="2" t="n">
-        <v>251</v>
+        <v>105</v>
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>AC 0443770</t>
+          <t>AE5643897</t>
         </is>
       </c>
       <c r="F390" s="3" t="inlineStr">
         <is>
-          <t>61310015590029</t>
+          <t>60102085590053</t>
         </is>
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>10.12.2018</t>
+          <t>29.12.2025</t>
         </is>
       </c>
       <c r="H390" s="3" t="inlineStr">
         <is>
-          <t>13.10.2001</t>
+          <t>01.02.2008</t>
         </is>
       </c>
     </row>
@@ -15033,30 +15032,30 @@
       </c>
       <c r="C391" s="7" t="inlineStr">
         <is>
-          <t>Rasulova Husnobod Bekmurod qizi</t>
+          <t>Primova Husnora Shovkat qizi</t>
         </is>
       </c>
       <c r="D391" s="5" t="n">
-        <v>392</v>
+        <v>251</v>
       </c>
       <c r="E391" s="5" t="inlineStr">
         <is>
-          <t>AD1615363</t>
+          <t>AC 0443770</t>
         </is>
       </c>
       <c r="F391" s="6" t="inlineStr">
         <is>
-          <t>62705055720049</t>
+          <t>61310015590029</t>
         </is>
       </c>
       <c r="G391" s="6" t="inlineStr">
         <is>
-          <t>03.08.2022</t>
+          <t>10.12.2018</t>
         </is>
       </c>
       <c r="H391" s="6" t="inlineStr">
         <is>
-          <t>27.05.2005</t>
+          <t>13.10.2001</t>
         </is>
       </c>
     </row>
@@ -15071,30 +15070,30 @@
       </c>
       <c r="C392" s="4" t="inlineStr">
         <is>
-          <t>Rayimova Nozliya Laziz qizi</t>
+          <t>Rasulova Husnobod Bekmurod qizi</t>
         </is>
       </c>
       <c r="D392" s="2" t="n">
-        <v>291</v>
+        <v>392</v>
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>AE4759683</t>
+          <t>AD1615363</t>
         </is>
       </c>
       <c r="F392" s="3" t="inlineStr">
         <is>
-          <t>62606085590056</t>
+          <t>62705055720049</t>
         </is>
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>24.10.2025</t>
+          <t>03.08.2022</t>
         </is>
       </c>
       <c r="H392" s="3" t="inlineStr">
         <is>
-          <t>26.06.2008</t>
+          <t>27.05.2005</t>
         </is>
       </c>
     </row>
@@ -15109,30 +15108,30 @@
       </c>
       <c r="C393" s="7" t="inlineStr">
         <is>
-          <t>Rustamova Charos O'ktam qizi</t>
+          <t>Rayimova Nozliya Laziz qizi</t>
         </is>
       </c>
       <c r="D393" s="5" t="n">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="E393" s="5" t="inlineStr">
         <is>
-          <t>AE4730990</t>
+          <t>AE4759683</t>
         </is>
       </c>
       <c r="F393" s="6" t="inlineStr">
         <is>
-          <t>60810085680017</t>
+          <t>62606085590056</t>
         </is>
       </c>
       <c r="G393" s="6" t="inlineStr">
         <is>
-          <t>22.10.2025</t>
+          <t>24.10.2025</t>
         </is>
       </c>
       <c r="H393" s="6" t="inlineStr">
         <is>
-          <t>08.10.2008</t>
+          <t>26.06.2008</t>
         </is>
       </c>
     </row>
@@ -15147,30 +15146,30 @@
       </c>
       <c r="C394" s="4" t="inlineStr">
         <is>
-          <t>Salayeva Dilroz Muroulla qizi</t>
+          <t>Rustamova Charos O'ktam qizi</t>
         </is>
       </c>
       <c r="D394" s="2" t="n">
-        <v>205</v>
+        <v>309</v>
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>AE3039330</t>
+          <t>AE4730990</t>
         </is>
       </c>
       <c r="F394" s="3" t="inlineStr">
         <is>
-          <t>60408085730030</t>
+          <t>60810085680017</t>
         </is>
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>16.06.2025</t>
+          <t>22.10.2025</t>
         </is>
       </c>
       <c r="H394" s="3" t="inlineStr">
         <is>
-          <t>04.08.2008</t>
+          <t>08.10.2008</t>
         </is>
       </c>
     </row>
@@ -15185,30 +15184,30 @@
       </c>
       <c r="C395" s="7" t="inlineStr">
         <is>
-          <t>Sayfiyeva Zarina Axmad qizi</t>
+          <t>Salayeva Dilroz Muroulla qizi</t>
         </is>
       </c>
       <c r="D395" s="5" t="n">
-        <v>37</v>
+        <v>205</v>
       </c>
       <c r="E395" s="5" t="inlineStr">
         <is>
-          <t>AD7984192</t>
+          <t>AE3039330</t>
         </is>
       </c>
       <c r="F395" s="6" t="inlineStr">
         <is>
-          <t>61007085590081</t>
+          <t>60408085730030</t>
         </is>
       </c>
       <c r="G395" s="6" t="inlineStr">
         <is>
-          <t>23.07.2024</t>
+          <t>16.06.2025</t>
         </is>
       </c>
       <c r="H395" s="6" t="inlineStr">
         <is>
-          <t>10.07.2008</t>
+          <t>04.08.2008</t>
         </is>
       </c>
     </row>
@@ -15223,30 +15222,30 @@
       </c>
       <c r="C396" s="4" t="inlineStr">
         <is>
-          <t>Sayidova Dilafro'z Qahramon qizi</t>
+          <t>Sayfiyeva Zarina Axmad qizi</t>
         </is>
       </c>
       <c r="D396" s="2" t="n">
-        <v>263</v>
+        <v>37</v>
       </c>
       <c r="E396" s="2" t="inlineStr">
         <is>
-          <t>AE6071273</t>
+          <t>AD7984192</t>
         </is>
       </c>
       <c r="F396" s="3" t="inlineStr">
         <is>
-          <t>62708095680047</t>
+          <t>61007085590081</t>
         </is>
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>27.01.2026</t>
+          <t>23.07.2024</t>
         </is>
       </c>
       <c r="H396" s="3" t="inlineStr">
         <is>
-          <t>27.08.2009</t>
+          <t>10.07.2008</t>
         </is>
       </c>
     </row>
@@ -15261,30 +15260,30 @@
       </c>
       <c r="C397" s="7" t="inlineStr">
         <is>
-          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
+          <t>Sayidova Dilafro'z Qahramon qizi</t>
         </is>
       </c>
       <c r="D397" s="5" t="n">
-        <v>107</v>
+        <v>263</v>
       </c>
       <c r="E397" s="5" t="inlineStr">
         <is>
-          <t>AE2370999</t>
+          <t>AE6071273</t>
         </is>
       </c>
       <c r="F397" s="6" t="inlineStr">
         <is>
-          <t>60307085730074</t>
+          <t>62708095680047</t>
         </is>
       </c>
       <c r="G397" s="6" t="inlineStr">
         <is>
-          <t>17.04.2025</t>
+          <t>27.01.2026</t>
         </is>
       </c>
       <c r="H397" s="6" t="inlineStr">
         <is>
-          <t>03.07.2008</t>
+          <t>27.08.2009</t>
         </is>
       </c>
     </row>
@@ -15299,30 +15298,30 @@
       </c>
       <c r="C398" s="4" t="inlineStr">
         <is>
-          <t>Shukurova Zilola Farxod qizi</t>
+          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
         </is>
       </c>
       <c r="D398" s="2" t="n">
-        <v>172</v>
+        <v>107</v>
       </c>
       <c r="E398" s="2" t="inlineStr">
         <is>
-          <t>AE1059205</t>
+          <t>AE2370999</t>
         </is>
       </c>
       <c r="F398" s="3" t="inlineStr">
         <is>
-          <t>60610085590150</t>
+          <t>60307085730074</t>
         </is>
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>17.04.2025</t>
         </is>
       </c>
       <c r="H398" s="3" t="inlineStr">
         <is>
-          <t>06.10.2008</t>
+          <t>03.07.2008</t>
         </is>
       </c>
     </row>
@@ -15337,30 +15336,30 @@
       </c>
       <c r="C399" s="7" t="inlineStr">
         <is>
-          <t>Temirova Rushana Sarvarovna</t>
+          <t>Shukurova Zilola Farxod qizi</t>
         </is>
       </c>
       <c r="D399" s="5" t="n">
-        <v>299</v>
+        <v>172</v>
       </c>
       <c r="E399" s="5" t="inlineStr">
         <is>
-          <t>AD9123776</t>
+          <t>AE1059205</t>
         </is>
       </c>
       <c r="F399" s="6" t="inlineStr">
         <is>
-          <t>60709085590113</t>
+          <t>60610085590150</t>
         </is>
       </c>
       <c r="G399" s="6" t="inlineStr">
         <is>
-          <t>23.10.2024</t>
+          <t>07.01.2025</t>
         </is>
       </c>
       <c r="H399" s="6" t="inlineStr">
         <is>
-          <t>07.09.2008</t>
+          <t>06.10.2008</t>
         </is>
       </c>
     </row>
@@ -15375,30 +15374,30 @@
       </c>
       <c r="C400" s="4" t="inlineStr">
         <is>
-          <t>Toshpo'latova Asila Akmal qizi</t>
+          <t>Temirova Rushana Sarvarovna</t>
         </is>
       </c>
       <c r="D400" s="2" t="n">
-        <v>112</v>
+        <v>299</v>
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>AE3444231</t>
+          <t>AD9123776</t>
         </is>
       </c>
       <c r="F400" s="3" t="inlineStr">
         <is>
-          <t>61709085590015</t>
+          <t>60709085590113</t>
         </is>
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>18.07.2025</t>
+          <t>23.10.2024</t>
         </is>
       </c>
       <c r="H400" s="3" t="inlineStr">
         <is>
-          <t>17.09.2008</t>
+          <t>07.09.2008</t>
         </is>
       </c>
     </row>
@@ -15413,28 +15412,30 @@
       </c>
       <c r="C401" s="7" t="inlineStr">
         <is>
-          <t>Tursunmurodova Diyora Jasur qizi</t>
-        </is>
-      </c>
-      <c r="D401" s="5" t="inlineStr"/>
+          <t>Toshpo'latova Asila Akmal qizi</t>
+        </is>
+      </c>
+      <c r="D401" s="5" t="n">
+        <v>112</v>
+      </c>
       <c r="E401" s="5" t="inlineStr">
         <is>
-          <t>AD9513015</t>
+          <t>AE3444231</t>
         </is>
       </c>
       <c r="F401" s="6" t="inlineStr">
         <is>
-          <t>61609075680011</t>
+          <t>61709085590015</t>
         </is>
       </c>
       <c r="G401" s="6" t="inlineStr">
         <is>
-          <t>21.11.2024</t>
+          <t>18.07.2025</t>
         </is>
       </c>
       <c r="H401" s="6" t="inlineStr">
         <is>
-          <t>16.09.2007</t>
+          <t>17.09.2008</t>
         </is>
       </c>
     </row>
@@ -15449,30 +15450,28 @@
       </c>
       <c r="C402" s="4" t="inlineStr">
         <is>
-          <t>Umirova Sevinch Avlayor qizi</t>
-        </is>
-      </c>
-      <c r="D402" s="2" t="n">
-        <v>298</v>
-      </c>
+          <t>Tursunmurodova Diyora Jasur qizi</t>
+        </is>
+      </c>
+      <c r="D402" s="2" t="inlineStr"/>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>AD1671106</t>
+          <t>AD9513015</t>
         </is>
       </c>
       <c r="F402" s="3" t="inlineStr">
         <is>
-          <t>60906055720101</t>
+          <t>61609075680011</t>
         </is>
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>18.08.2022</t>
+          <t>21.11.2024</t>
         </is>
       </c>
       <c r="H402" s="3" t="inlineStr">
         <is>
-          <t>09.06.2005</t>
+          <t>16.09.2007</t>
         </is>
       </c>
     </row>
@@ -15487,30 +15486,30 @@
       </c>
       <c r="C403" s="7" t="inlineStr">
         <is>
-          <t>Usmonova Yulduz Nu'mon qizi</t>
+          <t>Umirova Sevinch Avlayor qizi</t>
         </is>
       </c>
       <c r="D403" s="5" t="n">
-        <v>209</v>
+        <v>298</v>
       </c>
       <c r="E403" s="5" t="inlineStr">
         <is>
-          <t>AD9589389</t>
+          <t>AD1671106</t>
         </is>
       </c>
       <c r="F403" s="6" t="inlineStr">
         <is>
-          <t>62112075680077</t>
+          <t>60906055720101</t>
         </is>
       </c>
       <c r="G403" s="6" t="inlineStr">
         <is>
-          <t>27.11.2024</t>
+          <t>18.08.2022</t>
         </is>
       </c>
       <c r="H403" s="6" t="inlineStr">
         <is>
-          <t>21.12.2007</t>
+          <t>09.06.2005</t>
         </is>
       </c>
     </row>
@@ -15525,30 +15524,30 @@
       </c>
       <c r="C404" s="4" t="inlineStr">
         <is>
-          <t>Xaydarova Iroda Zarif qizi</t>
+          <t>Usmonova Yulduz Nu'mon qizi</t>
         </is>
       </c>
       <c r="D404" s="2" t="n">
-        <v>113</v>
+        <v>209</v>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>AE4240266</t>
+          <t>AD9589389</t>
         </is>
       </c>
       <c r="F404" s="3" t="inlineStr">
         <is>
-          <t>61906085590032</t>
+          <t>62112075680077</t>
         </is>
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>17.09.2025</t>
+          <t>27.11.2024</t>
         </is>
       </c>
       <c r="H404" s="3" t="inlineStr">
         <is>
-          <t>19.06.2008</t>
+          <t>21.12.2007</t>
         </is>
       </c>
     </row>
@@ -15563,30 +15562,30 @@
       </c>
       <c r="C405" s="7" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida Safar qizi</t>
+          <t>Xaydarova Iroda Zarif qizi</t>
         </is>
       </c>
       <c r="D405" s="5" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E405" s="5" t="inlineStr">
         <is>
-          <t>AD9786798</t>
+          <t>AE4240266</t>
         </is>
       </c>
       <c r="F405" s="6" t="inlineStr">
         <is>
-          <t>61911085590096</t>
+          <t>61906085590032</t>
         </is>
       </c>
       <c r="G405" s="6" t="inlineStr">
         <is>
-          <t>12.12.2024</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="H405" s="6" t="inlineStr">
         <is>
-          <t>19.11.2008</t>
+          <t>19.06.2008</t>
         </is>
       </c>
     </row>
@@ -15601,30 +15600,30 @@
       </c>
       <c r="C406" s="4" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
+          <t>Xayrullayeva Umida Safar qizi</t>
         </is>
       </c>
       <c r="D406" s="2" t="n">
-        <v>243</v>
+        <v>116</v>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>AE4328716</t>
+          <t>AD9786798</t>
         </is>
       </c>
       <c r="F406" s="3" t="inlineStr">
         <is>
-          <t>60201085720092</t>
+          <t>61911085590096</t>
         </is>
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>24.09.2025</t>
+          <t>12.12.2024</t>
         </is>
       </c>
       <c r="H406" s="3" t="inlineStr">
         <is>
-          <t>02.01.2008</t>
+          <t>19.11.2008</t>
         </is>
       </c>
     </row>
@@ -15639,30 +15638,30 @@
       </c>
       <c r="C407" s="7" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="D407" s="5" t="n">
-        <v>108</v>
+        <v>243</v>
       </c>
       <c r="E407" s="5" t="inlineStr">
         <is>
-          <t>AE4729924</t>
+          <t>AE4328716</t>
         </is>
       </c>
       <c r="F407" s="6" t="inlineStr">
         <is>
-          <t>62511085730064</t>
+          <t>60201085720092</t>
         </is>
       </c>
       <c r="G407" s="6" t="inlineStr">
         <is>
-          <t>22.10.2025</t>
+          <t>24.09.2025</t>
         </is>
       </c>
       <c r="H407" s="6" t="inlineStr">
         <is>
-          <t>25.11.2008</t>
+          <t>02.01.2008</t>
         </is>
       </c>
     </row>
@@ -15677,30 +15676,30 @@
       </c>
       <c r="C408" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Lobar Ural qizi</t>
+          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
         </is>
       </c>
       <c r="D408" s="2" t="n">
-        <v>234</v>
+        <v>108</v>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>AE2656510</t>
+          <t>AE4729924</t>
         </is>
       </c>
       <c r="F408" s="3" t="inlineStr">
         <is>
-          <t>62508085680062</t>
+          <t>62511085730064</t>
         </is>
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>13.05.2025</t>
+          <t>22.10.2025</t>
         </is>
       </c>
       <c r="H408" s="3" t="inlineStr">
         <is>
-          <t>25.08.2008</t>
+          <t>25.11.2008</t>
         </is>
       </c>
     </row>
@@ -15715,30 +15714,30 @@
       </c>
       <c r="C409" s="7" t="inlineStr">
         <is>
-          <t>Xurramova Sabina Yuldosh qizi</t>
+          <t>Xurramova Lobar Ural qizi</t>
         </is>
       </c>
       <c r="D409" s="5" t="n">
-        <v>52</v>
+        <v>234</v>
       </c>
       <c r="E409" s="5" t="inlineStr">
         <is>
-          <t>AC3081523</t>
+          <t>AE2656510</t>
         </is>
       </c>
       <c r="F409" s="6" t="inlineStr">
         <is>
-          <t>60803048230011</t>
+          <t>62508085680062</t>
         </is>
       </c>
       <c r="G409" s="6" t="inlineStr">
         <is>
-          <t>16.10.2020</t>
+          <t>13.05.2025</t>
         </is>
       </c>
       <c r="H409" s="6" t="inlineStr">
         <is>
-          <t>08.03.2004</t>
+          <t>25.08.2008</t>
         </is>
       </c>
     </row>
@@ -15748,35 +15747,35 @@
       </c>
       <c r="B410" s="3" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C410" s="4" t="inlineStr">
         <is>
-          <t>A'zamov Shohjaxon Sherali o'g'li</t>
+          <t>Xurramova Sabina Yuldosh qizi</t>
         </is>
       </c>
       <c r="D410" s="2" t="n">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>AD9855395</t>
+          <t>AC3081523</t>
         </is>
       </c>
       <c r="F410" s="3" t="inlineStr">
         <is>
-          <t>52510085590064</t>
+          <t>60803048230011</t>
         </is>
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>17.12.2024</t>
+          <t>16.10.2020</t>
         </is>
       </c>
       <c r="H410" s="3" t="inlineStr">
         <is>
-          <t>25.10.2008</t>
+          <t>08.03.2004</t>
         </is>
       </c>
     </row>
@@ -15791,30 +15790,30 @@
       </c>
       <c r="C411" s="7" t="inlineStr">
         <is>
-          <t>Abdixalilova Shohzoda Bahodir qizi</t>
+          <t>A'zamov Shohjaxon Sherali o'g'li</t>
         </is>
       </c>
       <c r="D411" s="5" t="n">
-        <v>274</v>
+        <v>86</v>
       </c>
       <c r="E411" s="5" t="inlineStr">
         <is>
-          <t>AD7053449</t>
+          <t>AD9855395</t>
         </is>
       </c>
       <c r="F411" s="6" t="inlineStr">
         <is>
-          <t>60603085720124</t>
+          <t>52510085590064</t>
         </is>
       </c>
       <c r="G411" s="6" t="inlineStr">
         <is>
-          <t>06.05.2024</t>
+          <t>17.12.2024</t>
         </is>
       </c>
       <c r="H411" s="6" t="inlineStr">
         <is>
-          <t>06.03.2008</t>
+          <t>25.10.2008</t>
         </is>
       </c>
     </row>
@@ -15829,30 +15828,30 @@
       </c>
       <c r="C412" s="4" t="inlineStr">
         <is>
-          <t>Abdiyeva Sabina G'ayrat qizi</t>
+          <t>Abdixalilova Shohzoda Bahodir qizi</t>
         </is>
       </c>
       <c r="D412" s="2" t="n">
-        <v>140</v>
+        <v>274</v>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>AE4860201</t>
+          <t>AD7053449</t>
         </is>
       </c>
       <c r="F412" s="3" t="inlineStr">
         <is>
-          <t>60108085590051</t>
+          <t>60603085720124</t>
         </is>
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>03.11.2025</t>
+          <t>06.05.2024</t>
         </is>
       </c>
       <c r="H412" s="3" t="inlineStr">
         <is>
-          <t>01.08.2008</t>
+          <t>06.03.2008</t>
         </is>
       </c>
     </row>
@@ -15867,30 +15866,30 @@
       </c>
       <c r="C413" s="7" t="inlineStr">
         <is>
-          <t>Abduraxmonova Zahrobonu Toxir qizi</t>
+          <t>Abdiyeva Sabina G'ayrat qizi</t>
         </is>
       </c>
       <c r="D413" s="5" t="n">
-        <v>204</v>
+        <v>140</v>
       </c>
       <c r="E413" s="5" t="inlineStr">
         <is>
-          <t>AE4193791</t>
+          <t>AE4860201</t>
         </is>
       </c>
       <c r="F413" s="6" t="inlineStr">
         <is>
-          <t>61805095590028</t>
+          <t>60108085590051</t>
         </is>
       </c>
       <c r="G413" s="6" t="inlineStr">
         <is>
-          <t>15.09.2025</t>
+          <t>03.11.2025</t>
         </is>
       </c>
       <c r="H413" s="6" t="inlineStr">
         <is>
-          <t>18.05.2009</t>
+          <t>01.08.2008</t>
         </is>
       </c>
     </row>
@@ -15905,30 +15904,30 @@
       </c>
       <c r="C414" s="4" t="inlineStr">
         <is>
-          <t>Eshpulatova Shahnoza Sherali qizi</t>
+          <t>Abduraxmonova Zahrobonu Toxir qizi</t>
         </is>
       </c>
       <c r="D414" s="2" t="n">
-        <v>5</v>
+        <v>204</v>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>AE1541155</t>
+          <t>AE4193791</t>
         </is>
       </c>
       <c r="F414" s="3" t="inlineStr">
         <is>
-          <t>61405085590065</t>
+          <t>61805095590028</t>
         </is>
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>07.02.2025</t>
+          <t>15.09.2025</t>
         </is>
       </c>
       <c r="H414" s="3" t="inlineStr">
         <is>
-          <t>14.05.2008</t>
+          <t>18.05.2009</t>
         </is>
       </c>
     </row>
@@ -15943,30 +15942,30 @@
       </c>
       <c r="C415" s="7" t="inlineStr">
         <is>
-          <t>Eshquvatova Yulduz Asliddin qizi</t>
+          <t>Eshpulatova Shahnoza Sherali qizi</t>
         </is>
       </c>
       <c r="D415" s="5" t="n">
-        <v>267</v>
+        <v>5</v>
       </c>
       <c r="E415" s="5" t="inlineStr">
         <is>
-          <t>AB5879899</t>
+          <t>AE1541155</t>
         </is>
       </c>
       <c r="F415" s="6" t="inlineStr">
         <is>
-          <t>40511985730032</t>
+          <t>61405085590065</t>
         </is>
       </c>
       <c r="G415" s="6" t="inlineStr">
         <is>
-          <t>08.02.2017</t>
+          <t>07.02.2025</t>
         </is>
       </c>
       <c r="H415" s="6" t="inlineStr">
         <is>
-          <t>05.11.1998</t>
+          <t>14.05.2008</t>
         </is>
       </c>
     </row>
@@ -15981,30 +15980,30 @@
       </c>
       <c r="C416" s="4" t="inlineStr">
         <is>
-          <t>G'aniyeva Asila G'ani qizi</t>
+          <t>Eshquvatova Yulduz Asliddin qizi</t>
         </is>
       </c>
       <c r="D416" s="2" t="n">
-        <v>381</v>
+        <v>267</v>
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
-          <t>AE5575300</t>
+          <t>AB5879899</t>
         </is>
       </c>
       <c r="F416" s="3" t="inlineStr">
         <is>
-          <t>41011925590038</t>
+          <t>40511985730032</t>
         </is>
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>23.12.2025</t>
+          <t>08.02.2017</t>
         </is>
       </c>
       <c r="H416" s="3" t="inlineStr">
         <is>
-          <t>10.11.1992</t>
+          <t>05.11.1998</t>
         </is>
       </c>
     </row>
@@ -16019,30 +16018,30 @@
       </c>
       <c r="C417" s="7" t="inlineStr">
         <is>
-          <t>Halimova Sevinch Ravshan qizi</t>
+          <t>G'aniyeva Asila G'ani qizi</t>
         </is>
       </c>
       <c r="D417" s="5" t="n">
-        <v>26</v>
+        <v>381</v>
       </c>
       <c r="E417" s="5" t="inlineStr">
         <is>
-          <t>AD8735102</t>
+          <t>AE5575300</t>
         </is>
       </c>
       <c r="F417" s="6" t="inlineStr">
         <is>
-          <t>60908085680060</t>
+          <t>41011925590038</t>
         </is>
       </c>
       <c r="G417" s="6" t="inlineStr">
         <is>
-          <t>23.09.2024</t>
+          <t>23.12.2025</t>
         </is>
       </c>
       <c r="H417" s="6" t="inlineStr">
         <is>
-          <t>09.08.2008</t>
+          <t>10.11.1992</t>
         </is>
       </c>
     </row>
@@ -16057,30 +16056,30 @@
       </c>
       <c r="C418" s="4" t="inlineStr">
         <is>
-          <t>Hamroqulova Marjona O'ktam qizi</t>
+          <t>Halimova Sevinch Ravshan qizi</t>
         </is>
       </c>
       <c r="D418" s="2" t="n">
-        <v>275</v>
+        <v>26</v>
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>AE1525748</t>
+          <t>AD8735102</t>
         </is>
       </c>
       <c r="F418" s="3" t="inlineStr">
         <is>
-          <t>61104085680018</t>
+          <t>60908085680060</t>
         </is>
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>06.02.2025</t>
+          <t>23.09.2024</t>
         </is>
       </c>
       <c r="H418" s="3" t="inlineStr">
         <is>
-          <t>11.04.2008</t>
+          <t>09.08.2008</t>
         </is>
       </c>
     </row>
@@ -16095,30 +16094,30 @@
       </c>
       <c r="C419" s="7" t="inlineStr">
         <is>
-          <t>Isomiddinova Ruhshona Shavkat qizi</t>
+          <t>Hamroqulova Marjona O'ktam qizi</t>
         </is>
       </c>
       <c r="D419" s="5" t="n">
-        <v>65</v>
+        <v>275</v>
       </c>
       <c r="E419" s="5" t="inlineStr">
         <is>
-          <t>AD7684354</t>
+          <t>AE1525748</t>
         </is>
       </c>
       <c r="F419" s="6" t="inlineStr">
         <is>
-          <t>63006085680064</t>
+          <t>61104085680018</t>
         </is>
       </c>
       <c r="G419" s="6" t="inlineStr">
         <is>
-          <t>01.07.2024</t>
+          <t>06.02.2025</t>
         </is>
       </c>
       <c r="H419" s="6" t="inlineStr">
         <is>
-          <t>30.06.2008</t>
+          <t>11.04.2008</t>
         </is>
       </c>
     </row>
@@ -16133,30 +16132,30 @@
       </c>
       <c r="C420" s="4" t="inlineStr">
         <is>
-          <t>Jalolov Javlonbek G'ani o'g'li</t>
+          <t>Isomiddinova Ruhshona Shavkat qizi</t>
         </is>
       </c>
       <c r="D420" s="2" t="n">
-        <v>211</v>
+        <v>65</v>
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>AE 4994200</t>
+          <t>AD7684354</t>
         </is>
       </c>
       <c r="F420" s="3" t="inlineStr">
         <is>
-          <t>53005095680054</t>
+          <t>63006085680064</t>
         </is>
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>11.11.2025</t>
+          <t>01.07.2024</t>
         </is>
       </c>
       <c r="H420" s="3" t="inlineStr">
         <is>
-          <t>30.05.2009</t>
+          <t>30.06.2008</t>
         </is>
       </c>
     </row>
@@ -16171,30 +16170,30 @@
       </c>
       <c r="C421" s="7" t="inlineStr">
         <is>
-          <t>Karimova Shaxina Fayzulla qizi</t>
+          <t>Jalolov Javlonbek G'ani o'g'li</t>
         </is>
       </c>
       <c r="D421" s="5" t="n">
-        <v>293</v>
+        <v>211</v>
       </c>
       <c r="E421" s="5" t="inlineStr">
         <is>
-          <t>AC0413538</t>
+          <t>AE 4994200</t>
         </is>
       </c>
       <c r="F421" s="6" t="inlineStr">
         <is>
-          <t>61511017890023</t>
+          <t>53005095680054</t>
         </is>
       </c>
       <c r="G421" s="6" t="inlineStr">
         <is>
-          <t>07.12.2018</t>
+          <t>11.11.2025</t>
         </is>
       </c>
       <c r="H421" s="6" t="inlineStr">
         <is>
-          <t>15.11.2001</t>
+          <t>30.05.2009</t>
         </is>
       </c>
     </row>
@@ -16209,30 +16208,30 @@
       </c>
       <c r="C422" s="4" t="inlineStr">
         <is>
-          <t>Mahmudova Gulsanam Nigmatovna</t>
+          <t>Karimova Shaxina Fayzulla qizi</t>
         </is>
       </c>
       <c r="D422" s="2" t="n">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
-          <t>AE1695093</t>
+          <t>AC0413538</t>
         </is>
       </c>
       <c r="F422" s="3" t="inlineStr">
         <is>
-          <t>62308085680109</t>
+          <t>61511017890023</t>
         </is>
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>20.02.2025</t>
+          <t>07.12.2018</t>
         </is>
       </c>
       <c r="H422" s="3" t="inlineStr">
         <is>
-          <t>23.08.2008</t>
+          <t>15.11.2001</t>
         </is>
       </c>
     </row>
@@ -16247,30 +16246,30 @@
       </c>
       <c r="C423" s="7" t="inlineStr">
         <is>
-          <t>Maxmudova Musallam Qamariddin qizi</t>
+          <t>Mahmudova Gulsanam Nigmatovna</t>
         </is>
       </c>
       <c r="D423" s="5" t="n">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="E423" s="5" t="inlineStr">
         <is>
-          <t>AE5297116</t>
+          <t>AE1695093</t>
         </is>
       </c>
       <c r="F423" s="6" t="inlineStr">
         <is>
-          <t>61303085680079</t>
+          <t>62308085680109</t>
         </is>
       </c>
       <c r="G423" s="6" t="inlineStr">
         <is>
-          <t>04.12.2025</t>
+          <t>20.02.2025</t>
         </is>
       </c>
       <c r="H423" s="6" t="inlineStr">
         <is>
-          <t>13.03.2008</t>
+          <t>23.08.2008</t>
         </is>
       </c>
     </row>
@@ -16285,30 +16284,30 @@
       </c>
       <c r="C424" s="4" t="inlineStr">
         <is>
-          <t>Murodova Ruhshona Ilhomovna</t>
+          <t>Maxmudova Musallam Qamariddin qizi</t>
         </is>
       </c>
       <c r="D424" s="2" t="n">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>AE3287114</t>
+          <t>AE5297116</t>
         </is>
       </c>
       <c r="F424" s="3" t="inlineStr">
         <is>
-          <t>61009085680098</t>
+          <t>61303085680079</t>
         </is>
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>07.07.2025</t>
+          <t>04.12.2025</t>
         </is>
       </c>
       <c r="H424" s="3" t="inlineStr">
         <is>
-          <t>10.09.2008</t>
+          <t>13.03.2008</t>
         </is>
       </c>
     </row>
@@ -16323,30 +16322,30 @@
       </c>
       <c r="C425" s="7" t="inlineStr">
         <is>
-          <t>Nafasova Sevinch Bollijon qizi</t>
+          <t>Murodova Ruhshona Ilhomovna</t>
         </is>
       </c>
       <c r="D425" s="5" t="n">
-        <v>266</v>
+        <v>72</v>
       </c>
       <c r="E425" s="5" t="inlineStr">
         <is>
-          <t>AE4668322</t>
+          <t>AE3287114</t>
         </is>
       </c>
       <c r="F425" s="6" t="inlineStr">
         <is>
-          <t>62708085730015</t>
+          <t>61009085680098</t>
         </is>
       </c>
       <c r="G425" s="6" t="inlineStr">
         <is>
-          <t>17.10.2025</t>
+          <t>07.07.2025</t>
         </is>
       </c>
       <c r="H425" s="6" t="inlineStr">
         <is>
-          <t>27.08.2008</t>
+          <t>10.09.2008</t>
         </is>
       </c>
     </row>
@@ -16361,30 +16360,30 @@
       </c>
       <c r="C426" s="4" t="inlineStr">
         <is>
-          <t>Pirnazarova Jasmina Olim qizi</t>
+          <t>Nafasova Sevinch Bollijon qizi</t>
         </is>
       </c>
       <c r="D426" s="2" t="n">
-        <v>13</v>
+        <v>266</v>
       </c>
       <c r="E426" s="2" t="inlineStr">
         <is>
-          <t>AE4198928</t>
+          <t>AE4668322</t>
         </is>
       </c>
       <c r="F426" s="3" t="inlineStr">
         <is>
-          <t>60506085680077</t>
+          <t>62708085730015</t>
         </is>
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>15.09.2025</t>
+          <t>17.10.2025</t>
         </is>
       </c>
       <c r="H426" s="3" t="inlineStr">
         <is>
-          <t>05.06.2008</t>
+          <t>27.08.2008</t>
         </is>
       </c>
     </row>
@@ -16399,30 +16398,30 @@
       </c>
       <c r="C427" s="7" t="inlineStr">
         <is>
-          <t>Qodirova Sabina Suxrob qizi</t>
+          <t>Pirnazarova Jasmina Olim qizi</t>
         </is>
       </c>
       <c r="D427" s="5" t="n">
-        <v>295</v>
+        <v>13</v>
       </c>
       <c r="E427" s="5" t="inlineStr">
         <is>
-          <t>AC2359638</t>
+          <t>AE4198928</t>
         </is>
       </c>
       <c r="F427" s="6" t="inlineStr">
         <is>
-          <t>60203045680015</t>
+          <t>60506085680077</t>
         </is>
       </c>
       <c r="G427" s="6" t="inlineStr">
         <is>
-          <t>03.11.2019</t>
+          <t>15.09.2025</t>
         </is>
       </c>
       <c r="H427" s="6" t="inlineStr">
         <is>
-          <t>02.03.2004</t>
+          <t>05.06.2008</t>
         </is>
       </c>
     </row>
@@ -16437,30 +16436,30 @@
       </c>
       <c r="C428" s="4" t="inlineStr">
         <is>
-          <t>Soyipova Dinora Sanjar qizi</t>
+          <t>Qodirova Sabina Suxrob qizi</t>
         </is>
       </c>
       <c r="D428" s="2" t="n">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="E428" s="2" t="inlineStr">
         <is>
-          <t>AD9484395</t>
+          <t>AC2359638</t>
         </is>
       </c>
       <c r="F428" s="3" t="inlineStr">
         <is>
-          <t>62208085590065</t>
+          <t>60203045680015</t>
         </is>
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>20.11.2024</t>
+          <t>03.11.2019</t>
         </is>
       </c>
       <c r="H428" s="3" t="inlineStr">
         <is>
-          <t>22.08.2008</t>
+          <t>02.03.2004</t>
         </is>
       </c>
     </row>
@@ -16475,30 +16474,30 @@
       </c>
       <c r="C429" s="7" t="inlineStr">
         <is>
-          <t>Suyarova Dinora Sodiq qizi</t>
+          <t>Soyipova Dinora Sanjar qizi</t>
         </is>
       </c>
       <c r="D429" s="5" t="n">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="E429" s="5" t="inlineStr">
         <is>
-          <t>AD9863476</t>
+          <t>AD9484395</t>
         </is>
       </c>
       <c r="F429" s="6" t="inlineStr">
         <is>
-          <t>60108085590037</t>
+          <t>62208085590065</t>
         </is>
       </c>
       <c r="G429" s="6" t="inlineStr">
         <is>
-          <t>18.12.2024</t>
+          <t>20.11.2024</t>
         </is>
       </c>
       <c r="H429" s="6" t="inlineStr">
         <is>
-          <t>01.08.2008</t>
+          <t>22.08.2008</t>
         </is>
       </c>
     </row>
@@ -16513,30 +16512,30 @@
       </c>
       <c r="C430" s="4" t="inlineStr">
         <is>
-          <t>Temirboyeva Iroda Baxtiyor qizi</t>
+          <t>Suyarova Dinora Sodiq qizi</t>
         </is>
       </c>
       <c r="D430" s="2" t="n">
-        <v>20</v>
+        <v>306</v>
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
-          <t>AD6024952</t>
+          <t>AD9863476</t>
         </is>
       </c>
       <c r="F430" s="3" t="inlineStr">
         <is>
-          <t>60112075590084</t>
+          <t>60108085590037</t>
         </is>
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>05.02.2024</t>
+          <t>18.12.2024</t>
         </is>
       </c>
       <c r="H430" s="3" t="inlineStr">
         <is>
-          <t>01.12.2007</t>
+          <t>01.08.2008</t>
         </is>
       </c>
     </row>
@@ -16551,30 +16550,30 @@
       </c>
       <c r="C431" s="7" t="inlineStr">
         <is>
-          <t>Tuychiyeva Farzona Dalerovna</t>
+          <t>Temirboyeva Iroda Baxtiyor qizi</t>
         </is>
       </c>
       <c r="D431" s="5" t="n">
-        <v>280</v>
+        <v>20</v>
       </c>
       <c r="E431" s="5" t="inlineStr">
         <is>
-          <t>AE4114421</t>
+          <t>AD6024952</t>
         </is>
       </c>
       <c r="F431" s="6" t="inlineStr">
         <is>
-          <t>60508095680049</t>
+          <t>60112075590084</t>
         </is>
       </c>
       <c r="G431" s="6" t="inlineStr">
         <is>
-          <t>09.09.2025</t>
+          <t>05.02.2024</t>
         </is>
       </c>
       <c r="H431" s="6" t="inlineStr">
         <is>
-          <t>05.08.2009</t>
+          <t>01.12.2007</t>
         </is>
       </c>
     </row>
@@ -16589,30 +16588,30 @@
       </c>
       <c r="C432" s="4" t="inlineStr">
         <is>
-          <t>Ulugbekova Zara Ulug'bek qizi</t>
+          <t>Tuychiyeva Farzona Dalerovna</t>
         </is>
       </c>
       <c r="D432" s="2" t="n">
-        <v>313</v>
+        <v>280</v>
       </c>
       <c r="E432" s="2" t="inlineStr">
         <is>
-          <t>AE4760779</t>
+          <t>AE4114421</t>
         </is>
       </c>
       <c r="F432" s="3" t="inlineStr">
         <is>
-          <t>61109085590127</t>
+          <t>60508095680049</t>
         </is>
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>24.10.2025</t>
+          <t>09.09.2025</t>
         </is>
       </c>
       <c r="H432" s="3" t="inlineStr">
         <is>
-          <t>11.09.2008</t>
+          <t>05.08.2009</t>
         </is>
       </c>
     </row>
@@ -16627,30 +16626,30 @@
       </c>
       <c r="C433" s="7" t="inlineStr">
         <is>
-          <t>Xamdamova Madina Abdiqodir qizi</t>
+          <t>Ulugbekova Zara Ulug'bek qizi</t>
         </is>
       </c>
       <c r="D433" s="5" t="n">
-        <v>14</v>
+        <v>313</v>
       </c>
       <c r="E433" s="5" t="inlineStr">
         <is>
-          <t>AB8517012</t>
+          <t>AE4760779</t>
         </is>
       </c>
       <c r="F433" s="6" t="inlineStr">
         <is>
-          <t>62701015680026</t>
+          <t>61109085590127</t>
         </is>
       </c>
       <c r="G433" s="6" t="inlineStr">
         <is>
-          <t>07.01.2018</t>
+          <t>24.10.2025</t>
         </is>
       </c>
       <c r="H433" s="6" t="inlineStr">
         <is>
-          <t>27.01.2001</t>
+          <t>11.09.2008</t>
         </is>
       </c>
     </row>
@@ -16665,30 +16664,30 @@
       </c>
       <c r="C434" s="4" t="inlineStr">
         <is>
-          <t>Xannonova Shohsanam Orif qizi</t>
+          <t>Xamdamova Madina Abdiqodir qizi</t>
         </is>
       </c>
       <c r="D434" s="2" t="n">
-        <v>181</v>
+        <v>14</v>
       </c>
       <c r="E434" s="2" t="inlineStr">
         <is>
-          <t>AD0284895</t>
+          <t>AB8517012</t>
         </is>
       </c>
       <c r="F434" s="3" t="inlineStr">
         <is>
-          <t>60206045680052</t>
+          <t>62701015680026</t>
         </is>
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>01.04.2021</t>
+          <t>07.01.2018</t>
         </is>
       </c>
       <c r="H434" s="3" t="inlineStr">
         <is>
-          <t>02.06.2004</t>
+          <t>27.01.2001</t>
         </is>
       </c>
     </row>
@@ -16703,30 +16702,30 @@
       </c>
       <c r="C435" s="7" t="inlineStr">
         <is>
-          <t>Xo'jaqulova Navbahor Azim qizi</t>
+          <t>Xannonova Shohsanam Orif qizi</t>
         </is>
       </c>
       <c r="D435" s="5" t="n">
-        <v>302</v>
+        <v>181</v>
       </c>
       <c r="E435" s="5" t="inlineStr">
         <is>
-          <t>AD4186543</t>
+          <t>AD0284895</t>
         </is>
       </c>
       <c r="F435" s="6" t="inlineStr">
         <is>
-          <t>62104025680040</t>
+          <t>60206045680052</t>
         </is>
       </c>
       <c r="G435" s="6" t="inlineStr">
         <is>
-          <t>07.08.2023</t>
+          <t>01.04.2021</t>
         </is>
       </c>
       <c r="H435" s="6" t="inlineStr">
         <is>
-          <t>21.04.2002</t>
+          <t>02.06.2004</t>
         </is>
       </c>
     </row>
@@ -16741,30 +16740,30 @@
       </c>
       <c r="C436" s="4" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura Dilmurod qizi</t>
+          <t>Xo'jaqulova Navbahor Azim qizi</t>
         </is>
       </c>
       <c r="D436" s="2" t="n">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E436" s="2" t="inlineStr">
         <is>
-          <t>AE1516812</t>
+          <t>AD4186543</t>
         </is>
       </c>
       <c r="F436" s="3" t="inlineStr">
         <is>
-          <t>60110085590193</t>
+          <t>62104025680040</t>
         </is>
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>06.02.2025</t>
+          <t>07.08.2023</t>
         </is>
       </c>
       <c r="H436" s="3" t="inlineStr">
         <is>
-          <t>01.10.2008</t>
+          <t>21.04.2002</t>
         </is>
       </c>
     </row>
@@ -16779,30 +16778,30 @@
       </c>
       <c r="C437" s="7" t="inlineStr">
         <is>
-          <t>Xujamuratova Durdona Bahrom qizi</t>
+          <t>Xolmurodova Dilnura Dilmurod qizi</t>
         </is>
       </c>
       <c r="D437" s="5" t="n">
-        <v>232</v>
+        <v>307</v>
       </c>
       <c r="E437" s="5" t="inlineStr">
         <is>
-          <t>AE5954513</t>
+          <t>AE1516812</t>
         </is>
       </c>
       <c r="F437" s="6" t="inlineStr">
         <is>
-          <t>62204085720105</t>
+          <t>60110085590193</t>
         </is>
       </c>
       <c r="G437" s="6" t="inlineStr">
         <is>
-          <t>20.01.2026</t>
+          <t>06.02.2025</t>
         </is>
       </c>
       <c r="H437" s="6" t="inlineStr">
         <is>
-          <t>22.04.2008</t>
+          <t>01.10.2008</t>
         </is>
       </c>
     </row>
@@ -16817,30 +16816,30 @@
       </c>
       <c r="C438" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
+          <t>Xujamuratova Durdona Bahrom qizi</t>
         </is>
       </c>
       <c r="D438" s="2" t="n">
-        <v>29</v>
+        <v>232</v>
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
-          <t>AC1847101</t>
+          <t>AE5954513</t>
         </is>
       </c>
       <c r="F438" s="3" t="inlineStr">
         <is>
-          <t>60411015680031</t>
+          <t>62204085720105</t>
         </is>
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>24.04.2019</t>
+          <t>20.01.2026</t>
         </is>
       </c>
       <c r="H438" s="3" t="inlineStr">
         <is>
-          <t>04.11.2001</t>
+          <t>22.04.2008</t>
         </is>
       </c>
     </row>
@@ -16855,30 +16854,30 @@
       </c>
       <c r="C439" s="7" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="D439" s="5" t="n">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="E439" s="5" t="inlineStr">
         <is>
-          <t>AD4921163</t>
+          <t>AC1847101</t>
         </is>
       </c>
       <c r="F439" s="6" t="inlineStr">
         <is>
-          <t>63004075680030</t>
+          <t>60411015680031</t>
         </is>
       </c>
       <c r="G439" s="6" t="inlineStr">
         <is>
-          <t>20.10.2023</t>
+          <t>24.04.2019</t>
         </is>
       </c>
       <c r="H439" s="6" t="inlineStr">
         <is>
-          <t>30.04.2007</t>
+          <t>04.11.2001</t>
         </is>
       </c>
     </row>
@@ -16893,30 +16892,30 @@
       </c>
       <c r="C440" s="4" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="D440" s="2" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="E440" s="2" t="inlineStr">
         <is>
-          <t>AE5015467</t>
+          <t>AD4921163</t>
         </is>
       </c>
       <c r="F440" s="3" t="inlineStr">
         <is>
-          <t>60110085590092</t>
+          <t>63004075680030</t>
         </is>
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>12.11.2025</t>
+          <t>20.10.2023</t>
         </is>
       </c>
       <c r="H440" s="3" t="inlineStr">
         <is>
-          <t>01.10.2008</t>
+          <t>30.04.2007</t>
         </is>
       </c>
     </row>
@@ -16931,30 +16930,30 @@
       </c>
       <c r="C441" s="7" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
+          <t>Xusanova Aziza Fazliddin qizi</t>
         </is>
       </c>
       <c r="D441" s="5" t="n">
-        <v>387</v>
+        <v>196</v>
       </c>
       <c r="E441" s="5" t="inlineStr">
         <is>
-          <t>AE5856503</t>
+          <t>AE5015467</t>
         </is>
       </c>
       <c r="F441" s="6" t="inlineStr">
         <is>
-          <t>63112085680039</t>
+          <t>60110085590092</t>
         </is>
       </c>
       <c r="G441" s="6" t="inlineStr">
         <is>
-          <t>14.01.2026</t>
+          <t>12.11.2025</t>
         </is>
       </c>
       <c r="H441" s="6" t="inlineStr">
         <is>
-          <t>31.12.2008</t>
+          <t>01.10.2008</t>
         </is>
       </c>
     </row>
@@ -16964,35 +16963,35 @@
       </c>
       <c r="B442" s="3" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C442" s="4" t="inlineStr">
         <is>
-          <t>Abdishukurova Gulsevar Xusniddin qizi</t>
+          <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="D442" s="2" t="n">
-        <v>238</v>
+        <v>387</v>
       </c>
       <c r="E442" s="2" t="inlineStr">
         <is>
-          <t>AE4148917</t>
+          <t>AE5856503</t>
         </is>
       </c>
       <c r="F442" s="3" t="inlineStr">
         <is>
-          <t>60609085720090</t>
+          <t>63112085680039</t>
         </is>
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>11.09.2025</t>
+          <t>14.01.2026</t>
         </is>
       </c>
       <c r="H442" s="3" t="inlineStr">
         <is>
-          <t>06.09.2008</t>
+          <t>31.12.2008</t>
         </is>
       </c>
     </row>
@@ -17007,30 +17006,30 @@
       </c>
       <c r="C443" s="7" t="inlineStr">
         <is>
-          <t>Ahmadova Munisa Bekzod qizi</t>
+          <t>Abdishukurova Gulsevar Xusniddin qizi</t>
         </is>
       </c>
       <c r="D443" s="5" t="n">
-        <v>33</v>
+        <v>238</v>
       </c>
       <c r="E443" s="5" t="inlineStr">
         <is>
-          <t>AE4831229</t>
+          <t>AE4148917</t>
         </is>
       </c>
       <c r="F443" s="6" t="inlineStr">
         <is>
-          <t>60409085680037</t>
+          <t>60609085720090</t>
         </is>
       </c>
       <c r="G443" s="6" t="inlineStr">
         <is>
-          <t>30.10.2025</t>
+          <t>11.09.2025</t>
         </is>
       </c>
       <c r="H443" s="6" t="inlineStr">
         <is>
-          <t>04.09.2008</t>
+          <t>06.09.2008</t>
         </is>
       </c>
     </row>
@@ -17045,30 +17044,30 @@
       </c>
       <c r="C444" s="4" t="inlineStr">
         <is>
-          <t>Ashirova Gulsanam Abduvali qizi</t>
+          <t>Ahmadova Munisa Bekzod qizi</t>
         </is>
       </c>
       <c r="D444" s="2" t="n">
-        <v>224</v>
+        <v>33</v>
       </c>
       <c r="E444" s="2" t="inlineStr">
         <is>
-          <t>AD6820021</t>
+          <t>AE4831229</t>
         </is>
       </c>
       <c r="F444" s="3" t="inlineStr">
         <is>
-          <t>62311065590082</t>
+          <t>60409085680037</t>
         </is>
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>15.04.2024</t>
+          <t>30.10.2025</t>
         </is>
       </c>
       <c r="H444" s="3" t="inlineStr">
         <is>
-          <t>23.11.2006</t>
+          <t>04.09.2008</t>
         </is>
       </c>
     </row>
@@ -17083,30 +17082,30 @@
       </c>
       <c r="C445" s="7" t="inlineStr">
         <is>
-          <t>Berdimurodova Nafosat Javlon qizi</t>
+          <t>Ashirova Gulsanam Abduvali qizi</t>
         </is>
       </c>
       <c r="D445" s="5" t="n">
-        <v>46</v>
+        <v>224</v>
       </c>
       <c r="E445" s="5" t="inlineStr">
         <is>
-          <t>AD9709558</t>
+          <t>AD6820021</t>
         </is>
       </c>
       <c r="F445" s="6" t="inlineStr">
         <is>
-          <t>60904075680023</t>
+          <t>62311065590082</t>
         </is>
       </c>
       <c r="G445" s="6" t="inlineStr">
         <is>
-          <t>06.12.2024</t>
+          <t>15.04.2024</t>
         </is>
       </c>
       <c r="H445" s="6" t="inlineStr">
         <is>
-          <t>09.04.2007</t>
+          <t>23.11.2006</t>
         </is>
       </c>
     </row>
@@ -17121,30 +17120,30 @@
       </c>
       <c r="C446" s="4" t="inlineStr">
         <is>
-          <t>Choriyeva Zahro Xayrullo qizi</t>
+          <t>Berdimurodova Nafosat Javlon qizi</t>
         </is>
       </c>
       <c r="D446" s="2" t="n">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="E446" s="2" t="inlineStr">
         <is>
-          <t>AD9654318</t>
+          <t>AD9709558</t>
         </is>
       </c>
       <c r="F446" s="3" t="inlineStr">
         <is>
-          <t>62802085590063</t>
+          <t>60904075680023</t>
         </is>
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>03.12.2024</t>
+          <t>06.12.2024</t>
         </is>
       </c>
       <c r="H446" s="3" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>09.04.2007</t>
         </is>
       </c>
     </row>
@@ -17159,30 +17158,30 @@
       </c>
       <c r="C447" s="7" t="inlineStr">
         <is>
-          <t>Ergasheva Shabbona Shodmon qizi</t>
+          <t>Choriyeva Zahro Xayrullo qizi</t>
         </is>
       </c>
       <c r="D447" s="5" t="n">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E447" s="5" t="inlineStr">
         <is>
-          <t>AE2374828</t>
+          <t>AD9654318</t>
         </is>
       </c>
       <c r="F447" s="6" t="inlineStr">
         <is>
-          <t>61803085680050</t>
+          <t>62802085590063</t>
         </is>
       </c>
       <c r="G447" s="6" t="inlineStr">
         <is>
-          <t>17.04.2025</t>
+          <t>03.12.2024</t>
         </is>
       </c>
       <c r="H447" s="6" t="inlineStr">
         <is>
-          <t>18.03.2008</t>
+          <t>28.02.2008</t>
         </is>
       </c>
     </row>
@@ -17197,30 +17196,30 @@
       </c>
       <c r="C448" s="4" t="inlineStr">
         <is>
-          <t>Eshboboyeva Fotima Nurali qizi</t>
+          <t>Ergasheva Shabbona Shodmon qizi</t>
         </is>
       </c>
       <c r="D448" s="2" t="n">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="E448" s="2" t="inlineStr">
         <is>
-          <t>AD0697178</t>
+          <t>AE2374828</t>
         </is>
       </c>
       <c r="F448" s="3" t="inlineStr">
         <is>
-          <t>61306045630044</t>
+          <t>61803085680050</t>
         </is>
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>05.10.2021</t>
+          <t>17.04.2025</t>
         </is>
       </c>
       <c r="H448" s="3" t="inlineStr">
         <is>
-          <t>13.06.2004</t>
+          <t>18.03.2008</t>
         </is>
       </c>
     </row>
@@ -17235,30 +17234,30 @@
       </c>
       <c r="C449" s="7" t="inlineStr">
         <is>
-          <t>G'ayratova Jasmina Sherali qizi</t>
+          <t>Eshboboyeva Fotima Nurali qizi</t>
         </is>
       </c>
       <c r="D449" s="5" t="n">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="E449" s="5" t="inlineStr">
         <is>
-          <t>AE3497923</t>
+          <t>AD0697178</t>
         </is>
       </c>
       <c r="F449" s="6" t="inlineStr">
         <is>
-          <t>60208085590146</t>
+          <t>61306045630044</t>
         </is>
       </c>
       <c r="G449" s="6" t="inlineStr">
         <is>
-          <t>23.07.2025</t>
+          <t>05.10.2021</t>
         </is>
       </c>
       <c r="H449" s="6" t="inlineStr">
         <is>
-          <t>02.08.2008</t>
+          <t>13.06.2004</t>
         </is>
       </c>
     </row>
@@ -17273,30 +17272,30 @@
       </c>
       <c r="C450" s="4" t="inlineStr">
         <is>
-          <t>Ixtiyorova Niginabonu Xolovna</t>
+          <t>G'ayratova Jasmina Sherali qizi</t>
         </is>
       </c>
       <c r="D450" s="2" t="n">
-        <v>227</v>
+        <v>97</v>
       </c>
       <c r="E450" s="2" t="inlineStr">
         <is>
-          <t>AD9335686</t>
+          <t>AE3497923</t>
         </is>
       </c>
       <c r="F450" s="3" t="inlineStr">
         <is>
-          <t>60710085680054</t>
+          <t>60208085590146</t>
         </is>
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>23.07.2025</t>
         </is>
       </c>
       <c r="H450" s="3" t="inlineStr">
         <is>
-          <t>07.10.2008</t>
+          <t>02.08.2008</t>
         </is>
       </c>
     </row>
@@ -17311,30 +17310,30 @@
       </c>
       <c r="C451" s="7" t="inlineStr">
         <is>
-          <t>Jabborova Bahoroy Shukurullo qizi</t>
+          <t>Ixtiyorova Niginabonu Xolovna</t>
         </is>
       </c>
       <c r="D451" s="5" t="n">
-        <v>202</v>
+        <v>227</v>
       </c>
       <c r="E451" s="5" t="inlineStr">
         <is>
-          <t>AE4255446</t>
+          <t>AD9335686</t>
         </is>
       </c>
       <c r="F451" s="6" t="inlineStr">
         <is>
-          <t>61510085680048</t>
+          <t>60710085680054</t>
         </is>
       </c>
       <c r="G451" s="6" t="inlineStr">
         <is>
-          <t>18.09.2025</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="H451" s="6" t="inlineStr">
         <is>
-          <t>15.10.2008</t>
+          <t>07.10.2008</t>
         </is>
       </c>
     </row>
@@ -17349,30 +17348,30 @@
       </c>
       <c r="C452" s="4" t="inlineStr">
         <is>
-          <t>Jalilova Jasmina Jamshid qizi</t>
+          <t>Jabborova Bahoroy Shukurullo qizi</t>
         </is>
       </c>
       <c r="D452" s="2" t="n">
-        <v>95</v>
+        <v>202</v>
       </c>
       <c r="E452" s="2" t="inlineStr">
         <is>
-          <t>AE4319796</t>
+          <t>AE4255446</t>
         </is>
       </c>
       <c r="F452" s="3" t="inlineStr">
         <is>
-          <t>60211085680014</t>
+          <t>61510085680048</t>
         </is>
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>23.09.2025</t>
+          <t>18.09.2025</t>
         </is>
       </c>
       <c r="H452" s="3" t="inlineStr">
         <is>
-          <t>02.11.2008</t>
+          <t>15.10.2008</t>
         </is>
       </c>
     </row>
@@ -17387,30 +17386,30 @@
       </c>
       <c r="C453" s="7" t="inlineStr">
         <is>
-          <t>Jumayeva Muxlisa Komiljon qizi</t>
+          <t>Jalilova Jasmina Jamshid qizi</t>
         </is>
       </c>
       <c r="D453" s="5" t="n">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="E453" s="5" t="inlineStr">
         <is>
-          <t>AB6258375</t>
+          <t>AE4319796</t>
         </is>
       </c>
       <c r="F453" s="6" t="inlineStr">
         <is>
-          <t>61701005680057</t>
+          <t>60211085680014</t>
         </is>
       </c>
       <c r="G453" s="6" t="inlineStr">
         <is>
-          <t>29.03.2017</t>
+          <t>23.09.2025</t>
         </is>
       </c>
       <c r="H453" s="6" t="inlineStr">
         <is>
-          <t>17.01.2000</t>
+          <t>02.11.2008</t>
         </is>
       </c>
     </row>
@@ -17425,30 +17424,30 @@
       </c>
       <c r="C454" s="4" t="inlineStr">
         <is>
-          <t>Jurayeva Madina Odil qizi</t>
+          <t>Jumayeva Muxlisa Komiljon qizi</t>
         </is>
       </c>
       <c r="D454" s="2" t="n">
-        <v>215</v>
+        <v>59</v>
       </c>
       <c r="E454" s="2" t="inlineStr">
         <is>
-          <t>AD9394305</t>
+          <t>AB6258375</t>
         </is>
       </c>
       <c r="F454" s="3" t="inlineStr">
         <is>
-          <t>62512075730060</t>
+          <t>61701005680057</t>
         </is>
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>13.11.2024</t>
+          <t>29.03.2017</t>
         </is>
       </c>
       <c r="H454" s="3" t="inlineStr">
         <is>
-          <t>25.12.2007</t>
+          <t>17.01.2000</t>
         </is>
       </c>
     </row>
@@ -17463,30 +17462,30 @@
       </c>
       <c r="C455" s="7" t="inlineStr">
         <is>
-          <t>Luxmonova Nozima Ilhom qizi</t>
+          <t>Jurayeva Madina Odil qizi</t>
         </is>
       </c>
       <c r="D455" s="5" t="n">
-        <v>139</v>
+        <v>215</v>
       </c>
       <c r="E455" s="5" t="inlineStr">
         <is>
-          <t>AE4290181</t>
+          <t>AD9394305</t>
         </is>
       </c>
       <c r="F455" s="6" t="inlineStr">
         <is>
-          <t>61611085680042</t>
+          <t>62512075730060</t>
         </is>
       </c>
       <c r="G455" s="6" t="inlineStr">
         <is>
-          <t>22.09.2025</t>
+          <t>13.11.2024</t>
         </is>
       </c>
       <c r="H455" s="6" t="inlineStr">
         <is>
-          <t>16.11.2008</t>
+          <t>25.12.2007</t>
         </is>
       </c>
     </row>
@@ -17501,30 +17500,30 @@
       </c>
       <c r="C456" s="4" t="inlineStr">
         <is>
-          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
+          <t>Luxmonova Nozima Ilhom qizi</t>
         </is>
       </c>
       <c r="D456" s="2" t="n">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="E456" s="2" t="inlineStr">
         <is>
-          <t>AD7829399</t>
+          <t>AE4290181</t>
         </is>
       </c>
       <c r="F456" s="3" t="inlineStr">
         <is>
-          <t>41902975680049</t>
+          <t>61611085680042</t>
         </is>
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>11.07.2024</t>
+          <t>22.09.2025</t>
         </is>
       </c>
       <c r="H456" s="3" t="inlineStr">
         <is>
-          <t>19.02.1997</t>
+          <t>16.11.2008</t>
         </is>
       </c>
     </row>
@@ -17539,30 +17538,30 @@
       </c>
       <c r="C457" s="7" t="inlineStr">
         <is>
-          <t>Murodova Munisa Muxtor qizi</t>
+          <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
         </is>
       </c>
       <c r="D457" s="5" t="n">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="E457" s="5" t="inlineStr">
         <is>
-          <t>AE2895049</t>
+          <t>AD7829399</t>
         </is>
       </c>
       <c r="F457" s="6" t="inlineStr">
         <is>
-          <t>62112085680050</t>
+          <t>41902975680049</t>
         </is>
       </c>
       <c r="G457" s="6" t="inlineStr">
         <is>
-          <t>03.06.2025</t>
+          <t>11.07.2024</t>
         </is>
       </c>
       <c r="H457" s="6" t="inlineStr">
         <is>
-          <t>21.12.2008</t>
+          <t>19.02.1997</t>
         </is>
       </c>
     </row>
@@ -17577,30 +17576,30 @@
       </c>
       <c r="C458" s="4" t="inlineStr">
         <is>
-          <t>Muzrapova Ruhshona Asrorxon qizi</t>
+          <t>Murodova Munisa Muxtor qizi</t>
         </is>
       </c>
       <c r="D458" s="2" t="n">
-        <v>69</v>
+        <v>167</v>
       </c>
       <c r="E458" s="2" t="inlineStr">
         <is>
-          <t>AD9123240</t>
+          <t>AE2895049</t>
         </is>
       </c>
       <c r="F458" s="3" t="inlineStr">
         <is>
-          <t>62710075590066</t>
+          <t>62112085680050</t>
         </is>
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>23.10.2024</t>
+          <t>03.06.2025</t>
         </is>
       </c>
       <c r="H458" s="3" t="inlineStr">
         <is>
-          <t>27.10.2007</t>
+          <t>21.12.2008</t>
         </is>
       </c>
     </row>
@@ -17615,30 +17614,30 @@
       </c>
       <c r="C459" s="7" t="inlineStr">
         <is>
-          <t>Nazarova Munisa Erkin qizi</t>
+          <t>Muzrapova Ruhshona Asrorxon qizi</t>
         </is>
       </c>
       <c r="D459" s="5" t="n">
-        <v>258</v>
+        <v>69</v>
       </c>
       <c r="E459" s="5" t="inlineStr">
         <is>
-          <t>AE7685867</t>
+          <t>AD9123240</t>
         </is>
       </c>
       <c r="F459" s="6" t="inlineStr">
         <is>
-          <t>41205925680015</t>
+          <t>62710075590066</t>
         </is>
       </c>
       <c r="G459" s="6" t="inlineStr">
         <is>
-          <t>17.06.2026</t>
+          <t>23.10.2024</t>
         </is>
       </c>
       <c r="H459" s="6" t="inlineStr">
         <is>
-          <t>12.05.1992</t>
+          <t>27.10.2007</t>
         </is>
       </c>
     </row>
@@ -17653,28 +17652,30 @@
       </c>
       <c r="C460" s="4" t="inlineStr">
         <is>
-          <t>Ne'matova Sevinch Hikmatullo qizi</t>
-        </is>
-      </c>
-      <c r="D460" s="2" t="inlineStr"/>
+          <t>Nazarova Munisa Erkin qizi</t>
+        </is>
+      </c>
+      <c r="D460" s="2" t="n">
+        <v>258</v>
+      </c>
       <c r="E460" s="2" t="inlineStr">
         <is>
-          <t>AE7082532</t>
+          <t>AE7685867</t>
         </is>
       </c>
       <c r="F460" s="3" t="inlineStr">
         <is>
-          <t>60212085680048</t>
+          <t>41205925680015</t>
         </is>
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>16.04.2026</t>
+          <t>17.06.2026</t>
         </is>
       </c>
       <c r="H460" s="3" t="inlineStr">
         <is>
-          <t>02.12.2008</t>
+          <t>12.05.1992</t>
         </is>
       </c>
     </row>
@@ -17689,30 +17690,28 @@
       </c>
       <c r="C461" s="7" t="inlineStr">
         <is>
-          <t>Normurodova Gulsanam Elyor qizi</t>
-        </is>
-      </c>
-      <c r="D461" s="5" t="n">
-        <v>136</v>
-      </c>
+          <t>Ne'matova Sevinch Hikmatullo qizi</t>
+        </is>
+      </c>
+      <c r="D461" s="5" t="inlineStr"/>
       <c r="E461" s="5" t="inlineStr">
         <is>
-          <t>AE4817469</t>
+          <t>AE7082532</t>
         </is>
       </c>
       <c r="F461" s="6" t="inlineStr">
         <is>
-          <t>61809085680096</t>
+          <t>60212085680048</t>
         </is>
       </c>
       <c r="G461" s="6" t="inlineStr">
         <is>
-          <t>29.10.2025</t>
+          <t>16.04.2026</t>
         </is>
       </c>
       <c r="H461" s="6" t="inlineStr">
         <is>
-          <t>18.09.2008</t>
+          <t>02.12.2008</t>
         </is>
       </c>
     </row>
@@ -17727,30 +17726,30 @@
       </c>
       <c r="C462" s="4" t="inlineStr">
         <is>
-          <t>Omonova Charos Orif qizi</t>
+          <t>Normurodova Gulsanam Elyor qizi</t>
         </is>
       </c>
       <c r="D462" s="2" t="n">
-        <v>230</v>
+        <v>136</v>
       </c>
       <c r="E462" s="2" t="inlineStr">
         <is>
-          <t>AE1338424</t>
+          <t>AE4817469</t>
         </is>
       </c>
       <c r="F462" s="3" t="inlineStr">
         <is>
-          <t>40306985590014</t>
+          <t>61809085680096</t>
         </is>
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>23.01.2025</t>
+          <t>29.10.2025</t>
         </is>
       </c>
       <c r="H462" s="3" t="inlineStr">
         <is>
-          <t>03.06.1998</t>
+          <t>18.09.2008</t>
         </is>
       </c>
     </row>
@@ -17765,28 +17764,30 @@
       </c>
       <c r="C463" s="7" t="inlineStr">
         <is>
-          <t>Oripova Sevinch G'olib qizi</t>
-        </is>
-      </c>
-      <c r="D463" s="5" t="inlineStr"/>
+          <t>Omonova Charos Orif qizi</t>
+        </is>
+      </c>
+      <c r="D463" s="5" t="n">
+        <v>230</v>
+      </c>
       <c r="E463" s="5" t="inlineStr">
         <is>
-          <t>AE3333890</t>
+          <t>AE1338424</t>
         </is>
       </c>
       <c r="F463" s="6" t="inlineStr">
         <is>
-          <t>62007085680095</t>
+          <t>40306985590014</t>
         </is>
       </c>
       <c r="G463" s="6" t="inlineStr">
         <is>
-          <t>09.07.2025</t>
+          <t>23.01.2025</t>
         </is>
       </c>
       <c r="H463" s="6" t="inlineStr">
         <is>
-          <t>20.07.2008</t>
+          <t>03.06.1998</t>
         </is>
       </c>
     </row>
@@ -17801,30 +17802,28 @@
       </c>
       <c r="C464" s="4" t="inlineStr">
         <is>
-          <t>Ozodova Klara Fayzullayevna</t>
-        </is>
-      </c>
-      <c r="D464" s="2" t="n">
-        <v>285</v>
-      </c>
+          <t>Oripova Sevinch G'olib qizi</t>
+        </is>
+      </c>
+      <c r="D464" s="2" t="inlineStr"/>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>AD6663341</t>
+          <t>AE3333890</t>
         </is>
       </c>
       <c r="F464" s="3" t="inlineStr">
         <is>
-          <t>60803075590140</t>
+          <t>62007085680095</t>
         </is>
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>01.04.2024</t>
+          <t>09.07.2025</t>
         </is>
       </c>
       <c r="H464" s="3" t="inlineStr">
         <is>
-          <t>08.03.2007</t>
+          <t>20.07.2008</t>
         </is>
       </c>
     </row>
@@ -17839,30 +17838,30 @@
       </c>
       <c r="C465" s="7" t="inlineStr">
         <is>
-          <t>Saidova Dilso'z Ilyos qizi</t>
+          <t>Ozodova Klara Fayzullayevna</t>
         </is>
       </c>
       <c r="D465" s="5" t="n">
-        <v>67</v>
+        <v>285</v>
       </c>
       <c r="E465" s="5" t="inlineStr">
         <is>
-          <t>AE6043288</t>
+          <t>AD6663341</t>
         </is>
       </c>
       <c r="F465" s="6" t="inlineStr">
         <is>
-          <t>60511085680024</t>
+          <t>60803075590140</t>
         </is>
       </c>
       <c r="G465" s="6" t="inlineStr">
         <is>
-          <t>26.01.2026</t>
+          <t>01.04.2024</t>
         </is>
       </c>
       <c r="H465" s="6" t="inlineStr">
         <is>
-          <t>05.11.2008</t>
+          <t>08.03.2007</t>
         </is>
       </c>
     </row>
@@ -17877,30 +17876,30 @@
       </c>
       <c r="C466" s="4" t="inlineStr">
         <is>
-          <t>Sharipova Diyora Jasur qizi</t>
+          <t>Saidova Dilso'z Ilyos qizi</t>
         </is>
       </c>
       <c r="D466" s="2" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="E466" s="2" t="inlineStr">
         <is>
-          <t>AE5776687</t>
+          <t>AE6043288</t>
         </is>
       </c>
       <c r="F466" s="3" t="inlineStr">
         <is>
-          <t>62307095590022</t>
+          <t>60511085680024</t>
         </is>
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>09.01.2026</t>
+          <t>26.01.2026</t>
         </is>
       </c>
       <c r="H466" s="3" t="inlineStr">
         <is>
-          <t>23.07.2009</t>
+          <t>05.11.2008</t>
         </is>
       </c>
     </row>
@@ -17915,30 +17914,30 @@
       </c>
       <c r="C467" s="7" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Sharipova Diyora Jasur qizi</t>
         </is>
       </c>
       <c r="D467" s="5" t="n">
-        <v>388</v>
+        <v>57</v>
       </c>
       <c r="E467" s="5" t="inlineStr">
         <is>
-          <t>AD0914473</t>
+          <t>AE5776687</t>
         </is>
       </c>
       <c r="F467" s="6" t="inlineStr">
         <is>
-          <t>62803055590089</t>
+          <t>62307095590022</t>
         </is>
       </c>
       <c r="G467" s="6" t="inlineStr">
         <is>
-          <t>14.12.2021</t>
+          <t>09.01.2026</t>
         </is>
       </c>
       <c r="H467" s="6" t="inlineStr">
         <is>
-          <t>28.03.2005</t>
+          <t>23.07.2009</t>
         </is>
       </c>
     </row>
@@ -17953,30 +17952,30 @@
       </c>
       <c r="C468" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="D468" s="2" t="n">
-        <v>276</v>
+        <v>388</v>
       </c>
       <c r="E468" s="2" t="inlineStr">
         <is>
-          <t>AD6026687</t>
+          <t>AD0914473</t>
         </is>
       </c>
       <c r="F468" s="3" t="inlineStr">
         <is>
-          <t>61407075590019</t>
+          <t>62803055590089</t>
         </is>
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>06.02.2024</t>
+          <t>14.12.2021</t>
         </is>
       </c>
       <c r="H468" s="3" t="inlineStr">
         <is>
-          <t>14.07.2007</t>
+          <t>28.03.2005</t>
         </is>
       </c>
     </row>
@@ -17991,30 +17990,30 @@
       </c>
       <c r="C469" s="7" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="D469" s="5" t="n">
-        <v>218</v>
+        <v>276</v>
       </c>
       <c r="E469" s="5" t="inlineStr">
         <is>
-          <t>AE5949204</t>
+          <t>AD6026687</t>
         </is>
       </c>
       <c r="F469" s="6" t="inlineStr">
         <is>
-          <t>62710085680012</t>
+          <t>61407075590019</t>
         </is>
       </c>
       <c r="G469" s="6" t="inlineStr">
         <is>
-          <t>20.01.2026</t>
+          <t>06.02.2024</t>
         </is>
       </c>
       <c r="H469" s="6" t="inlineStr">
         <is>
-          <t>27.10.2008</t>
+          <t>14.07.2007</t>
         </is>
       </c>
     </row>
@@ -18029,20 +18028,20 @@
       </c>
       <c r="C470" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="D470" s="2" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E470" s="2" t="inlineStr">
         <is>
-          <t>AE5949016</t>
+          <t>AE5949204</t>
         </is>
       </c>
       <c r="F470" s="3" t="inlineStr">
         <is>
-          <t>62710085680029</t>
+          <t>62710085680012</t>
         </is>
       </c>
       <c r="G470" s="3" t="inlineStr">
@@ -18067,30 +18066,30 @@
       </c>
       <c r="C471" s="7" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="D471" s="5" t="n">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="E471" s="5" t="inlineStr">
         <is>
-          <t>AE4384190</t>
+          <t>AE5949016</t>
         </is>
       </c>
       <c r="F471" s="6" t="inlineStr">
         <is>
-          <t>61810085590061</t>
+          <t>62710085680029</t>
         </is>
       </c>
       <c r="G471" s="6" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>20.01.2026</t>
         </is>
       </c>
       <c r="H471" s="6" t="inlineStr">
         <is>
-          <t>18.10.2008</t>
+          <t>27.10.2008</t>
         </is>
       </c>
     </row>
@@ -18105,30 +18104,30 @@
       </c>
       <c r="C472" s="4" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="D472" s="2" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="E472" s="2" t="inlineStr">
         <is>
-          <t>AD8362477</t>
+          <t>AE4384190</t>
         </is>
       </c>
       <c r="F472" s="3" t="inlineStr">
         <is>
-          <t>42601955730024</t>
+          <t>61810085590061</t>
         </is>
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>23.08.2024</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="H472" s="3" t="inlineStr">
         <is>
-          <t>26.01.1995</t>
+          <t>18.10.2008</t>
         </is>
       </c>
     </row>
@@ -18143,30 +18142,30 @@
       </c>
       <c r="C473" s="7" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
         </is>
       </c>
       <c r="D473" s="5" t="n">
-        <v>118</v>
+        <v>183</v>
       </c>
       <c r="E473" s="5" t="inlineStr">
         <is>
-          <t>AE1419035</t>
+          <t>AD8362477</t>
         </is>
       </c>
       <c r="F473" s="6" t="inlineStr">
         <is>
-          <t>61309085590066</t>
+          <t>42601955730024</t>
         </is>
       </c>
       <c r="G473" s="6" t="inlineStr">
         <is>
-          <t>29.01.2025</t>
+          <t>23.08.2024</t>
         </is>
       </c>
       <c r="H473" s="6" t="inlineStr">
         <is>
-          <t>13.09.2008</t>
+          <t>26.01.1995</t>
         </is>
       </c>
     </row>
@@ -18176,35 +18175,35 @@
       </c>
       <c r="B474" s="3" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C474" s="4" t="inlineStr">
         <is>
-          <t>Abdinazarova Dilafro'z Burxon qizi</t>
+          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="D474" s="2" t="n">
-        <v>273</v>
+        <v>118</v>
       </c>
       <c r="E474" s="2" t="inlineStr">
         <is>
-          <t>AE3704528</t>
+          <t>AE1419035</t>
         </is>
       </c>
       <c r="F474" s="3" t="inlineStr">
         <is>
-          <t>40401955680037</t>
+          <t>61309085590066</t>
         </is>
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>08.08.2025</t>
+          <t>29.01.2025</t>
         </is>
       </c>
       <c r="H474" s="3" t="inlineStr">
         <is>
-          <t>04.01.1995</t>
+          <t>13.09.2008</t>
         </is>
       </c>
     </row>
@@ -18219,30 +18218,30 @@
       </c>
       <c r="C475" s="7" t="inlineStr">
         <is>
-          <t>Abdixoliqova Elmira Farxod qizi</t>
+          <t>Abdinazarova Dilafro'z Burxon qizi</t>
         </is>
       </c>
       <c r="D475" s="5" t="n">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="E475" s="5" t="inlineStr">
         <is>
-          <t>AE4512271</t>
+          <t>AE3704528</t>
         </is>
       </c>
       <c r="F475" s="6" t="inlineStr">
         <is>
-          <t>62501095720012</t>
+          <t>40401955680037</t>
         </is>
       </c>
       <c r="G475" s="6" t="inlineStr">
         <is>
-          <t>07.10.2025</t>
+          <t>08.08.2025</t>
         </is>
       </c>
       <c r="H475" s="6" t="inlineStr">
         <is>
-          <t>25.01.2009</t>
+          <t>04.01.1995</t>
         </is>
       </c>
     </row>
@@ -18257,30 +18256,30 @@
       </c>
       <c r="C476" s="4" t="inlineStr">
         <is>
-          <t>Azimova Zahroxon Abdirauf qizi</t>
+          <t>Abdixoliqova Elmira Farxod qizi</t>
         </is>
       </c>
       <c r="D476" s="2" t="n">
-        <v>318</v>
+        <v>286</v>
       </c>
       <c r="E476" s="2" t="inlineStr">
         <is>
-          <t>AD5290004</t>
+          <t>AE4512271</t>
         </is>
       </c>
       <c r="F476" s="3" t="inlineStr">
         <is>
-          <t>61312065590013</t>
+          <t>62501095720012</t>
         </is>
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>01.12.2023</t>
+          <t>07.10.2025</t>
         </is>
       </c>
       <c r="H476" s="3" t="inlineStr">
         <is>
-          <t>13.12.2006</t>
+          <t>25.01.2009</t>
         </is>
       </c>
     </row>
@@ -18295,30 +18294,30 @@
       </c>
       <c r="C477" s="7" t="inlineStr">
         <is>
-          <t>Bahodirova Asila Olmos qizi</t>
+          <t>Azimova Zahroxon Abdirauf qizi</t>
         </is>
       </c>
       <c r="D477" s="5" t="n">
-        <v>44</v>
+        <v>318</v>
       </c>
       <c r="E477" s="5" t="inlineStr">
         <is>
-          <t>AE1222596</t>
+          <t>AD5290004</t>
         </is>
       </c>
       <c r="F477" s="6" t="inlineStr">
         <is>
-          <t>61711085590032</t>
+          <t>61312065590013</t>
         </is>
       </c>
       <c r="G477" s="6" t="inlineStr">
         <is>
-          <t>16.01.2025</t>
+          <t>01.12.2023</t>
         </is>
       </c>
       <c r="H477" s="6" t="inlineStr">
         <is>
-          <t>17.11.2008</t>
+          <t>13.12.2006</t>
         </is>
       </c>
     </row>
@@ -18333,30 +18332,30 @@
       </c>
       <c r="C478" s="4" t="inlineStr">
         <is>
-          <t>Davlatova Gulnoza Husan qizi</t>
+          <t>Bahodirova Asila Olmos qizi</t>
         </is>
       </c>
       <c r="D478" s="2" t="n">
-        <v>310</v>
+        <v>44</v>
       </c>
       <c r="E478" s="2" t="inlineStr">
         <is>
-          <t>AD8208717</t>
+          <t>AE1222596</t>
         </is>
       </c>
       <c r="F478" s="3" t="inlineStr">
         <is>
-          <t>41508955590021</t>
+          <t>61711085590032</t>
         </is>
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>12.08.2024</t>
+          <t>16.01.2025</t>
         </is>
       </c>
       <c r="H478" s="3" t="inlineStr">
         <is>
-          <t>15.08.1995</t>
+          <t>17.11.2008</t>
         </is>
       </c>
     </row>
@@ -18371,30 +18370,30 @@
       </c>
       <c r="C479" s="7" t="inlineStr">
         <is>
-          <t>Eshimova Zilola Bekzod qizi</t>
+          <t>Davlatova Gulnoza Husan qizi</t>
         </is>
       </c>
       <c r="D479" s="5" t="n">
-        <v>174</v>
+        <v>310</v>
       </c>
       <c r="E479" s="5" t="inlineStr">
         <is>
-          <t>AE2935693</t>
+          <t>AD8208717</t>
         </is>
       </c>
       <c r="F479" s="6" t="inlineStr">
         <is>
-          <t>61506085730076</t>
+          <t>41508955590021</t>
         </is>
       </c>
       <c r="G479" s="6" t="inlineStr">
         <is>
-          <t>09.06.2025</t>
+          <t>12.08.2024</t>
         </is>
       </c>
       <c r="H479" s="6" t="inlineStr">
         <is>
-          <t>15.06.2008</t>
+          <t>15.08.1995</t>
         </is>
       </c>
     </row>
@@ -18409,28 +18408,30 @@
       </c>
       <c r="C480" s="4" t="inlineStr">
         <is>
-          <t>Irgasheva Dinora Shodmon qizi</t>
-        </is>
-      </c>
-      <c r="D480" s="2" t="inlineStr"/>
+          <t>Eshimova Zilola Bekzod qizi</t>
+        </is>
+      </c>
+      <c r="D480" s="2" t="n">
+        <v>174</v>
+      </c>
       <c r="E480" s="2" t="inlineStr">
         <is>
-          <t>AC 2430931</t>
+          <t>AE2935693</t>
         </is>
       </c>
       <c r="F480" s="3" t="inlineStr">
         <is>
-          <t>60106035590029</t>
+          <t>61506085730076</t>
         </is>
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>15.11.2019</t>
+          <t>09.06.2025</t>
         </is>
       </c>
       <c r="H480" s="3" t="inlineStr">
         <is>
-          <t>01.06.2003</t>
+          <t>15.06.2008</t>
         </is>
       </c>
     </row>
@@ -18445,30 +18446,28 @@
       </c>
       <c r="C481" s="7" t="inlineStr">
         <is>
-          <t>Jalilova Shabnam Ozodjon qizi</t>
-        </is>
-      </c>
-      <c r="D481" s="5" t="n">
-        <v>17</v>
-      </c>
+          <t>Irgasheva Dinora Shodmon qizi</t>
+        </is>
+      </c>
+      <c r="D481" s="5" t="inlineStr"/>
       <c r="E481" s="5" t="inlineStr">
         <is>
-          <t>AD9937321</t>
+          <t>AC 2430931</t>
         </is>
       </c>
       <c r="F481" s="6" t="inlineStr">
         <is>
-          <t>60603085590037</t>
+          <t>60106035590029</t>
         </is>
       </c>
       <c r="G481" s="6" t="inlineStr">
         <is>
-          <t>24.12.2024</t>
+          <t>15.11.2019</t>
         </is>
       </c>
       <c r="H481" s="6" t="inlineStr">
         <is>
-          <t>06.03.2008</t>
+          <t>01.06.2003</t>
         </is>
       </c>
     </row>
@@ -18483,30 +18482,30 @@
       </c>
       <c r="C482" s="4" t="inlineStr">
         <is>
-          <t>Jumayeva Husnida Shovkat qizi</t>
+          <t>Jalilova Shabnam Ozodjon qizi</t>
         </is>
       </c>
       <c r="D482" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E482" s="2" t="inlineStr">
         <is>
-          <t>AE6299685</t>
+          <t>AD9937321</t>
         </is>
       </c>
       <c r="F482" s="3" t="inlineStr">
         <is>
-          <t>60907085590063</t>
+          <t>60603085590037</t>
         </is>
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>11.02.2026</t>
+          <t>24.12.2024</t>
         </is>
       </c>
       <c r="H482" s="3" t="inlineStr">
         <is>
-          <t>09.07.2008</t>
+          <t>06.03.2008</t>
         </is>
       </c>
     </row>
@@ -18521,30 +18520,30 @@
       </c>
       <c r="C483" s="7" t="inlineStr">
         <is>
-          <t>Karimova Nozliya Rustamovna</t>
+          <t>Jumayeva Husnida Shovkat qizi</t>
         </is>
       </c>
       <c r="D483" s="5" t="n">
-        <v>250</v>
+        <v>18</v>
       </c>
       <c r="E483" s="5" t="inlineStr">
         <is>
-          <t>AE4674508</t>
+          <t>AE6299685</t>
         </is>
       </c>
       <c r="F483" s="6" t="inlineStr">
         <is>
-          <t>61502085680047</t>
+          <t>60907085590063</t>
         </is>
       </c>
       <c r="G483" s="6" t="inlineStr">
         <is>
-          <t>18.10.2025</t>
+          <t>11.02.2026</t>
         </is>
       </c>
       <c r="H483" s="6" t="inlineStr">
         <is>
-          <t>15.02.2008</t>
+          <t>09.07.2008</t>
         </is>
       </c>
     </row>
@@ -18559,30 +18558,30 @@
       </c>
       <c r="C484" s="4" t="inlineStr">
         <is>
-          <t>Mahmadmurodova Sevara Safarali qizi</t>
+          <t>Karimova Nozliya Rustamovna</t>
         </is>
       </c>
       <c r="D484" s="2" t="n">
-        <v>390</v>
+        <v>250</v>
       </c>
       <c r="E484" s="2" t="inlineStr">
         <is>
-          <t>AE2103843</t>
+          <t>AE4674508</t>
         </is>
       </c>
       <c r="F484" s="3" t="inlineStr">
         <is>
-          <t>60705005680087</t>
+          <t>61502085680047</t>
         </is>
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>27.03.2025</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="H484" s="3" t="inlineStr">
         <is>
-          <t>07.05.2000</t>
+          <t>15.02.2008</t>
         </is>
       </c>
     </row>
@@ -18597,30 +18596,30 @@
       </c>
       <c r="C485" s="7" t="inlineStr">
         <is>
-          <t>Mahmatqulova Nilufar Qayum qizi</t>
+          <t>Mahmadmurodova Sevara Safarali qizi</t>
         </is>
       </c>
       <c r="D485" s="5" t="n">
-        <v>314</v>
+        <v>390</v>
       </c>
       <c r="E485" s="5" t="inlineStr">
         <is>
-          <t>AE6047826</t>
+          <t>AE2103843</t>
         </is>
       </c>
       <c r="F485" s="6" t="inlineStr">
         <is>
-          <t>60806085590115</t>
+          <t>60705005680087</t>
         </is>
       </c>
       <c r="G485" s="6" t="inlineStr">
         <is>
-          <t>26.01.2026</t>
+          <t>27.03.2025</t>
         </is>
       </c>
       <c r="H485" s="6" t="inlineStr">
         <is>
-          <t>08.06.2008</t>
+          <t>07.05.2000</t>
         </is>
       </c>
     </row>
@@ -18635,30 +18634,30 @@
       </c>
       <c r="C486" s="4" t="inlineStr">
         <is>
-          <t>Mahmudova Maftuna To'ra qizi</t>
+          <t>Mahmatqulova Nilufar Qayum qizi</t>
         </is>
       </c>
       <c r="D486" s="2" t="n">
-        <v>120</v>
+        <v>314</v>
       </c>
       <c r="E486" s="2" t="inlineStr">
         <is>
-          <t>AE4270256</t>
+          <t>AE6047826</t>
         </is>
       </c>
       <c r="F486" s="3" t="inlineStr">
         <is>
-          <t>61707085680068</t>
+          <t>60806085590115</t>
         </is>
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>19.09.2025</t>
+          <t>26.01.2026</t>
         </is>
       </c>
       <c r="H486" s="3" t="inlineStr">
         <is>
-          <t>17.07.2008</t>
+          <t>08.06.2008</t>
         </is>
       </c>
     </row>
@@ -18673,20 +18672,20 @@
       </c>
       <c r="C487" s="7" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda Nosir qizi</t>
+          <t>Mahmudova Maftuna To'ra qizi</t>
         </is>
       </c>
       <c r="D487" s="5" t="n">
-        <v>199</v>
+        <v>120</v>
       </c>
       <c r="E487" s="5" t="inlineStr">
         <is>
-          <t>AE4263249</t>
+          <t>AE4270256</t>
         </is>
       </c>
       <c r="F487" s="6" t="inlineStr">
         <is>
-          <t>60710085680047</t>
+          <t>61707085680068</t>
         </is>
       </c>
       <c r="G487" s="6" t="inlineStr">
@@ -18696,7 +18695,7 @@
       </c>
       <c r="H487" s="6" t="inlineStr">
         <is>
-          <t>07.10.2008</t>
+          <t>17.07.2008</t>
         </is>
       </c>
     </row>
@@ -18711,30 +18710,30 @@
       </c>
       <c r="C488" s="4" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda Hasan qizi</t>
+          <t>Mannonova Shahrizoda Nosir qizi</t>
         </is>
       </c>
       <c r="D488" s="2" t="n">
-        <v>253</v>
+        <v>199</v>
       </c>
       <c r="E488" s="2" t="inlineStr">
         <is>
-          <t>AE5221552</t>
+          <t>AE4263249</t>
         </is>
       </c>
       <c r="F488" s="3" t="inlineStr">
         <is>
-          <t>60106075720246</t>
+          <t>60710085680047</t>
         </is>
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>28.11.2025</t>
+          <t>19.09.2025</t>
         </is>
       </c>
       <c r="H488" s="3" t="inlineStr">
         <is>
-          <t>01.06.2007</t>
+          <t>07.10.2008</t>
         </is>
       </c>
     </row>
@@ -18749,30 +18748,30 @@
       </c>
       <c r="C489" s="7" t="inlineStr">
         <is>
-          <t>Muminova Sevinch Uchqun qizi</t>
+          <t>Maxmarajabova Zerda Hasan qizi</t>
         </is>
       </c>
       <c r="D489" s="5" t="n">
-        <v>163</v>
+        <v>253</v>
       </c>
       <c r="E489" s="5" t="inlineStr">
         <is>
-          <t>AE2259069</t>
+          <t>AE5221552</t>
         </is>
       </c>
       <c r="F489" s="6" t="inlineStr">
         <is>
-          <t>63001085590111</t>
+          <t>60106075720246</t>
         </is>
       </c>
       <c r="G489" s="6" t="inlineStr">
         <is>
-          <t>09.04.2025</t>
+          <t>28.11.2025</t>
         </is>
       </c>
       <c r="H489" s="6" t="inlineStr">
         <is>
-          <t>30.01.2008</t>
+          <t>01.06.2007</t>
         </is>
       </c>
     </row>
@@ -18787,30 +18786,30 @@
       </c>
       <c r="C490" s="4" t="inlineStr">
         <is>
-          <t>Mustafayeva Nargiza Ulug'bek qizi</t>
+          <t>Muminova Sevinch Uchqun qizi</t>
         </is>
       </c>
       <c r="D490" s="2" t="n">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="E490" s="2" t="inlineStr">
         <is>
-          <t>AB8521319</t>
+          <t>AE2259069</t>
         </is>
       </c>
       <c r="F490" s="3" t="inlineStr">
         <is>
-          <t>62906005590060</t>
+          <t>63001085590111</t>
         </is>
       </c>
       <c r="G490" s="3" t="inlineStr">
         <is>
-          <t>02.01.2018</t>
+          <t>09.04.2025</t>
         </is>
       </c>
       <c r="H490" s="3" t="inlineStr">
         <is>
-          <t>29.06.2000</t>
+          <t>30.01.2008</t>
         </is>
       </c>
     </row>
@@ -18825,30 +18824,30 @@
       </c>
       <c r="C491" s="7" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Mustafayeva Nargiza Ulug'bek qizi</t>
         </is>
       </c>
       <c r="D491" s="5" t="n">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="E491" s="5" t="inlineStr">
         <is>
-          <t>AE2428256</t>
+          <t>AB8521319</t>
         </is>
       </c>
       <c r="F491" s="6" t="inlineStr">
         <is>
-          <t>60506085590066</t>
+          <t>62906005590060</t>
         </is>
       </c>
       <c r="G491" s="6" t="inlineStr">
         <is>
-          <t>22.04.2025</t>
+          <t>02.01.2018</t>
         </is>
       </c>
       <c r="H491" s="6" t="inlineStr">
         <is>
-          <t>05.06.2008</t>
+          <t>29.06.2000</t>
         </is>
       </c>
     </row>
@@ -18863,30 +18862,30 @@
       </c>
       <c r="C492" s="4" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
         </is>
       </c>
       <c r="D492" s="2" t="n">
-        <v>212</v>
+        <v>176</v>
       </c>
       <c r="E492" s="2" t="inlineStr">
         <is>
-          <t>AB5359926</t>
+          <t>AE2428256</t>
         </is>
       </c>
       <c r="F492" s="3" t="inlineStr">
         <is>
-          <t>40211995680023</t>
+          <t>60506085590066</t>
         </is>
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>12.12.2016</t>
+          <t>22.04.2025</t>
         </is>
       </c>
       <c r="H492" s="3" t="inlineStr">
         <is>
-          <t>02.11.1999</t>
+          <t>05.06.2008</t>
         </is>
       </c>
     </row>
@@ -18901,30 +18900,30 @@
       </c>
       <c r="C493" s="7" t="inlineStr">
         <is>
-          <t>Niyozova Sevara Turoqulovna</t>
+          <t>Narziyeva Intizor Iskandar qizi</t>
         </is>
       </c>
       <c r="D493" s="5" t="n">
-        <v>304</v>
+        <v>212</v>
       </c>
       <c r="E493" s="5" t="inlineStr">
         <is>
-          <t>AD9706738</t>
+          <t>AB5359926</t>
         </is>
       </c>
       <c r="F493" s="6" t="inlineStr">
         <is>
-          <t>412068 9256 0120</t>
+          <t>40211995680023</t>
         </is>
       </c>
       <c r="G493" s="6" t="inlineStr">
         <is>
-          <t>05.12.2024</t>
+          <t>12.12.2016</t>
         </is>
       </c>
       <c r="H493" s="6" t="inlineStr">
         <is>
-          <t>12.06.1989</t>
+          <t>02.11.1999</t>
         </is>
       </c>
     </row>
@@ -18939,30 +18938,30 @@
       </c>
       <c r="C494" s="4" t="inlineStr">
         <is>
-          <t>Nurillayeva Sevinch Mashrab qizi</t>
+          <t>Niyozova Sevara Turoqulovna</t>
         </is>
       </c>
       <c r="D494" s="2" t="n">
-        <v>246</v>
+        <v>304</v>
       </c>
       <c r="E494" s="2" t="inlineStr">
         <is>
-          <t>AD9494409</t>
+          <t>AD9706738</t>
         </is>
       </c>
       <c r="F494" s="3" t="inlineStr">
         <is>
-          <t>60504085680019</t>
+          <t>412068 9256 0120</t>
         </is>
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>26.09.2025</t>
+          <t>05.12.2024</t>
         </is>
       </c>
       <c r="H494" s="3" t="inlineStr">
         <is>
-          <t>05.04.2008</t>
+          <t>12.06.1989</t>
         </is>
       </c>
     </row>
@@ -18977,30 +18976,30 @@
       </c>
       <c r="C495" s="7" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Nurillayeva Sevinch Mashrab qizi</t>
         </is>
       </c>
       <c r="D495" s="5" t="n">
-        <v>47</v>
+        <v>246</v>
       </c>
       <c r="E495" s="5" t="inlineStr">
         <is>
-          <t>AD0776916</t>
+          <t>AD9494409</t>
         </is>
       </c>
       <c r="F495" s="6" t="inlineStr">
         <is>
-          <t>62012045590040</t>
+          <t>60504085680019</t>
         </is>
       </c>
       <c r="G495" s="6" t="inlineStr">
         <is>
-          <t>02.11.2021</t>
+          <t>26.09.2025</t>
         </is>
       </c>
       <c r="H495" s="6" t="inlineStr">
         <is>
-          <t>20.12.2004</t>
+          <t>05.04.2008</t>
         </is>
       </c>
     </row>
@@ -19015,30 +19014,30 @@
       </c>
       <c r="C496" s="4" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="D496" s="2" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E496" s="2" t="inlineStr">
         <is>
-          <t>AE2118072</t>
+          <t>AD0776916</t>
         </is>
       </c>
       <c r="F496" s="3" t="inlineStr">
         <is>
-          <t>62201085590064</t>
+          <t>62012045590040</t>
         </is>
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>28.03.2025</t>
+          <t>02.11.2021</t>
         </is>
       </c>
       <c r="H496" s="3" t="inlineStr">
         <is>
-          <t>22.01.2008</t>
+          <t>20.12.2004</t>
         </is>
       </c>
     </row>
@@ -19053,30 +19052,30 @@
       </c>
       <c r="C497" s="7" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso Farhod qizi</t>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
         </is>
       </c>
       <c r="D497" s="5" t="n">
-        <v>187</v>
+        <v>55</v>
       </c>
       <c r="E497" s="5" t="inlineStr">
         <is>
-          <t>AE1143288</t>
+          <t>AE2118072</t>
         </is>
       </c>
       <c r="F497" s="6" t="inlineStr">
         <is>
-          <t>62911085630012</t>
+          <t>62201085590064</t>
         </is>
       </c>
       <c r="G497" s="6" t="inlineStr">
         <is>
-          <t>10.01.2025</t>
+          <t>28.03.2025</t>
         </is>
       </c>
       <c r="H497" s="6" t="inlineStr">
         <is>
-          <t>29.11.2008</t>
+          <t>22.01.2008</t>
         </is>
       </c>
     </row>
@@ -19091,30 +19090,30 @@
       </c>
       <c r="C498" s="4" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
+          <t>Quchqarova Zebiniso Farhod qizi</t>
         </is>
       </c>
       <c r="D498" s="2" t="n">
-        <v>271</v>
+        <v>187</v>
       </c>
       <c r="E498" s="2" t="inlineStr">
         <is>
-          <t>AE4246251</t>
+          <t>AE1143288</t>
         </is>
       </c>
       <c r="F498" s="3" t="inlineStr">
         <is>
-          <t>62702085680028</t>
+          <t>62911085630012</t>
         </is>
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>18.09.2025</t>
+          <t>10.01.2025</t>
         </is>
       </c>
       <c r="H498" s="3" t="inlineStr">
         <is>
-          <t>27.02.2008</t>
+          <t>29.11.2008</t>
         </is>
       </c>
     </row>
@@ -19129,30 +19128,30 @@
       </c>
       <c r="C499" s="7" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="D499" s="5" t="n">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="E499" s="5" t="inlineStr">
         <is>
-          <t>AD8686485</t>
+          <t>AE4246251</t>
         </is>
       </c>
       <c r="F499" s="6" t="inlineStr">
         <is>
-          <t>62201085590019</t>
+          <t>62702085680028</t>
         </is>
       </c>
       <c r="G499" s="6" t="inlineStr">
         <is>
-          <t>19.09.2024</t>
+          <t>18.09.2025</t>
         </is>
       </c>
       <c r="H499" s="6" t="inlineStr">
         <is>
-          <t>22.01.2008</t>
+          <t>27.02.2008</t>
         </is>
       </c>
     </row>
@@ -19167,30 +19166,30 @@
       </c>
       <c r="C500" s="4" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="D500" s="2" t="n">
-        <v>32</v>
+        <v>254</v>
       </c>
       <c r="E500" s="2" t="inlineStr">
         <is>
-          <t>AC1805235</t>
+          <t>AD8686485</t>
         </is>
       </c>
       <c r="F500" s="3" t="inlineStr">
         <is>
-          <t>60409015590065</t>
+          <t>62201085590019</t>
         </is>
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>08.04.2019</t>
+          <t>19.09.2024</t>
         </is>
       </c>
       <c r="H500" s="3" t="inlineStr">
         <is>
-          <t>04.09.2001</t>
+          <t>22.01.2008</t>
         </is>
       </c>
     </row>
@@ -19205,28 +19204,30 @@
       </c>
       <c r="C501" s="7" t="inlineStr">
         <is>
-          <t>Sayfieva Sarvinoz Zafar qizi</t>
-        </is>
-      </c>
-      <c r="D501" s="5" t="inlineStr"/>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
+        </is>
+      </c>
+      <c r="D501" s="5" t="n">
+        <v>32</v>
+      </c>
       <c r="E501" s="5" t="inlineStr">
         <is>
-          <t>AB6304158</t>
+          <t>AC1805235</t>
         </is>
       </c>
       <c r="F501" s="6" t="inlineStr">
         <is>
-          <t>415079 8559 0074</t>
+          <t>60409015590065</t>
         </is>
       </c>
       <c r="G501" s="6" t="inlineStr">
         <is>
-          <t>28.03.2017</t>
+          <t>08.04.2019</t>
         </is>
       </c>
       <c r="H501" s="6" t="inlineStr">
         <is>
-          <t>15.07.1998</t>
+          <t>04.09.2001</t>
         </is>
       </c>
     </row>
@@ -19241,30 +19242,28 @@
       </c>
       <c r="C502" s="4" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
-        </is>
-      </c>
-      <c r="D502" s="2" t="n">
-        <v>3</v>
-      </c>
+          <t>Sayfieva Sarvinoz Zafar qizi</t>
+        </is>
+      </c>
+      <c r="D502" s="2" t="inlineStr"/>
       <c r="E502" s="2" t="inlineStr">
         <is>
-          <t>AE4385111</t>
+          <t>AB6304158</t>
         </is>
       </c>
       <c r="F502" s="3" t="inlineStr">
         <is>
-          <t>62203085730015</t>
+          <t>415079 8559 0074</t>
         </is>
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>28.03.2017</t>
         </is>
       </c>
       <c r="H502" s="3" t="inlineStr">
         <is>
-          <t>22.03.2008</t>
+          <t>15.07.1998</t>
         </is>
       </c>
     </row>
@@ -19279,30 +19278,30 @@
       </c>
       <c r="C503" s="7" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="D503" s="5" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E503" s="5" t="inlineStr">
         <is>
-          <t>AD2624840</t>
+          <t>AE4385111</t>
         </is>
       </c>
       <c r="F503" s="6" t="inlineStr">
         <is>
-          <t>62408065590018</t>
+          <t>62203085730015</t>
         </is>
       </c>
       <c r="G503" s="6" t="inlineStr">
         <is>
-          <t>18.02.2023</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="H503" s="6" t="inlineStr">
         <is>
-          <t>24.08.2006</t>
+          <t>22.03.2008</t>
         </is>
       </c>
     </row>
@@ -19317,30 +19316,30 @@
       </c>
       <c r="C504" s="4" t="inlineStr">
         <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="D504" s="2" t="n">
-        <v>283</v>
+        <v>21</v>
       </c>
       <c r="E504" s="2" t="inlineStr">
         <is>
-          <t>AB5702170</t>
+          <t>AD2624840</t>
         </is>
       </c>
       <c r="F504" s="3" t="inlineStr">
         <is>
-          <t>42601925680010</t>
+          <t>62408065590018</t>
         </is>
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>19.01.2017</t>
+          <t>18.02.2023</t>
         </is>
       </c>
       <c r="H504" s="3" t="inlineStr">
         <is>
-          <t>26.01.1992</t>
+          <t>24.08.2006</t>
         </is>
       </c>
     </row>
@@ -19355,30 +19354,30 @@
       </c>
       <c r="C505" s="7" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
         </is>
       </c>
       <c r="D505" s="5" t="n">
-        <v>138</v>
+        <v>283</v>
       </c>
       <c r="E505" s="5" t="inlineStr">
         <is>
-          <t>AD2922676</t>
+          <t>AB5702170</t>
         </is>
       </c>
       <c r="F505" s="6" t="inlineStr">
         <is>
-          <t>61604065590015</t>
+          <t>42601925680010</t>
         </is>
       </c>
       <c r="G505" s="6" t="inlineStr">
         <is>
-          <t>01.04.2023</t>
+          <t>19.01.2017</t>
         </is>
       </c>
       <c r="H505" s="6" t="inlineStr">
         <is>
-          <t>16.04.2006</t>
+          <t>26.01.1992</t>
         </is>
       </c>
     </row>
@@ -19393,30 +19392,30 @@
       </c>
       <c r="C506" s="4" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="D506" s="2" t="n">
-        <v>247</v>
+        <v>138</v>
       </c>
       <c r="E506" s="2" t="inlineStr">
         <is>
-          <t>AE4629898</t>
+          <t>AD2922676</t>
         </is>
       </c>
       <c r="F506" s="3" t="inlineStr">
         <is>
-          <t>62802085680012</t>
+          <t>61604065590015</t>
         </is>
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>15.10.2025</t>
+          <t>01.04.2023</t>
         </is>
       </c>
       <c r="H506" s="3" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>16.04.2006</t>
         </is>
       </c>
     </row>
@@ -19431,30 +19430,104 @@
       </c>
       <c r="C507" s="7" t="inlineStr">
         <is>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+        </is>
+      </c>
+      <c r="D507" s="5" t="n">
+        <v>247</v>
+      </c>
+      <c r="E507" s="5" t="inlineStr">
+        <is>
+          <t>AE4629898</t>
+        </is>
+      </c>
+      <c r="F507" s="6" t="inlineStr">
+        <is>
+          <t>62802085680012</t>
+        </is>
+      </c>
+      <c r="G507" s="6" t="inlineStr">
+        <is>
+          <t>15.10.2025</t>
+        </is>
+      </c>
+      <c r="H507" s="6" t="inlineStr">
+        <is>
+          <t>28.02.2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="508" ht="22" customHeight="1">
+      <c r="A508" s="2" t="n">
+        <v>507</v>
+      </c>
+      <c r="B508" s="3" t="inlineStr">
+        <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C508" s="4" t="inlineStr">
+        <is>
           <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
-      <c r="D507" s="5" t="n">
+      <c r="D508" s="2" t="n">
         <v>93</v>
       </c>
-      <c r="E507" s="5" t="inlineStr">
+      <c r="E508" s="2" t="inlineStr">
         <is>
           <t>AE4688777</t>
         </is>
       </c>
-      <c r="F507" s="6" t="inlineStr">
+      <c r="F508" s="3" t="inlineStr">
         <is>
           <t>63007085680074</t>
         </is>
       </c>
-      <c r="G507" s="6" t="inlineStr">
+      <c r="G508" s="3" t="inlineStr">
         <is>
           <t>20.10.2025</t>
         </is>
       </c>
-      <c r="H507" s="6" t="inlineStr">
+      <c r="H508" s="3" t="inlineStr">
         <is>
           <t>30.07.2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="509" ht="22" customHeight="1">
+      <c r="A509" s="5" t="n">
+        <v>508</v>
+      </c>
+      <c r="B509" s="6" t="inlineStr">
+        <is>
+          <t>26-07</t>
+        </is>
+      </c>
+      <c r="C509" s="7" t="inlineStr">
+        <is>
+          <t>Ergasheva Madina Tulqin qizi</t>
+        </is>
+      </c>
+      <c r="D509" s="5" t="inlineStr"/>
+      <c r="E509" s="5" t="inlineStr">
+        <is>
+          <t>AC0429133</t>
+        </is>
+      </c>
+      <c r="F509" s="6" t="inlineStr">
+        <is>
+          <t>62501027890026</t>
+        </is>
+      </c>
+      <c r="G509" s="6" t="inlineStr">
+        <is>
+          <t>07.12.2018</t>
+        </is>
+      </c>
+      <c r="H509" s="6" t="inlineStr">
+        <is>
+          <t>25.01.2002</t>
         </is>
       </c>
     </row>
@@ -24791,7 +24864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -25275,30 +25348,28 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Turayeva Dilsuz Oybek qizi</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>268</v>
-      </c>
+          <t>Shermatova Gulsun Xurshid qizi</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>AE5053541</t>
+          <t>AE5836574</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>61205095590053</t>
+          <t>60802085590029</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>15.11.2025</t>
+          <t>13.01.2026</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>12.05.2009</t>
+          <t>08.02.2008</t>
         </is>
       </c>
     </row>
@@ -25313,30 +25384,30 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Turg'unova Jasmina Turg'un qizi</t>
+          <t>Turayeva Dilsuz Oybek qizi</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>122</v>
+        <v>268</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>AE6171425</t>
+          <t>AE5053541</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>62802085590087</t>
+          <t>61205095590053</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>03.02.2026</t>
+          <t>15.11.2025</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>12.05.2009</t>
         </is>
       </c>
     </row>
@@ -25351,28 +25422,66 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
+          <t>Turg'unova Jasmina Turg'un qizi</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>122</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>AE6171425</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>62802085590087</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>03.02.2026</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>28.02.2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>26-01</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
           <t>Ziyodullayeva Jasmina Alisher qizi</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D16" s="2" t="n">
         <v>233</v>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>AD9812146</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>61206075590076</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>13.12.2024</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>12.06.2007</t>
         </is>
@@ -33075,6 +33184,108 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>T/R</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Guruh</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>F.I.SH (Talaba)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Shartnoma №</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Pasport seriya va raqami</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>JSHSHIR (PINFL)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Pasport berilgan sanasi</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Tug'ilgan sanasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>26-07</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Ergasheva Madina Tulqin qizi</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>AC0429133</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>62501027890026</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>07.12.2018</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>25.01.2002</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
